--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="105">
   <si>
     <t>#</t>
   </si>
@@ -180,10 +180,10 @@
     <t>250层,1/10掉落</t>
   </si>
   <si>
-    <t>1006</t>
-  </si>
-  <si>
-    <t>等级丹</t>
+    <t>220036</t>
+  </si>
+  <si>
+    <t>等级丹*10</t>
   </si>
   <si>
     <t>每百层大概2.5个</t>
@@ -264,6 +264,36 @@
     <t>道士之魂</t>
   </si>
   <si>
+    <t>220032</t>
+  </si>
+  <si>
+    <t>副本劵*2</t>
+  </si>
+  <si>
+    <t>220033</t>
+  </si>
+  <si>
+    <t>Boss劵*2</t>
+  </si>
+  <si>
+    <t>220034</t>
+  </si>
+  <si>
+    <t>四格碎片*4</t>
+  </si>
+  <si>
+    <t>220035</t>
+  </si>
+  <si>
+    <t>图鉴碎片*4</t>
+  </si>
+  <si>
+    <t>220037</t>
+  </si>
+  <si>
+    <t>等级丹*15</t>
+  </si>
+  <si>
     <t>BOSS杀手</t>
   </si>
   <si>
@@ -324,7 +354,10 @@
     <t>10倍数，低概率掉落</t>
   </si>
   <si>
-    <t>极·圣者遗物</t>
+    <t>极·副本契约</t>
+  </si>
+  <si>
+    <t>极·BOSS契约</t>
   </si>
   <si>
     <t>220016</t>
@@ -1005,19 +1038,22 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1337,7 +1373,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L64"/>
+  <dimension ref="C1:L74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1366,80 +1402,80 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1447,7 +1483,7 @@
       <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="9" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -1460,7 +1496,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="2">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="I6" s="2">
         <v>1</v>
@@ -1476,7 +1512,7 @@
       <c r="C7" s="2">
         <v>2</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -1489,7 +1525,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="2">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="I7" s="2">
         <v>1</v>
@@ -1505,7 +1541,7 @@
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -1534,7 +1570,7 @@
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="10" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -1563,7 +1599,7 @@
       <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="11" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -1592,7 +1628,7 @@
       <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="11" t="s">
         <v>24</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -1621,7 +1657,7 @@
       <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="11" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -1708,7 +1744,7 @@
       <c r="C15" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="10" t="s">
         <v>31</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -1733,32 +1769,32 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C16" s="2">
+    <row r="16" s="3" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C16" s="3">
         <v>11</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="3">
         <v>10</v>
       </c>
-      <c r="G16" s="2">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2">
+      <c r="G16" s="3">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3">
         <v>10000</v>
       </c>
-      <c r="I16" s="2">
-        <v>1</v>
-      </c>
-      <c r="J16" s="2">
+      <c r="I16" s="3">
+        <v>1</v>
+      </c>
+      <c r="J16" s="3">
         <v>50</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="K16" s="3" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1766,7 +1802,7 @@
       <c r="C17" s="1">
         <v>12</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="10" t="s">
         <v>36</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -1795,7 +1831,7 @@
       <c r="C18" s="2">
         <v>13</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="9" t="s">
         <v>39</v>
       </c>
       <c r="E18" s="2" t="s">
@@ -1808,7 +1844,7 @@
         <v>300</v>
       </c>
       <c r="H18" s="2">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="I18" s="2">
         <v>1</v>
@@ -1820,32 +1856,32 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C19" s="2">
+    <row r="19" s="3" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C19" s="3">
         <v>14</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="2">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2">
+      <c r="F19" s="3">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3">
         <v>100</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="3">
         <v>10000</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I19" s="3">
         <v>3</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="3">
         <v>2</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="K19" s="3" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1853,7 +1889,7 @@
       <c r="C20" s="1">
         <v>15</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="10" t="s">
         <v>45</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -1882,7 +1918,7 @@
       <c r="C21" s="1">
         <v>16</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="10" t="s">
         <v>47</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -1911,7 +1947,7 @@
       <c r="C22" s="1">
         <v>17</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="10" t="s">
         <v>50</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -1940,7 +1976,7 @@
       <c r="C23" s="1">
         <v>18</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="10" t="s">
         <v>51</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -1969,7 +2005,7 @@
       <c r="C24" s="1">
         <v>19</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="10" t="s">
         <v>52</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -1998,7 +2034,7 @@
       <c r="C25" s="1">
         <v>20</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="10" t="s">
         <v>53</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -2027,7 +2063,7 @@
       <c r="C26" s="1">
         <v>21</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E26" s="1" t="s">
@@ -2040,7 +2076,7 @@
         <v>1001</v>
       </c>
       <c r="H26" s="1">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="I26" s="1">
         <v>1</v>
@@ -2056,7 +2092,7 @@
       <c r="C27" s="1">
         <v>22</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="10" t="s">
         <v>55</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -2069,7 +2105,7 @@
         <v>1001</v>
       </c>
       <c r="H27" s="1">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="I27" s="1">
         <v>1</v>
@@ -2085,7 +2121,7 @@
       <c r="C28" s="1">
         <v>23</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E28" s="1" t="s">
@@ -2114,7 +2150,7 @@
       <c r="C29" s="1">
         <v>24</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="10" t="s">
         <v>57</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -2143,7 +2179,7 @@
       <c r="C30" s="1">
         <v>25</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="10" t="s">
         <v>58</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -2172,7 +2208,7 @@
       <c r="C31" s="1">
         <v>26</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="10" t="s">
         <v>59</v>
       </c>
       <c r="E31" s="1" t="s">
@@ -2201,7 +2237,7 @@
       <c r="C32" s="1">
         <v>27</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="10" t="s">
         <v>60</v>
       </c>
       <c r="E32" s="1" t="s">
@@ -2230,7 +2266,7 @@
       <c r="C33" s="1">
         <v>28</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="10" t="s">
         <v>61</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -2259,7 +2295,7 @@
       <c r="C34" s="1">
         <v>29</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -2288,7 +2324,7 @@
       <c r="C35" s="1">
         <v>30</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="10" t="s">
         <v>65</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -2313,311 +2349,181 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="4:4">
-      <c r="D36" s="5"/>
-    </row>
-    <row r="37" customHeight="1" spans="3:11">
-      <c r="C37" s="1">
-        <v>101</v>
-      </c>
-      <c r="D37" s="6">
-        <v>180001</v>
-      </c>
-      <c r="E37" s="1" t="s">
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C36" s="2">
+        <v>31</v>
+      </c>
+      <c r="D36" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="F37" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G37" s="1">
-        <v>1</v>
-      </c>
-      <c r="H37" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I37" s="1">
-        <v>100</v>
-      </c>
-      <c r="J37" s="1">
-        <v>1</v>
-      </c>
-      <c r="K37" s="1" t="s">
+      <c r="E36" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:11">
+      <c r="F36" s="2">
+        <v>50</v>
+      </c>
+      <c r="G36" s="2">
+        <v>1501</v>
+      </c>
+      <c r="H36" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I36" s="2">
+        <v>1</v>
+      </c>
+      <c r="J36" s="2">
+        <v>200</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C37" s="2">
+        <v>32</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F37" s="2">
+        <v>5</v>
+      </c>
+      <c r="G37" s="2">
+        <v>1501</v>
+      </c>
+      <c r="H37" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I37" s="2">
+        <v>1</v>
+      </c>
+      <c r="J37" s="2">
+        <v>20</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C38" s="1">
-        <v>102</v>
-      </c>
-      <c r="D38" s="6">
-        <v>180002</v>
+        <v>33</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>71</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F38" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G38" s="1">
-        <v>1</v>
-      </c>
-      <c r="H38" s="1">
-        <v>1000</v>
+        <v>50</v>
+      </c>
+      <c r="G38" s="2">
+        <v>1501</v>
+      </c>
+      <c r="H38" s="2">
+        <v>10000</v>
       </c>
       <c r="I38" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="J38" s="1">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:11">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="20" customHeight="1" spans="3:11">
       <c r="C39" s="1">
-        <v>103</v>
-      </c>
-      <c r="D39" s="6">
-        <v>180003</v>
+        <v>34</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>73</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F39" s="1">
-        <v>150000</v>
-      </c>
-      <c r="G39" s="1">
-        <v>1</v>
-      </c>
-      <c r="H39" s="1">
-        <v>1000</v>
+        <v>50</v>
+      </c>
+      <c r="G39" s="2">
+        <v>1501</v>
+      </c>
+      <c r="H39" s="2">
+        <v>10000</v>
       </c>
       <c r="I39" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="J39" s="1">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:11">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" s="3" customFormat="1" customHeight="1" spans="3:11">
       <c r="C40" s="1">
-        <v>104</v>
-      </c>
-      <c r="D40" s="6">
-        <v>180004</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F40" s="1">
-        <v>8000</v>
-      </c>
-      <c r="G40" s="1">
-        <v>1</v>
-      </c>
-      <c r="H40" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I40" s="1">
-        <v>100</v>
-      </c>
-      <c r="J40" s="1">
-        <v>1</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:11">
-      <c r="C41" s="1">
-        <v>105</v>
-      </c>
-      <c r="D41" s="6">
-        <v>180005</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F41" s="1">
-        <v>3000</v>
-      </c>
-      <c r="G41" s="1">
-        <v>1</v>
-      </c>
-      <c r="H41" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I41" s="1">
-        <v>100</v>
-      </c>
-      <c r="J41" s="1">
-        <v>1</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:11">
-      <c r="C42" s="1">
-        <v>106</v>
-      </c>
-      <c r="D42" s="6">
-        <v>180006</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F42" s="1">
-        <v>50000</v>
-      </c>
-      <c r="G42" s="1">
-        <v>1</v>
-      </c>
-      <c r="H42" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I42" s="1">
-        <v>100</v>
-      </c>
-      <c r="J42" s="1">
-        <v>10</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:11">
-      <c r="C43" s="1">
-        <v>107</v>
-      </c>
-      <c r="D43" s="6">
-        <v>180007</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F43" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G43" s="1">
-        <v>1</v>
-      </c>
-      <c r="H43" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I43" s="1">
-        <v>100</v>
-      </c>
-      <c r="J43" s="1">
-        <v>1</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:11">
-      <c r="C44" s="1">
-        <v>108</v>
-      </c>
-      <c r="D44" s="6">
-        <v>180008</v>
-      </c>
-      <c r="E44" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D40" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F44" s="1">
-        <v>20000</v>
-      </c>
-      <c r="G44" s="1">
-        <v>1</v>
-      </c>
-      <c r="H44" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I44" s="1">
-        <v>100</v>
-      </c>
-      <c r="J44" s="1">
-        <v>2</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:11">
-      <c r="C45" s="1">
-        <v>109</v>
-      </c>
-      <c r="D45" s="6">
-        <v>180009</v>
-      </c>
-      <c r="E45" s="1" t="s">
+      <c r="E40" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F45" s="1">
-        <v>3000</v>
-      </c>
-      <c r="G45" s="1">
-        <v>1</v>
-      </c>
-      <c r="H45" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I45" s="1">
-        <v>100</v>
-      </c>
-      <c r="J45" s="1">
-        <v>1</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:11">
-      <c r="C46" s="1">
-        <v>110</v>
-      </c>
-      <c r="D46" s="6">
-        <v>180010</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F46" s="1">
+      <c r="F40" s="3">
+        <v>6</v>
+      </c>
+      <c r="G40" s="3">
+        <v>1501</v>
+      </c>
+      <c r="H40" s="2">
         <v>10000</v>
       </c>
-      <c r="G46" s="1">
-        <v>1</v>
-      </c>
-      <c r="H46" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I46" s="1">
-        <v>100</v>
-      </c>
-      <c r="J46" s="1">
-        <v>1</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>68</v>
-      </c>
+      <c r="I40" s="3">
+        <v>1</v>
+      </c>
+      <c r="J40" s="3">
+        <v>25</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="4:4">
+      <c r="D41" s="6"/>
+    </row>
+    <row r="42" customHeight="1" spans="4:4">
+      <c r="D42" s="6"/>
+    </row>
+    <row r="43" customHeight="1" spans="4:4">
+      <c r="D43" s="6"/>
+    </row>
+    <row r="44" customHeight="1" spans="4:4">
+      <c r="D44" s="6"/>
+    </row>
+    <row r="45" customHeight="1" spans="4:4">
+      <c r="D45" s="6"/>
+    </row>
+    <row r="46" customHeight="1" spans="4:4">
+      <c r="D46" s="6"/>
     </row>
     <row r="47" customHeight="1" spans="3:11">
       <c r="C47" s="1">
-        <v>111</v>
-      </c>
-      <c r="D47" s="6">
-        <v>180011</v>
+        <v>101</v>
+      </c>
+      <c r="D47" s="8">
+        <v>180001</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F47" s="1">
-        <v>100000</v>
+        <v>2000</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -2629,24 +2535,24 @@
         <v>100</v>
       </c>
       <c r="J47" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:11">
       <c r="C48" s="1">
-        <v>112</v>
-      </c>
-      <c r="D48" s="6">
-        <v>180012</v>
+        <v>102</v>
+      </c>
+      <c r="D48" s="8">
+        <v>180002</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>79</v>
       </c>
       <c r="F48" s="1">
-        <v>100000</v>
+        <v>4000</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -2658,24 +2564,24 @@
         <v>100</v>
       </c>
       <c r="J48" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:11">
       <c r="C49" s="1">
-        <v>113</v>
-      </c>
-      <c r="D49" s="6">
-        <v>180013</v>
+        <v>103</v>
+      </c>
+      <c r="D49" s="8">
+        <v>180003</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F49" s="1">
-        <v>50000</v>
+        <v>150000</v>
       </c>
       <c r="G49" s="1">
         <v>1</v>
@@ -2687,24 +2593,24 @@
         <v>100</v>
       </c>
       <c r="J49" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:11">
       <c r="C50" s="1">
-        <v>114</v>
-      </c>
-      <c r="D50" s="6">
-        <v>180014</v>
+        <v>104</v>
+      </c>
+      <c r="D50" s="8">
+        <v>180004</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F50" s="1">
-        <v>100000</v>
+        <v>8000</v>
       </c>
       <c r="G50" s="1">
         <v>1</v>
@@ -2716,24 +2622,24 @@
         <v>100</v>
       </c>
       <c r="J50" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:11">
       <c r="C51" s="1">
-        <v>115</v>
-      </c>
-      <c r="D51" s="6">
-        <v>180015</v>
+        <v>105</v>
+      </c>
+      <c r="D51" s="8">
+        <v>180005</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F51" s="1">
-        <v>100000</v>
+        <v>3000</v>
       </c>
       <c r="G51" s="1">
         <v>1</v>
@@ -2745,24 +2651,24 @@
         <v>100</v>
       </c>
       <c r="J51" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:11">
       <c r="C52" s="1">
-        <v>120</v>
-      </c>
-      <c r="D52" s="6">
-        <v>180020</v>
+        <v>106</v>
+      </c>
+      <c r="D52" s="8">
+        <v>180006</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>83</v>
       </c>
       <c r="F52" s="1">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="G52" s="1">
         <v>1</v>
@@ -2774,24 +2680,24 @@
         <v>100</v>
       </c>
       <c r="J52" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:11">
       <c r="C53" s="1">
-        <v>121</v>
-      </c>
-      <c r="D53" s="6">
-        <v>180021</v>
+        <v>107</v>
+      </c>
+      <c r="D53" s="8">
+        <v>180007</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>84</v>
       </c>
       <c r="F53" s="1">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="G53" s="1">
         <v>1</v>
@@ -2806,27 +2712,56 @@
         <v>1</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:11">
+      <c r="C54" s="1">
+        <v>108</v>
+      </c>
+      <c r="D54" s="8">
+        <v>180008</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F54" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1</v>
+      </c>
+      <c r="H54" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I54" s="1">
+        <v>100</v>
+      </c>
+      <c r="J54" s="1">
+        <v>2</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
       <c r="C55" s="1">
-        <v>130</v>
-      </c>
-      <c r="D55" s="1">
-        <v>180030</v>
+        <v>109</v>
+      </c>
+      <c r="D55" s="8">
+        <v>180009</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F55" s="1">
-        <v>5</v>
+        <v>3000</v>
       </c>
       <c r="G55" s="1">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="H55" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I55" s="1">
         <v>100</v>
@@ -2835,33 +2770,27 @@
         <v>1</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="1:11">
-      <c r="A56" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>0</v>
-      </c>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:11">
       <c r="C56" s="1">
-        <v>131</v>
-      </c>
-      <c r="D56" s="1">
-        <v>180031</v>
+        <v>110</v>
+      </c>
+      <c r="D56" s="8">
+        <v>180010</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>87</v>
       </c>
       <c r="F56" s="1">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="G56" s="1">
-        <v>1501</v>
+        <v>1</v>
       </c>
       <c r="H56" s="1">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I56" s="1">
         <v>100</v>
@@ -2870,104 +2799,394 @@
         <v>1</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:11">
+      <c r="C57" s="1">
+        <v>111</v>
+      </c>
+      <c r="D57" s="8">
+        <v>180011</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F57" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G57" s="1">
+        <v>1</v>
+      </c>
+      <c r="H57" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I57" s="1">
+        <v>100</v>
+      </c>
+      <c r="J57" s="1">
+        <v>10</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:11">
+      <c r="C58" s="1">
+        <v>112</v>
+      </c>
+      <c r="D58" s="8">
+        <v>180012</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F58" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G58" s="1">
+        <v>1</v>
+      </c>
+      <c r="H58" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I58" s="1">
+        <v>100</v>
+      </c>
+      <c r="J58" s="1">
+        <v>10</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
       <c r="C59" s="1">
-        <v>201</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>88</v>
+        <v>113</v>
+      </c>
+      <c r="D59" s="8">
+        <v>180013</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F59" s="1">
-        <v>5</v>
+        <v>50000</v>
       </c>
       <c r="G59" s="1">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="H59" s="1">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="I59" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="J59" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:11">
       <c r="C60" s="1">
-        <v>202</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>90</v>
+        <v>114</v>
+      </c>
+      <c r="D60" s="8">
+        <v>180014</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>91</v>
       </c>
       <c r="F60" s="1">
-        <v>5</v>
+        <v>100000</v>
       </c>
       <c r="G60" s="1">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="H60" s="1">
         <v>1000</v>
       </c>
       <c r="I60" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J60" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:11">
       <c r="C61" s="1">
+        <v>115</v>
+      </c>
+      <c r="D61" s="8">
+        <v>180015</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F61" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G61" s="1">
+        <v>1</v>
+      </c>
+      <c r="H61" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I61" s="1">
+        <v>100</v>
+      </c>
+      <c r="J61" s="1">
+        <v>10</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:11">
+      <c r="C62" s="1">
+        <v>120</v>
+      </c>
+      <c r="D62" s="8">
+        <v>180020</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F62" s="1">
+        <v>10000</v>
+      </c>
+      <c r="G62" s="1">
+        <v>1</v>
+      </c>
+      <c r="H62" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I62" s="1">
+        <v>100</v>
+      </c>
+      <c r="J62" s="1">
+        <v>1</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:11">
+      <c r="C63" s="1">
+        <v>121</v>
+      </c>
+      <c r="D63" s="8">
+        <v>180021</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F63" s="1">
+        <v>10000</v>
+      </c>
+      <c r="G63" s="1">
+        <v>1</v>
+      </c>
+      <c r="H63" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I63" s="1">
+        <v>100</v>
+      </c>
+      <c r="J63" s="1">
+        <v>1</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:11">
+      <c r="C65" s="1">
+        <v>130</v>
+      </c>
+      <c r="D65" s="1">
+        <v>180030</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F65" s="1">
+        <v>5</v>
+      </c>
+      <c r="G65" s="1">
+        <v>1001</v>
+      </c>
+      <c r="H65" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I65" s="1">
+        <v>100</v>
+      </c>
+      <c r="J65" s="1">
+        <v>1</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:11">
+      <c r="C66" s="1">
+        <v>131</v>
+      </c>
+      <c r="D66" s="8">
+        <v>180032</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F66" s="1">
+        <v>2</v>
+      </c>
+      <c r="G66" s="1">
+        <v>1501</v>
+      </c>
+      <c r="H66" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I66" s="1">
+        <v>100</v>
+      </c>
+      <c r="J66" s="1">
+        <v>1</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:11">
+      <c r="C67" s="1">
+        <v>132</v>
+      </c>
+      <c r="D67" s="8">
+        <v>180033</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F67" s="1">
+        <v>2</v>
+      </c>
+      <c r="G67" s="1">
+        <v>1501</v>
+      </c>
+      <c r="H67" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I67" s="1">
+        <v>100</v>
+      </c>
+      <c r="J67" s="1">
+        <v>1</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:11">
+      <c r="C69" s="1">
+        <v>201</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F69" s="1">
+        <v>5</v>
+      </c>
+      <c r="G69" s="1">
+        <v>150</v>
+      </c>
+      <c r="H69" s="1">
+        <v>1200</v>
+      </c>
+      <c r="I69" s="1">
+        <v>20</v>
+      </c>
+      <c r="J69" s="1">
+        <v>2</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:11">
+      <c r="C70" s="1">
+        <v>202</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F70" s="1">
+        <v>5</v>
+      </c>
+      <c r="G70" s="1">
+        <v>200</v>
+      </c>
+      <c r="H70" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I70" s="1">
+        <v>30</v>
+      </c>
+      <c r="J70" s="1">
+        <v>2</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:11">
+      <c r="C71" s="1">
         <v>203</v>
       </c>
-      <c r="D61" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F61" s="1">
+      <c r="D71" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F71" s="1">
         <v>15</v>
       </c>
-      <c r="G61" s="1">
+      <c r="G71" s="1">
         <v>1050</v>
       </c>
-      <c r="H61" s="1">
+      <c r="H71" s="1">
         <v>1500</v>
       </c>
-      <c r="I61" s="1">
+      <c r="I71" s="1">
         <v>51</v>
       </c>
-      <c r="J61" s="1">
+      <c r="J71" s="1">
         <v>2</v>
       </c>
-      <c r="K61" s="1" t="s">
+      <c r="K71" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="4:4">
-      <c r="D62" s="6"/>
-    </row>
-    <row r="63" customHeight="1" spans="4:4">
-      <c r="D63" s="6"/>
-    </row>
-    <row r="64" customHeight="1" spans="4:4">
-      <c r="D64" s="6"/>
+    <row r="72" customHeight="1" spans="4:4">
+      <c r="D72" s="8"/>
+    </row>
+    <row r="73" customHeight="1" spans="4:4">
+      <c r="D73" s="8"/>
+    </row>
+    <row r="74" customHeight="1" spans="4:4">
+      <c r="D74" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="106">
   <si>
     <t>#</t>
   </si>
@@ -358,6 +358,9 @@
   </si>
   <si>
     <t>极·BOSS契约</t>
+  </si>
+  <si>
+    <t>极.财富契约</t>
   </si>
   <si>
     <t>220016</t>
@@ -1373,7 +1376,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:L74"/>
+  <dimension ref="C1:L75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -3092,56 +3095,56 @@
         <v>96</v>
       </c>
     </row>
-    <row r="69" customHeight="1" spans="3:11">
-      <c r="C69" s="1">
-        <v>201</v>
-      </c>
-      <c r="D69" s="10" t="s">
+    <row r="68" customHeight="1" spans="3:11">
+      <c r="C68" s="1">
+        <v>133</v>
+      </c>
+      <c r="D68" s="8">
+        <v>180034</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="F68" s="1">
+        <v>2</v>
+      </c>
+      <c r="G68" s="1">
+        <v>1501</v>
+      </c>
+      <c r="H68" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I68" s="1">
         <v>100</v>
       </c>
-      <c r="F69" s="1">
-        <v>5</v>
-      </c>
-      <c r="G69" s="1">
-        <v>150</v>
-      </c>
-      <c r="H69" s="1">
-        <v>1200</v>
-      </c>
-      <c r="I69" s="1">
-        <v>20</v>
-      </c>
-      <c r="J69" s="1">
-        <v>2</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>44</v>
+      <c r="J68" s="1">
+        <v>1</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
       <c r="C70" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D70" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="F70" s="1">
         <v>5</v>
       </c>
       <c r="G70" s="1">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H70" s="1">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="I70" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J70" s="1">
         <v>2</v>
@@ -3152,25 +3155,25 @@
     </row>
     <row r="71" customHeight="1" spans="3:11">
       <c r="C71" s="1">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D71" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="F71" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G71" s="1">
-        <v>1050</v>
+        <v>200</v>
       </c>
       <c r="H71" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I71" s="1">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="J71" s="1">
         <v>2</v>
@@ -3179,14 +3182,43 @@
         <v>44</v>
       </c>
     </row>
-    <row r="72" customHeight="1" spans="4:4">
-      <c r="D72" s="8"/>
+    <row r="72" customHeight="1" spans="3:11">
+      <c r="C72" s="1">
+        <v>203</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F72" s="1">
+        <v>15</v>
+      </c>
+      <c r="G72" s="1">
+        <v>1050</v>
+      </c>
+      <c r="H72" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I72" s="1">
+        <v>51</v>
+      </c>
+      <c r="J72" s="1">
+        <v>2</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="73" customHeight="1" spans="4:4">
       <c r="D73" s="8"/>
     </row>
     <row r="74" customHeight="1" spans="4:4">
       <c r="D74" s="8"/>
+    </row>
+    <row r="75" customHeight="1" spans="4:4">
+      <c r="D75" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -1563,7 +1563,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>19</v>
@@ -1592,7 +1592,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>19</v>
@@ -1621,7 +1621,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>16</v>
@@ -1650,7 +1650,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>16</v>
@@ -1708,7 +1708,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>16</v>
@@ -1737,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>16</v>
@@ -1969,7 +1969,7 @@
         <v>1</v>
       </c>
       <c r="J22" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>19</v>
@@ -1998,7 +1998,7 @@
         <v>1</v>
       </c>
       <c r="J23" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>19</v>
@@ -2027,7 +2027,7 @@
         <v>1</v>
       </c>
       <c r="J24" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>19</v>
@@ -2056,7 +2056,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>19</v>
@@ -2085,7 +2085,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>19</v>
@@ -2114,7 +2114,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>19</v>
@@ -2143,7 +2143,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>16</v>
@@ -2172,7 +2172,7 @@
         <v>1</v>
       </c>
       <c r="J29" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>16</v>
@@ -2230,7 +2230,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>16</v>
@@ -2259,7 +2259,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>16</v>
@@ -2363,7 +2363,7 @@
         <v>68</v>
       </c>
       <c r="F36" s="2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G36" s="2">
         <v>1501</v>
@@ -2392,7 +2392,7 @@
         <v>70</v>
       </c>
       <c r="F37" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G37" s="2">
         <v>1501</v>
@@ -2433,7 +2433,7 @@
         <v>1</v>
       </c>
       <c r="J38" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K38" s="1" t="s">
         <v>19</v>
@@ -2462,7 +2462,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K39" s="1" t="s">
         <v>19</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -3048,7 +3048,7 @@
         <v>97</v>
       </c>
       <c r="F66" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G66" s="1">
         <v>1501</v>
@@ -3077,7 +3077,7 @@
         <v>98</v>
       </c>
       <c r="F67" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G67" s="1">
         <v>1501</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -141,7 +141,7 @@
     <t>沙城图鉴</t>
   </si>
   <si>
-    <t>2006</t>
+    <t>2005</t>
   </si>
   <si>
     <t>红色图鉴</t>
@@ -1940,7 +1940,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>49</v>
@@ -3051,7 +3051,7 @@
         <v>1</v>
       </c>
       <c r="G66" s="1">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H66" s="1">
         <v>3000</v>
@@ -3080,7 +3080,7 @@
         <v>1</v>
       </c>
       <c r="G67" s="1">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H67" s="1">
         <v>3000</v>
@@ -3109,7 +3109,7 @@
         <v>2</v>
       </c>
       <c r="G68" s="1">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H68" s="1">
         <v>3000</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="108">
   <si>
     <t>#</t>
   </si>
@@ -292,6 +292,12 @@
   </si>
   <si>
     <t>等级丹*15</t>
+  </si>
+  <si>
+    <t>220038</t>
+  </si>
+  <si>
+    <t>天赋秘籍</t>
   </si>
   <si>
     <t>BOSS杀手</t>
@@ -2497,8 +2503,31 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="4:4">
-      <c r="D41" s="6"/>
+    <row r="41" s="1" customFormat="1" ht="20" customHeight="1" spans="3:10">
+      <c r="C41" s="1">
+        <v>36</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F41" s="1">
+        <v>5</v>
+      </c>
+      <c r="G41" s="2">
+        <v>500</v>
+      </c>
+      <c r="H41" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I41" s="1">
+        <v>30</v>
+      </c>
+      <c r="J41" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="42" customHeight="1" spans="4:4">
       <c r="D42" s="6"/>
@@ -2523,7 +2552,7 @@
         <v>180001</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F47" s="1">
         <v>2000</v>
@@ -2541,7 +2570,7 @@
         <v>1</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:11">
@@ -2552,7 +2581,7 @@
         <v>180002</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F48" s="1">
         <v>4000</v>
@@ -2570,7 +2599,7 @@
         <v>1</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:11">
@@ -2581,7 +2610,7 @@
         <v>180003</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F49" s="1">
         <v>150000</v>
@@ -2599,7 +2628,7 @@
         <v>10</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:11">
@@ -2610,7 +2639,7 @@
         <v>180004</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F50" s="1">
         <v>8000</v>
@@ -2628,7 +2657,7 @@
         <v>1</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:11">
@@ -2639,7 +2668,7 @@
         <v>180005</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F51" s="1">
         <v>3000</v>
@@ -2657,7 +2686,7 @@
         <v>1</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:11">
@@ -2668,7 +2697,7 @@
         <v>180006</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F52" s="1">
         <v>50000</v>
@@ -2686,7 +2715,7 @@
         <v>10</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:11">
@@ -2697,7 +2726,7 @@
         <v>180007</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F53" s="1">
         <v>2000</v>
@@ -2715,7 +2744,7 @@
         <v>1</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:11">
@@ -2726,7 +2755,7 @@
         <v>180008</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F54" s="1">
         <v>20000</v>
@@ -2744,7 +2773,7 @@
         <v>2</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
@@ -2755,7 +2784,7 @@
         <v>180009</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F55" s="1">
         <v>3000</v>
@@ -2773,7 +2802,7 @@
         <v>1</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
@@ -2784,7 +2813,7 @@
         <v>180010</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F56" s="1">
         <v>10000</v>
@@ -2802,7 +2831,7 @@
         <v>1</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:11">
@@ -2813,7 +2842,7 @@
         <v>180011</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F57" s="1">
         <v>100000</v>
@@ -2831,7 +2860,7 @@
         <v>10</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:11">
@@ -2842,7 +2871,7 @@
         <v>180012</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F58" s="1">
         <v>100000</v>
@@ -2860,7 +2889,7 @@
         <v>10</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
@@ -2871,7 +2900,7 @@
         <v>180013</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F59" s="1">
         <v>50000</v>
@@ -2889,7 +2918,7 @@
         <v>1</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:11">
@@ -2900,7 +2929,7 @@
         <v>180014</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F60" s="1">
         <v>100000</v>
@@ -2918,7 +2947,7 @@
         <v>10</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:11">
@@ -2929,7 +2958,7 @@
         <v>180015</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F61" s="1">
         <v>100000</v>
@@ -2947,7 +2976,7 @@
         <v>10</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:11">
@@ -2958,7 +2987,7 @@
         <v>180020</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F62" s="1">
         <v>10000</v>
@@ -2976,7 +3005,7 @@
         <v>1</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:11">
@@ -2987,7 +3016,7 @@
         <v>180021</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F63" s="1">
         <v>10000</v>
@@ -3005,7 +3034,7 @@
         <v>1</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:11">
@@ -3016,7 +3045,7 @@
         <v>180030</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F65" s="1">
         <v>5</v>
@@ -3034,7 +3063,7 @@
         <v>1</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:11">
@@ -3045,7 +3074,7 @@
         <v>180032</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F66" s="1">
         <v>1</v>
@@ -3063,7 +3092,7 @@
         <v>1</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
@@ -3074,7 +3103,7 @@
         <v>180033</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F67" s="1">
         <v>1</v>
@@ -3092,7 +3121,7 @@
         <v>1</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:11">
@@ -3103,7 +3132,7 @@
         <v>180034</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F68" s="1">
         <v>2</v>
@@ -3121,7 +3150,7 @@
         <v>1</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
@@ -3129,10 +3158,10 @@
         <v>201</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F70" s="1">
         <v>5</v>
@@ -3158,10 +3187,10 @@
         <v>202</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F71" s="1">
         <v>5</v>
@@ -3187,10 +3216,10 @@
         <v>203</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F72" s="1">
         <v>15</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -3083,7 +3083,7 @@
         <v>1001</v>
       </c>
       <c r="H66" s="1">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="I66" s="1">
         <v>100</v>
@@ -3109,10 +3109,10 @@
         <v>1</v>
       </c>
       <c r="G67" s="1">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="H67" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I67" s="1">
         <v>100</v>
@@ -3138,10 +3138,10 @@
         <v>2</v>
       </c>
       <c r="G68" s="1">
-        <v>1001</v>
+        <v>1501</v>
       </c>
       <c r="H68" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I68" s="1">
         <v>100</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -3083,7 +3083,7 @@
         <v>1001</v>
       </c>
       <c r="H66" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I66" s="1">
         <v>100</v>
@@ -3109,7 +3109,7 @@
         <v>1</v>
       </c>
       <c r="G67" s="1">
-        <v>2001</v>
+        <v>1501</v>
       </c>
       <c r="H67" s="1">
         <v>2500</v>
@@ -3138,10 +3138,10 @@
         <v>2</v>
       </c>
       <c r="G68" s="1">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H68" s="1">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="I68" s="1">
         <v>100</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -1047,9 +1047,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1057,11 +1059,13 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1382,7 +1386,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:L75"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1411,80 +1415,80 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1492,7 +1496,7 @@
       <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="12" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -1521,7 +1525,7 @@
       <c r="C7" s="2">
         <v>2</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -1550,7 +1554,7 @@
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -1579,7 +1583,7 @@
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -1608,7 +1612,7 @@
       <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="14" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -1637,7 +1641,7 @@
       <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="14" t="s">
         <v>24</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -1666,7 +1670,7 @@
       <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="14" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -1753,7 +1757,7 @@
       <c r="C15" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="13" t="s">
         <v>31</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -1782,7 +1786,7 @@
       <c r="C16" s="3">
         <v>11</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -1811,7 +1815,7 @@
       <c r="C17" s="1">
         <v>12</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="13" t="s">
         <v>36</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -1840,7 +1844,7 @@
       <c r="C18" s="2">
         <v>13</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E18" s="2" t="s">
@@ -1869,7 +1873,7 @@
       <c r="C19" s="3">
         <v>14</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="15" t="s">
         <v>42</v>
       </c>
       <c r="E19" s="3" t="s">
@@ -1898,7 +1902,7 @@
       <c r="C20" s="1">
         <v>15</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="13" t="s">
         <v>45</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -1927,7 +1931,7 @@
       <c r="C21" s="1">
         <v>16</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="13" t="s">
         <v>47</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -1956,7 +1960,7 @@
       <c r="C22" s="1">
         <v>17</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="13" t="s">
         <v>50</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -1985,7 +1989,7 @@
       <c r="C23" s="1">
         <v>18</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="13" t="s">
         <v>51</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -2014,7 +2018,7 @@
       <c r="C24" s="1">
         <v>19</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="13" t="s">
         <v>52</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -2043,7 +2047,7 @@
       <c r="C25" s="1">
         <v>20</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="13" t="s">
         <v>53</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -2072,7 +2076,7 @@
       <c r="C26" s="1">
         <v>21</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="13" t="s">
         <v>54</v>
       </c>
       <c r="E26" s="1" t="s">
@@ -2101,7 +2105,7 @@
       <c r="C27" s="1">
         <v>22</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="13" t="s">
         <v>55</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -2126,148 +2130,158 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C28" s="1">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5">
         <v>23</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="5">
         <v>10</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G28" s="5">
         <v>1001</v>
       </c>
-      <c r="H28" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I28" s="1">
-        <v>1</v>
-      </c>
-      <c r="J28" s="1">
-        <v>10000</v>
-      </c>
-      <c r="K28" s="1" t="s">
+      <c r="H28" s="5">
+        <v>10000</v>
+      </c>
+      <c r="I28" s="5">
+        <v>1</v>
+      </c>
+      <c r="J28" s="5">
+        <v>10000</v>
+      </c>
+      <c r="K28" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C29" s="1">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5">
         <v>24</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="5">
         <v>10</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G29" s="5">
         <v>1001</v>
       </c>
-      <c r="H29" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I29" s="1">
-        <v>1</v>
-      </c>
-      <c r="J29" s="1">
-        <v>10000</v>
-      </c>
-      <c r="K29" s="1" t="s">
+      <c r="H29" s="5">
+        <v>10000</v>
+      </c>
+      <c r="I29" s="5">
+        <v>1</v>
+      </c>
+      <c r="J29" s="5">
+        <v>10000</v>
+      </c>
+      <c r="K29" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="3:11">
-      <c r="C30" s="1">
+    <row r="30" s="4" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3">
         <v>25</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="3">
         <v>4</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G30" s="3">
         <v>1001</v>
       </c>
-      <c r="H30" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I30" s="1">
-        <v>1</v>
-      </c>
-      <c r="J30" s="1">
+      <c r="H30" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I30" s="3">
+        <v>1</v>
+      </c>
+      <c r="J30" s="3">
         <v>20</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="K30" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="3:11">
-      <c r="C31" s="1">
+    <row r="31" customHeight="1" spans="1:11">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5">
         <v>26</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="5">
         <v>10</v>
       </c>
-      <c r="G31" s="1">
+      <c r="G31" s="5">
         <v>1001</v>
       </c>
-      <c r="H31" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I31" s="1">
-        <v>1</v>
-      </c>
-      <c r="J31" s="1">
-        <v>10000</v>
-      </c>
-      <c r="K31" s="1" t="s">
+      <c r="H31" s="5">
+        <v>10000</v>
+      </c>
+      <c r="I31" s="5">
+        <v>1</v>
+      </c>
+      <c r="J31" s="5">
+        <v>10000</v>
+      </c>
+      <c r="K31" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="3:11">
-      <c r="C32" s="1">
+    <row r="32" customHeight="1" spans="1:11">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5">
         <v>27</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="5">
         <v>10</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G32" s="5">
         <v>1001</v>
       </c>
-      <c r="H32" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I32" s="1">
-        <v>1</v>
-      </c>
-      <c r="J32" s="1">
-        <v>10000</v>
-      </c>
-      <c r="K32" s="1" t="s">
+      <c r="H32" s="5">
+        <v>10000</v>
+      </c>
+      <c r="I32" s="5">
+        <v>1</v>
+      </c>
+      <c r="J32" s="5">
+        <v>10000</v>
+      </c>
+      <c r="K32" s="5" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2275,7 +2289,7 @@
       <c r="C33" s="1">
         <v>28</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="13" t="s">
         <v>61</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -2304,7 +2318,7 @@
       <c r="C34" s="1">
         <v>29</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="13" t="s">
         <v>63</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -2333,7 +2347,7 @@
       <c r="C35" s="1">
         <v>30</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="13" t="s">
         <v>65</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -2358,127 +2372,127 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C36" s="2">
+    <row r="36" s="3" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C36" s="3">
         <v>31</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D36" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="3">
         <v>30</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G36" s="3">
         <v>1501</v>
       </c>
-      <c r="H36" s="2">
-        <v>10000</v>
-      </c>
-      <c r="I36" s="2">
-        <v>1</v>
-      </c>
-      <c r="J36" s="2">
+      <c r="H36" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I36" s="3">
+        <v>1</v>
+      </c>
+      <c r="J36" s="3">
         <v>200</v>
       </c>
-      <c r="K36" s="2" t="s">
+      <c r="K36" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C37" s="2">
+    <row r="37" s="3" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C37" s="3">
         <v>32</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="3">
         <v>3</v>
       </c>
-      <c r="G37" s="2">
+      <c r="G37" s="3">
         <v>1501</v>
       </c>
-      <c r="H37" s="2">
-        <v>10000</v>
-      </c>
-      <c r="I37" s="2">
-        <v>1</v>
-      </c>
-      <c r="J37" s="2">
+      <c r="H37" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I37" s="3">
+        <v>1</v>
+      </c>
+      <c r="J37" s="3">
         <v>20</v>
       </c>
-      <c r="K37" s="2" t="s">
+      <c r="K37" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C38" s="1">
+    <row r="38" s="5" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C38" s="5">
         <v>33</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="5">
         <v>50</v>
       </c>
-      <c r="G38" s="2">
+      <c r="G38" s="5">
         <v>1501</v>
       </c>
-      <c r="H38" s="2">
-        <v>10000</v>
-      </c>
-      <c r="I38" s="1">
-        <v>1</v>
-      </c>
-      <c r="J38" s="1">
-        <v>10000</v>
-      </c>
-      <c r="K38" s="1" t="s">
+      <c r="H38" s="5">
+        <v>10000</v>
+      </c>
+      <c r="I38" s="5">
+        <v>1</v>
+      </c>
+      <c r="J38" s="5">
+        <v>10000</v>
+      </c>
+      <c r="K38" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" ht="20" customHeight="1" spans="3:11">
-      <c r="C39" s="1">
+    <row r="39" s="5" customFormat="1" ht="20" customHeight="1" spans="3:11">
+      <c r="C39" s="5">
         <v>34</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="5">
         <v>50</v>
       </c>
-      <c r="G39" s="2">
+      <c r="G39" s="5">
         <v>1501</v>
       </c>
-      <c r="H39" s="2">
-        <v>10000</v>
-      </c>
-      <c r="I39" s="1">
-        <v>1</v>
-      </c>
-      <c r="J39" s="1">
-        <v>10000</v>
-      </c>
-      <c r="K39" s="1" t="s">
+      <c r="H39" s="5">
+        <v>10000</v>
+      </c>
+      <c r="I39" s="5">
+        <v>1</v>
+      </c>
+      <c r="J39" s="5">
+        <v>10000</v>
+      </c>
+      <c r="K39" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C40" s="1">
+      <c r="C40" s="3">
         <v>35</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="15" t="s">
         <v>75</v>
       </c>
       <c r="E40" s="3" t="s">
@@ -2490,7 +2504,7 @@
       <c r="G40" s="3">
         <v>1501</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H40" s="3">
         <v>10000</v>
       </c>
       <c r="I40" s="3">
@@ -2507,7 +2521,7 @@
       <c r="C41" s="1">
         <v>36</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="13" t="s">
         <v>77</v>
       </c>
       <c r="E41" s="1" t="s">
@@ -2530,25 +2544,25 @@
       </c>
     </row>
     <row r="42" customHeight="1" spans="4:4">
-      <c r="D42" s="6"/>
+      <c r="D42" s="8"/>
     </row>
     <row r="43" customHeight="1" spans="4:4">
-      <c r="D43" s="6"/>
+      <c r="D43" s="8"/>
     </row>
     <row r="44" customHeight="1" spans="4:4">
-      <c r="D44" s="6"/>
+      <c r="D44" s="8"/>
     </row>
     <row r="45" customHeight="1" spans="4:4">
-      <c r="D45" s="6"/>
+      <c r="D45" s="8"/>
     </row>
     <row r="46" customHeight="1" spans="4:4">
-      <c r="D46" s="6"/>
+      <c r="D46" s="8"/>
     </row>
     <row r="47" customHeight="1" spans="3:11">
       <c r="C47" s="1">
         <v>101</v>
       </c>
-      <c r="D47" s="8">
+      <c r="D47" s="11">
         <v>180001</v>
       </c>
       <c r="E47" s="1" t="s">
@@ -2577,7 +2591,7 @@
       <c r="C48" s="1">
         <v>102</v>
       </c>
-      <c r="D48" s="8">
+      <c r="D48" s="11">
         <v>180002</v>
       </c>
       <c r="E48" s="1" t="s">
@@ -2606,7 +2620,7 @@
       <c r="C49" s="1">
         <v>103</v>
       </c>
-      <c r="D49" s="8">
+      <c r="D49" s="11">
         <v>180003</v>
       </c>
       <c r="E49" s="1" t="s">
@@ -2635,7 +2649,7 @@
       <c r="C50" s="1">
         <v>104</v>
       </c>
-      <c r="D50" s="8">
+      <c r="D50" s="11">
         <v>180004</v>
       </c>
       <c r="E50" s="1" t="s">
@@ -2664,7 +2678,7 @@
       <c r="C51" s="1">
         <v>105</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="11">
         <v>180005</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -2693,7 +2707,7 @@
       <c r="C52" s="1">
         <v>106</v>
       </c>
-      <c r="D52" s="8">
+      <c r="D52" s="11">
         <v>180006</v>
       </c>
       <c r="E52" s="1" t="s">
@@ -2722,7 +2736,7 @@
       <c r="C53" s="1">
         <v>107</v>
       </c>
-      <c r="D53" s="8">
+      <c r="D53" s="11">
         <v>180007</v>
       </c>
       <c r="E53" s="1" t="s">
@@ -2751,7 +2765,7 @@
       <c r="C54" s="1">
         <v>108</v>
       </c>
-      <c r="D54" s="8">
+      <c r="D54" s="11">
         <v>180008</v>
       </c>
       <c r="E54" s="1" t="s">
@@ -2780,7 +2794,7 @@
       <c r="C55" s="1">
         <v>109</v>
       </c>
-      <c r="D55" s="8">
+      <c r="D55" s="11">
         <v>180009</v>
       </c>
       <c r="E55" s="1" t="s">
@@ -2809,7 +2823,7 @@
       <c r="C56" s="1">
         <v>110</v>
       </c>
-      <c r="D56" s="8">
+      <c r="D56" s="11">
         <v>180010</v>
       </c>
       <c r="E56" s="1" t="s">
@@ -2838,7 +2852,7 @@
       <c r="C57" s="1">
         <v>111</v>
       </c>
-      <c r="D57" s="8">
+      <c r="D57" s="11">
         <v>180011</v>
       </c>
       <c r="E57" s="1" t="s">
@@ -2867,7 +2881,7 @@
       <c r="C58" s="1">
         <v>112</v>
       </c>
-      <c r="D58" s="8">
+      <c r="D58" s="11">
         <v>180012</v>
       </c>
       <c r="E58" s="1" t="s">
@@ -2896,7 +2910,7 @@
       <c r="C59" s="1">
         <v>113</v>
       </c>
-      <c r="D59" s="8">
+      <c r="D59" s="11">
         <v>180013</v>
       </c>
       <c r="E59" s="1" t="s">
@@ -2925,7 +2939,7 @@
       <c r="C60" s="1">
         <v>114</v>
       </c>
-      <c r="D60" s="8">
+      <c r="D60" s="11">
         <v>180014</v>
       </c>
       <c r="E60" s="1" t="s">
@@ -2954,7 +2968,7 @@
       <c r="C61" s="1">
         <v>115</v>
       </c>
-      <c r="D61" s="8">
+      <c r="D61" s="11">
         <v>180015</v>
       </c>
       <c r="E61" s="1" t="s">
@@ -2983,7 +2997,7 @@
       <c r="C62" s="1">
         <v>120</v>
       </c>
-      <c r="D62" s="8">
+      <c r="D62" s="11">
         <v>180020</v>
       </c>
       <c r="E62" s="1" t="s">
@@ -3012,7 +3026,7 @@
       <c r="C63" s="1">
         <v>121</v>
       </c>
-      <c r="D63" s="8">
+      <c r="D63" s="11">
         <v>180021</v>
       </c>
       <c r="E63" s="1" t="s">
@@ -3070,7 +3084,7 @@
       <c r="C66" s="1">
         <v>131</v>
       </c>
-      <c r="D66" s="8">
+      <c r="D66" s="11">
         <v>180032</v>
       </c>
       <c r="E66" s="1" t="s">
@@ -3099,7 +3113,7 @@
       <c r="C67" s="1">
         <v>132</v>
       </c>
-      <c r="D67" s="8">
+      <c r="D67" s="11">
         <v>180033</v>
       </c>
       <c r="E67" s="1" t="s">
@@ -3128,7 +3142,7 @@
       <c r="C68" s="1">
         <v>133</v>
       </c>
-      <c r="D68" s="8">
+      <c r="D68" s="11">
         <v>180034</v>
       </c>
       <c r="E68" s="1" t="s">
@@ -3157,7 +3171,7 @@
       <c r="C70" s="1">
         <v>201</v>
       </c>
-      <c r="D70" s="10" t="s">
+      <c r="D70" s="13" t="s">
         <v>102</v>
       </c>
       <c r="E70" s="1" t="s">
@@ -3186,7 +3200,7 @@
       <c r="C71" s="1">
         <v>202</v>
       </c>
-      <c r="D71" s="10" t="s">
+      <c r="D71" s="13" t="s">
         <v>104</v>
       </c>
       <c r="E71" s="1" t="s">
@@ -3215,7 +3229,7 @@
       <c r="C72" s="1">
         <v>203</v>
       </c>
-      <c r="D72" s="10" t="s">
+      <c r="D72" s="13" t="s">
         <v>106</v>
       </c>
       <c r="E72" s="1" t="s">
@@ -3241,13 +3255,13 @@
       </c>
     </row>
     <row r="73" customHeight="1" spans="4:4">
-      <c r="D73" s="8"/>
+      <c r="D73" s="11"/>
     </row>
     <row r="74" customHeight="1" spans="4:4">
-      <c r="D74" s="8"/>
+      <c r="D74" s="11"/>
     </row>
     <row r="75" customHeight="1" spans="4:4">
-      <c r="D75" s="8"/>
+      <c r="D75" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="112">
   <si>
     <t>#</t>
   </si>
@@ -300,6 +300,12 @@
     <t>天赋秘籍</t>
   </si>
   <si>
+    <t>220041</t>
+  </si>
+  <si>
+    <t>改造石</t>
+  </si>
+  <si>
     <t>BOSS杀手</t>
   </si>
   <si>
@@ -367,6 +373,12 @@
   </si>
   <si>
     <t>极.财富契约</t>
+  </si>
+  <si>
+    <t>极.魔法书</t>
+  </si>
+  <si>
+    <t>极.无限之魂</t>
   </si>
   <si>
     <t>220016</t>
@@ -1047,11 +1059,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1059,13 +1069,11 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1386,7 +1394,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1415,80 +1423,80 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C4" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="C4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1496,7 +1504,7 @@
       <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="9" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -1525,7 +1533,7 @@
       <c r="C7" s="2">
         <v>2</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -1554,7 +1562,7 @@
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -1583,7 +1591,7 @@
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="10" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -1612,7 +1620,7 @@
       <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="11" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -1641,7 +1649,7 @@
       <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="11" t="s">
         <v>24</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -1670,7 +1678,7 @@
       <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="11" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -1757,7 +1765,7 @@
       <c r="C15" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="10" t="s">
         <v>31</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -1782,32 +1790,32 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" s="3" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C16" s="3">
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C16" s="2">
         <v>11</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <v>10</v>
       </c>
-      <c r="G16" s="3">
-        <v>1</v>
-      </c>
-      <c r="H16" s="3">
-        <v>10000</v>
-      </c>
-      <c r="I16" s="3">
-        <v>1</v>
-      </c>
-      <c r="J16" s="3">
+      <c r="G16" s="2">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1</v>
+      </c>
+      <c r="J16" s="2">
         <v>50</v>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="K16" s="2" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1815,7 +1823,7 @@
       <c r="C17" s="1">
         <v>12</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="10" t="s">
         <v>36</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -1844,7 +1852,7 @@
       <c r="C18" s="2">
         <v>13</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="9" t="s">
         <v>39</v>
       </c>
       <c r="E18" s="2" t="s">
@@ -1869,32 +1877,32 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" s="3" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C19" s="3">
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C19" s="2">
         <v>14</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="3">
-        <v>1</v>
-      </c>
-      <c r="G19" s="3">
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2">
         <v>100</v>
       </c>
-      <c r="H19" s="3">
-        <v>10000</v>
-      </c>
-      <c r="I19" s="3">
+      <c r="H19" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I19" s="2">
         <v>3</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="2">
         <v>2</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="K19" s="2" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1902,7 +1910,7 @@
       <c r="C20" s="1">
         <v>15</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="10" t="s">
         <v>45</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -1931,7 +1939,7 @@
       <c r="C21" s="1">
         <v>16</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="10" t="s">
         <v>47</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -1960,7 +1968,7 @@
       <c r="C22" s="1">
         <v>17</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="10" t="s">
         <v>50</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -1989,7 +1997,7 @@
       <c r="C23" s="1">
         <v>18</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="10" t="s">
         <v>51</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -2018,7 +2026,7 @@
       <c r="C24" s="1">
         <v>19</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="10" t="s">
         <v>52</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -2047,7 +2055,7 @@
       <c r="C25" s="1">
         <v>20</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="10" t="s">
         <v>53</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -2076,7 +2084,7 @@
       <c r="C26" s="1">
         <v>21</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E26" s="1" t="s">
@@ -2105,7 +2113,7 @@
       <c r="C27" s="1">
         <v>22</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="10" t="s">
         <v>55</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -2131,157 +2139,155 @@
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3">
         <v>23</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="3">
         <v>10</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="3">
         <v>1001</v>
       </c>
-      <c r="H28" s="5">
-        <v>10000</v>
-      </c>
-      <c r="I28" s="5">
-        <v>1</v>
-      </c>
-      <c r="J28" s="5">
-        <v>10000</v>
-      </c>
-      <c r="K28" s="5" t="s">
+      <c r="H28" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I28" s="3">
+        <v>1</v>
+      </c>
+      <c r="J28" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K28" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3">
         <v>24</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D29" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="3">
         <v>10</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="3">
         <v>1001</v>
       </c>
-      <c r="H29" s="5">
-        <v>10000</v>
-      </c>
-      <c r="I29" s="5">
-        <v>1</v>
-      </c>
-      <c r="J29" s="5">
-        <v>10000</v>
-      </c>
-      <c r="K29" s="5" t="s">
+      <c r="H29" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I29" s="3">
+        <v>1</v>
+      </c>
+      <c r="J29" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="30" s="4" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3">
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C30" s="2">
         <v>25</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="2">
         <v>4</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="2">
         <v>1001</v>
       </c>
-      <c r="H30" s="3">
-        <v>10000</v>
-      </c>
-      <c r="I30" s="3">
-        <v>1</v>
-      </c>
-      <c r="J30" s="3">
+      <c r="H30" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I30" s="2">
+        <v>1</v>
+      </c>
+      <c r="J30" s="2">
         <v>20</v>
       </c>
-      <c r="K30" s="3" t="s">
+      <c r="K30" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:11">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3">
         <v>26</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="3">
         <v>10</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="3">
         <v>1001</v>
       </c>
-      <c r="H31" s="5">
-        <v>10000</v>
-      </c>
-      <c r="I31" s="5">
-        <v>1</v>
-      </c>
-      <c r="J31" s="5">
-        <v>10000</v>
-      </c>
-      <c r="K31" s="5" t="s">
+      <c r="H31" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I31" s="3">
+        <v>1</v>
+      </c>
+      <c r="J31" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K31" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:11">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3">
         <v>27</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="3">
         <v>10</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G32" s="3">
         <v>1001</v>
       </c>
-      <c r="H32" s="5">
-        <v>10000</v>
-      </c>
-      <c r="I32" s="5">
-        <v>1</v>
-      </c>
-      <c r="J32" s="5">
-        <v>10000</v>
-      </c>
-      <c r="K32" s="5" t="s">
+      <c r="H32" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>1</v>
+      </c>
+      <c r="J32" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K32" s="3" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2289,7 +2295,7 @@
       <c r="C33" s="1">
         <v>28</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="10" t="s">
         <v>61</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -2318,7 +2324,7 @@
       <c r="C34" s="1">
         <v>29</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -2347,7 +2353,7 @@
       <c r="C35" s="1">
         <v>30</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="10" t="s">
         <v>65</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -2372,148 +2378,148 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" s="3" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C36" s="3">
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C36" s="2">
         <v>31</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D36" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="2">
         <v>30</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36" s="2">
         <v>1501</v>
       </c>
-      <c r="H36" s="3">
-        <v>10000</v>
-      </c>
-      <c r="I36" s="3">
-        <v>1</v>
-      </c>
-      <c r="J36" s="3">
+      <c r="H36" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I36" s="2">
+        <v>1</v>
+      </c>
+      <c r="J36" s="2">
         <v>200</v>
       </c>
-      <c r="K36" s="3" t="s">
+      <c r="K36" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="37" s="3" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C37" s="3">
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C37" s="2">
         <v>32</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D37" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="2">
         <v>3</v>
       </c>
-      <c r="G37" s="3">
+      <c r="G37" s="2">
         <v>1501</v>
       </c>
-      <c r="H37" s="3">
-        <v>10000</v>
-      </c>
-      <c r="I37" s="3">
-        <v>1</v>
-      </c>
-      <c r="J37" s="3">
+      <c r="H37" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I37" s="2">
+        <v>1</v>
+      </c>
+      <c r="J37" s="2">
         <v>20</v>
       </c>
-      <c r="K37" s="3" t="s">
+      <c r="K37" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" s="5" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C38" s="5">
+    <row r="38" s="3" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C38" s="3">
         <v>33</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="D38" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="3">
         <v>50</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="3">
         <v>1501</v>
       </c>
-      <c r="H38" s="5">
-        <v>10000</v>
-      </c>
-      <c r="I38" s="5">
-        <v>1</v>
-      </c>
-      <c r="J38" s="5">
-        <v>10000</v>
-      </c>
-      <c r="K38" s="5" t="s">
+      <c r="H38" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I38" s="3">
+        <v>1</v>
+      </c>
+      <c r="J38" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K38" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="39" s="5" customFormat="1" ht="20" customHeight="1" spans="3:11">
-      <c r="C39" s="5">
+    <row r="39" s="3" customFormat="1" ht="20" customHeight="1" spans="3:11">
+      <c r="C39" s="3">
         <v>34</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D39" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39" s="3">
         <v>50</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="3">
         <v>1501</v>
       </c>
-      <c r="H39" s="5">
-        <v>10000</v>
-      </c>
-      <c r="I39" s="5">
-        <v>1</v>
-      </c>
-      <c r="J39" s="5">
-        <v>10000</v>
-      </c>
-      <c r="K39" s="5" t="s">
+      <c r="H39" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I39" s="3">
+        <v>1</v>
+      </c>
+      <c r="J39" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K39" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="40" s="3" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C40" s="3">
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C40" s="2">
         <v>35</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40" s="2">
         <v>6</v>
       </c>
-      <c r="G40" s="3">
+      <c r="G40" s="2">
         <v>1501</v>
       </c>
-      <c r="H40" s="3">
-        <v>10000</v>
-      </c>
-      <c r="I40" s="3">
-        <v>1</v>
-      </c>
-      <c r="J40" s="3">
+      <c r="H40" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I40" s="2">
+        <v>1</v>
+      </c>
+      <c r="J40" s="2">
         <v>25</v>
       </c>
-      <c r="K40" s="3" t="s">
+      <c r="K40" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2521,7 +2527,7 @@
       <c r="C41" s="1">
         <v>36</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E41" s="1" t="s">
@@ -2543,30 +2549,53 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="4:4">
-      <c r="D42" s="8"/>
+    <row r="42" s="1" customFormat="1" ht="20" customHeight="1" spans="3:10">
+      <c r="C42" s="1">
+        <v>37</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F42" s="1">
+        <v>5</v>
+      </c>
+      <c r="G42" s="2">
+        <v>1500</v>
+      </c>
+      <c r="H42" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I42" s="1">
+        <v>10</v>
+      </c>
+      <c r="J42" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="43" customHeight="1" spans="4:4">
-      <c r="D43" s="8"/>
+      <c r="D43" s="6"/>
     </row>
     <row r="44" customHeight="1" spans="4:4">
-      <c r="D44" s="8"/>
+      <c r="D44" s="6"/>
     </row>
     <row r="45" customHeight="1" spans="4:4">
-      <c r="D45" s="8"/>
+      <c r="D45" s="6"/>
     </row>
     <row r="46" customHeight="1" spans="4:4">
-      <c r="D46" s="8"/>
+      <c r="D46" s="6"/>
     </row>
     <row r="47" customHeight="1" spans="3:11">
       <c r="C47" s="1">
         <v>101</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="8">
         <v>180001</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F47" s="1">
         <v>2000</v>
@@ -2584,18 +2613,18 @@
         <v>1</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:11">
       <c r="C48" s="1">
         <v>102</v>
       </c>
-      <c r="D48" s="11">
+      <c r="D48" s="8">
         <v>180002</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F48" s="1">
         <v>4000</v>
@@ -2613,18 +2642,18 @@
         <v>1</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:11">
       <c r="C49" s="1">
         <v>103</v>
       </c>
-      <c r="D49" s="11">
+      <c r="D49" s="8">
         <v>180003</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F49" s="1">
         <v>150000</v>
@@ -2642,18 +2671,18 @@
         <v>10</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:11">
       <c r="C50" s="1">
         <v>104</v>
       </c>
-      <c r="D50" s="11">
+      <c r="D50" s="8">
         <v>180004</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F50" s="1">
         <v>8000</v>
@@ -2671,18 +2700,18 @@
         <v>1</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:11">
       <c r="C51" s="1">
         <v>105</v>
       </c>
-      <c r="D51" s="11">
+      <c r="D51" s="8">
         <v>180005</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F51" s="1">
         <v>3000</v>
@@ -2700,18 +2729,18 @@
         <v>1</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:11">
       <c r="C52" s="1">
         <v>106</v>
       </c>
-      <c r="D52" s="11">
+      <c r="D52" s="8">
         <v>180006</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F52" s="1">
         <v>50000</v>
@@ -2729,18 +2758,18 @@
         <v>10</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:11">
       <c r="C53" s="1">
         <v>107</v>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="8">
         <v>180007</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F53" s="1">
         <v>2000</v>
@@ -2758,18 +2787,18 @@
         <v>1</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:11">
       <c r="C54" s="1">
         <v>108</v>
       </c>
-      <c r="D54" s="11">
+      <c r="D54" s="8">
         <v>180008</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F54" s="1">
         <v>20000</v>
@@ -2787,18 +2816,18 @@
         <v>2</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
       <c r="C55" s="1">
         <v>109</v>
       </c>
-      <c r="D55" s="11">
+      <c r="D55" s="8">
         <v>180009</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F55" s="1">
         <v>3000</v>
@@ -2816,18 +2845,18 @@
         <v>1</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
       <c r="C56" s="1">
         <v>110</v>
       </c>
-      <c r="D56" s="11">
+      <c r="D56" s="8">
         <v>180010</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F56" s="1">
         <v>10000</v>
@@ -2845,18 +2874,18 @@
         <v>1</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:11">
       <c r="C57" s="1">
         <v>111</v>
       </c>
-      <c r="D57" s="11">
+      <c r="D57" s="8">
         <v>180011</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F57" s="1">
         <v>100000</v>
@@ -2874,18 +2903,18 @@
         <v>10</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:11">
       <c r="C58" s="1">
         <v>112</v>
       </c>
-      <c r="D58" s="11">
+      <c r="D58" s="8">
         <v>180012</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F58" s="1">
         <v>100000</v>
@@ -2903,18 +2932,18 @@
         <v>10</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
       <c r="C59" s="1">
         <v>113</v>
       </c>
-      <c r="D59" s="11">
+      <c r="D59" s="8">
         <v>180013</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F59" s="1">
         <v>50000</v>
@@ -2932,18 +2961,18 @@
         <v>1</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:11">
       <c r="C60" s="1">
         <v>114</v>
       </c>
-      <c r="D60" s="11">
+      <c r="D60" s="8">
         <v>180014</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F60" s="1">
         <v>100000</v>
@@ -2961,18 +2990,18 @@
         <v>10</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:11">
       <c r="C61" s="1">
         <v>115</v>
       </c>
-      <c r="D61" s="11">
+      <c r="D61" s="8">
         <v>180015</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F61" s="1">
         <v>100000</v>
@@ -2990,18 +3019,18 @@
         <v>10</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:11">
       <c r="C62" s="1">
         <v>120</v>
       </c>
-      <c r="D62" s="11">
+      <c r="D62" s="8">
         <v>180020</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F62" s="1">
         <v>10000</v>
@@ -3019,18 +3048,18 @@
         <v>1</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:11">
       <c r="C63" s="1">
         <v>121</v>
       </c>
-      <c r="D63" s="11">
+      <c r="D63" s="8">
         <v>180021</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F63" s="1">
         <v>10000</v>
@@ -3048,56 +3077,27 @@
         <v>1</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:11">
-      <c r="C65" s="1">
-        <v>130</v>
-      </c>
-      <c r="D65" s="1">
-        <v>180030</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F65" s="1">
-        <v>5</v>
-      </c>
-      <c r="G65" s="1">
-        <v>1001</v>
-      </c>
-      <c r="H65" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I65" s="1">
-        <v>100</v>
-      </c>
-      <c r="J65" s="1">
-        <v>1</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:11">
       <c r="C66" s="1">
-        <v>131</v>
-      </c>
-      <c r="D66" s="11">
-        <v>180032</v>
+        <v>130</v>
+      </c>
+      <c r="D66" s="1">
+        <v>180030</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>99</v>
       </c>
       <c r="F66" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G66" s="1">
         <v>1001</v>
       </c>
       <c r="H66" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I66" s="1">
         <v>100</v>
@@ -3106,27 +3106,27 @@
         <v>1</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
       <c r="C67" s="1">
-        <v>132</v>
-      </c>
-      <c r="D67" s="11">
-        <v>180033</v>
+        <v>131</v>
+      </c>
+      <c r="D67" s="8">
+        <v>180032</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F67" s="1">
         <v>1</v>
       </c>
       <c r="G67" s="1">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H67" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I67" s="1">
         <v>100</v>
@@ -3135,24 +3135,24 @@
         <v>1</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:11">
       <c r="C68" s="1">
-        <v>133</v>
-      </c>
-      <c r="D68" s="11">
-        <v>180034</v>
+        <v>132</v>
+      </c>
+      <c r="D68" s="8">
+        <v>180033</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F68" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G68" s="1">
-        <v>1001</v>
+        <v>1501</v>
       </c>
       <c r="H68" s="1">
         <v>2500</v>
@@ -3164,104 +3164,191 @@
         <v>1</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:11">
+      <c r="C69" s="1">
+        <v>133</v>
+      </c>
+      <c r="D69" s="8">
+        <v>180034</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F69" s="1">
+        <v>2</v>
+      </c>
+      <c r="G69" s="1">
+        <v>1001</v>
+      </c>
+      <c r="H69" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I69" s="1">
+        <v>100</v>
+      </c>
+      <c r="J69" s="1">
+        <v>1</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
       <c r="C70" s="1">
-        <v>201</v>
-      </c>
-      <c r="D70" s="13" t="s">
-        <v>102</v>
+        <v>134</v>
+      </c>
+      <c r="D70" s="8">
+        <v>180035</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F70" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G70" s="1">
-        <v>150</v>
+        <v>2000</v>
       </c>
       <c r="H70" s="1">
-        <v>1200</v>
+        <v>2500</v>
       </c>
       <c r="I70" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="J70" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
       <c r="C71" s="1">
-        <v>202</v>
-      </c>
-      <c r="D71" s="13" t="s">
-        <v>104</v>
+        <v>135</v>
+      </c>
+      <c r="D71" s="8">
+        <v>180036</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>105</v>
       </c>
       <c r="F71" s="1">
+        <v>1</v>
+      </c>
+      <c r="G71" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H71" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I71" s="1">
+        <v>100</v>
+      </c>
+      <c r="J71" s="1">
+        <v>1</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:11">
+      <c r="C74" s="1">
+        <v>201</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F74" s="1">
         <v>5</v>
       </c>
-      <c r="G71" s="1">
+      <c r="G74" s="1">
+        <v>150</v>
+      </c>
+      <c r="H74" s="1">
+        <v>1200</v>
+      </c>
+      <c r="I74" s="1">
+        <v>20</v>
+      </c>
+      <c r="J74" s="1">
+        <v>2</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:11">
+      <c r="C75" s="1">
+        <v>202</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F75" s="1">
+        <v>5</v>
+      </c>
+      <c r="G75" s="1">
         <v>200</v>
       </c>
-      <c r="H71" s="1">
+      <c r="H75" s="1">
         <v>1000</v>
       </c>
-      <c r="I71" s="1">
+      <c r="I75" s="1">
         <v>30</v>
       </c>
-      <c r="J71" s="1">
+      <c r="J75" s="1">
         <v>2</v>
       </c>
-      <c r="K71" s="1" t="s">
+      <c r="K75" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="72" customHeight="1" spans="3:11">
-      <c r="C72" s="1">
+    <row r="76" customHeight="1" spans="3:11">
+      <c r="C76" s="1">
         <v>203</v>
       </c>
-      <c r="D72" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F72" s="1">
+      <c r="D76" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F76" s="1">
         <v>15</v>
       </c>
-      <c r="G72" s="1">
+      <c r="G76" s="1">
         <v>1050</v>
       </c>
-      <c r="H72" s="1">
+      <c r="H76" s="1">
         <v>1500</v>
       </c>
-      <c r="I72" s="1">
+      <c r="I76" s="1">
         <v>51</v>
       </c>
-      <c r="J72" s="1">
+      <c r="J76" s="1">
         <v>2</v>
       </c>
-      <c r="K72" s="1" t="s">
+      <c r="K76" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="73" customHeight="1" spans="4:4">
-      <c r="D73" s="11"/>
-    </row>
-    <row r="74" customHeight="1" spans="4:4">
-      <c r="D74" s="11"/>
-    </row>
-    <row r="75" customHeight="1" spans="4:4">
-      <c r="D75" s="11"/>
+    <row r="77" customHeight="1" spans="4:4">
+      <c r="D77" s="8"/>
+    </row>
+    <row r="78" customHeight="1" spans="4:4">
+      <c r="D78" s="8"/>
+    </row>
+    <row r="79" customHeight="1" spans="4:4">
+      <c r="D79" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="112">
   <si>
     <t>#</t>
   </si>
@@ -2560,23 +2560,46 @@
         <v>80</v>
       </c>
       <c r="F42" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G42" s="2">
         <v>1500</v>
       </c>
       <c r="H42" s="2">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="I42" s="1">
+        <v>5</v>
+      </c>
+      <c r="J42" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="20" customHeight="1" spans="3:10">
+      <c r="C43" s="1">
+        <v>38</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F43" s="1">
         <v>10</v>
       </c>
-      <c r="J42" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="4:4">
-      <c r="D43" s="6"/>
+      <c r="G43" s="2">
+        <v>2001</v>
+      </c>
+      <c r="H43" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I43" s="1">
+        <v>1</v>
+      </c>
+      <c r="J43" s="1">
+        <v>25</v>
+      </c>
     </row>
     <row r="44" customHeight="1" spans="4:4">
       <c r="D44" s="6"/>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -2308,13 +2308,13 @@
         <v>1250</v>
       </c>
       <c r="H33" s="1">
-        <v>1250</v>
+        <v>3250</v>
       </c>
       <c r="I33" s="1">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="J33" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>33</v>
@@ -2337,13 +2337,13 @@
         <v>1350</v>
       </c>
       <c r="H34" s="1">
-        <v>1350</v>
+        <v>3350</v>
       </c>
       <c r="I34" s="1">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="J34" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>38</v>
@@ -2366,13 +2366,13 @@
         <v>1450</v>
       </c>
       <c r="H35" s="1">
-        <v>1450</v>
+        <v>3450</v>
       </c>
       <c r="I35" s="1">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="J35" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>38</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -588,12 +588,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2572,7 +2572,7 @@
         <v>5</v>
       </c>
       <c r="J42" s="1">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="20" customHeight="1" spans="3:10">
@@ -2598,7 +2598,7 @@
         <v>1</v>
       </c>
       <c r="J43" s="1">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="4:4">

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -588,12 +588,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2560,7 +2560,7 @@
         <v>80</v>
       </c>
       <c r="F42" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G42" s="2">
         <v>1500</v>
@@ -2572,7 +2572,7 @@
         <v>5</v>
       </c>
       <c r="J42" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="20" customHeight="1" spans="3:10">
@@ -2586,7 +2586,7 @@
         <v>80</v>
       </c>
       <c r="F43" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G43" s="2">
         <v>2001</v>
@@ -2598,7 +2598,7 @@
         <v>1</v>
       </c>
       <c r="J43" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="4:4">

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -2560,7 +2560,7 @@
         <v>80</v>
       </c>
       <c r="F42" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G42" s="2">
         <v>1500</v>
@@ -2586,7 +2586,7 @@
         <v>80</v>
       </c>
       <c r="F43" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G43" s="2">
         <v>2001</v>
@@ -2595,7 +2595,7 @@
         <v>10000</v>
       </c>
       <c r="I43" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J43" s="1">
         <v>30</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -2624,7 +2624,7 @@
         <v>2000</v>
       </c>
       <c r="G47" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H47" s="1">
         <v>1000</v>
@@ -2653,7 +2653,7 @@
         <v>4000</v>
       </c>
       <c r="G48" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H48" s="1">
         <v>1000</v>
@@ -2682,7 +2682,7 @@
         <v>150000</v>
       </c>
       <c r="G49" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H49" s="1">
         <v>1000</v>
@@ -2711,7 +2711,7 @@
         <v>8000</v>
       </c>
       <c r="G50" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H50" s="1">
         <v>1000</v>
@@ -2740,7 +2740,7 @@
         <v>3000</v>
       </c>
       <c r="G51" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H51" s="1">
         <v>1000</v>
@@ -2769,7 +2769,7 @@
         <v>50000</v>
       </c>
       <c r="G52" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H52" s="1">
         <v>1000</v>
@@ -2798,7 +2798,7 @@
         <v>2000</v>
       </c>
       <c r="G53" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H53" s="1">
         <v>1000</v>
@@ -2827,7 +2827,7 @@
         <v>20000</v>
       </c>
       <c r="G54" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H54" s="1">
         <v>1000</v>
@@ -2856,7 +2856,7 @@
         <v>3000</v>
       </c>
       <c r="G55" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H55" s="1">
         <v>1000</v>
@@ -2885,7 +2885,7 @@
         <v>10000</v>
       </c>
       <c r="G56" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H56" s="1">
         <v>1000</v>
@@ -2914,7 +2914,7 @@
         <v>100000</v>
       </c>
       <c r="G57" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H57" s="1">
         <v>1000</v>
@@ -2943,7 +2943,7 @@
         <v>100000</v>
       </c>
       <c r="G58" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H58" s="1">
         <v>1000</v>
@@ -2972,7 +2972,7 @@
         <v>50000</v>
       </c>
       <c r="G59" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H59" s="1">
         <v>1000</v>
@@ -3001,7 +3001,7 @@
         <v>100000</v>
       </c>
       <c r="G60" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H60" s="1">
         <v>1000</v>
@@ -3030,7 +3030,7 @@
         <v>100000</v>
       </c>
       <c r="G61" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H61" s="1">
         <v>1000</v>
@@ -3059,7 +3059,7 @@
         <v>10000</v>
       </c>
       <c r="G62" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H62" s="1">
         <v>1000</v>
@@ -3088,7 +3088,7 @@
         <v>10000</v>
       </c>
       <c r="G63" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H63" s="1">
         <v>1000</v>
@@ -3117,7 +3117,7 @@
         <v>5</v>
       </c>
       <c r="G66" s="1">
-        <v>1001</v>
+        <v>1100</v>
       </c>
       <c r="H66" s="1">
         <v>1500</v>
@@ -3146,7 +3146,7 @@
         <v>1</v>
       </c>
       <c r="G67" s="1">
-        <v>1001</v>
+        <v>1100</v>
       </c>
       <c r="H67" s="1">
         <v>2000</v>
@@ -3175,10 +3175,10 @@
         <v>1</v>
       </c>
       <c r="G68" s="1">
-        <v>1501</v>
+        <v>1600</v>
       </c>
       <c r="H68" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I68" s="1">
         <v>100</v>
@@ -3204,7 +3204,7 @@
         <v>2</v>
       </c>
       <c r="G69" s="1">
-        <v>1001</v>
+        <v>1100</v>
       </c>
       <c r="H69" s="1">
         <v>2500</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -138,7 +138,7 @@
     <t>2000</t>
   </si>
   <si>
-    <t>沙城图鉴</t>
+    <t>龙城图鉴</t>
   </si>
   <si>
     <t>2005</t>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -2691,7 +2691,7 @@
         <v>100</v>
       </c>
       <c r="J49" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>82</v>
@@ -2778,7 +2778,7 @@
         <v>100</v>
       </c>
       <c r="J52" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>82</v>
@@ -2923,7 +2923,7 @@
         <v>100</v>
       </c>
       <c r="J57" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K57" s="1" t="s">
         <v>82</v>
@@ -2952,7 +2952,7 @@
         <v>100</v>
       </c>
       <c r="J58" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K58" s="1" t="s">
         <v>82</v>
@@ -2981,7 +2981,7 @@
         <v>100</v>
       </c>
       <c r="J59" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K59" s="1" t="s">
         <v>82</v>
@@ -3010,7 +3010,7 @@
         <v>100</v>
       </c>
       <c r="J60" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K60" s="1" t="s">
         <v>82</v>
@@ -3039,7 +3039,7 @@
         <v>100</v>
       </c>
       <c r="J61" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K61" s="1" t="s">
         <v>82</v>
@@ -3068,7 +3068,7 @@
         <v>100</v>
       </c>
       <c r="J62" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K62" s="1" t="s">
         <v>82</v>
@@ -3097,7 +3097,7 @@
         <v>100</v>
       </c>
       <c r="J63" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K63" s="1" t="s">
         <v>82</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="133">
   <si>
     <t>#</t>
   </si>
@@ -397,6 +397,69 @@
   </si>
   <si>
     <t>魂骨</t>
+  </si>
+  <si>
+    <t>220101</t>
+  </si>
+  <si>
+    <t>白色宠物</t>
+  </si>
+  <si>
+    <t>1天一个</t>
+  </si>
+  <si>
+    <t>220102</t>
+  </si>
+  <si>
+    <t>绿色宠物</t>
+  </si>
+  <si>
+    <t>2天一个</t>
+  </si>
+  <si>
+    <t>220103</t>
+  </si>
+  <si>
+    <t>蓝色宠物</t>
+  </si>
+  <si>
+    <t>3天一个</t>
+  </si>
+  <si>
+    <t>220104</t>
+  </si>
+  <si>
+    <t>紫色宠物</t>
+  </si>
+  <si>
+    <t>4天一个</t>
+  </si>
+  <si>
+    <t>220105</t>
+  </si>
+  <si>
+    <t>橙色宠物</t>
+  </si>
+  <si>
+    <t>5天一个</t>
+  </si>
+  <si>
+    <t>220106</t>
+  </si>
+  <si>
+    <t>红色宠物</t>
+  </si>
+  <si>
+    <t>6天一个</t>
+  </si>
+  <si>
+    <t>220107</t>
+  </si>
+  <si>
+    <t>金色宠物</t>
+  </si>
+  <si>
+    <t>7天一个</t>
   </si>
 </sst>
 </file>
@@ -409,7 +472,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -442,6 +505,12 @@
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF05073B"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -929,137 +998,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1071,6 +1140,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
@@ -1394,7 +1464,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1504,7 +1574,7 @@
       <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -1533,7 +1603,7 @@
       <c r="C7" s="2">
         <v>2</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -1562,7 +1632,7 @@
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -1591,7 +1661,7 @@
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -1620,7 +1690,7 @@
       <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="12" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -1649,7 +1719,7 @@
       <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -1678,7 +1748,7 @@
       <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -1765,7 +1835,7 @@
       <c r="C15" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="11" t="s">
         <v>31</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -1794,7 +1864,7 @@
       <c r="C16" s="2">
         <v>11</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="10" t="s">
         <v>34</v>
       </c>
       <c r="E16" s="2" t="s">
@@ -1823,7 +1893,7 @@
       <c r="C17" s="1">
         <v>12</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="11" t="s">
         <v>36</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -1852,7 +1922,7 @@
       <c r="C18" s="2">
         <v>13</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="10" t="s">
         <v>39</v>
       </c>
       <c r="E18" s="2" t="s">
@@ -1881,7 +1951,7 @@
       <c r="C19" s="2">
         <v>14</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="10" t="s">
         <v>42</v>
       </c>
       <c r="E19" s="2" t="s">
@@ -1910,7 +1980,7 @@
       <c r="C20" s="1">
         <v>15</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="11" t="s">
         <v>45</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -1939,7 +2009,7 @@
       <c r="C21" s="1">
         <v>16</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="11" t="s">
         <v>47</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -1968,7 +2038,7 @@
       <c r="C22" s="1">
         <v>17</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="11" t="s">
         <v>50</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -1997,7 +2067,7 @@
       <c r="C23" s="1">
         <v>18</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="11" t="s">
         <v>51</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -2026,7 +2096,7 @@
       <c r="C24" s="1">
         <v>19</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="11" t="s">
         <v>52</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -2055,7 +2125,7 @@
       <c r="C25" s="1">
         <v>20</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="11" t="s">
         <v>53</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -2084,7 +2154,7 @@
       <c r="C26" s="1">
         <v>21</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="11" t="s">
         <v>54</v>
       </c>
       <c r="E26" s="1" t="s">
@@ -2113,7 +2183,7 @@
       <c r="C27" s="1">
         <v>22</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="11" t="s">
         <v>55</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -2144,7 +2214,7 @@
       <c r="C28" s="3">
         <v>23</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="13" t="s">
         <v>56</v>
       </c>
       <c r="E28" s="3" t="s">
@@ -2175,7 +2245,7 @@
       <c r="C29" s="3">
         <v>24</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="13" t="s">
         <v>57</v>
       </c>
       <c r="E29" s="3" t="s">
@@ -2204,7 +2274,7 @@
       <c r="C30" s="2">
         <v>25</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="10" t="s">
         <v>58</v>
       </c>
       <c r="E30" s="2" t="s">
@@ -2235,7 +2305,7 @@
       <c r="C31" s="3">
         <v>26</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="13" t="s">
         <v>59</v>
       </c>
       <c r="E31" s="3" t="s">
@@ -2266,7 +2336,7 @@
       <c r="C32" s="3">
         <v>27</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="13" t="s">
         <v>60</v>
       </c>
       <c r="E32" s="3" t="s">
@@ -2295,7 +2365,7 @@
       <c r="C33" s="1">
         <v>28</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="11" t="s">
         <v>61</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -2324,7 +2394,7 @@
       <c r="C34" s="1">
         <v>29</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="11" t="s">
         <v>63</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -2353,7 +2423,7 @@
       <c r="C35" s="1">
         <v>30</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="11" t="s">
         <v>65</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -2382,7 +2452,7 @@
       <c r="C36" s="2">
         <v>31</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="D36" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E36" s="2" t="s">
@@ -2411,7 +2481,7 @@
       <c r="C37" s="2">
         <v>32</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E37" s="2" t="s">
@@ -2440,7 +2510,7 @@
       <c r="C38" s="3">
         <v>33</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="13" t="s">
         <v>71</v>
       </c>
       <c r="E38" s="3" t="s">
@@ -2469,7 +2539,7 @@
       <c r="C39" s="3">
         <v>34</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="13" t="s">
         <v>73</v>
       </c>
       <c r="E39" s="3" t="s">
@@ -2498,7 +2568,7 @@
       <c r="C40" s="2">
         <v>35</v>
       </c>
-      <c r="D40" s="9" t="s">
+      <c r="D40" s="10" t="s">
         <v>75</v>
       </c>
       <c r="E40" s="2" t="s">
@@ -2527,7 +2597,7 @@
       <c r="C41" s="1">
         <v>36</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="11" t="s">
         <v>77</v>
       </c>
       <c r="E41" s="1" t="s">
@@ -2553,7 +2623,7 @@
       <c r="C42" s="1">
         <v>37</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="11" t="s">
         <v>79</v>
       </c>
       <c r="E42" s="1" t="s">
@@ -2579,7 +2649,7 @@
       <c r="C43" s="1">
         <v>38</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="11" t="s">
         <v>79</v>
       </c>
       <c r="E43" s="1" t="s">
@@ -3281,7 +3351,7 @@
       <c r="C74" s="1">
         <v>201</v>
       </c>
-      <c r="D74" s="10" t="s">
+      <c r="D74" s="11" t="s">
         <v>106</v>
       </c>
       <c r="E74" s="1" t="s">
@@ -3310,7 +3380,7 @@
       <c r="C75" s="1">
         <v>202</v>
       </c>
-      <c r="D75" s="10" t="s">
+      <c r="D75" s="11" t="s">
         <v>108</v>
       </c>
       <c r="E75" s="1" t="s">
@@ -3339,7 +3409,7 @@
       <c r="C76" s="1">
         <v>203</v>
       </c>
-      <c r="D76" s="10" t="s">
+      <c r="D76" s="11" t="s">
         <v>110</v>
       </c>
       <c r="E76" s="1" t="s">
@@ -3367,11 +3437,208 @@
     <row r="77" customHeight="1" spans="4:4">
       <c r="D77" s="8"/>
     </row>
-    <row r="78" customHeight="1" spans="4:4">
-      <c r="D78" s="8"/>
-    </row>
-    <row r="79" customHeight="1" spans="4:4">
-      <c r="D79" s="8"/>
+    <row r="78" customHeight="1" spans="3:11">
+      <c r="C78" s="1">
+        <v>301</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F78" s="1">
+        <v>1</v>
+      </c>
+      <c r="G78" s="1">
+        <v>100</v>
+      </c>
+      <c r="H78" s="1">
+        <v>500</v>
+      </c>
+      <c r="I78" s="1">
+        <v>10</v>
+      </c>
+      <c r="J78" s="1">
+        <v>1</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:11">
+      <c r="C79" s="1">
+        <v>302</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F79" s="1">
+        <v>1</v>
+      </c>
+      <c r="G79" s="1">
+        <v>501</v>
+      </c>
+      <c r="H79" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I79" s="1">
+        <v>20</v>
+      </c>
+      <c r="J79" s="1">
+        <v>1</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:11">
+      <c r="C80" s="1">
+        <v>303</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F80" s="1">
+        <v>1</v>
+      </c>
+      <c r="G80" s="1">
+        <v>1001</v>
+      </c>
+      <c r="H80" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I80" s="1">
+        <v>30</v>
+      </c>
+      <c r="J80" s="1">
+        <v>1</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:11">
+      <c r="C81" s="1">
+        <v>304</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F81" s="1">
+        <v>1</v>
+      </c>
+      <c r="G81" s="1">
+        <v>1501</v>
+      </c>
+      <c r="H81" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I81" s="1">
+        <v>50</v>
+      </c>
+      <c r="J81" s="1">
+        <v>1</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:11">
+      <c r="C82" s="1">
+        <v>305</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="F82" s="1">
+        <v>1</v>
+      </c>
+      <c r="G82" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H82" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I82" s="1">
+        <v>80</v>
+      </c>
+      <c r="J82" s="1">
+        <v>1</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:11">
+      <c r="C83" s="1">
+        <v>306</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="F83" s="1">
+        <v>1</v>
+      </c>
+      <c r="G83" s="1">
+        <v>2500</v>
+      </c>
+      <c r="H83" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I83" s="1">
+        <v>90</v>
+      </c>
+      <c r="J83" s="1">
+        <v>1</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:11">
+      <c r="C84" s="1">
+        <v>307</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="F84" s="1">
+        <v>1</v>
+      </c>
+      <c r="G84" s="1">
+        <v>3501</v>
+      </c>
+      <c r="H84" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I84" s="1">
+        <v>100</v>
+      </c>
+      <c r="J84" s="1">
+        <v>1</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>132</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -3448,10 +3448,10 @@
         <v>113</v>
       </c>
       <c r="F78" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G78" s="1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H78" s="1">
         <v>500</v>
@@ -3477,7 +3477,7 @@
         <v>116</v>
       </c>
       <c r="F79" s="1">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G79" s="1">
         <v>501</v>
@@ -3486,7 +3486,7 @@
         <v>1000</v>
       </c>
       <c r="I79" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J79" s="1">
         <v>1</v>
@@ -3506,7 +3506,7 @@
         <v>119</v>
       </c>
       <c r="F80" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G80" s="1">
         <v>1001</v>
@@ -3515,7 +3515,7 @@
         <v>1500</v>
       </c>
       <c r="I80" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J80" s="1">
         <v>1</v>
@@ -3535,7 +3535,7 @@
         <v>122</v>
       </c>
       <c r="F81" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G81" s="1">
         <v>1501</v>
@@ -3544,7 +3544,7 @@
         <v>2000</v>
       </c>
       <c r="I81" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J81" s="1">
         <v>1</v>
@@ -3564,16 +3564,16 @@
         <v>125</v>
       </c>
       <c r="F82" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G82" s="1">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="H82" s="1">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I82" s="1">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J82" s="1">
         <v>1</v>
@@ -3593,16 +3593,16 @@
         <v>128</v>
       </c>
       <c r="F83" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G83" s="1">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="H83" s="1">
         <v>3500</v>
       </c>
       <c r="I83" s="1">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="J83" s="1">
         <v>1</v>
@@ -3625,7 +3625,7 @@
         <v>1</v>
       </c>
       <c r="G84" s="1">
-        <v>3501</v>
+        <v>3502</v>
       </c>
       <c r="H84" s="1">
         <v>5000</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -3535,7 +3535,7 @@
         <v>122</v>
       </c>
       <c r="F81" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G81" s="1">
         <v>1501</v>
@@ -3544,7 +3544,7 @@
         <v>2000</v>
       </c>
       <c r="I81" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J81" s="1">
         <v>1</v>
@@ -3564,16 +3564,16 @@
         <v>125</v>
       </c>
       <c r="F82" s="1">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G82" s="1">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H82" s="1">
         <v>3000</v>
       </c>
       <c r="I82" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J82" s="1">
         <v>1</v>
@@ -3593,16 +3593,16 @@
         <v>128</v>
       </c>
       <c r="F83" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G83" s="1">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="H83" s="1">
         <v>3500</v>
       </c>
       <c r="I83" s="1">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="J83" s="1">
         <v>1</v>
@@ -3622,16 +3622,16 @@
         <v>131</v>
       </c>
       <c r="F84" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G84" s="1">
-        <v>3502</v>
+        <v>3001</v>
       </c>
       <c r="H84" s="1">
         <v>5000</v>
       </c>
       <c r="I84" s="1">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="J84" s="1">
         <v>1</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="135">
   <si>
     <t>#</t>
   </si>
@@ -360,6 +360,9 @@
     <t>神戒之源</t>
   </si>
   <si>
+    <t>传世契约</t>
+  </si>
+  <si>
     <t>极·卖身契</t>
   </si>
   <si>
@@ -379,6 +382,9 @@
   </si>
   <si>
     <t>极.无限之魂</t>
+  </si>
+  <si>
+    <t>极·传世契约</t>
   </si>
   <si>
     <t>220016</t>
@@ -3173,6 +3179,35 @@
         <v>82</v>
       </c>
     </row>
+    <row r="64" customHeight="1" spans="3:11">
+      <c r="C64" s="1">
+        <v>122</v>
+      </c>
+      <c r="D64" s="8">
+        <v>180022</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F64" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G64" s="1">
+        <v>100</v>
+      </c>
+      <c r="H64" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I64" s="1">
+        <v>100</v>
+      </c>
+      <c r="J64" s="1">
+        <v>1</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
     <row r="66" customHeight="1" spans="3:11">
       <c r="C66" s="1">
         <v>130</v>
@@ -3181,7 +3216,7 @@
         <v>180030</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F66" s="1">
         <v>5</v>
@@ -3199,7 +3234,7 @@
         <v>1</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
@@ -3210,7 +3245,7 @@
         <v>180032</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F67" s="1">
         <v>1</v>
@@ -3228,7 +3263,7 @@
         <v>1</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:11">
@@ -3239,7 +3274,7 @@
         <v>180033</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F68" s="1">
         <v>1</v>
@@ -3257,7 +3292,7 @@
         <v>1</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
@@ -3268,7 +3303,7 @@
         <v>180034</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F69" s="1">
         <v>2</v>
@@ -3277,7 +3312,7 @@
         <v>1100</v>
       </c>
       <c r="H69" s="1">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I69" s="1">
         <v>100</v>
@@ -3286,7 +3321,7 @@
         <v>1</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
@@ -3297,7 +3332,7 @@
         <v>180035</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F70" s="1">
         <v>1</v>
@@ -3315,7 +3350,7 @@
         <v>1</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
@@ -3326,7 +3361,7 @@
         <v>180036</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F71" s="1">
         <v>1</v>
@@ -3344,7 +3379,36 @@
         <v>1</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:11">
+      <c r="C72" s="1">
+        <v>136</v>
+      </c>
+      <c r="D72" s="8">
+        <v>180037</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F72" s="1">
+        <v>1</v>
+      </c>
+      <c r="G72" s="1">
+        <v>2500</v>
+      </c>
+      <c r="H72" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I72" s="1">
+        <v>100</v>
+      </c>
+      <c r="J72" s="1">
+        <v>1</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
@@ -3352,10 +3416,10 @@
         <v>201</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F74" s="1">
         <v>5</v>
@@ -3381,10 +3445,10 @@
         <v>202</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F75" s="1">
         <v>5</v>
@@ -3410,10 +3474,10 @@
         <v>203</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F76" s="1">
         <v>15</v>
@@ -3442,10 +3506,10 @@
         <v>301</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F78" s="1">
         <v>20</v>
@@ -3463,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:11">
@@ -3471,10 +3535,10 @@
         <v>302</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F79" s="1">
         <v>15</v>
@@ -3492,7 +3556,7 @@
         <v>1</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:11">
@@ -3500,10 +3564,10 @@
         <v>303</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F80" s="1">
         <v>10</v>
@@ -3521,7 +3585,7 @@
         <v>1</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:11">
@@ -3529,10 +3593,10 @@
         <v>304</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F81" s="1">
         <v>8</v>
@@ -3550,7 +3614,7 @@
         <v>1</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:11">
@@ -3558,10 +3622,10 @@
         <v>305</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F82" s="1">
         <v>15</v>
@@ -3579,7 +3643,7 @@
         <v>1</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:11">
@@ -3587,10 +3651,10 @@
         <v>306</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F83" s="1">
         <v>10</v>
@@ -3608,7 +3672,7 @@
         <v>1</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:11">
@@ -3616,10 +3680,10 @@
         <v>307</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F84" s="1">
         <v>5</v>
@@ -3637,7 +3701,7 @@
         <v>1</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -3132,7 +3132,7 @@
         <v>97</v>
       </c>
       <c r="F62" s="1">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="G62" s="1">
         <v>100</v>
@@ -3161,7 +3161,7 @@
         <v>98</v>
       </c>
       <c r="F63" s="1">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="G63" s="1">
         <v>100</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -3399,7 +3399,7 @@
         <v>2500</v>
       </c>
       <c r="H72" s="1">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="I72" s="1">
         <v>100</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -663,12 +663,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="139">
   <si>
     <t>#</t>
   </si>
@@ -304,6 +304,18 @@
   </si>
   <si>
     <t>改造石</t>
+  </si>
+  <si>
+    <t>1010</t>
+  </si>
+  <si>
+    <t>金色精华</t>
+  </si>
+  <si>
+    <t>1011</t>
+  </si>
+  <si>
+    <t>暗金精华</t>
   </si>
   <si>
     <t>BOSS杀手</t>
@@ -663,12 +675,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1964,7 +1976,7 @@
         <v>43</v>
       </c>
       <c r="F19" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G19" s="2">
         <v>100</v>
@@ -1976,7 +1988,7 @@
         <v>3</v>
       </c>
       <c r="J19" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>44</v>
@@ -2677,11 +2689,63 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="4:4">
-      <c r="D44" s="6"/>
-    </row>
-    <row r="45" customHeight="1" spans="4:4">
-      <c r="D45" s="6"/>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C44" s="1">
+        <v>39</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F44" s="2">
+        <v>5</v>
+      </c>
+      <c r="G44" s="2">
+        <v>2500</v>
+      </c>
+      <c r="H44" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I44" s="2">
+        <v>1</v>
+      </c>
+      <c r="J44" s="2">
+        <v>10</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C45" s="1">
+        <v>40</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F45" s="2">
+        <v>5</v>
+      </c>
+      <c r="G45" s="2">
+        <v>3200</v>
+      </c>
+      <c r="H45" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I45" s="2">
+        <v>1</v>
+      </c>
+      <c r="J45" s="2">
+        <v>10</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="46" customHeight="1" spans="4:4">
       <c r="D46" s="6"/>
@@ -2694,7 +2758,7 @@
         <v>180001</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F47" s="1">
         <v>2000</v>
@@ -2712,7 +2776,7 @@
         <v>1</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:11">
@@ -2723,7 +2787,7 @@
         <v>180002</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F48" s="1">
         <v>4000</v>
@@ -2741,7 +2805,7 @@
         <v>1</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:11">
@@ -2752,7 +2816,7 @@
         <v>180003</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F49" s="1">
         <v>150000</v>
@@ -2770,7 +2834,7 @@
         <v>5</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:11">
@@ -2781,7 +2845,7 @@
         <v>180004</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F50" s="1">
         <v>8000</v>
@@ -2799,7 +2863,7 @@
         <v>1</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:11">
@@ -2810,7 +2874,7 @@
         <v>180005</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F51" s="1">
         <v>3000</v>
@@ -2828,7 +2892,7 @@
         <v>1</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:11">
@@ -2839,7 +2903,7 @@
         <v>180006</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F52" s="1">
         <v>50000</v>
@@ -2857,7 +2921,7 @@
         <v>5</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:11">
@@ -2868,7 +2932,7 @@
         <v>180007</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F53" s="1">
         <v>2000</v>
@@ -2886,7 +2950,7 @@
         <v>1</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:11">
@@ -2897,7 +2961,7 @@
         <v>180008</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F54" s="1">
         <v>20000</v>
@@ -2915,7 +2979,7 @@
         <v>2</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
@@ -2926,7 +2990,7 @@
         <v>180009</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F55" s="1">
         <v>3000</v>
@@ -2944,7 +3008,7 @@
         <v>1</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
@@ -2955,7 +3019,7 @@
         <v>180010</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F56" s="1">
         <v>10000</v>
@@ -2973,7 +3037,7 @@
         <v>1</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:11">
@@ -2984,7 +3048,7 @@
         <v>180011</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F57" s="1">
         <v>100000</v>
@@ -3002,7 +3066,7 @@
         <v>5</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:11">
@@ -3013,7 +3077,7 @@
         <v>180012</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F58" s="1">
         <v>100000</v>
@@ -3031,7 +3095,7 @@
         <v>5</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
@@ -3042,7 +3106,7 @@
         <v>180013</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F59" s="1">
         <v>50000</v>
@@ -3060,7 +3124,7 @@
         <v>5</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:11">
@@ -3071,7 +3135,7 @@
         <v>180014</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F60" s="1">
         <v>100000</v>
@@ -3089,7 +3153,7 @@
         <v>5</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:11">
@@ -3100,7 +3164,7 @@
         <v>180015</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F61" s="1">
         <v>100000</v>
@@ -3118,7 +3182,7 @@
         <v>5</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:11">
@@ -3129,7 +3193,7 @@
         <v>180020</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F62" s="1">
         <v>30000</v>
@@ -3147,7 +3211,7 @@
         <v>2</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:11">
@@ -3158,7 +3222,7 @@
         <v>180021</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F63" s="1">
         <v>30000</v>
@@ -3176,7 +3240,7 @@
         <v>2</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:11">
@@ -3187,7 +3251,7 @@
         <v>180022</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F64" s="1">
         <v>3000</v>
@@ -3205,7 +3269,7 @@
         <v>1</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:11">
@@ -3216,7 +3280,7 @@
         <v>180030</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F66" s="1">
         <v>5</v>
@@ -3234,7 +3298,7 @@
         <v>1</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
@@ -3245,7 +3309,7 @@
         <v>180032</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F67" s="1">
         <v>1</v>
@@ -3263,7 +3327,7 @@
         <v>1</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:11">
@@ -3274,7 +3338,7 @@
         <v>180033</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F68" s="1">
         <v>1</v>
@@ -3292,7 +3356,7 @@
         <v>1</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
@@ -3303,7 +3367,7 @@
         <v>180034</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F69" s="1">
         <v>2</v>
@@ -3321,7 +3385,7 @@
         <v>1</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
@@ -3332,7 +3396,7 @@
         <v>180035</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F70" s="1">
         <v>1</v>
@@ -3350,7 +3414,7 @@
         <v>1</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
@@ -3361,7 +3425,7 @@
         <v>180036</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F71" s="1">
         <v>1</v>
@@ -3379,7 +3443,7 @@
         <v>1</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
@@ -3390,7 +3454,7 @@
         <v>180037</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F72" s="1">
         <v>1</v>
@@ -3408,7 +3472,7 @@
         <v>1</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
@@ -3416,10 +3480,10 @@
         <v>201</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F74" s="1">
         <v>5</v>
@@ -3445,10 +3509,10 @@
         <v>202</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F75" s="1">
         <v>5</v>
@@ -3474,10 +3538,10 @@
         <v>203</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F76" s="1">
         <v>15</v>
@@ -3506,10 +3570,10 @@
         <v>301</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F78" s="1">
         <v>20</v>
@@ -3527,7 +3591,7 @@
         <v>1</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:11">
@@ -3535,10 +3599,10 @@
         <v>302</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F79" s="1">
         <v>15</v>
@@ -3556,7 +3620,7 @@
         <v>1</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:11">
@@ -3564,10 +3628,10 @@
         <v>303</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F80" s="1">
         <v>10</v>
@@ -3585,7 +3649,7 @@
         <v>1</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:11">
@@ -3593,10 +3657,10 @@
         <v>304</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F81" s="1">
         <v>8</v>
@@ -3614,7 +3678,7 @@
         <v>1</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:11">
@@ -3622,10 +3686,10 @@
         <v>305</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F82" s="1">
         <v>15</v>
@@ -3643,7 +3707,7 @@
         <v>1</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:11">
@@ -3651,10 +3715,10 @@
         <v>306</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F83" s="1">
         <v>10</v>
@@ -3672,7 +3736,7 @@
         <v>1</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:11">
@@ -3680,10 +3744,10 @@
         <v>307</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F84" s="1">
         <v>5</v>
@@ -3701,7 +3765,7 @@
         <v>1</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="141">
   <si>
     <t>#</t>
   </si>
@@ -397,6 +397,12 @@
   </si>
   <si>
     <t>极·传世契约</t>
+  </si>
+  <si>
+    <t>极·万界图</t>
+  </si>
+  <si>
+    <t>极·金蛟剪</t>
   </si>
   <si>
     <t>220016</t>
@@ -1482,7 +1488,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L86"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -3475,12 +3481,41 @@
         <v>105</v>
       </c>
     </row>
+    <row r="73" customHeight="1" spans="3:11">
+      <c r="C73" s="1">
+        <v>137</v>
+      </c>
+      <c r="D73" s="8">
+        <v>180038</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F73" s="1">
+        <v>5</v>
+      </c>
+      <c r="G73" s="1">
+        <v>1600</v>
+      </c>
+      <c r="H73" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I73" s="1">
+        <v>100</v>
+      </c>
+      <c r="J73" s="1">
+        <v>1</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
     <row r="74" customHeight="1" spans="3:11">
       <c r="C74" s="1">
-        <v>201</v>
-      </c>
-      <c r="D74" s="11" t="s">
-        <v>112</v>
+        <v>138</v>
+      </c>
+      <c r="D74" s="8">
+        <v>180039</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>113</v>
@@ -3489,71 +3524,42 @@
         <v>5</v>
       </c>
       <c r="G74" s="1">
-        <v>150</v>
+        <v>2000</v>
       </c>
       <c r="H74" s="1">
-        <v>1200</v>
+        <v>3500</v>
       </c>
       <c r="I74" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="J74" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="75" customHeight="1" spans="3:11">
-      <c r="C75" s="1">
-        <v>202</v>
-      </c>
-      <c r="D75" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F75" s="1">
-        <v>5</v>
-      </c>
-      <c r="G75" s="1">
-        <v>200</v>
-      </c>
-      <c r="H75" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I75" s="1">
-        <v>30</v>
-      </c>
-      <c r="J75" s="1">
-        <v>2</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
       <c r="C76" s="1">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F76" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G76" s="1">
-        <v>1050</v>
+        <v>150</v>
       </c>
       <c r="H76" s="1">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="I76" s="1">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="J76" s="1">
         <v>2</v>
@@ -3562,201 +3568,201 @@
         <v>44</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="4:4">
-      <c r="D77" s="8"/>
+    <row r="77" customHeight="1" spans="3:11">
+      <c r="C77" s="1">
+        <v>202</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F77" s="1">
+        <v>5</v>
+      </c>
+      <c r="G77" s="1">
+        <v>200</v>
+      </c>
+      <c r="H77" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I77" s="1">
+        <v>30</v>
+      </c>
+      <c r="J77" s="1">
+        <v>2</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="78" customHeight="1" spans="3:11">
       <c r="C78" s="1">
-        <v>301</v>
+        <v>203</v>
       </c>
       <c r="D78" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="E78" s="9" t="s">
+      <c r="E78" s="1" t="s">
         <v>119</v>
       </c>
       <c r="F78" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G78" s="1">
-        <v>101</v>
+        <v>1050</v>
       </c>
       <c r="H78" s="1">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="I78" s="1">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="J78" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="79" customHeight="1" spans="3:11">
-      <c r="C79" s="1">
-        <v>302</v>
-      </c>
-      <c r="D79" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="F79" s="1">
-        <v>15</v>
-      </c>
-      <c r="G79" s="1">
-        <v>501</v>
-      </c>
-      <c r="H79" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I79" s="1">
-        <v>10</v>
-      </c>
-      <c r="J79" s="1">
-        <v>1</v>
-      </c>
-      <c r="K79" s="1" t="s">
-        <v>123</v>
-      </c>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="4:4">
+      <c r="D79" s="8"/>
     </row>
     <row r="80" customHeight="1" spans="3:11">
       <c r="C80" s="1">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F80" s="1">
+        <v>20</v>
+      </c>
+      <c r="G80" s="1">
+        <v>101</v>
+      </c>
+      <c r="H80" s="1">
+        <v>500</v>
+      </c>
+      <c r="I80" s="1">
         <v>10</v>
       </c>
-      <c r="G80" s="1">
-        <v>1001</v>
-      </c>
-      <c r="H80" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I80" s="1">
-        <v>20</v>
-      </c>
       <c r="J80" s="1">
         <v>1</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:11">
       <c r="C81" s="1">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F81" s="1">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G81" s="1">
-        <v>1501</v>
+        <v>501</v>
       </c>
       <c r="H81" s="1">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I81" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J81" s="1">
         <v>1</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:11">
       <c r="C82" s="1">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F82" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G82" s="1">
-        <v>2001</v>
+        <v>1001</v>
       </c>
       <c r="H82" s="1">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="I82" s="1">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="J82" s="1">
         <v>1</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:11">
       <c r="C83" s="1">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F83" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G83" s="1">
-        <v>2501</v>
+        <v>1501</v>
       </c>
       <c r="H83" s="1">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="I83" s="1">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="J83" s="1">
         <v>1</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:11">
       <c r="C84" s="1">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F84" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G84" s="1">
-        <v>3001</v>
+        <v>2001</v>
       </c>
       <c r="H84" s="1">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="I84" s="1">
         <v>52</v>
@@ -3765,7 +3771,65 @@
         <v>1</v>
       </c>
       <c r="K84" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:11">
+      <c r="C85" s="1">
+        <v>306</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="F85" s="1">
+        <v>10</v>
+      </c>
+      <c r="G85" s="1">
+        <v>2501</v>
+      </c>
+      <c r="H85" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I85" s="1">
+        <v>52</v>
+      </c>
+      <c r="J85" s="1">
+        <v>1</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:11">
+      <c r="C86" s="1">
+        <v>307</v>
+      </c>
+      <c r="D86" s="11" t="s">
         <v>138</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F86" s="1">
+        <v>5</v>
+      </c>
+      <c r="G86" s="1">
+        <v>3001</v>
+      </c>
+      <c r="H86" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I86" s="1">
+        <v>52</v>
+      </c>
+      <c r="J86" s="1">
+        <v>1</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -3492,7 +3492,7 @@
         <v>112</v>
       </c>
       <c r="F73" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G73" s="1">
         <v>1600</v>
@@ -3521,7 +3521,7 @@
         <v>113</v>
       </c>
       <c r="F74" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G74" s="1">
         <v>2000</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="143">
   <si>
     <t>#</t>
   </si>
@@ -316,6 +316,12 @@
   </si>
   <si>
     <t>暗金精华</t>
+  </si>
+  <si>
+    <t>1012</t>
+  </si>
+  <si>
+    <t>开孔石</t>
   </si>
   <si>
     <t>BOSS杀手</t>
@@ -1488,7 +1494,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L86"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2753,50 +2759,47 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="4:4">
-      <c r="D46" s="6"/>
-    </row>
-    <row r="47" customHeight="1" spans="3:11">
-      <c r="C47" s="1">
-        <v>101</v>
-      </c>
-      <c r="D47" s="8">
-        <v>180001</v>
-      </c>
-      <c r="E47" s="1" t="s">
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C46" s="1">
+        <v>41</v>
+      </c>
+      <c r="D46" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="F47" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G47" s="1">
-        <v>100</v>
-      </c>
-      <c r="H47" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I47" s="1">
-        <v>100</v>
-      </c>
-      <c r="J47" s="1">
-        <v>1</v>
-      </c>
-      <c r="K47" s="1" t="s">
+      <c r="E46" s="1" t="s">
         <v>86</v>
       </c>
+      <c r="F46" s="2">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2">
+        <v>1500</v>
+      </c>
+      <c r="H46" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I46" s="2">
+        <v>30</v>
+      </c>
+      <c r="J46" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="4:4">
+      <c r="D47" s="6"/>
     </row>
     <row r="48" customHeight="1" spans="3:11">
       <c r="C48" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D48" s="8">
-        <v>180002</v>
+        <v>180001</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>87</v>
       </c>
       <c r="F48" s="1">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G48" s="1">
         <v>100</v>
@@ -2811,21 +2814,21 @@
         <v>1</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:11">
       <c r="C49" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D49" s="8">
-        <v>180003</v>
+        <v>180002</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F49" s="1">
-        <v>150000</v>
+        <v>4000</v>
       </c>
       <c r="G49" s="1">
         <v>100</v>
@@ -2837,24 +2840,24 @@
         <v>100</v>
       </c>
       <c r="J49" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:11">
       <c r="C50" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D50" s="8">
-        <v>180004</v>
+        <v>180003</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F50" s="1">
-        <v>8000</v>
+        <v>150000</v>
       </c>
       <c r="G50" s="1">
         <v>100</v>
@@ -2866,24 +2869,24 @@
         <v>100</v>
       </c>
       <c r="J50" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:11">
       <c r="C51" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D51" s="8">
-        <v>180005</v>
+        <v>180004</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F51" s="1">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="G51" s="1">
         <v>100</v>
@@ -2898,21 +2901,21 @@
         <v>1</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:11">
       <c r="C52" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D52" s="8">
-        <v>180006</v>
+        <v>180005</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F52" s="1">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="G52" s="1">
         <v>100</v>
@@ -2924,24 +2927,24 @@
         <v>100</v>
       </c>
       <c r="J52" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:11">
       <c r="C53" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D53" s="8">
-        <v>180007</v>
+        <v>180006</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F53" s="1">
-        <v>2000</v>
+        <v>50000</v>
       </c>
       <c r="G53" s="1">
         <v>100</v>
@@ -2953,24 +2956,24 @@
         <v>100</v>
       </c>
       <c r="J53" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:11">
       <c r="C54" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D54" s="8">
-        <v>180008</v>
+        <v>180007</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F54" s="1">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="G54" s="1">
         <v>100</v>
@@ -2982,24 +2985,24 @@
         <v>100</v>
       </c>
       <c r="J54" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
       <c r="C55" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D55" s="8">
-        <v>180009</v>
+        <v>180008</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F55" s="1">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="G55" s="1">
         <v>100</v>
@@ -3011,24 +3014,24 @@
         <v>100</v>
       </c>
       <c r="J55" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
       <c r="C56" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D56" s="8">
-        <v>180010</v>
+        <v>180009</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F56" s="1">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="G56" s="1">
         <v>100</v>
@@ -3043,21 +3046,21 @@
         <v>1</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:11">
       <c r="C57" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D57" s="8">
-        <v>180011</v>
+        <v>180010</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F57" s="1">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="G57" s="1">
         <v>100</v>
@@ -3069,21 +3072,21 @@
         <v>100</v>
       </c>
       <c r="J57" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:11">
       <c r="C58" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D58" s="8">
-        <v>180012</v>
+        <v>180011</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F58" s="1">
         <v>100000</v>
@@ -3101,21 +3104,21 @@
         <v>5</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
       <c r="C59" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D59" s="8">
-        <v>180013</v>
+        <v>180012</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F59" s="1">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="G59" s="1">
         <v>100</v>
@@ -3130,21 +3133,21 @@
         <v>5</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:11">
       <c r="C60" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D60" s="8">
-        <v>180014</v>
+        <v>180013</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F60" s="1">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G60" s="1">
         <v>100</v>
@@ -3159,18 +3162,18 @@
         <v>5</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:11">
       <c r="C61" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D61" s="8">
-        <v>180015</v>
+        <v>180014</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F61" s="1">
         <v>100000</v>
@@ -3188,21 +3191,21 @@
         <v>5</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:11">
       <c r="C62" s="1">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D62" s="8">
-        <v>180020</v>
+        <v>180015</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F62" s="1">
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="G62" s="1">
         <v>100</v>
@@ -3214,21 +3217,21 @@
         <v>100</v>
       </c>
       <c r="J62" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:11">
       <c r="C63" s="1">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D63" s="8">
-        <v>180021</v>
+        <v>180020</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F63" s="1">
         <v>30000</v>
@@ -3246,21 +3249,21 @@
         <v>2</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:11">
       <c r="C64" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D64" s="8">
-        <v>180022</v>
+        <v>180021</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F64" s="1">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="G64" s="1">
         <v>100</v>
@@ -3272,59 +3275,59 @@
         <v>100</v>
       </c>
       <c r="J64" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="3:11">
-      <c r="C66" s="1">
-        <v>130</v>
-      </c>
-      <c r="D66" s="1">
-        <v>180030</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F66" s="1">
-        <v>5</v>
-      </c>
-      <c r="G66" s="1">
-        <v>1100</v>
-      </c>
-      <c r="H66" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I66" s="1">
-        <v>100</v>
-      </c>
-      <c r="J66" s="1">
-        <v>1</v>
-      </c>
-      <c r="K66" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:11">
+      <c r="C65" s="1">
+        <v>122</v>
+      </c>
+      <c r="D65" s="8">
+        <v>180022</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>105</v>
+      </c>
+      <c r="F65" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G65" s="1">
+        <v>100</v>
+      </c>
+      <c r="H65" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I65" s="1">
+        <v>100</v>
+      </c>
+      <c r="J65" s="1">
+        <v>1</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
       <c r="C67" s="1">
-        <v>131</v>
-      </c>
-      <c r="D67" s="8">
-        <v>180032</v>
+        <v>130</v>
+      </c>
+      <c r="D67" s="1">
+        <v>180030</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F67" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G67" s="1">
         <v>1100</v>
       </c>
       <c r="H67" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I67" s="1">
         <v>100</v>
@@ -3333,24 +3336,24 @@
         <v>1</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:11">
       <c r="C68" s="1">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D68" s="8">
-        <v>180033</v>
+        <v>180032</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F68" s="1">
         <v>1</v>
       </c>
       <c r="G68" s="1">
-        <v>1600</v>
+        <v>1100</v>
       </c>
       <c r="H68" s="1">
         <v>2000</v>
@@ -3362,27 +3365,27 @@
         <v>1</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
       <c r="C69" s="1">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D69" s="8">
-        <v>180034</v>
+        <v>180033</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F69" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G69" s="1">
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="H69" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I69" s="1">
         <v>100</v>
@@ -3391,27 +3394,27 @@
         <v>1</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
       <c r="C70" s="1">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D70" s="8">
-        <v>180035</v>
+        <v>180034</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F70" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G70" s="1">
-        <v>2000</v>
+        <v>1100</v>
       </c>
       <c r="H70" s="1">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I70" s="1">
         <v>100</v>
@@ -3420,18 +3423,18 @@
         <v>1</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
       <c r="C71" s="1">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D71" s="8">
-        <v>180036</v>
+        <v>180035</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F71" s="1">
         <v>1</v>
@@ -3449,28 +3452,28 @@
         <v>1</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
       <c r="C72" s="1">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D72" s="8">
-        <v>180037</v>
+        <v>180036</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F72" s="1">
         <v>1</v>
       </c>
       <c r="G72" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H72" s="1">
         <v>2500</v>
       </c>
-      <c r="H72" s="1">
-        <v>3500</v>
-      </c>
       <c r="I72" s="1">
         <v>100</v>
       </c>
@@ -3478,24 +3481,24 @@
         <v>1</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
       <c r="C73" s="1">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D73" s="8">
-        <v>180038</v>
+        <v>180037</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F73" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G73" s="1">
-        <v>1600</v>
+        <v>2500</v>
       </c>
       <c r="H73" s="1">
         <v>3500</v>
@@ -3507,24 +3510,24 @@
         <v>1</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
       <c r="C74" s="1">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D74" s="8">
-        <v>180039</v>
+        <v>180038</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F74" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" s="1">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="H74" s="1">
         <v>3500</v>
@@ -3536,41 +3539,41 @@
         <v>1</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="76" customHeight="1" spans="3:11">
-      <c r="C76" s="1">
-        <v>201</v>
-      </c>
-      <c r="D76" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="E76" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:11">
+      <c r="C75" s="1">
+        <v>138</v>
+      </c>
+      <c r="D75" s="8">
+        <v>180039</v>
+      </c>
+      <c r="E75" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F76" s="1">
-        <v>5</v>
-      </c>
-      <c r="G76" s="1">
-        <v>150</v>
-      </c>
-      <c r="H76" s="1">
-        <v>1200</v>
-      </c>
-      <c r="I76" s="1">
-        <v>20</v>
-      </c>
-      <c r="J76" s="1">
-        <v>2</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>44</v>
+      <c r="F75" s="1">
+        <v>3</v>
+      </c>
+      <c r="G75" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H75" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I75" s="1">
+        <v>100</v>
+      </c>
+      <c r="J75" s="1">
+        <v>1</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:11">
       <c r="C77" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D77" s="11" t="s">
         <v>116</v>
@@ -3582,13 +3585,13 @@
         <v>5</v>
       </c>
       <c r="G77" s="1">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H77" s="1">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="I77" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J77" s="1">
         <v>2</v>
@@ -3599,7 +3602,7 @@
     </row>
     <row r="78" customHeight="1" spans="3:11">
       <c r="C78" s="1">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D78" s="11" t="s">
         <v>118</v>
@@ -3608,16 +3611,16 @@
         <v>119</v>
       </c>
       <c r="F78" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G78" s="1">
-        <v>1050</v>
+        <v>200</v>
       </c>
       <c r="H78" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I78" s="1">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="J78" s="1">
         <v>2</v>
@@ -3626,56 +3629,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="79" customHeight="1" spans="4:4">
-      <c r="D79" s="8"/>
-    </row>
-    <row r="80" customHeight="1" spans="3:11">
-      <c r="C80" s="1">
-        <v>301</v>
-      </c>
-      <c r="D80" s="11" t="s">
+    <row r="79" customHeight="1" spans="3:11">
+      <c r="C79" s="1">
+        <v>203</v>
+      </c>
+      <c r="D79" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="E80" s="9" t="s">
+      <c r="E79" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F80" s="1">
-        <v>20</v>
-      </c>
-      <c r="G80" s="1">
-        <v>101</v>
-      </c>
-      <c r="H80" s="1">
-        <v>500</v>
-      </c>
-      <c r="I80" s="1">
-        <v>10</v>
-      </c>
-      <c r="J80" s="1">
-        <v>1</v>
-      </c>
-      <c r="K80" s="1" t="s">
-        <v>122</v>
-      </c>
+      <c r="F79" s="1">
+        <v>15</v>
+      </c>
+      <c r="G79" s="1">
+        <v>1050</v>
+      </c>
+      <c r="H79" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I79" s="1">
+        <v>51</v>
+      </c>
+      <c r="J79" s="1">
+        <v>2</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="4:4">
+      <c r="D80" s="8"/>
     </row>
     <row r="81" customHeight="1" spans="3:11">
       <c r="C81" s="1">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D81" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E81" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="E81" s="9" t="s">
-        <v>124</v>
-      </c>
       <c r="F81" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G81" s="1">
-        <v>501</v>
+        <v>101</v>
       </c>
       <c r="H81" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="I81" s="1">
         <v>10</v>
@@ -3684,56 +3687,56 @@
         <v>1</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:11">
       <c r="C82" s="1">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D82" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E82" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="E82" s="9" t="s">
+      <c r="F82" s="1">
+        <v>15</v>
+      </c>
+      <c r="G82" s="1">
+        <v>501</v>
+      </c>
+      <c r="H82" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I82" s="1">
+        <v>10</v>
+      </c>
+      <c r="J82" s="1">
+        <v>1</v>
+      </c>
+      <c r="K82" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="F82" s="1">
-        <v>10</v>
-      </c>
-      <c r="G82" s="1">
-        <v>1001</v>
-      </c>
-      <c r="H82" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I82" s="1">
-        <v>20</v>
-      </c>
-      <c r="J82" s="1">
-        <v>1</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:11">
       <c r="C83" s="1">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D83" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E83" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="E83" s="9" t="s">
-        <v>130</v>
-      </c>
       <c r="F83" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G83" s="1">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H83" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I83" s="1">
         <v>20</v>
@@ -3742,56 +3745,56 @@
         <v>1</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:11">
       <c r="C84" s="1">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D84" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E84" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="E84" s="9" t="s">
+      <c r="F84" s="1">
+        <v>8</v>
+      </c>
+      <c r="G84" s="1">
+        <v>1501</v>
+      </c>
+      <c r="H84" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I84" s="1">
+        <v>20</v>
+      </c>
+      <c r="J84" s="1">
+        <v>1</v>
+      </c>
+      <c r="K84" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="F84" s="1">
-        <v>15</v>
-      </c>
-      <c r="G84" s="1">
-        <v>2001</v>
-      </c>
-      <c r="H84" s="1">
-        <v>3000</v>
-      </c>
-      <c r="I84" s="1">
-        <v>52</v>
-      </c>
-      <c r="J84" s="1">
-        <v>1</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:11">
       <c r="C85" s="1">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D85" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E85" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="E85" s="9" t="s">
-        <v>136</v>
-      </c>
       <c r="F85" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G85" s="1">
-        <v>2501</v>
+        <v>2001</v>
       </c>
       <c r="H85" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="I85" s="1">
         <v>52</v>
@@ -3800,27 +3803,27 @@
         <v>1</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:11">
       <c r="C86" s="1">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D86" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="E86" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="E86" s="9" t="s">
-        <v>139</v>
-      </c>
       <c r="F86" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G86" s="1">
-        <v>3001</v>
+        <v>2501</v>
       </c>
       <c r="H86" s="1">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="I86" s="1">
         <v>52</v>
@@ -3829,7 +3832,36 @@
         <v>1</v>
       </c>
       <c r="K86" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:11">
+      <c r="C87" s="1">
+        <v>307</v>
+      </c>
+      <c r="D87" s="11" t="s">
         <v>140</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="F87" s="1">
+        <v>5</v>
+      </c>
+      <c r="G87" s="1">
+        <v>3001</v>
+      </c>
+      <c r="H87" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I87" s="1">
+        <v>52</v>
+      </c>
+      <c r="J87" s="1">
+        <v>1</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -2779,7 +2779,7 @@
         <v>10000</v>
       </c>
       <c r="I46" s="2">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="J46" s="2">
         <v>1</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -687,12 +687,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2779,7 +2779,7 @@
         <v>10000</v>
       </c>
       <c r="I46" s="2">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="J46" s="2">
         <v>1</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -687,12 +687,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3817,7 +3817,7 @@
         <v>138</v>
       </c>
       <c r="F86" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G86" s="1">
         <v>2501</v>
@@ -3846,7 +3846,7 @@
         <v>141</v>
       </c>
       <c r="F87" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G87" s="1">
         <v>3001</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="146">
   <si>
     <t>#</t>
   </si>
@@ -490,6 +490,15 @@
   </si>
   <si>
     <t>7天一个</t>
+  </si>
+  <si>
+    <t>金图鉴1</t>
+  </si>
+  <si>
+    <t>金图鉴2</t>
+  </si>
+  <si>
+    <t>金图鉴3</t>
   </si>
 </sst>
 </file>
@@ -1494,15 +1503,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="9.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.625" style="1" customWidth="1"/>
-    <col min="6" max="7" width="12.25" style="1" customWidth="1"/>
-    <col min="8" max="10" width="11.125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="23.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.75221238938053" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6283185840708" style="1" customWidth="1"/>
+    <col min="6" max="7" width="12.2477876106195" style="1" customWidth="1"/>
+    <col min="8" max="10" width="11.1238938053097" style="1" customWidth="1"/>
+    <col min="11" max="11" width="23.1238938053097" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -3794,7 +3803,7 @@
         <v>2001</v>
       </c>
       <c r="H85" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I85" s="1">
         <v>52</v>
@@ -3823,7 +3832,7 @@
         <v>2501</v>
       </c>
       <c r="H86" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="I86" s="1">
         <v>52</v>
@@ -3852,7 +3861,7 @@
         <v>3001</v>
       </c>
       <c r="H87" s="1">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="I87" s="1">
         <v>52</v>
@@ -3862,6 +3871,84 @@
       </c>
       <c r="K87" s="1" t="s">
         <v>142</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="3:10">
+      <c r="C89" s="1">
+        <v>311</v>
+      </c>
+      <c r="D89" s="1">
+        <v>806</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F89" s="1">
+        <v>10</v>
+      </c>
+      <c r="G89" s="1">
+        <v>3500</v>
+      </c>
+      <c r="H89" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I89" s="1">
+        <v>3</v>
+      </c>
+      <c r="J89" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="3:10">
+      <c r="C90" s="1">
+        <v>312</v>
+      </c>
+      <c r="D90" s="1">
+        <v>807</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F90" s="1">
+        <v>10</v>
+      </c>
+      <c r="G90" s="1">
+        <v>3500</v>
+      </c>
+      <c r="H90" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I90" s="1">
+        <v>3</v>
+      </c>
+      <c r="J90" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="3:10">
+      <c r="C91" s="1">
+        <v>313</v>
+      </c>
+      <c r="D91" s="1">
+        <v>808</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F91" s="1">
+        <v>10</v>
+      </c>
+      <c r="G91" s="1">
+        <v>3500</v>
+      </c>
+      <c r="H91" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I91" s="1">
+        <v>3</v>
+      </c>
+      <c r="J91" s="1">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="149">
   <si>
     <t>#</t>
   </si>
@@ -492,10 +492,19 @@
     <t>7天一个</t>
   </si>
   <si>
+    <t>2007</t>
+  </si>
+  <si>
     <t>金图鉴1</t>
   </si>
   <si>
+    <t>2008</t>
+  </si>
+  <si>
     <t>金图鉴2</t>
+  </si>
+  <si>
+    <t>2009</t>
   </si>
   <si>
     <t>金图鉴3</t>
@@ -3877,11 +3886,11 @@
       <c r="C89" s="1">
         <v>311</v>
       </c>
-      <c r="D89" s="1">
-        <v>806</v>
+      <c r="D89" s="12" t="s">
+        <v>143</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F89" s="1">
         <v>10</v>
@@ -3903,14 +3912,14 @@
       <c r="C90" s="1">
         <v>312</v>
       </c>
-      <c r="D90" s="1">
-        <v>807</v>
+      <c r="D90" s="12" t="s">
+        <v>145</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F90" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G90" s="1">
         <v>3500</v>
@@ -3929,14 +3938,14 @@
       <c r="C91" s="1">
         <v>313</v>
       </c>
-      <c r="D91" s="1">
-        <v>808</v>
+      <c r="D91" s="12" t="s">
+        <v>147</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F91" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G91" s="1">
         <v>3500</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="151">
   <si>
     <t>#</t>
   </si>
@@ -508,6 +508,12 @@
   </si>
   <si>
     <t>金图鉴3</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>暗金图鉴</t>
   </si>
 </sst>
 </file>
@@ -1512,7 +1518,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -3893,10 +3899,10 @@
         <v>144</v>
       </c>
       <c r="F89" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G89" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="H89" s="1">
         <v>5000</v>
@@ -3919,10 +3925,10 @@
         <v>146</v>
       </c>
       <c r="F90" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G90" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="H90" s="1">
         <v>5000</v>
@@ -3945,10 +3951,10 @@
         <v>148</v>
       </c>
       <c r="F91" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G91" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="H91" s="1">
         <v>5000</v>
@@ -3958,6 +3964,32 @@
       </c>
       <c r="J91" s="1">
         <v>11</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="3:10">
+      <c r="C92" s="1">
+        <v>314</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F92" s="1">
+        <v>2</v>
+      </c>
+      <c r="G92" s="1">
+        <v>3500</v>
+      </c>
+      <c r="H92" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I92" s="1">
+        <v>1</v>
+      </c>
+      <c r="J92" s="1">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -711,12 +711,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3986,10 +3986,10 @@
         <v>5000</v>
       </c>
       <c r="I92" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J92" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="153">
   <si>
     <t>#</t>
   </si>
@@ -322,6 +322,12 @@
   </si>
   <si>
     <t>开孔石</t>
+  </si>
+  <si>
+    <t>1013</t>
+  </si>
+  <si>
+    <t>时装精华</t>
   </si>
   <si>
     <t>BOSS杀手</t>
@@ -711,12 +717,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1518,7 +1524,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:L93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2809,50 +2815,47 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="4:4">
-      <c r="D47" s="6"/>
-    </row>
-    <row r="48" customHeight="1" spans="3:11">
-      <c r="C48" s="1">
-        <v>101</v>
-      </c>
-      <c r="D48" s="8">
-        <v>180001</v>
-      </c>
-      <c r="E48" s="1" t="s">
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C47" s="1">
+        <v>42</v>
+      </c>
+      <c r="D47" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="F48" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G48" s="1">
-        <v>100</v>
-      </c>
-      <c r="H48" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I48" s="1">
-        <v>100</v>
-      </c>
-      <c r="J48" s="1">
-        <v>1</v>
-      </c>
-      <c r="K48" s="1" t="s">
+      <c r="E47" s="1" t="s">
         <v>88</v>
       </c>
+      <c r="F47" s="2">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2">
+        <v>1007</v>
+      </c>
+      <c r="H47" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I47" s="2">
+        <v>37</v>
+      </c>
+      <c r="J47" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="4:4">
+      <c r="D48" s="6"/>
     </row>
     <row r="49" customHeight="1" spans="3:11">
       <c r="C49" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D49" s="8">
-        <v>180002</v>
+        <v>180001</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>89</v>
       </c>
       <c r="F49" s="1">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G49" s="1">
         <v>100</v>
@@ -2867,21 +2870,21 @@
         <v>1</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:11">
       <c r="C50" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D50" s="8">
-        <v>180003</v>
+        <v>180002</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F50" s="1">
-        <v>150000</v>
+        <v>4000</v>
       </c>
       <c r="G50" s="1">
         <v>100</v>
@@ -2893,24 +2896,24 @@
         <v>100</v>
       </c>
       <c r="J50" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:11">
       <c r="C51" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D51" s="8">
-        <v>180004</v>
+        <v>180003</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F51" s="1">
-        <v>8000</v>
+        <v>150000</v>
       </c>
       <c r="G51" s="1">
         <v>100</v>
@@ -2922,24 +2925,24 @@
         <v>100</v>
       </c>
       <c r="J51" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:11">
       <c r="C52" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D52" s="8">
-        <v>180005</v>
+        <v>180004</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F52" s="1">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="G52" s="1">
         <v>100</v>
@@ -2954,21 +2957,21 @@
         <v>1</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:11">
       <c r="C53" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D53" s="8">
-        <v>180006</v>
+        <v>180005</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F53" s="1">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="G53" s="1">
         <v>100</v>
@@ -2980,24 +2983,24 @@
         <v>100</v>
       </c>
       <c r="J53" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:11">
       <c r="C54" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D54" s="8">
-        <v>180007</v>
+        <v>180006</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F54" s="1">
-        <v>2000</v>
+        <v>50000</v>
       </c>
       <c r="G54" s="1">
         <v>100</v>
@@ -3009,24 +3012,24 @@
         <v>100</v>
       </c>
       <c r="J54" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
       <c r="C55" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D55" s="8">
-        <v>180008</v>
+        <v>180007</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F55" s="1">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="G55" s="1">
         <v>100</v>
@@ -3038,24 +3041,24 @@
         <v>100</v>
       </c>
       <c r="J55" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
       <c r="C56" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D56" s="8">
-        <v>180009</v>
+        <v>180008</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F56" s="1">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="G56" s="1">
         <v>100</v>
@@ -3067,24 +3070,24 @@
         <v>100</v>
       </c>
       <c r="J56" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:11">
       <c r="C57" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D57" s="8">
-        <v>180010</v>
+        <v>180009</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F57" s="1">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="G57" s="1">
         <v>100</v>
@@ -3099,21 +3102,21 @@
         <v>1</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:11">
       <c r="C58" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D58" s="8">
-        <v>180011</v>
+        <v>180010</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F58" s="1">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="G58" s="1">
         <v>100</v>
@@ -3125,21 +3128,21 @@
         <v>100</v>
       </c>
       <c r="J58" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
       <c r="C59" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D59" s="8">
-        <v>180012</v>
+        <v>180011</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F59" s="1">
         <v>100000</v>
@@ -3157,21 +3160,21 @@
         <v>5</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:11">
       <c r="C60" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D60" s="8">
-        <v>180013</v>
+        <v>180012</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F60" s="1">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="G60" s="1">
         <v>100</v>
@@ -3186,21 +3189,21 @@
         <v>5</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:11">
       <c r="C61" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D61" s="8">
-        <v>180014</v>
+        <v>180013</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F61" s="1">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G61" s="1">
         <v>100</v>
@@ -3215,18 +3218,18 @@
         <v>5</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:11">
       <c r="C62" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D62" s="8">
-        <v>180015</v>
+        <v>180014</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F62" s="1">
         <v>100000</v>
@@ -3244,21 +3247,21 @@
         <v>5</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:11">
       <c r="C63" s="1">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D63" s="8">
-        <v>180020</v>
+        <v>180015</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F63" s="1">
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="G63" s="1">
         <v>100</v>
@@ -3270,21 +3273,21 @@
         <v>100</v>
       </c>
       <c r="J63" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:11">
       <c r="C64" s="1">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D64" s="8">
-        <v>180021</v>
+        <v>180020</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F64" s="1">
         <v>30000</v>
@@ -3302,21 +3305,21 @@
         <v>2</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:11">
       <c r="C65" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D65" s="8">
-        <v>180022</v>
+        <v>180021</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F65" s="1">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="G65" s="1">
         <v>100</v>
@@ -3328,59 +3331,59 @@
         <v>100</v>
       </c>
       <c r="J65" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="3:11">
-      <c r="C67" s="1">
-        <v>130</v>
-      </c>
-      <c r="D67" s="1">
-        <v>180030</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F67" s="1">
-        <v>5</v>
-      </c>
-      <c r="G67" s="1">
-        <v>1100</v>
-      </c>
-      <c r="H67" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I67" s="1">
-        <v>100</v>
-      </c>
-      <c r="J67" s="1">
-        <v>1</v>
-      </c>
-      <c r="K67" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:11">
+      <c r="C66" s="1">
+        <v>122</v>
+      </c>
+      <c r="D66" s="8">
+        <v>180022</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>107</v>
+      </c>
+      <c r="F66" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G66" s="1">
+        <v>100</v>
+      </c>
+      <c r="H66" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I66" s="1">
+        <v>100</v>
+      </c>
+      <c r="J66" s="1">
+        <v>1</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:11">
       <c r="C68" s="1">
-        <v>131</v>
-      </c>
-      <c r="D68" s="8">
-        <v>180032</v>
+        <v>130</v>
+      </c>
+      <c r="D68" s="1">
+        <v>180030</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>108</v>
       </c>
       <c r="F68" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G68" s="1">
         <v>1100</v>
       </c>
       <c r="H68" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I68" s="1">
         <v>100</v>
@@ -3389,24 +3392,24 @@
         <v>1</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
       <c r="C69" s="1">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D69" s="8">
-        <v>180033</v>
+        <v>180032</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F69" s="1">
         <v>1</v>
       </c>
       <c r="G69" s="1">
-        <v>1600</v>
+        <v>1100</v>
       </c>
       <c r="H69" s="1">
         <v>2000</v>
@@ -3418,27 +3421,27 @@
         <v>1</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
       <c r="C70" s="1">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D70" s="8">
-        <v>180034</v>
+        <v>180033</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F70" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G70" s="1">
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="H70" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I70" s="1">
         <v>100</v>
@@ -3447,27 +3450,27 @@
         <v>1</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
       <c r="C71" s="1">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D71" s="8">
-        <v>180035</v>
+        <v>180034</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F71" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G71" s="1">
-        <v>2000</v>
+        <v>1100</v>
       </c>
       <c r="H71" s="1">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I71" s="1">
         <v>100</v>
@@ -3476,18 +3479,18 @@
         <v>1</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
       <c r="C72" s="1">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D72" s="8">
-        <v>180036</v>
+        <v>180035</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F72" s="1">
         <v>1</v>
@@ -3505,28 +3508,28 @@
         <v>1</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
       <c r="C73" s="1">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D73" s="8">
-        <v>180037</v>
+        <v>180036</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F73" s="1">
         <v>1</v>
       </c>
       <c r="G73" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H73" s="1">
         <v>2500</v>
       </c>
-      <c r="H73" s="1">
-        <v>3500</v>
-      </c>
       <c r="I73" s="1">
         <v>100</v>
       </c>
@@ -3534,24 +3537,24 @@
         <v>1</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
       <c r="C74" s="1">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D74" s="8">
-        <v>180038</v>
+        <v>180037</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F74" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G74" s="1">
-        <v>1600</v>
+        <v>2500</v>
       </c>
       <c r="H74" s="1">
         <v>3500</v>
@@ -3563,24 +3566,24 @@
         <v>1</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:11">
       <c r="C75" s="1">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D75" s="8">
-        <v>180039</v>
+        <v>180038</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F75" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G75" s="1">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="H75" s="1">
         <v>3500</v>
@@ -3592,41 +3595,41 @@
         <v>1</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="77" customHeight="1" spans="3:11">
-      <c r="C77" s="1">
-        <v>201</v>
-      </c>
-      <c r="D77" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="E77" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:11">
+      <c r="C76" s="1">
+        <v>138</v>
+      </c>
+      <c r="D76" s="8">
+        <v>180039</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F77" s="1">
-        <v>5</v>
-      </c>
-      <c r="G77" s="1">
-        <v>150</v>
-      </c>
-      <c r="H77" s="1">
-        <v>1200</v>
-      </c>
-      <c r="I77" s="1">
-        <v>20</v>
-      </c>
-      <c r="J77" s="1">
-        <v>2</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>44</v>
+      <c r="F76" s="1">
+        <v>3</v>
+      </c>
+      <c r="G76" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H76" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I76" s="1">
+        <v>100</v>
+      </c>
+      <c r="J76" s="1">
+        <v>1</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:11">
       <c r="C78" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D78" s="11" t="s">
         <v>118</v>
@@ -3638,13 +3641,13 @@
         <v>5</v>
       </c>
       <c r="G78" s="1">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H78" s="1">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="I78" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J78" s="1">
         <v>2</v>
@@ -3655,7 +3658,7 @@
     </row>
     <row r="79" customHeight="1" spans="3:11">
       <c r="C79" s="1">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D79" s="11" t="s">
         <v>120</v>
@@ -3664,16 +3667,16 @@
         <v>121</v>
       </c>
       <c r="F79" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G79" s="1">
-        <v>1050</v>
+        <v>200</v>
       </c>
       <c r="H79" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I79" s="1">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="J79" s="1">
         <v>2</v>
@@ -3682,56 +3685,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="80" customHeight="1" spans="4:4">
-      <c r="D80" s="8"/>
-    </row>
-    <row r="81" customHeight="1" spans="3:11">
-      <c r="C81" s="1">
-        <v>301</v>
-      </c>
-      <c r="D81" s="11" t="s">
+    <row r="80" customHeight="1" spans="3:11">
+      <c r="C80" s="1">
+        <v>203</v>
+      </c>
+      <c r="D80" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="E81" s="9" t="s">
+      <c r="E80" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F81" s="1">
-        <v>20</v>
-      </c>
-      <c r="G81" s="1">
-        <v>101</v>
-      </c>
-      <c r="H81" s="1">
-        <v>500</v>
-      </c>
-      <c r="I81" s="1">
-        <v>10</v>
-      </c>
-      <c r="J81" s="1">
-        <v>1</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>124</v>
-      </c>
+      <c r="F80" s="1">
+        <v>15</v>
+      </c>
+      <c r="G80" s="1">
+        <v>1050</v>
+      </c>
+      <c r="H80" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I80" s="1">
+        <v>51</v>
+      </c>
+      <c r="J80" s="1">
+        <v>2</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="4:4">
+      <c r="D81" s="8"/>
     </row>
     <row r="82" customHeight="1" spans="3:11">
       <c r="C82" s="1">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D82" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E82" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E82" s="9" t="s">
-        <v>126</v>
-      </c>
       <c r="F82" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G82" s="1">
-        <v>501</v>
+        <v>101</v>
       </c>
       <c r="H82" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="I82" s="1">
         <v>10</v>
@@ -3740,56 +3743,56 @@
         <v>1</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:11">
       <c r="C83" s="1">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D83" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E83" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="E83" s="9" t="s">
+      <c r="F83" s="1">
+        <v>15</v>
+      </c>
+      <c r="G83" s="1">
+        <v>501</v>
+      </c>
+      <c r="H83" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I83" s="1">
+        <v>10</v>
+      </c>
+      <c r="J83" s="1">
+        <v>1</v>
+      </c>
+      <c r="K83" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="F83" s="1">
-        <v>10</v>
-      </c>
-      <c r="G83" s="1">
-        <v>1001</v>
-      </c>
-      <c r="H83" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I83" s="1">
-        <v>20</v>
-      </c>
-      <c r="J83" s="1">
-        <v>1</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:11">
       <c r="C84" s="1">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D84" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E84" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="E84" s="9" t="s">
-        <v>132</v>
-      </c>
       <c r="F84" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G84" s="1">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H84" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I84" s="1">
         <v>20</v>
@@ -3798,56 +3801,56 @@
         <v>1</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:11">
       <c r="C85" s="1">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D85" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E85" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="E85" s="9" t="s">
+      <c r="F85" s="1">
+        <v>8</v>
+      </c>
+      <c r="G85" s="1">
+        <v>1501</v>
+      </c>
+      <c r="H85" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I85" s="1">
+        <v>20</v>
+      </c>
+      <c r="J85" s="1">
+        <v>1</v>
+      </c>
+      <c r="K85" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="F85" s="1">
-        <v>15</v>
-      </c>
-      <c r="G85" s="1">
-        <v>2001</v>
-      </c>
-      <c r="H85" s="1">
-        <v>2500</v>
-      </c>
-      <c r="I85" s="1">
-        <v>52</v>
-      </c>
-      <c r="J85" s="1">
-        <v>1</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:11">
       <c r="C86" s="1">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D86" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="E86" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="E86" s="9" t="s">
-        <v>138</v>
-      </c>
       <c r="F86" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G86" s="1">
-        <v>2501</v>
+        <v>2001</v>
       </c>
       <c r="H86" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I86" s="1">
         <v>52</v>
@@ -3856,27 +3859,27 @@
         <v>1</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:11">
       <c r="C87" s="1">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D87" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E87" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="E87" s="9" t="s">
-        <v>141</v>
-      </c>
       <c r="F87" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G87" s="1">
-        <v>3001</v>
+        <v>2501</v>
       </c>
       <c r="H87" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="I87" s="1">
         <v>52</v>
@@ -3885,38 +3888,41 @@
         <v>1</v>
       </c>
       <c r="K87" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="3:11">
+      <c r="C88" s="1">
+        <v>307</v>
+      </c>
+      <c r="D88" s="11" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="89" customHeight="1" spans="3:10">
-      <c r="C89" s="1">
-        <v>311</v>
-      </c>
-      <c r="D89" s="12" t="s">
+      <c r="E88" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="F88" s="1">
+        <v>3</v>
+      </c>
+      <c r="G88" s="1">
+        <v>3001</v>
+      </c>
+      <c r="H88" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I88" s="1">
+        <v>52</v>
+      </c>
+      <c r="J88" s="1">
+        <v>1</v>
+      </c>
+      <c r="K88" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="F89" s="1">
-        <v>20</v>
-      </c>
-      <c r="G89" s="1">
-        <v>3000</v>
-      </c>
-      <c r="H89" s="1">
-        <v>5000</v>
-      </c>
-      <c r="I89" s="1">
-        <v>3</v>
-      </c>
-      <c r="J89" s="1">
-        <v>33</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:10">
       <c r="C90" s="1">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D90" s="12" t="s">
         <v>145</v>
@@ -3925,7 +3931,7 @@
         <v>146</v>
       </c>
       <c r="F90" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G90" s="1">
         <v>3000</v>
@@ -3937,12 +3943,12 @@
         <v>3</v>
       </c>
       <c r="J90" s="1">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:10">
       <c r="C91" s="1">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D91" s="12" t="s">
         <v>147</v>
@@ -3951,7 +3957,7 @@
         <v>148</v>
       </c>
       <c r="F91" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G91" s="1">
         <v>3000</v>
@@ -3963,12 +3969,12 @@
         <v>3</v>
       </c>
       <c r="J91" s="1">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:10">
       <c r="C92" s="1">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D92" s="12" t="s">
         <v>149</v>
@@ -3977,18 +3983,44 @@
         <v>150</v>
       </c>
       <c r="F92" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G92" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="H92" s="1">
         <v>5000</v>
       </c>
       <c r="I92" s="1">
+        <v>3</v>
+      </c>
+      <c r="J92" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="3:10">
+      <c r="C93" s="1">
+        <v>314</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F93" s="1">
+        <v>2</v>
+      </c>
+      <c r="G93" s="1">
+        <v>3500</v>
+      </c>
+      <c r="H93" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I93" s="1">
         <v>4</v>
       </c>
-      <c r="J92" s="1">
+      <c r="J93" s="1">
         <v>5</v>
       </c>
     </row>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -2835,7 +2835,7 @@
         <v>10000</v>
       </c>
       <c r="I47" s="2">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="J47" s="2">
         <v>2</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="154">
   <si>
     <t>#</t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>Max</t>
+  </si>
+  <si>
+    <t>Number</t>
   </si>
   <si>
     <t>int</t>
@@ -1524,35 +1527,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:M93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="9.75221238938053" style="1" customWidth="1"/>
     <col min="5" max="5" width="12.6283185840708" style="1" customWidth="1"/>
     <col min="6" max="7" width="12.2477876106195" style="1" customWidth="1"/>
-    <col min="8" max="10" width="11.1238938053097" style="1" customWidth="1"/>
-    <col min="11" max="11" width="23.1238938053097" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="8" max="11" width="11.1238938053097" style="1" customWidth="1"/>
+    <col min="12" max="12" width="23.1238938053097" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="11:12">
-      <c r="K1" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" customHeight="1" spans="12:13">
       <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="11:12">
-      <c r="K2" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
+    </row>
+    <row r="2" customHeight="1" spans="12:13">
       <c r="L2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="M2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
@@ -1577,8 +1580,11 @@
       <c r="J3" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="K3" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C4" s="4" t="s">
         <v>1</v>
       </c>
@@ -1603,42 +1609,48 @@
       <c r="J4" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="K4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="G5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:11">
+        <v>10</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" s="2">
         <v>100</v>
@@ -1655,19 +1667,22 @@
       <c r="J6" s="2">
         <v>500</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K6" s="2">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" s="2">
         <v>10</v>
@@ -1684,19 +1699,22 @@
       <c r="J7" s="2">
         <v>50</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F8" s="1">
         <v>50</v>
@@ -1713,19 +1731,22 @@
       <c r="J8" s="1">
         <v>10000</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="3:11">
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F9" s="1">
         <v>50</v>
@@ -1742,19 +1763,22 @@
       <c r="J9" s="1">
         <v>10000</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K9" s="2">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10" s="1">
         <v>10</v>
@@ -1771,19 +1795,22 @@
       <c r="J10" s="1">
         <v>10000</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K10" s="2">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" s="1">
         <v>10</v>
@@ -1800,19 +1827,22 @@
       <c r="J11" s="1">
         <v>10000</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:11">
+      <c r="K11" s="2">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:12">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12" s="1">
         <v>4</v>
@@ -1829,11 +1859,14 @@
       <c r="J12" s="1">
         <v>20</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:11">
+      <c r="K12" s="2">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:12">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1841,7 +1874,7 @@
         <v>3001</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F13" s="1">
         <v>10</v>
@@ -1858,11 +1891,14 @@
       <c r="J13" s="1">
         <v>10000</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:11">
+      <c r="K13" s="2">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:12">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1870,7 +1906,7 @@
         <v>3002</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F14" s="1">
         <v>10</v>
@@ -1887,19 +1923,22 @@
       <c r="J14" s="1">
         <v>10000</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:11">
+      <c r="K14" s="2">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:12">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F15" s="1">
         <v>30</v>
@@ -1916,19 +1955,22 @@
       <c r="J15" s="1">
         <v>1</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C16" s="2">
         <v>11</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F16" s="2">
         <v>10</v>
@@ -1945,19 +1987,22 @@
       <c r="J16" s="2">
         <v>50</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:11">
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:12">
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F17" s="1">
         <v>20</v>
@@ -1974,19 +2019,22 @@
       <c r="J17" s="1">
         <v>1</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K17" s="2">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C18" s="2">
         <v>13</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F18" s="2">
         <v>12</v>
@@ -2003,19 +2051,22 @@
       <c r="J18" s="2">
         <v>25</v>
       </c>
-      <c r="K18" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C19" s="2">
         <v>14</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F19" s="2">
         <v>10</v>
@@ -2032,19 +2083,22 @@
       <c r="J19" s="2">
         <v>10</v>
       </c>
-      <c r="K19" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K19" s="2">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C20" s="1">
         <v>15</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" s="1">
         <v>20</v>
@@ -2061,19 +2115,22 @@
       <c r="J20" s="1">
         <v>1</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K20" s="2">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C21" s="1">
         <v>16</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F21" s="1">
         <v>2</v>
@@ -2090,19 +2147,22 @@
       <c r="J21" s="1">
         <v>20</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="20" customHeight="1" spans="3:11">
+      <c r="K21" s="2">
+        <v>1</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
       <c r="C22" s="1">
         <v>17</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F22" s="1">
         <v>50</v>
@@ -2119,19 +2179,22 @@
       <c r="J22" s="1">
         <v>10000</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:11">
+      <c r="K22" s="2">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:12">
       <c r="C23" s="1">
         <v>18</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F23" s="1">
         <v>50</v>
@@ -2148,19 +2211,22 @@
       <c r="J23" s="1">
         <v>10000</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:11">
+      <c r="K23" s="2">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:12">
       <c r="C24" s="1">
         <v>19</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F24" s="1">
         <v>50</v>
@@ -2177,19 +2243,22 @@
       <c r="J24" s="1">
         <v>10000</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:11">
+      <c r="K24" s="2">
+        <v>1</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:12">
       <c r="C25" s="1">
         <v>20</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F25" s="1">
         <v>50</v>
@@ -2206,19 +2275,22 @@
       <c r="J25" s="1">
         <v>10000</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:11">
+      <c r="K25" s="2">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:12">
       <c r="C26" s="1">
         <v>21</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F26" s="1">
         <v>50</v>
@@ -2235,19 +2307,22 @@
       <c r="J26" s="1">
         <v>10000</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:11">
+      <c r="K26" s="2">
+        <v>1</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:12">
       <c r="C27" s="1">
         <v>22</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F27" s="1">
         <v>50</v>
@@ -2264,21 +2339,24 @@
       <c r="J27" s="1">
         <v>10000</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:11">
+      <c r="K27" s="2">
+        <v>1</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3">
         <v>23</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F28" s="3">
         <v>10</v>
@@ -2295,21 +2373,24 @@
       <c r="J28" s="3">
         <v>10000</v>
       </c>
-      <c r="K28" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:11">
+      <c r="K28" s="2">
+        <v>1</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3">
         <v>24</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F29" s="3">
         <v>10</v>
@@ -2326,19 +2407,22 @@
       <c r="J29" s="3">
         <v>10000</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K29" s="2">
+        <v>1</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C30" s="2">
         <v>25</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F30" s="2">
         <v>4</v>
@@ -2355,21 +2439,24 @@
       <c r="J30" s="2">
         <v>20</v>
       </c>
-      <c r="K30" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:11">
+      <c r="K30" s="2">
+        <v>1</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:12">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3">
         <v>26</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F31" s="3">
         <v>10</v>
@@ -2386,21 +2473,24 @@
       <c r="J31" s="3">
         <v>10000</v>
       </c>
-      <c r="K31" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="1:11">
+      <c r="K31" s="2">
+        <v>1</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:12">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3">
         <v>27</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F32" s="3">
         <v>10</v>
@@ -2417,19 +2507,22 @@
       <c r="J32" s="3">
         <v>10000</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:11">
+      <c r="K32" s="2">
+        <v>1</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:12">
       <c r="C33" s="1">
         <v>28</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F33" s="1">
         <v>10</v>
@@ -2446,19 +2539,22 @@
       <c r="J33" s="1">
         <v>3</v>
       </c>
-      <c r="K33" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:11">
+      <c r="K33" s="2">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:12">
       <c r="C34" s="1">
         <v>29</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F34" s="1">
         <v>10</v>
@@ -2475,19 +2571,22 @@
       <c r="J34" s="1">
         <v>3</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K34" s="2">
+        <v>1</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C35" s="1">
         <v>30</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F35" s="1">
         <v>10</v>
@@ -2504,19 +2603,22 @@
       <c r="J35" s="1">
         <v>3</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K35" s="2">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C36" s="2">
         <v>31</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F36" s="2">
         <v>30</v>
@@ -2533,19 +2635,22 @@
       <c r="J36" s="2">
         <v>200</v>
       </c>
-      <c r="K36" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K36" s="2">
+        <v>1</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C37" s="2">
         <v>32</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F37" s="2">
         <v>3</v>
@@ -2562,19 +2667,22 @@
       <c r="J37" s="2">
         <v>20</v>
       </c>
-      <c r="K37" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" s="3" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K37" s="2">
+        <v>1</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" s="3" customFormat="1" customHeight="1" spans="3:12">
       <c r="C38" s="3">
         <v>33</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F38" s="3">
         <v>50</v>
@@ -2591,19 +2699,22 @@
       <c r="J38" s="3">
         <v>10000</v>
       </c>
-      <c r="K38" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="39" s="3" customFormat="1" ht="20" customHeight="1" spans="3:11">
+      <c r="K38" s="2">
+        <v>1</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" s="3" customFormat="1" ht="20" customHeight="1" spans="3:12">
       <c r="C39" s="3">
         <v>34</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F39" s="3">
         <v>50</v>
@@ -2620,19 +2731,22 @@
       <c r="J39" s="3">
         <v>10000</v>
       </c>
-      <c r="K39" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K39" s="2">
+        <v>1</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C40" s="2">
         <v>35</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F40" s="2">
         <v>6</v>
@@ -2649,19 +2763,22 @@
       <c r="J40" s="2">
         <v>25</v>
       </c>
-      <c r="K40" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" ht="20" customHeight="1" spans="3:10">
+      <c r="K40" s="2">
+        <v>1</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="20" customHeight="1" spans="3:11">
       <c r="C41" s="1">
         <v>36</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F41" s="1">
         <v>5</v>
@@ -2678,16 +2795,19 @@
       <c r="J41" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" s="1" customFormat="1" ht="20" customHeight="1" spans="3:10">
+      <c r="K41" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="20" customHeight="1" spans="3:11">
       <c r="C42" s="1">
         <v>37</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F42" s="1">
         <v>12</v>
@@ -2704,16 +2824,19 @@
       <c r="J42" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="43" s="1" customFormat="1" ht="20" customHeight="1" spans="3:10">
+      <c r="K42" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="20" customHeight="1" spans="3:11">
       <c r="C43" s="1">
         <v>38</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F43" s="1">
         <v>12</v>
@@ -2730,16 +2853,19 @@
       <c r="J43" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K43" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C44" s="1">
         <v>39</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F44" s="2">
         <v>5</v>
@@ -2756,19 +2882,22 @@
       <c r="J44" s="2">
         <v>10</v>
       </c>
-      <c r="K44" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K44" s="2">
+        <v>1</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C45" s="1">
         <v>40</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F45" s="2">
         <v>5</v>
@@ -2785,19 +2914,22 @@
       <c r="J45" s="2">
         <v>10</v>
       </c>
-      <c r="K45" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="K45" s="2">
+        <v>1</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:11">
       <c r="C46" s="1">
         <v>41</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F46" s="2">
         <v>1</v>
@@ -2814,16 +2946,19 @@
       <c r="J46" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="K46" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:11">
       <c r="C47" s="1">
         <v>42</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F47" s="2">
         <v>1</v>
@@ -2840,11 +2975,14 @@
       <c r="J47" s="2">
         <v>2</v>
       </c>
+      <c r="K47" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" customHeight="1" spans="4:4">
       <c r="D48" s="6"/>
     </row>
-    <row r="49" customHeight="1" spans="3:11">
+    <row r="49" customHeight="1" spans="3:12">
       <c r="C49" s="1">
         <v>101</v>
       </c>
@@ -2852,7 +2990,7 @@
         <v>180001</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F49" s="1">
         <v>2000</v>
@@ -2869,11 +3007,14 @@
       <c r="J49" s="1">
         <v>1</v>
       </c>
-      <c r="K49" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:11">
+      <c r="K49" s="2">
+        <v>1</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:12">
       <c r="C50" s="1">
         <v>102</v>
       </c>
@@ -2881,7 +3022,7 @@
         <v>180002</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F50" s="1">
         <v>4000</v>
@@ -2898,11 +3039,14 @@
       <c r="J50" s="1">
         <v>1</v>
       </c>
-      <c r="K50" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:11">
+      <c r="K50" s="2">
+        <v>1</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:12">
       <c r="C51" s="1">
         <v>103</v>
       </c>
@@ -2910,7 +3054,7 @@
         <v>180003</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F51" s="1">
         <v>150000</v>
@@ -2927,11 +3071,14 @@
       <c r="J51" s="1">
         <v>5</v>
       </c>
-      <c r="K51" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:11">
+      <c r="K51" s="2">
+        <v>1</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:12">
       <c r="C52" s="1">
         <v>104</v>
       </c>
@@ -2939,7 +3086,7 @@
         <v>180004</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F52" s="1">
         <v>8000</v>
@@ -2956,11 +3103,14 @@
       <c r="J52" s="1">
         <v>1</v>
       </c>
-      <c r="K52" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:11">
+      <c r="K52" s="2">
+        <v>1</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:12">
       <c r="C53" s="1">
         <v>105</v>
       </c>
@@ -2968,7 +3118,7 @@
         <v>180005</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F53" s="1">
         <v>3000</v>
@@ -2985,11 +3135,14 @@
       <c r="J53" s="1">
         <v>1</v>
       </c>
-      <c r="K53" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:11">
+      <c r="K53" s="2">
+        <v>1</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:12">
       <c r="C54" s="1">
         <v>106</v>
       </c>
@@ -2997,7 +3150,7 @@
         <v>180006</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F54" s="1">
         <v>50000</v>
@@ -3014,11 +3167,14 @@
       <c r="J54" s="1">
         <v>5</v>
       </c>
-      <c r="K54" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:11">
+      <c r="K54" s="2">
+        <v>1</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:12">
       <c r="C55" s="1">
         <v>107</v>
       </c>
@@ -3026,7 +3182,7 @@
         <v>180007</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F55" s="1">
         <v>2000</v>
@@ -3043,11 +3199,14 @@
       <c r="J55" s="1">
         <v>1</v>
       </c>
-      <c r="K55" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:11">
+      <c r="K55" s="2">
+        <v>1</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:12">
       <c r="C56" s="1">
         <v>108</v>
       </c>
@@ -3055,7 +3214,7 @@
         <v>180008</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F56" s="1">
         <v>20000</v>
@@ -3072,11 +3231,14 @@
       <c r="J56" s="1">
         <v>2</v>
       </c>
-      <c r="K56" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:11">
+      <c r="K56" s="2">
+        <v>1</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:12">
       <c r="C57" s="1">
         <v>109</v>
       </c>
@@ -3084,7 +3246,7 @@
         <v>180009</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F57" s="1">
         <v>3000</v>
@@ -3101,11 +3263,14 @@
       <c r="J57" s="1">
         <v>1</v>
       </c>
-      <c r="K57" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:11">
+      <c r="K57" s="2">
+        <v>1</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:12">
       <c r="C58" s="1">
         <v>110</v>
       </c>
@@ -3113,7 +3278,7 @@
         <v>180010</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F58" s="1">
         <v>10000</v>
@@ -3130,11 +3295,14 @@
       <c r="J58" s="1">
         <v>1</v>
       </c>
-      <c r="K58" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:11">
+      <c r="K58" s="2">
+        <v>1</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:12">
       <c r="C59" s="1">
         <v>111</v>
       </c>
@@ -3142,7 +3310,7 @@
         <v>180011</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F59" s="1">
         <v>100000</v>
@@ -3159,11 +3327,14 @@
       <c r="J59" s="1">
         <v>5</v>
       </c>
-      <c r="K59" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:11">
+      <c r="K59" s="2">
+        <v>1</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:12">
       <c r="C60" s="1">
         <v>112</v>
       </c>
@@ -3171,7 +3342,7 @@
         <v>180012</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F60" s="1">
         <v>100000</v>
@@ -3188,11 +3359,14 @@
       <c r="J60" s="1">
         <v>5</v>
       </c>
-      <c r="K60" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:11">
+      <c r="K60" s="2">
+        <v>1</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:12">
       <c r="C61" s="1">
         <v>113</v>
       </c>
@@ -3200,7 +3374,7 @@
         <v>180013</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F61" s="1">
         <v>50000</v>
@@ -3217,11 +3391,14 @@
       <c r="J61" s="1">
         <v>5</v>
       </c>
-      <c r="K61" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="3:11">
+      <c r="K61" s="2">
+        <v>1</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:12">
       <c r="C62" s="1">
         <v>114</v>
       </c>
@@ -3229,7 +3406,7 @@
         <v>180014</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F62" s="1">
         <v>100000</v>
@@ -3246,11 +3423,14 @@
       <c r="J62" s="1">
         <v>5</v>
       </c>
-      <c r="K62" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="3:11">
+      <c r="K62" s="2">
+        <v>1</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:12">
       <c r="C63" s="1">
         <v>115</v>
       </c>
@@ -3258,7 +3438,7 @@
         <v>180015</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F63" s="1">
         <v>100000</v>
@@ -3275,11 +3455,14 @@
       <c r="J63" s="1">
         <v>5</v>
       </c>
-      <c r="K63" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:11">
+      <c r="K63" s="2">
+        <v>1</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:12">
       <c r="C64" s="1">
         <v>120</v>
       </c>
@@ -3287,7 +3470,7 @@
         <v>180020</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F64" s="1">
         <v>30000</v>
@@ -3304,11 +3487,14 @@
       <c r="J64" s="1">
         <v>2</v>
       </c>
-      <c r="K64" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:11">
+      <c r="K64" s="2">
+        <v>1</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:12">
       <c r="C65" s="1">
         <v>121</v>
       </c>
@@ -3316,7 +3502,7 @@
         <v>180021</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F65" s="1">
         <v>30000</v>
@@ -3333,11 +3519,14 @@
       <c r="J65" s="1">
         <v>2</v>
       </c>
-      <c r="K65" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="3:11">
+      <c r="K65" s="2">
+        <v>1</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:12">
       <c r="C66" s="1">
         <v>122</v>
       </c>
@@ -3345,7 +3534,7 @@
         <v>180022</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F66" s="1">
         <v>3000</v>
@@ -3362,11 +3551,14 @@
       <c r="J66" s="1">
         <v>1</v>
       </c>
-      <c r="K66" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="68" customHeight="1" spans="3:11">
+      <c r="K66" s="2">
+        <v>1</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:12">
       <c r="C68" s="1">
         <v>130</v>
       </c>
@@ -3374,7 +3566,7 @@
         <v>180030</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F68" s="1">
         <v>5</v>
@@ -3391,11 +3583,14 @@
       <c r="J68" s="1">
         <v>1</v>
       </c>
-      <c r="K68" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="69" customHeight="1" spans="3:11">
+      <c r="K68" s="2">
+        <v>1</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:12">
       <c r="C69" s="1">
         <v>131</v>
       </c>
@@ -3403,7 +3598,7 @@
         <v>180032</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F69" s="1">
         <v>1</v>
@@ -3420,11 +3615,14 @@
       <c r="J69" s="1">
         <v>1</v>
       </c>
-      <c r="K69" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="3:11">
+      <c r="K69" s="2">
+        <v>1</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:12">
       <c r="C70" s="1">
         <v>132</v>
       </c>
@@ -3432,7 +3630,7 @@
         <v>180033</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F70" s="1">
         <v>1</v>
@@ -3449,11 +3647,14 @@
       <c r="J70" s="1">
         <v>1</v>
       </c>
-      <c r="K70" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="71" customHeight="1" spans="3:11">
+      <c r="K70" s="2">
+        <v>1</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:12">
       <c r="C71" s="1">
         <v>133</v>
       </c>
@@ -3461,7 +3662,7 @@
         <v>180034</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F71" s="1">
         <v>2</v>
@@ -3478,11 +3679,14 @@
       <c r="J71" s="1">
         <v>1</v>
       </c>
-      <c r="K71" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="72" customHeight="1" spans="3:11">
+      <c r="K71" s="2">
+        <v>1</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:12">
       <c r="C72" s="1">
         <v>134</v>
       </c>
@@ -3490,7 +3694,7 @@
         <v>180035</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F72" s="1">
         <v>1</v>
@@ -3507,11 +3711,14 @@
       <c r="J72" s="1">
         <v>1</v>
       </c>
-      <c r="K72" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="73" customHeight="1" spans="3:11">
+      <c r="K72" s="2">
+        <v>1</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:12">
       <c r="C73" s="1">
         <v>135</v>
       </c>
@@ -3519,7 +3726,7 @@
         <v>180036</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F73" s="1">
         <v>1</v>
@@ -3536,11 +3743,14 @@
       <c r="J73" s="1">
         <v>1</v>
       </c>
-      <c r="K73" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="74" customHeight="1" spans="3:11">
+      <c r="K73" s="2">
+        <v>1</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:12">
       <c r="C74" s="1">
         <v>136</v>
       </c>
@@ -3548,7 +3758,7 @@
         <v>180037</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F74" s="1">
         <v>1</v>
@@ -3565,11 +3775,14 @@
       <c r="J74" s="1">
         <v>1</v>
       </c>
-      <c r="K74" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="75" customHeight="1" spans="3:11">
+      <c r="K74" s="2">
+        <v>1</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:12">
       <c r="C75" s="1">
         <v>137</v>
       </c>
@@ -3577,7 +3790,7 @@
         <v>180038</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F75" s="1">
         <v>4</v>
@@ -3594,11 +3807,14 @@
       <c r="J75" s="1">
         <v>1</v>
       </c>
-      <c r="K75" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="76" customHeight="1" spans="3:11">
+      <c r="K75" s="2">
+        <v>1</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:12">
       <c r="C76" s="1">
         <v>138</v>
       </c>
@@ -3606,7 +3822,7 @@
         <v>180039</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F76" s="1">
         <v>3</v>
@@ -3623,19 +3839,22 @@
       <c r="J76" s="1">
         <v>1</v>
       </c>
-      <c r="K76" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="78" customHeight="1" spans="3:11">
+      <c r="K76" s="2">
+        <v>1</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:12">
       <c r="C78" s="1">
         <v>201</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F78" s="1">
         <v>5</v>
@@ -3652,19 +3871,22 @@
       <c r="J78" s="1">
         <v>2</v>
       </c>
-      <c r="K78" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="79" customHeight="1" spans="3:11">
+      <c r="K78" s="2">
+        <v>1</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:12">
       <c r="C79" s="1">
         <v>202</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F79" s="1">
         <v>5</v>
@@ -3681,19 +3903,22 @@
       <c r="J79" s="1">
         <v>2</v>
       </c>
-      <c r="K79" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="80" customHeight="1" spans="3:11">
+      <c r="K79" s="2">
+        <v>1</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:12">
       <c r="C80" s="1">
         <v>203</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F80" s="1">
         <v>15</v>
@@ -3710,22 +3935,25 @@
       <c r="J80" s="1">
         <v>2</v>
       </c>
-      <c r="K80" s="1" t="s">
-        <v>44</v>
+      <c r="K80" s="2">
+        <v>1</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="4:4">
       <c r="D81" s="8"/>
     </row>
-    <row r="82" customHeight="1" spans="3:11">
+    <row r="82" customHeight="1" spans="3:12">
       <c r="C82" s="1">
         <v>301</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F82" s="1">
         <v>20</v>
@@ -3742,19 +3970,22 @@
       <c r="J82" s="1">
         <v>1</v>
       </c>
-      <c r="K82" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="83" customHeight="1" spans="3:11">
+      <c r="K82" s="2">
+        <v>1</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:12">
       <c r="C83" s="1">
         <v>302</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F83" s="1">
         <v>15</v>
@@ -3771,19 +4002,22 @@
       <c r="J83" s="1">
         <v>1</v>
       </c>
-      <c r="K83" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="84" customHeight="1" spans="3:11">
+      <c r="K83" s="2">
+        <v>1</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:12">
       <c r="C84" s="1">
         <v>303</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F84" s="1">
         <v>10</v>
@@ -3800,19 +4034,22 @@
       <c r="J84" s="1">
         <v>1</v>
       </c>
-      <c r="K84" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="85" customHeight="1" spans="3:11">
+      <c r="K84" s="2">
+        <v>1</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:12">
       <c r="C85" s="1">
         <v>304</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F85" s="1">
         <v>8</v>
@@ -3829,19 +4066,22 @@
       <c r="J85" s="1">
         <v>1</v>
       </c>
-      <c r="K85" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="86" customHeight="1" spans="3:11">
+      <c r="K85" s="2">
+        <v>1</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:12">
       <c r="C86" s="1">
         <v>305</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F86" s="1">
         <v>15</v>
@@ -3858,19 +4098,22 @@
       <c r="J86" s="1">
         <v>1</v>
       </c>
-      <c r="K86" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="87" customHeight="1" spans="3:11">
+      <c r="K86" s="2">
+        <v>1</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:12">
       <c r="C87" s="1">
         <v>306</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F87" s="1">
         <v>7</v>
@@ -3887,19 +4130,22 @@
       <c r="J87" s="1">
         <v>1</v>
       </c>
-      <c r="K87" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="88" customHeight="1" spans="3:11">
+      <c r="K87" s="2">
+        <v>1</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="3:12">
       <c r="C88" s="1">
         <v>307</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F88" s="1">
         <v>3</v>
@@ -3916,19 +4162,22 @@
       <c r="J88" s="1">
         <v>1</v>
       </c>
-      <c r="K88" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="90" customHeight="1" spans="3:10">
+      <c r="K88" s="2">
+        <v>1</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="3:11">
       <c r="C90" s="1">
         <v>311</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F90" s="1">
         <v>20</v>
@@ -3945,16 +4194,19 @@
       <c r="J90" s="1">
         <v>33</v>
       </c>
-    </row>
-    <row r="91" customHeight="1" spans="3:10">
+      <c r="K90" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="3:11">
       <c r="C91" s="1">
         <v>312</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F91" s="1">
         <v>10</v>
@@ -3971,16 +4223,19 @@
       <c r="J91" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="92" customHeight="1" spans="3:10">
+      <c r="K91" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="3:11">
       <c r="C92" s="1">
         <v>313</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F92" s="1">
         <v>5</v>
@@ -3997,16 +4252,19 @@
       <c r="J92" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="93" customHeight="1" spans="3:10">
+      <c r="K92" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="3:11">
       <c r="C93" s="1">
         <v>314</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F93" s="1">
         <v>2</v>
@@ -4022,6 +4280,9 @@
       </c>
       <c r="J93" s="1">
         <v>5</v>
+      </c>
+      <c r="K93" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="139">
   <si>
     <t>#</t>
   </si>
@@ -675,12 +675,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1474,7 +1474,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M113"/>
+  <dimension ref="C1:M114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -4364,31 +4364,31 @@
         <v>11004</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="E107" s="7" t="s">
-        <v>119</v>
+        <v>116</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="F107" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G107" s="1">
-        <v>101</v>
+        <v>4001</v>
       </c>
       <c r="H107" s="1">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="I107" s="1">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="J107" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K107" s="2">
         <v>1</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:12">
@@ -4396,19 +4396,19 @@
         <v>11005</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F108" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G108" s="1">
-        <v>501</v>
+        <v>101</v>
       </c>
       <c r="H108" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="I108" s="1">
         <v>10</v>
@@ -4420,7 +4420,7 @@
         <v>1</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:12">
@@ -4428,23 +4428,23 @@
         <v>11006</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F109" s="1">
+        <v>15</v>
+      </c>
+      <c r="G109" s="1">
+        <v>501</v>
+      </c>
+      <c r="H109" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I109" s="1">
         <v>10</v>
       </c>
-      <c r="G109" s="1">
-        <v>1001</v>
-      </c>
-      <c r="H109" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I109" s="1">
-        <v>20</v>
-      </c>
       <c r="J109" s="1">
         <v>1</v>
       </c>
@@ -4452,7 +4452,7 @@
         <v>1</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:12">
@@ -4460,19 +4460,19 @@
         <v>11007</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F110" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G110" s="1">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H110" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I110" s="1">
         <v>20</v>
@@ -4484,7 +4484,7 @@
         <v>1</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:12">
@@ -4492,22 +4492,22 @@
         <v>11008</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F111" s="1">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G111" s="1">
-        <v>2001</v>
+        <v>1501</v>
       </c>
       <c r="H111" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I111" s="1">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="J111" s="1">
         <v>1</v>
@@ -4516,7 +4516,7 @@
         <v>1</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:12">
@@ -4524,19 +4524,19 @@
         <v>11009</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F112" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G112" s="1">
-        <v>2501</v>
+        <v>2001</v>
       </c>
       <c r="H112" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I112" s="1">
         <v>52</v>
@@ -4548,7 +4548,7 @@
         <v>1</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:12">
@@ -4556,19 +4556,19 @@
         <v>11010</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F113" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G113" s="1">
-        <v>3001</v>
+        <v>2501</v>
       </c>
       <c r="H113" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="I113" s="1">
         <v>52</v>
@@ -4580,6 +4580,38 @@
         <v>1</v>
       </c>
       <c r="L113" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="3:12">
+      <c r="C114" s="1">
+        <v>11011</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="E114" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F114" s="1">
+        <v>3</v>
+      </c>
+      <c r="G114" s="1">
+        <v>3001</v>
+      </c>
+      <c r="H114" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I114" s="1">
+        <v>52</v>
+      </c>
+      <c r="J114" s="1">
+        <v>1</v>
+      </c>
+      <c r="K114" s="2">
+        <v>1</v>
+      </c>
+      <c r="L114" s="1" t="s">
         <v>138</v>
       </c>
     </row>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="140">
   <si>
     <t>#</t>
   </si>
@@ -174,6 +174,57 @@
     <t>道士之魂</t>
   </si>
   <si>
+    <t>1007</t>
+  </si>
+  <si>
+    <t>红装精华</t>
+  </si>
+  <si>
+    <t>打完500层，3天一个</t>
+  </si>
+  <si>
+    <t>220013</t>
+  </si>
+  <si>
+    <t>高级书页</t>
+  </si>
+  <si>
+    <t>220038</t>
+  </si>
+  <si>
+    <t>天赋秘籍</t>
+  </si>
+  <si>
+    <t>220041</t>
+  </si>
+  <si>
+    <t>改造石</t>
+  </si>
+  <si>
+    <t>1010</t>
+  </si>
+  <si>
+    <t>金色精华</t>
+  </si>
+  <si>
+    <t>1011</t>
+  </si>
+  <si>
+    <t>暗金精华</t>
+  </si>
+  <si>
+    <t>1012</t>
+  </si>
+  <si>
+    <t>开孔石</t>
+  </si>
+  <si>
+    <t>1013</t>
+  </si>
+  <si>
+    <t>时装精华</t>
+  </si>
+  <si>
     <t>220036</t>
   </si>
   <si>
@@ -189,55 +240,7 @@
     <t>等级丹*15</t>
   </si>
   <si>
-    <t>1007</t>
-  </si>
-  <si>
-    <t>红装精华</t>
-  </si>
-  <si>
-    <t>打完500层，3天一个</t>
-  </si>
-  <si>
-    <t>220013</t>
-  </si>
-  <si>
-    <t>高级书页</t>
-  </si>
-  <si>
-    <t>220038</t>
-  </si>
-  <si>
-    <t>天赋秘籍</t>
-  </si>
-  <si>
-    <t>220041</t>
-  </si>
-  <si>
-    <t>改造石</t>
-  </si>
-  <si>
-    <t>1010</t>
-  </si>
-  <si>
-    <t>金色精华</t>
-  </si>
-  <si>
-    <t>1011</t>
-  </si>
-  <si>
-    <t>暗金精华</t>
-  </si>
-  <si>
-    <t>1012</t>
-  </si>
-  <si>
-    <t>开孔石</t>
-  </si>
-  <si>
-    <t>1013</t>
-  </si>
-  <si>
-    <t>时装精华</t>
+    <t>等级丹*20</t>
   </si>
   <si>
     <t>220002</t>
@@ -675,12 +678,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1474,7 +1477,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M114"/>
+  <dimension ref="C1:M115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1952,19 +1955,19 @@
         <v>38</v>
       </c>
       <c r="F17" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G17" s="2">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H17" s="2">
-        <v>1500</v>
+        <v>10000</v>
       </c>
       <c r="I17" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J17" s="2">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="K17" s="2">
         <v>1</v>
@@ -1984,10 +1987,10 @@
         <v>41</v>
       </c>
       <c r="F18" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G18" s="2">
-        <v>1501</v>
+        <v>1</v>
       </c>
       <c r="H18" s="2">
         <v>10000</v>
@@ -1996,315 +1999,315 @@
         <v>1</v>
       </c>
       <c r="J18" s="2">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K18" s="2">
         <v>1</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:12">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="20" customHeight="1" spans="3:11">
       <c r="C19" s="2">
         <v>14</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="2">
-        <v>10</v>
+      <c r="F19" s="1">
+        <v>5</v>
       </c>
       <c r="G19" s="2">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H19" s="2">
         <v>10000</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I19" s="1">
+        <v>30</v>
+      </c>
+      <c r="J19" s="1">
         <v>3</v>
       </c>
-      <c r="J19" s="2">
-        <v>10</v>
-      </c>
       <c r="K19" s="2">
         <v>1</v>
       </c>
-      <c r="L19" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:12">
+    </row>
+    <row r="20" s="1" customFormat="1" ht="20" customHeight="1" spans="3:11">
       <c r="C20" s="2">
         <v>15</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" s="2">
-        <v>10</v>
+      <c r="F20" s="1">
+        <v>12</v>
       </c>
       <c r="G20" s="2">
-        <v>1</v>
+        <v>1500</v>
       </c>
       <c r="H20" s="2">
         <v>10000</v>
       </c>
-      <c r="I20" s="2">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2">
+      <c r="I20" s="1">
+        <v>3</v>
+      </c>
+      <c r="J20" s="1">
         <v>50</v>
       </c>
       <c r="K20" s="2">
         <v>1</v>
       </c>
-      <c r="L20" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="20" customHeight="1" spans="3:11">
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C21" s="2">
         <v>16</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="1">
+      <c r="F21" s="2">
         <v>5</v>
       </c>
       <c r="G21" s="2">
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="H21" s="2">
         <v>10000</v>
       </c>
-      <c r="I21" s="1">
-        <v>30</v>
-      </c>
-      <c r="J21" s="1">
-        <v>3</v>
+      <c r="I21" s="2">
+        <v>1</v>
+      </c>
+      <c r="J21" s="2">
+        <v>10</v>
       </c>
       <c r="K21" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="20" customHeight="1" spans="3:11">
+      <c r="L21" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C22" s="2">
         <v>17</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F22" s="1">
-        <v>12</v>
+      <c r="F22" s="2">
+        <v>5</v>
       </c>
       <c r="G22" s="2">
-        <v>1500</v>
+        <v>3200</v>
       </c>
       <c r="H22" s="2">
         <v>10000</v>
       </c>
-      <c r="I22" s="1">
-        <v>3</v>
-      </c>
-      <c r="J22" s="1">
-        <v>50</v>
+      <c r="I22" s="2">
+        <v>1</v>
+      </c>
+      <c r="J22" s="2">
+        <v>10</v>
       </c>
       <c r="K22" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="L22" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:11">
       <c r="C23" s="2">
         <v>18</v>
       </c>
       <c r="D23" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="F23" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G23" s="2">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="H23" s="2">
         <v>10000</v>
       </c>
       <c r="I23" s="2">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="J23" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K23" s="2">
         <v>1</v>
       </c>
-      <c r="L23" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:12">
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:11">
       <c r="C24" s="2">
         <v>19</v>
       </c>
       <c r="D24" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="F24" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G24" s="2">
-        <v>3200</v>
+        <v>1007</v>
       </c>
       <c r="H24" s="2">
         <v>10000</v>
       </c>
       <c r="I24" s="2">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="J24" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K24" s="2">
         <v>1</v>
       </c>
-      <c r="L24" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C25" s="2">
-        <v>20</v>
-      </c>
-      <c r="D25" s="8" t="s">
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="4:4">
+      <c r="D25" s="4"/>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C26" s="2">
+        <v>151</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F26" s="2">
+        <v>12</v>
+      </c>
+      <c r="G26" s="2">
+        <v>300</v>
+      </c>
+      <c r="H26" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I26" s="2">
+        <v>1</v>
+      </c>
+      <c r="J26" s="2">
+        <v>25</v>
+      </c>
+      <c r="K26" s="2">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F25" s="2">
-        <v>1</v>
-      </c>
-      <c r="G25" s="2">
-        <v>1500</v>
-      </c>
-      <c r="H25" s="2">
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C27" s="2">
+        <v>152</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F27" s="2">
+        <v>6</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1501</v>
+      </c>
+      <c r="H27" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I27" s="2">
+        <v>1</v>
+      </c>
+      <c r="J27" s="2">
+        <v>25</v>
+      </c>
+      <c r="K27" s="2">
+        <v>1</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C28" s="2">
+        <v>153</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="2">
+        <v>3</v>
+      </c>
+      <c r="G28" s="2">
+        <v>4001</v>
+      </c>
+      <c r="H28" s="2">
         <v>10000</v>
       </c>
-      <c r="I25" s="2">
-        <v>59</v>
-      </c>
-      <c r="J25" s="2">
-        <v>1</v>
-      </c>
-      <c r="K25" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C26" s="2">
-        <v>21</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F26" s="2">
-        <v>1</v>
-      </c>
-      <c r="G26" s="2">
-        <v>1007</v>
-      </c>
-      <c r="H26" s="2">
-        <v>10000</v>
-      </c>
-      <c r="I26" s="2">
-        <v>53</v>
-      </c>
-      <c r="J26" s="2">
+      <c r="I28" s="2">
+        <v>1</v>
+      </c>
+      <c r="J28" s="2">
+        <v>15</v>
+      </c>
+      <c r="K28" s="2">
         <v>2</v>
       </c>
-      <c r="K26" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D28" s="4"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C29" s="1">
-        <v>100</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="1" t="s">
+      <c r="L28" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="4:4">
+      <c r="D29" s="4"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C30" s="1">
+        <v>100</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F29" s="1">
-        <v>50</v>
-      </c>
-      <c r="G29" s="1">
-        <v>1</v>
-      </c>
-      <c r="H29" s="1">
-        <v>300</v>
-      </c>
-      <c r="I29" s="1">
-        <v>1</v>
-      </c>
-      <c r="J29" s="1">
-        <v>10000</v>
-      </c>
-      <c r="K29" s="2">
-        <v>1</v>
-      </c>
-      <c r="L29" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
-      <c r="C30" s="1">
-        <v>101</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="F30" s="1">
         <v>50</v>
       </c>
       <c r="G30" s="1">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="H30" s="1">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I30" s="1">
         <v>1</v>
@@ -2313,30 +2316,30 @@
         <v>10000</v>
       </c>
       <c r="K30" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L30" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C31" s="1">
+        <v>101</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:12">
-      <c r="C31" s="1">
-        <v>102</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="F31" s="1">
         <v>50</v>
       </c>
       <c r="G31" s="1">
-        <v>601</v>
+        <v>301</v>
       </c>
       <c r="H31" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="I31" s="1">
         <v>1</v>
@@ -2345,30 +2348,30 @@
         <v>10000</v>
       </c>
       <c r="K31" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:12">
       <c r="C32" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F32" s="1">
         <v>50</v>
       </c>
       <c r="G32" s="1">
-        <v>1001</v>
+        <v>601</v>
       </c>
       <c r="H32" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I32" s="1">
         <v>1</v>
@@ -2377,62 +2380,62 @@
         <v>10000</v>
       </c>
       <c r="K32" s="2">
+        <v>4</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:12">
+      <c r="C33" s="1">
+        <v>103</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F33" s="1">
+        <v>50</v>
+      </c>
+      <c r="G33" s="1">
+        <v>1001</v>
+      </c>
+      <c r="H33" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I33" s="1">
+        <v>1</v>
+      </c>
+      <c r="J33" s="1">
+        <v>10000</v>
+      </c>
+      <c r="K33" s="2">
         <v>10</v>
       </c>
-      <c r="L32" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C33" s="1">
-        <v>104</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F33" s="2">
-        <v>50</v>
-      </c>
-      <c r="G33" s="2">
-        <v>1501</v>
-      </c>
-      <c r="H33" s="2">
-        <v>3500</v>
-      </c>
-      <c r="I33" s="2">
-        <v>1</v>
-      </c>
-      <c r="J33" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K33" s="2">
-        <v>20</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>61</v>
+      <c r="L33" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C34" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F34" s="2">
         <v>50</v>
       </c>
       <c r="G34" s="2">
-        <v>3501</v>
+        <v>1501</v>
       </c>
       <c r="H34" s="2">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="I34" s="2">
         <v>1</v>
@@ -2441,65 +2444,65 @@
         <v>10000</v>
       </c>
       <c r="K34" s="2">
+        <v>20</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C35" s="1">
+        <v>105</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35" s="2">
+        <v>50</v>
+      </c>
+      <c r="G35" s="2">
+        <v>3501</v>
+      </c>
+      <c r="H35" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I35" s="2">
+        <v>1</v>
+      </c>
+      <c r="J35" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K35" s="2">
         <v>40</v>
       </c>
-      <c r="L34" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D35" s="4"/>
-    </row>
-    <row r="36" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
-      <c r="C36" s="2">
+      <c r="L35" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="4:4">
+      <c r="D36" s="4"/>
+    </row>
+    <row r="37" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C37" s="2">
         <v>200</v>
       </c>
-      <c r="D36" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E36" s="2" t="s">
+      <c r="D37" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="F36" s="2">
-        <v>50</v>
-      </c>
-      <c r="G36" s="2">
-        <v>1</v>
-      </c>
-      <c r="H36" s="2">
-        <v>300</v>
-      </c>
-      <c r="I36" s="2">
-        <v>1</v>
-      </c>
-      <c r="J36" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K36" s="2">
-        <v>1</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C37" s="2">
-        <v>201</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>62</v>
-      </c>
       <c r="E37" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F37" s="2">
         <v>50</v>
       </c>
       <c r="G37" s="2">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="H37" s="2">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I37" s="2">
         <v>1</v>
@@ -2508,30 +2511,30 @@
         <v>10000</v>
       </c>
       <c r="K37" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C38" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F38" s="2">
         <v>50</v>
       </c>
       <c r="G38" s="2">
-        <v>601</v>
+        <v>301</v>
       </c>
       <c r="H38" s="2">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="I38" s="2">
         <v>1</v>
@@ -2540,30 +2543,30 @@
         <v>10000</v>
       </c>
       <c r="K38" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C39" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F39" s="2">
         <v>50</v>
       </c>
       <c r="G39" s="2">
-        <v>1001</v>
+        <v>601</v>
       </c>
       <c r="H39" s="2">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I39" s="2">
         <v>1</v>
@@ -2572,30 +2575,30 @@
         <v>10000</v>
       </c>
       <c r="K39" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="40" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C40" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F40" s="2">
         <v>50</v>
       </c>
       <c r="G40" s="2">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H40" s="2">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="I40" s="2">
         <v>1</v>
@@ -2604,30 +2607,30 @@
         <v>10000</v>
       </c>
       <c r="K40" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
       <c r="C41" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F41" s="2">
         <v>50</v>
       </c>
       <c r="G41" s="2">
-        <v>3501</v>
+        <v>1501</v>
       </c>
       <c r="H41" s="2">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="I41" s="2">
         <v>1</v>
@@ -2636,65 +2639,65 @@
         <v>10000</v>
       </c>
       <c r="K41" s="2">
+        <v>20</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C42" s="2">
+        <v>205</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F42" s="2">
+        <v>50</v>
+      </c>
+      <c r="G42" s="2">
+        <v>3501</v>
+      </c>
+      <c r="H42" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I42" s="2">
+        <v>1</v>
+      </c>
+      <c r="J42" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K42" s="2">
         <v>40</v>
       </c>
-      <c r="L41" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" s="2" customFormat="1" ht="20" customHeight="1" spans="4:4">
-      <c r="D42" s="4"/>
-    </row>
-    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C43" s="2">
-        <v>300</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F43" s="2">
-        <v>10</v>
-      </c>
-      <c r="G43" s="2">
-        <v>1</v>
-      </c>
-      <c r="H43" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I43" s="2">
-        <v>1</v>
-      </c>
-      <c r="J43" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K43" s="2">
-        <v>1</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="L42" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" ht="20" customHeight="1" spans="4:4">
+      <c r="D43" s="4"/>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C44" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F44" s="2">
         <v>10</v>
       </c>
       <c r="G44" s="2">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="H44" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I44" s="2">
         <v>1</v>
@@ -2703,7 +2706,7 @@
         <v>10000</v>
       </c>
       <c r="K44" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>21</v>
@@ -2711,22 +2714,22 @@
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C45" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F45" s="2">
         <v>10</v>
       </c>
       <c r="G45" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H45" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I45" s="2">
         <v>1</v>
@@ -2735,63 +2738,63 @@
         <v>10000</v>
       </c>
       <c r="K45" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="46" s="2" customFormat="1" customHeight="1"/>
-    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C47" s="2">
-        <v>400</v>
-      </c>
-      <c r="D47" s="10" t="s">
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C46" s="2">
+        <v>302</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F47" s="2">
+      <c r="F46" s="2">
         <v>10</v>
       </c>
-      <c r="G47" s="2">
-        <v>50</v>
-      </c>
-      <c r="H47" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I47" s="2">
-        <v>1</v>
-      </c>
-      <c r="J47" s="2">
+      <c r="G46" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H46" s="2">
         <v>10000</v>
       </c>
-      <c r="K47" s="2">
-        <v>1</v>
-      </c>
-      <c r="L47" s="2" t="s">
+      <c r="I46" s="2">
+        <v>1</v>
+      </c>
+      <c r="J46" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K46" s="2">
+        <v>3</v>
+      </c>
+      <c r="L46" s="2" t="s">
         <v>21</v>
       </c>
     </row>
+    <row r="47" s="2" customFormat="1" customHeight="1"/>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C48" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F48" s="2">
         <v>10</v>
       </c>
       <c r="G48" s="2">
-        <v>1001</v>
+        <v>50</v>
       </c>
       <c r="H48" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I48" s="2">
         <v>1</v>
@@ -2800,7 +2803,7 @@
         <v>10000</v>
       </c>
       <c r="K48" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>21</v>
@@ -2808,22 +2811,22 @@
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C49" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F49" s="2">
         <v>10</v>
       </c>
       <c r="G49" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H49" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I49" s="2">
         <v>1</v>
@@ -2832,63 +2835,63 @@
         <v>10000</v>
       </c>
       <c r="K49" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="50" s="2" customFormat="1" customHeight="1"/>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C51" s="2">
-        <v>500</v>
-      </c>
-      <c r="D51" s="10" t="s">
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C50" s="2">
+        <v>402</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F51" s="2">
-        <v>4</v>
-      </c>
-      <c r="G51" s="2">
-        <v>150</v>
-      </c>
-      <c r="H51" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I51" s="2">
-        <v>1</v>
-      </c>
-      <c r="J51" s="2">
-        <v>20</v>
-      </c>
-      <c r="K51" s="2">
-        <v>1</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
+      <c r="F50" s="2">
+        <v>10</v>
+      </c>
+      <c r="G50" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H50" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I50" s="2">
+        <v>1</v>
+      </c>
+      <c r="J50" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K50" s="2">
+        <v>3</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1"/>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C52" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F52" s="2">
         <v>4</v>
       </c>
       <c r="G52" s="2">
-        <v>1001</v>
+        <v>150</v>
       </c>
       <c r="H52" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I52" s="2">
         <v>1</v>
@@ -2897,30 +2900,30 @@
         <v>20</v>
       </c>
       <c r="K52" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C53" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F53" s="2">
         <v>4</v>
       </c>
       <c r="G53" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H53" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I53" s="2">
         <v>1</v>
@@ -2929,63 +2932,63 @@
         <v>20</v>
       </c>
       <c r="K53" s="2">
+        <v>2</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C54" s="2">
+        <v>502</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F54" s="2">
+        <v>4</v>
+      </c>
+      <c r="G54" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H54" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I54" s="2">
+        <v>1</v>
+      </c>
+      <c r="J54" s="2">
+        <v>20</v>
+      </c>
+      <c r="K54" s="2">
         <v>3</v>
       </c>
-      <c r="L53" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="54" s="2" customFormat="1" customHeight="1"/>
-    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C55" s="2">
-        <v>600</v>
-      </c>
-      <c r="D55" s="2">
-        <v>3001</v>
-      </c>
-      <c r="E55" s="2" t="s">
+      <c r="L54" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F55" s="2">
-        <v>10</v>
-      </c>
-      <c r="G55" s="2">
-        <v>1</v>
-      </c>
-      <c r="H55" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I55" s="2">
-        <v>1</v>
-      </c>
-      <c r="J55" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K55" s="2">
-        <v>1</v>
-      </c>
-      <c r="L55" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
+    </row>
+    <row r="55" s="2" customFormat="1" customHeight="1"/>
     <row r="56" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C56" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D56" s="2">
         <v>3001</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F56" s="2">
         <v>10</v>
       </c>
       <c r="G56" s="2">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="H56" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I56" s="2">
         <v>1</v>
@@ -2994,7 +2997,7 @@
         <v>10000</v>
       </c>
       <c r="K56" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>21</v>
@@ -3002,22 +3005,22 @@
     </row>
     <row r="57" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C57" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D57" s="2">
         <v>3001</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F57" s="2">
         <v>10</v>
       </c>
       <c r="G57" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H57" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I57" s="2">
         <v>1</v>
@@ -3026,63 +3029,63 @@
         <v>10000</v>
       </c>
       <c r="K57" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="58" s="2" customFormat="1" customHeight="1"/>
-    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C59" s="2">
-        <v>700</v>
-      </c>
-      <c r="D59" s="2">
-        <v>3002</v>
-      </c>
-      <c r="E59" s="2" t="s">
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C58" s="2">
+        <v>602</v>
+      </c>
+      <c r="D58" s="2">
+        <v>3001</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F58" s="2">
         <v>10</v>
       </c>
-      <c r="G59" s="2">
-        <v>200</v>
-      </c>
-      <c r="H59" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I59" s="2">
-        <v>1</v>
-      </c>
-      <c r="J59" s="2">
+      <c r="G58" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H58" s="2">
         <v>10000</v>
       </c>
-      <c r="K59" s="2">
-        <v>1</v>
-      </c>
-      <c r="L59" s="2" t="s">
+      <c r="I58" s="2">
+        <v>1</v>
+      </c>
+      <c r="J58" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K58" s="2">
+        <v>3</v>
+      </c>
+      <c r="L58" s="2" t="s">
         <v>21</v>
       </c>
     </row>
+    <row r="59" s="2" customFormat="1" customHeight="1"/>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C60" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D60" s="2">
         <v>3002</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F60" s="2">
         <v>10</v>
       </c>
       <c r="G60" s="2">
-        <v>1001</v>
+        <v>200</v>
       </c>
       <c r="H60" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I60" s="2">
         <v>1</v>
@@ -3091,7 +3094,7 @@
         <v>10000</v>
       </c>
       <c r="K60" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>21</v>
@@ -3099,22 +3102,22 @@
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C61" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D61" s="2">
         <v>3002</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F61" s="2">
         <v>10</v>
       </c>
       <c r="G61" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H61" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I61" s="2">
         <v>1</v>
@@ -3123,53 +3126,53 @@
         <v>10000</v>
       </c>
       <c r="K61" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="11:11">
-      <c r="K62" s="2"/>
-    </row>
-    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C63" s="2">
-        <v>800</v>
-      </c>
-      <c r="D63" s="2">
-        <v>3003</v>
-      </c>
-      <c r="E63" s="2" t="s">
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C62" s="2">
+        <v>702</v>
+      </c>
+      <c r="D62" s="2">
+        <v>3002</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F63" s="2">
-        <v>2</v>
-      </c>
-      <c r="G63" s="2">
-        <v>4001</v>
-      </c>
-      <c r="H63" s="2">
-        <v>5000</v>
-      </c>
-      <c r="I63" s="2">
-        <v>7</v>
-      </c>
-      <c r="J63" s="2">
-        <v>13</v>
-      </c>
-      <c r="K63" s="2">
-        <v>5</v>
-      </c>
-      <c r="L63" s="2" t="s">
+      <c r="F62" s="2">
+        <v>10</v>
+      </c>
+      <c r="G62" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H62" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I62" s="2">
+        <v>1</v>
+      </c>
+      <c r="J62" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K62" s="2">
+        <v>3</v>
+      </c>
+      <c r="L62" s="2" t="s">
         <v>21</v>
       </c>
+    </row>
+    <row r="63" customHeight="1" spans="11:11">
+      <c r="K63" s="2"/>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C64" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D64" s="2">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>74</v>
@@ -3184,59 +3187,62 @@
         <v>5000</v>
       </c>
       <c r="I64" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J64" s="2">
+        <v>13</v>
+      </c>
+      <c r="K64" s="2">
         <v>5</v>
-      </c>
-      <c r="K64" s="2">
-        <v>1</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="3:11">
-      <c r="C66" s="1">
-        <v>901</v>
-      </c>
-      <c r="D66" s="11" t="s">
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C65" s="2">
+        <v>801</v>
+      </c>
+      <c r="D65" s="2">
+        <v>3004</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F66" s="1">
-        <v>20</v>
-      </c>
-      <c r="G66" s="1">
-        <v>3001</v>
-      </c>
-      <c r="H66" s="1">
-        <v>4000</v>
-      </c>
-      <c r="I66" s="1">
-        <v>3</v>
-      </c>
-      <c r="J66" s="1">
-        <v>30</v>
-      </c>
-      <c r="K66" s="2">
-        <v>1</v>
+      <c r="F65" s="2">
+        <v>2</v>
+      </c>
+      <c r="G65" s="2">
+        <v>4001</v>
+      </c>
+      <c r="H65" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I65" s="2">
+        <v>9</v>
+      </c>
+      <c r="J65" s="2">
+        <v>5</v>
+      </c>
+      <c r="K65" s="2">
+        <v>1</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
       <c r="C67" s="1">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D67" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="F67" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G67" s="1">
         <v>3001</v>
@@ -3248,7 +3254,7 @@
         <v>3</v>
       </c>
       <c r="J67" s="1">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="K67" s="2">
         <v>1</v>
@@ -3256,16 +3262,16 @@
     </row>
     <row r="68" customHeight="1" spans="3:11">
       <c r="C68" s="1">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D68" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="F68" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G68" s="1">
         <v>3001</v>
@@ -3277,7 +3283,7 @@
         <v>3</v>
       </c>
       <c r="J68" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K68" s="2">
         <v>1</v>
@@ -3285,28 +3291,28 @@
     </row>
     <row r="69" customHeight="1" spans="3:11">
       <c r="C69" s="1">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="D69" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="F69" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G69" s="1">
-        <v>3501</v>
+        <v>3001</v>
       </c>
       <c r="H69" s="1">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="I69" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J69" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K69" s="2">
         <v>1</v>
@@ -3314,45 +3320,45 @@
     </row>
     <row r="70" customHeight="1" spans="3:11">
       <c r="C70" s="1">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F70" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G70" s="1">
-        <v>4001</v>
+        <v>3501</v>
       </c>
       <c r="H70" s="1">
         <v>5000</v>
       </c>
       <c r="I70" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J70" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K70" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
       <c r="C71" s="1">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D71" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="F71" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G71" s="1">
         <v>4001</v>
@@ -3364,7 +3370,7 @@
         <v>3</v>
       </c>
       <c r="J71" s="1">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K71" s="2">
         <v>2</v>
@@ -3372,16 +3378,16 @@
     </row>
     <row r="72" customHeight="1" spans="3:11">
       <c r="C72" s="1">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D72" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E72" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="F72" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G72" s="1">
         <v>4001</v>
@@ -3393,56 +3399,53 @@
         <v>3</v>
       </c>
       <c r="J72" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K72" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="3:12">
-      <c r="C75" s="1">
-        <v>10001</v>
-      </c>
-      <c r="D75" s="6">
-        <v>180001</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F75" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G75" s="1">
-        <v>100</v>
-      </c>
-      <c r="H75" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I75" s="1">
-        <v>100</v>
-      </c>
-      <c r="J75" s="1">
-        <v>1</v>
-      </c>
-      <c r="K75" s="2">
-        <v>1</v>
-      </c>
-      <c r="L75" s="1" t="s">
-        <v>84</v>
+    <row r="73" customHeight="1" spans="3:11">
+      <c r="C73" s="1">
+        <v>907</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F73" s="1">
+        <v>3</v>
+      </c>
+      <c r="G73" s="1">
+        <v>4001</v>
+      </c>
+      <c r="H73" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I73" s="1">
+        <v>3</v>
+      </c>
+      <c r="J73" s="1">
+        <v>2</v>
+      </c>
+      <c r="K73" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:12">
       <c r="C76" s="1">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="D76" s="6">
-        <v>180002</v>
+        <v>180001</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F76" s="1">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G76" s="1">
         <v>100</v>
@@ -3460,21 +3463,21 @@
         <v>1</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:12">
       <c r="C77" s="1">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="D77" s="6">
-        <v>180003</v>
+        <v>180002</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>86</v>
       </c>
       <c r="F77" s="1">
-        <v>150000</v>
+        <v>4000</v>
       </c>
       <c r="G77" s="1">
         <v>100</v>
@@ -3486,27 +3489,27 @@
         <v>100</v>
       </c>
       <c r="J77" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K77" s="2">
         <v>1</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:12">
       <c r="C78" s="1">
-        <v>10004</v>
+        <v>10003</v>
       </c>
       <c r="D78" s="6">
-        <v>180004</v>
+        <v>180003</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>87</v>
       </c>
       <c r="F78" s="1">
-        <v>8000</v>
+        <v>150000</v>
       </c>
       <c r="G78" s="1">
         <v>100</v>
@@ -3518,27 +3521,27 @@
         <v>100</v>
       </c>
       <c r="J78" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K78" s="2">
         <v>1</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:12">
       <c r="C79" s="1">
-        <v>10005</v>
+        <v>10004</v>
       </c>
       <c r="D79" s="6">
-        <v>180005</v>
+        <v>180004</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>88</v>
       </c>
       <c r="F79" s="1">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="G79" s="1">
         <v>100</v>
@@ -3556,21 +3559,21 @@
         <v>1</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:12">
       <c r="C80" s="1">
-        <v>10006</v>
+        <v>10005</v>
       </c>
       <c r="D80" s="6">
-        <v>180006</v>
+        <v>180005</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>89</v>
       </c>
       <c r="F80" s="1">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="G80" s="1">
         <v>100</v>
@@ -3582,27 +3585,27 @@
         <v>100</v>
       </c>
       <c r="J80" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K80" s="2">
         <v>1</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:12">
       <c r="C81" s="1">
-        <v>10007</v>
+        <v>10006</v>
       </c>
       <c r="D81" s="6">
-        <v>180007</v>
+        <v>180006</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>90</v>
       </c>
       <c r="F81" s="1">
-        <v>2000</v>
+        <v>50000</v>
       </c>
       <c r="G81" s="1">
         <v>100</v>
@@ -3614,27 +3617,27 @@
         <v>100</v>
       </c>
       <c r="J81" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K81" s="2">
         <v>1</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:12">
       <c r="C82" s="1">
-        <v>10008</v>
+        <v>10007</v>
       </c>
       <c r="D82" s="6">
-        <v>180008</v>
+        <v>180007</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>91</v>
       </c>
       <c r="F82" s="1">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="G82" s="1">
         <v>100</v>
@@ -3646,27 +3649,27 @@
         <v>100</v>
       </c>
       <c r="J82" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K82" s="2">
         <v>1</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:12">
       <c r="C83" s="1">
-        <v>10009</v>
+        <v>10008</v>
       </c>
       <c r="D83" s="6">
-        <v>180009</v>
+        <v>180008</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>92</v>
       </c>
       <c r="F83" s="1">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="G83" s="1">
         <v>100</v>
@@ -3678,27 +3681,27 @@
         <v>100</v>
       </c>
       <c r="J83" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K83" s="2">
         <v>1</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:12">
       <c r="C84" s="1">
-        <v>10010</v>
+        <v>10009</v>
       </c>
       <c r="D84" s="6">
-        <v>180010</v>
+        <v>180009</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F84" s="1">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="G84" s="1">
         <v>100</v>
@@ -3716,21 +3719,21 @@
         <v>1</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:12">
       <c r="C85" s="1">
-        <v>10011</v>
+        <v>10010</v>
       </c>
       <c r="D85" s="6">
-        <v>180011</v>
+        <v>180010</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>94</v>
       </c>
       <c r="F85" s="1">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="G85" s="1">
         <v>100</v>
@@ -3742,21 +3745,21 @@
         <v>100</v>
       </c>
       <c r="J85" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K85" s="2">
         <v>1</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:12">
       <c r="C86" s="1">
-        <v>10012</v>
+        <v>10011</v>
       </c>
       <c r="D86" s="6">
-        <v>180012</v>
+        <v>180011</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>95</v>
@@ -3780,21 +3783,21 @@
         <v>1</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:12">
       <c r="C87" s="1">
-        <v>10013</v>
+        <v>10012</v>
       </c>
       <c r="D87" s="6">
-        <v>180013</v>
+        <v>180012</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>96</v>
       </c>
       <c r="F87" s="1">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="G87" s="1">
         <v>100</v>
@@ -3812,21 +3815,21 @@
         <v>1</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:12">
       <c r="C88" s="1">
-        <v>10014</v>
+        <v>10013</v>
       </c>
       <c r="D88" s="6">
-        <v>180014</v>
+        <v>180013</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>97</v>
       </c>
       <c r="F88" s="1">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G88" s="1">
         <v>100</v>
@@ -3844,15 +3847,15 @@
         <v>1</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:12">
       <c r="C89" s="1">
-        <v>10015</v>
+        <v>10014</v>
       </c>
       <c r="D89" s="6">
-        <v>180015</v>
+        <v>180014</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>98</v>
@@ -3876,21 +3879,21 @@
         <v>1</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:12">
       <c r="C90" s="1">
-        <v>10016</v>
+        <v>10015</v>
       </c>
       <c r="D90" s="6">
-        <v>180020</v>
+        <v>180015</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>99</v>
       </c>
       <c r="F90" s="1">
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="G90" s="1">
         <v>100</v>
@@ -3902,21 +3905,21 @@
         <v>100</v>
       </c>
       <c r="J90" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K90" s="2">
         <v>1</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:12">
       <c r="C91" s="1">
-        <v>10017</v>
+        <v>10016</v>
       </c>
       <c r="D91" s="6">
-        <v>180021</v>
+        <v>180020</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>100</v>
@@ -3940,21 +3943,21 @@
         <v>1</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:12">
       <c r="C92" s="1">
-        <v>10018</v>
+        <v>10017</v>
       </c>
       <c r="D92" s="6">
-        <v>180022</v>
+        <v>180021</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>101</v>
       </c>
       <c r="F92" s="1">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="G92" s="1">
         <v>100</v>
@@ -3966,65 +3969,65 @@
         <v>100</v>
       </c>
       <c r="J92" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K92" s="2">
         <v>1</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="94" customHeight="1" spans="3:12">
-      <c r="C94" s="1">
-        <v>10030</v>
-      </c>
-      <c r="D94" s="1">
-        <v>180030</v>
-      </c>
-      <c r="E94" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="3:12">
+      <c r="C93" s="1">
+        <v>10018</v>
+      </c>
+      <c r="D93" s="6">
+        <v>180022</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F94" s="1">
-        <v>5</v>
-      </c>
-      <c r="G94" s="1">
-        <v>1100</v>
-      </c>
-      <c r="H94" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I94" s="1">
-        <v>100</v>
-      </c>
-      <c r="J94" s="1">
-        <v>1</v>
-      </c>
-      <c r="K94" s="2">
-        <v>1</v>
-      </c>
-      <c r="L94" s="1" t="s">
-        <v>103</v>
+      <c r="F93" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G93" s="1">
+        <v>100</v>
+      </c>
+      <c r="H93" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I93" s="1">
+        <v>100</v>
+      </c>
+      <c r="J93" s="1">
+        <v>1</v>
+      </c>
+      <c r="K93" s="2">
+        <v>1</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:12">
       <c r="C95" s="1">
-        <v>10031</v>
-      </c>
-      <c r="D95" s="6">
-        <v>180032</v>
+        <v>10030</v>
+      </c>
+      <c r="D95" s="1">
+        <v>180030</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F95" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G95" s="1">
         <v>1100</v>
       </c>
       <c r="H95" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I95" s="1">
         <v>100</v>
@@ -4036,15 +4039,15 @@
         <v>1</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:12">
       <c r="C96" s="1">
-        <v>10032</v>
+        <v>10031</v>
       </c>
       <c r="D96" s="6">
-        <v>180033</v>
+        <v>180032</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>105</v>
@@ -4053,7 +4056,7 @@
         <v>1</v>
       </c>
       <c r="G96" s="1">
-        <v>1600</v>
+        <v>1100</v>
       </c>
       <c r="H96" s="1">
         <v>2000</v>
@@ -4068,27 +4071,27 @@
         <v>1</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:12">
       <c r="C97" s="1">
-        <v>10033</v>
+        <v>10032</v>
       </c>
       <c r="D97" s="6">
-        <v>180034</v>
+        <v>180033</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F97" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G97" s="1">
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="H97" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I97" s="1">
         <v>100</v>
@@ -4100,27 +4103,27 @@
         <v>1</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:12">
       <c r="C98" s="1">
-        <v>10034</v>
+        <v>10033</v>
       </c>
       <c r="D98" s="6">
-        <v>180035</v>
+        <v>180034</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>107</v>
       </c>
       <c r="F98" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G98" s="1">
-        <v>2000</v>
+        <v>1100</v>
       </c>
       <c r="H98" s="1">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I98" s="1">
         <v>100</v>
@@ -4132,15 +4135,15 @@
         <v>1</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:12">
       <c r="C99" s="1">
-        <v>10035</v>
+        <v>10034</v>
       </c>
       <c r="D99" s="6">
-        <v>180036</v>
+        <v>180035</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>108</v>
@@ -4164,15 +4167,15 @@
         <v>1</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:12">
       <c r="C100" s="1">
-        <v>10036</v>
+        <v>10035</v>
       </c>
       <c r="D100" s="6">
-        <v>180037</v>
+        <v>180036</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>109</v>
@@ -4181,11 +4184,11 @@
         <v>1</v>
       </c>
       <c r="G100" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H100" s="1">
         <v>2500</v>
       </c>
-      <c r="H100" s="1">
-        <v>3500</v>
-      </c>
       <c r="I100" s="1">
         <v>100</v>
       </c>
@@ -4196,24 +4199,24 @@
         <v>1</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:12">
       <c r="C101" s="1">
-        <v>10037</v>
+        <v>10036</v>
       </c>
       <c r="D101" s="6">
-        <v>180038</v>
+        <v>180037</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>110</v>
       </c>
       <c r="F101" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G101" s="1">
-        <v>1600</v>
+        <v>2500</v>
       </c>
       <c r="H101" s="1">
         <v>3500</v>
@@ -4228,24 +4231,24 @@
         <v>1</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:12">
       <c r="C102" s="1">
-        <v>10038</v>
+        <v>10037</v>
       </c>
       <c r="D102" s="6">
-        <v>180039</v>
+        <v>180038</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>111</v>
       </c>
       <c r="F102" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G102" s="1">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="H102" s="1">
         <v>3500</v>
@@ -4260,62 +4263,62 @@
         <v>1</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="104" customHeight="1" spans="3:12">
-      <c r="C104" s="1">
-        <v>11001</v>
-      </c>
-      <c r="D104" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="3:12">
+      <c r="C103" s="1">
+        <v>10038</v>
+      </c>
+      <c r="D103" s="6">
+        <v>180039</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E104" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F104" s="1">
-        <v>5</v>
-      </c>
-      <c r="G104" s="1">
-        <v>150</v>
-      </c>
-      <c r="H104" s="1">
-        <v>1200</v>
-      </c>
-      <c r="I104" s="1">
-        <v>20</v>
-      </c>
-      <c r="J104" s="1">
-        <v>2</v>
-      </c>
-      <c r="K104" s="2">
-        <v>1</v>
-      </c>
-      <c r="L104" s="1" t="s">
-        <v>44</v>
+      <c r="F103" s="1">
+        <v>3</v>
+      </c>
+      <c r="G103" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H103" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I103" s="1">
+        <v>100</v>
+      </c>
+      <c r="J103" s="1">
+        <v>1</v>
+      </c>
+      <c r="K103" s="2">
+        <v>1</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:12">
       <c r="C105" s="1">
-        <v>11002</v>
+        <v>11001</v>
       </c>
       <c r="D105" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="F105" s="1">
         <v>5</v>
       </c>
       <c r="G105" s="1">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H105" s="1">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="I105" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J105" s="1">
         <v>2</v>
@@ -4324,30 +4327,30 @@
         <v>1</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:12">
       <c r="C106" s="1">
-        <v>11003</v>
+        <v>11002</v>
       </c>
       <c r="D106" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E106" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="F106" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G106" s="1">
-        <v>1050</v>
+        <v>200</v>
       </c>
       <c r="H106" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I106" s="1">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="J106" s="1">
         <v>2</v>
@@ -4356,30 +4359,30 @@
         <v>1</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:12">
       <c r="C107" s="1">
-        <v>11004</v>
+        <v>11003</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F107" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G107" s="1">
-        <v>4001</v>
+        <v>1050</v>
       </c>
       <c r="H107" s="1">
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="I107" s="1">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J107" s="1">
         <v>2</v>
@@ -4388,59 +4391,59 @@
         <v>1</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:12">
       <c r="C108" s="1">
-        <v>11005</v>
+        <v>11004</v>
       </c>
       <c r="D108" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E108" s="7" t="s">
-        <v>119</v>
-      </c>
       <c r="F108" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G108" s="1">
-        <v>101</v>
+        <v>4001</v>
       </c>
       <c r="H108" s="1">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="I108" s="1">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="J108" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K108" s="2">
         <v>1</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>120</v>
+        <v>39</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:12">
       <c r="C109" s="1">
-        <v>11006</v>
+        <v>11005</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F109" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G109" s="1">
-        <v>501</v>
+        <v>101</v>
       </c>
       <c r="H109" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="I109" s="1">
         <v>10</v>
@@ -4452,59 +4455,59 @@
         <v>1</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:12">
       <c r="C110" s="1">
-        <v>11007</v>
+        <v>11006</v>
       </c>
       <c r="D110" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F110" s="1">
+        <v>15</v>
+      </c>
+      <c r="G110" s="1">
+        <v>501</v>
+      </c>
+      <c r="H110" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I110" s="1">
+        <v>10</v>
+      </c>
+      <c r="J110" s="1">
+        <v>1</v>
+      </c>
+      <c r="K110" s="2">
+        <v>1</v>
+      </c>
+      <c r="L110" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="E110" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="F110" s="1">
-        <v>10</v>
-      </c>
-      <c r="G110" s="1">
-        <v>1001</v>
-      </c>
-      <c r="H110" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I110" s="1">
-        <v>20</v>
-      </c>
-      <c r="J110" s="1">
-        <v>1</v>
-      </c>
-      <c r="K110" s="2">
-        <v>1</v>
-      </c>
-      <c r="L110" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:12">
       <c r="C111" s="1">
-        <v>11008</v>
+        <v>11007</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F111" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G111" s="1">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H111" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I111" s="1">
         <v>20</v>
@@ -4516,59 +4519,59 @@
         <v>1</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:12">
       <c r="C112" s="1">
-        <v>11009</v>
+        <v>11008</v>
       </c>
       <c r="D112" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E112" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="F112" s="1">
+        <v>8</v>
+      </c>
+      <c r="G112" s="1">
+        <v>1501</v>
+      </c>
+      <c r="H112" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I112" s="1">
+        <v>20</v>
+      </c>
+      <c r="J112" s="1">
+        <v>1</v>
+      </c>
+      <c r="K112" s="2">
+        <v>1</v>
+      </c>
+      <c r="L112" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="E112" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="F112" s="1">
-        <v>15</v>
-      </c>
-      <c r="G112" s="1">
-        <v>2001</v>
-      </c>
-      <c r="H112" s="1">
-        <v>2500</v>
-      </c>
-      <c r="I112" s="1">
-        <v>52</v>
-      </c>
-      <c r="J112" s="1">
-        <v>1</v>
-      </c>
-      <c r="K112" s="2">
-        <v>1</v>
-      </c>
-      <c r="L112" s="1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:12">
       <c r="C113" s="1">
-        <v>11010</v>
+        <v>11009</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F113" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G113" s="1">
-        <v>2501</v>
+        <v>2001</v>
       </c>
       <c r="H113" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I113" s="1">
         <v>52</v>
@@ -4580,27 +4583,27 @@
         <v>1</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:12">
       <c r="C114" s="1">
-        <v>11011</v>
+        <v>11010</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F114" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G114" s="1">
-        <v>3001</v>
+        <v>2501</v>
       </c>
       <c r="H114" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="I114" s="1">
         <v>52</v>
@@ -4612,7 +4615,39 @@
         <v>1</v>
       </c>
       <c r="L114" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="3:12">
+      <c r="C115" s="1">
+        <v>11011</v>
+      </c>
+      <c r="D115" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E115" s="7" t="s">
         <v>138</v>
+      </c>
+      <c r="F115" s="1">
+        <v>3</v>
+      </c>
+      <c r="G115" s="1">
+        <v>3001</v>
+      </c>
+      <c r="H115" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I115" s="1">
+        <v>52</v>
+      </c>
+      <c r="J115" s="1">
+        <v>1</v>
+      </c>
+      <c r="K115" s="2">
+        <v>1</v>
+      </c>
+      <c r="L115" s="1" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="142">
   <si>
     <t>#</t>
   </si>
@@ -223,6 +223,12 @@
   </si>
   <si>
     <t>时装精华</t>
+  </si>
+  <si>
+    <t>1014</t>
+  </si>
+  <si>
+    <t>超级书页</t>
   </si>
   <si>
     <t>220036</t>
@@ -678,12 +684,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1477,15 +1483,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M115"/>
+  <dimension ref="C1:M116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="9.75221238938053" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.6283185840708" style="1" customWidth="1"/>
-    <col min="6" max="7" width="12.2477876106195" style="1" customWidth="1"/>
-    <col min="8" max="11" width="11.1238938053097" style="1" customWidth="1"/>
-    <col min="12" max="12" width="23.1238938053097" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="12.25" style="1" customWidth="1"/>
+    <col min="8" max="11" width="11.125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="23.125" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1859,7 +1865,7 @@
         <v>32</v>
       </c>
       <c r="F14" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G14" s="1">
         <v>1250</v>
@@ -1891,7 +1897,7 @@
         <v>34</v>
       </c>
       <c r="F15" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G15" s="1">
         <v>1350</v>
@@ -1923,7 +1929,7 @@
         <v>36</v>
       </c>
       <c r="F16" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G16" s="1">
         <v>1450</v>
@@ -2176,7 +2182,7 @@
         <v>1007</v>
       </c>
       <c r="H24" s="2">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="I24" s="2">
         <v>53</v>
@@ -2188,59 +2194,56 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C26" s="2">
-        <v>151</v>
-      </c>
-      <c r="D26" s="8" t="s">
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C25" s="2">
+        <v>20</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E25" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F26" s="2">
-        <v>12</v>
-      </c>
-      <c r="G26" s="2">
-        <v>300</v>
-      </c>
-      <c r="H26" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I26" s="2">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2">
-        <v>25</v>
-      </c>
-      <c r="K26" s="2">
-        <v>1</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>56</v>
-      </c>
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2">
+        <v>2003</v>
+      </c>
+      <c r="H25" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I25" s="2">
+        <v>61</v>
+      </c>
+      <c r="J25" s="2">
+        <v>1</v>
+      </c>
+      <c r="K25" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="4:4">
+      <c r="D26" s="4"/>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C27" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D27" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="F27" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G27" s="2">
-        <v>1501</v>
+        <v>300</v>
       </c>
       <c r="H27" s="2">
-        <v>4000</v>
+        <v>1500</v>
       </c>
       <c r="I27" s="2">
         <v>1</v>
@@ -2252,94 +2255,94 @@
         <v>1</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C28" s="2">
+        <v>152</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F28" s="2">
+        <v>6</v>
+      </c>
+      <c r="G28" s="2">
+        <v>1501</v>
+      </c>
+      <c r="H28" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I28" s="2">
+        <v>1</v>
+      </c>
+      <c r="J28" s="2">
+        <v>25</v>
+      </c>
+      <c r="K28" s="2">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C29" s="2">
         <v>153</v>
       </c>
-      <c r="D28" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" s="2">
+      <c r="D29" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F29" s="2">
         <v>3</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G29" s="2">
         <v>4001</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H29" s="2">
         <v>10000</v>
       </c>
-      <c r="I28" s="2">
-        <v>1</v>
-      </c>
-      <c r="J28" s="2">
+      <c r="I29" s="2">
+        <v>1</v>
+      </c>
+      <c r="J29" s="2">
         <v>15</v>
       </c>
-      <c r="K28" s="2">
+      <c r="K29" s="2">
         <v>2</v>
       </c>
-      <c r="L28" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D29" s="4"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C30" s="1">
-        <v>100</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="1">
-        <v>50</v>
-      </c>
-      <c r="G30" s="1">
-        <v>1</v>
-      </c>
-      <c r="H30" s="1">
-        <v>300</v>
-      </c>
-      <c r="I30" s="1">
-        <v>1</v>
-      </c>
-      <c r="J30" s="1">
-        <v>10000</v>
-      </c>
-      <c r="K30" s="2">
-        <v>1</v>
-      </c>
-      <c r="L30" s="1" t="s">
+      <c r="L29" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="4:4">
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C31" s="1">
+        <v>100</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
-      <c r="C31" s="1">
-        <v>101</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>60</v>
-      </c>
       <c r="E31" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F31" s="1">
         <v>50</v>
       </c>
       <c r="G31" s="1">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="H31" s="1">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I31" s="1">
         <v>1</v>
@@ -2348,30 +2351,30 @@
         <v>10000</v>
       </c>
       <c r="K31" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L31" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C32" s="1">
+        <v>101</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:12">
-      <c r="C32" s="1">
-        <v>102</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>60</v>
-      </c>
       <c r="E32" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F32" s="1">
         <v>50</v>
       </c>
       <c r="G32" s="1">
-        <v>601</v>
+        <v>301</v>
       </c>
       <c r="H32" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="I32" s="1">
         <v>1</v>
@@ -2380,30 +2383,30 @@
         <v>10000</v>
       </c>
       <c r="K32" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:12">
       <c r="C33" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F33" s="1">
         <v>50</v>
       </c>
       <c r="G33" s="1">
-        <v>1001</v>
+        <v>601</v>
       </c>
       <c r="H33" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I33" s="1">
         <v>1</v>
@@ -2412,62 +2415,62 @@
         <v>10000</v>
       </c>
       <c r="K33" s="2">
+        <v>4</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:12">
+      <c r="C34" s="1">
+        <v>103</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F34" s="1">
+        <v>50</v>
+      </c>
+      <c r="G34" s="1">
+        <v>1001</v>
+      </c>
+      <c r="H34" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1</v>
+      </c>
+      <c r="J34" s="1">
+        <v>10000</v>
+      </c>
+      <c r="K34" s="2">
         <v>10</v>
       </c>
-      <c r="L33" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C34" s="1">
-        <v>104</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F34" s="2">
-        <v>50</v>
-      </c>
-      <c r="G34" s="2">
-        <v>1501</v>
-      </c>
-      <c r="H34" s="2">
-        <v>3500</v>
-      </c>
-      <c r="I34" s="2">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K34" s="2">
-        <v>20</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>62</v>
+      <c r="L34" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C35" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F35" s="2">
         <v>50</v>
       </c>
       <c r="G35" s="2">
-        <v>3501</v>
+        <v>1501</v>
       </c>
       <c r="H35" s="2">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="I35" s="2">
         <v>1</v>
@@ -2476,65 +2479,65 @@
         <v>10000</v>
       </c>
       <c r="K35" s="2">
+        <v>20</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C36" s="1">
+        <v>105</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F36" s="2">
+        <v>50</v>
+      </c>
+      <c r="G36" s="2">
+        <v>3501</v>
+      </c>
+      <c r="H36" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I36" s="2">
+        <v>1</v>
+      </c>
+      <c r="J36" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K36" s="2">
         <v>40</v>
       </c>
-      <c r="L35" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D36" s="4"/>
-    </row>
-    <row r="37" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
-      <c r="C37" s="2">
+      <c r="L36" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="4:4">
+      <c r="D37" s="4"/>
+    </row>
+    <row r="38" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C38" s="2">
         <v>200</v>
       </c>
-      <c r="D37" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F37" s="2">
-        <v>50</v>
-      </c>
-      <c r="G37" s="2">
-        <v>1</v>
-      </c>
-      <c r="H37" s="2">
-        <v>300</v>
-      </c>
-      <c r="I37" s="2">
-        <v>1</v>
-      </c>
-      <c r="J37" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K37" s="2">
-        <v>1</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C38" s="2">
-        <v>201</v>
-      </c>
       <c r="D38" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F38" s="2">
         <v>50</v>
       </c>
       <c r="G38" s="2">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="H38" s="2">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I38" s="2">
         <v>1</v>
@@ -2543,30 +2546,30 @@
         <v>10000</v>
       </c>
       <c r="K38" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C39" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F39" s="2">
         <v>50</v>
       </c>
       <c r="G39" s="2">
-        <v>601</v>
+        <v>301</v>
       </c>
       <c r="H39" s="2">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="I39" s="2">
         <v>1</v>
@@ -2575,30 +2578,30 @@
         <v>10000</v>
       </c>
       <c r="K39" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C40" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F40" s="2">
         <v>50</v>
       </c>
       <c r="G40" s="2">
-        <v>1001</v>
+        <v>601</v>
       </c>
       <c r="H40" s="2">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I40" s="2">
         <v>1</v>
@@ -2607,30 +2610,30 @@
         <v>10000</v>
       </c>
       <c r="K40" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="41" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C41" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F41" s="2">
         <v>50</v>
       </c>
       <c r="G41" s="2">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H41" s="2">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="I41" s="2">
         <v>1</v>
@@ -2639,30 +2642,30 @@
         <v>10000</v>
       </c>
       <c r="K41" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
       <c r="C42" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F42" s="2">
         <v>50</v>
       </c>
       <c r="G42" s="2">
-        <v>3501</v>
+        <v>1501</v>
       </c>
       <c r="H42" s="2">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="I42" s="2">
         <v>1</v>
@@ -2671,65 +2674,65 @@
         <v>10000</v>
       </c>
       <c r="K42" s="2">
+        <v>20</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C43" s="2">
+        <v>205</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F43" s="2">
+        <v>50</v>
+      </c>
+      <c r="G43" s="2">
+        <v>3501</v>
+      </c>
+      <c r="H43" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I43" s="2">
+        <v>1</v>
+      </c>
+      <c r="J43" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K43" s="2">
         <v>40</v>
       </c>
-      <c r="L42" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" ht="20" customHeight="1" spans="4:4">
-      <c r="D43" s="4"/>
-    </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C44" s="2">
-        <v>300</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F44" s="2">
-        <v>10</v>
-      </c>
-      <c r="G44" s="2">
-        <v>1</v>
-      </c>
-      <c r="H44" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I44" s="2">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K44" s="2">
-        <v>1</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="L43" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" ht="20" customHeight="1" spans="4:4">
+      <c r="D44" s="4"/>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C45" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F45" s="2">
         <v>10</v>
       </c>
       <c r="G45" s="2">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="H45" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I45" s="2">
         <v>1</v>
@@ -2738,7 +2741,7 @@
         <v>10000</v>
       </c>
       <c r="K45" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>21</v>
@@ -2746,22 +2749,22 @@
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C46" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F46" s="2">
         <v>10</v>
       </c>
       <c r="G46" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H46" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I46" s="2">
         <v>1</v>
@@ -2770,63 +2773,63 @@
         <v>10000</v>
       </c>
       <c r="K46" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="47" s="2" customFormat="1" customHeight="1"/>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C48" s="2">
-        <v>400</v>
-      </c>
-      <c r="D48" s="10" t="s">
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C47" s="2">
+        <v>302</v>
+      </c>
+      <c r="D47" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E47" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F47" s="2">
         <v>10</v>
       </c>
-      <c r="G48" s="2">
-        <v>50</v>
-      </c>
-      <c r="H48" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I48" s="2">
-        <v>1</v>
-      </c>
-      <c r="J48" s="2">
+      <c r="G47" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H47" s="2">
         <v>10000</v>
       </c>
-      <c r="K48" s="2">
-        <v>1</v>
-      </c>
-      <c r="L48" s="2" t="s">
+      <c r="I47" s="2">
+        <v>1</v>
+      </c>
+      <c r="J47" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K47" s="2">
+        <v>3</v>
+      </c>
+      <c r="L47" s="2" t="s">
         <v>21</v>
       </c>
     </row>
+    <row r="48" s="2" customFormat="1" customHeight="1"/>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C49" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F49" s="2">
         <v>10</v>
       </c>
       <c r="G49" s="2">
-        <v>1001</v>
+        <v>50</v>
       </c>
       <c r="H49" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I49" s="2">
         <v>1</v>
@@ -2835,7 +2838,7 @@
         <v>10000</v>
       </c>
       <c r="K49" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>21</v>
@@ -2843,22 +2846,22 @@
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C50" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F50" s="2">
         <v>10</v>
       </c>
       <c r="G50" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H50" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I50" s="2">
         <v>1</v>
@@ -2867,63 +2870,63 @@
         <v>10000</v>
       </c>
       <c r="K50" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="51" s="2" customFormat="1" customHeight="1"/>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C52" s="2">
-        <v>500</v>
-      </c>
-      <c r="D52" s="10" t="s">
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C51" s="2">
+        <v>402</v>
+      </c>
+      <c r="D51" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E51" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F52" s="2">
-        <v>4</v>
-      </c>
-      <c r="G52" s="2">
-        <v>150</v>
-      </c>
-      <c r="H52" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I52" s="2">
-        <v>1</v>
-      </c>
-      <c r="J52" s="2">
-        <v>20</v>
-      </c>
-      <c r="K52" s="2">
-        <v>1</v>
-      </c>
-      <c r="L52" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
+      <c r="F51" s="2">
+        <v>10</v>
+      </c>
+      <c r="G51" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H51" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I51" s="2">
+        <v>1</v>
+      </c>
+      <c r="J51" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K51" s="2">
+        <v>3</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" customHeight="1"/>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C53" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F53" s="2">
         <v>4</v>
       </c>
       <c r="G53" s="2">
-        <v>1001</v>
+        <v>150</v>
       </c>
       <c r="H53" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I53" s="2">
         <v>1</v>
@@ -2932,30 +2935,30 @@
         <v>20</v>
       </c>
       <c r="K53" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C54" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F54" s="2">
         <v>4</v>
       </c>
       <c r="G54" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H54" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I54" s="2">
         <v>1</v>
@@ -2964,63 +2967,63 @@
         <v>20</v>
       </c>
       <c r="K54" s="2">
+        <v>2</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C55" s="2">
+        <v>502</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F55" s="2">
+        <v>4</v>
+      </c>
+      <c r="G55" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H55" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I55" s="2">
+        <v>1</v>
+      </c>
+      <c r="J55" s="2">
+        <v>20</v>
+      </c>
+      <c r="K55" s="2">
         <v>3</v>
       </c>
-      <c r="L54" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="55" s="2" customFormat="1" customHeight="1"/>
-    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C56" s="2">
-        <v>600</v>
-      </c>
-      <c r="D56" s="2">
-        <v>3001</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F56" s="2">
-        <v>10</v>
-      </c>
-      <c r="G56" s="2">
-        <v>1</v>
-      </c>
-      <c r="H56" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I56" s="2">
-        <v>1</v>
-      </c>
-      <c r="J56" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K56" s="2">
-        <v>1</v>
-      </c>
-      <c r="L56" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
+      <c r="L55" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="56" s="2" customFormat="1" customHeight="1"/>
     <row r="57" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C57" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D57" s="2">
         <v>3001</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F57" s="2">
         <v>10</v>
       </c>
       <c r="G57" s="2">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="H57" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I57" s="2">
         <v>1</v>
@@ -3029,7 +3032,7 @@
         <v>10000</v>
       </c>
       <c r="K57" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>21</v>
@@ -3037,22 +3040,22 @@
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C58" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D58" s="2">
         <v>3001</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F58" s="2">
         <v>10</v>
       </c>
       <c r="G58" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H58" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I58" s="2">
         <v>1</v>
@@ -3061,63 +3064,63 @@
         <v>10000</v>
       </c>
       <c r="K58" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="59" s="2" customFormat="1" customHeight="1"/>
-    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C60" s="2">
-        <v>700</v>
-      </c>
-      <c r="D60" s="2">
-        <v>3002</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F60" s="2">
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C59" s="2">
+        <v>602</v>
+      </c>
+      <c r="D59" s="2">
+        <v>3001</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F59" s="2">
         <v>10</v>
       </c>
-      <c r="G60" s="2">
-        <v>200</v>
-      </c>
-      <c r="H60" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I60" s="2">
-        <v>1</v>
-      </c>
-      <c r="J60" s="2">
+      <c r="G59" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H59" s="2">
         <v>10000</v>
       </c>
-      <c r="K60" s="2">
-        <v>1</v>
-      </c>
-      <c r="L60" s="2" t="s">
+      <c r="I59" s="2">
+        <v>1</v>
+      </c>
+      <c r="J59" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K59" s="2">
+        <v>3</v>
+      </c>
+      <c r="L59" s="2" t="s">
         <v>21</v>
       </c>
     </row>
+    <row r="60" s="2" customFormat="1" customHeight="1"/>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C61" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D61" s="2">
         <v>3002</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F61" s="2">
         <v>10</v>
       </c>
       <c r="G61" s="2">
-        <v>1001</v>
+        <v>200</v>
       </c>
       <c r="H61" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I61" s="2">
         <v>1</v>
@@ -3126,7 +3129,7 @@
         <v>10000</v>
       </c>
       <c r="K61" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>21</v>
@@ -3134,22 +3137,22 @@
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C62" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D62" s="2">
         <v>3002</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F62" s="2">
         <v>10</v>
       </c>
       <c r="G62" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H62" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I62" s="2">
         <v>1</v>
@@ -3158,56 +3161,56 @@
         <v>10000</v>
       </c>
       <c r="K62" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="63" customHeight="1" spans="11:11">
-      <c r="K63" s="2"/>
-    </row>
-    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C64" s="2">
-        <v>800</v>
-      </c>
-      <c r="D64" s="2">
-        <v>3003</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F64" s="2">
-        <v>2</v>
-      </c>
-      <c r="G64" s="2">
-        <v>4001</v>
-      </c>
-      <c r="H64" s="2">
-        <v>5000</v>
-      </c>
-      <c r="I64" s="2">
-        <v>7</v>
-      </c>
-      <c r="J64" s="2">
-        <v>13</v>
-      </c>
-      <c r="K64" s="2">
-        <v>5</v>
-      </c>
-      <c r="L64" s="2" t="s">
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C63" s="2">
+        <v>702</v>
+      </c>
+      <c r="D63" s="2">
+        <v>3002</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F63" s="2">
+        <v>10</v>
+      </c>
+      <c r="G63" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H63" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I63" s="2">
+        <v>1</v>
+      </c>
+      <c r="J63" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K63" s="2">
+        <v>3</v>
+      </c>
+      <c r="L63" s="2" t="s">
         <v>21</v>
       </c>
+    </row>
+    <row r="64" customHeight="1" spans="11:11">
+      <c r="K64" s="2"/>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C65" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D65" s="2">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F65" s="2">
         <v>2</v>
@@ -3219,50 +3222,53 @@
         <v>5000</v>
       </c>
       <c r="I65" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J65" s="2">
+        <v>13</v>
+      </c>
+      <c r="K65" s="2">
         <v>5</v>
-      </c>
-      <c r="K65" s="2">
-        <v>1</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="3:11">
-      <c r="C67" s="1">
-        <v>901</v>
-      </c>
-      <c r="D67" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E67" s="1" t="s">
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C66" s="2">
+        <v>801</v>
+      </c>
+      <c r="D66" s="2">
+        <v>3004</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F67" s="1">
-        <v>20</v>
-      </c>
-      <c r="G67" s="1">
-        <v>3001</v>
-      </c>
-      <c r="H67" s="1">
-        <v>4000</v>
-      </c>
-      <c r="I67" s="1">
-        <v>3</v>
-      </c>
-      <c r="J67" s="1">
-        <v>30</v>
-      </c>
-      <c r="K67" s="2">
-        <v>1</v>
+      <c r="F66" s="2">
+        <v>2</v>
+      </c>
+      <c r="G66" s="2">
+        <v>4001</v>
+      </c>
+      <c r="H66" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I66" s="2">
+        <v>9</v>
+      </c>
+      <c r="J66" s="2">
+        <v>5</v>
+      </c>
+      <c r="K66" s="2">
+        <v>1</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:11">
       <c r="C68" s="1">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D68" s="11" t="s">
         <v>78</v>
@@ -3271,7 +3277,7 @@
         <v>79</v>
       </c>
       <c r="F68" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G68" s="1">
         <v>3001</v>
@@ -3283,7 +3289,7 @@
         <v>3</v>
       </c>
       <c r="J68" s="1">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="K68" s="2">
         <v>1</v>
@@ -3291,7 +3297,7 @@
     </row>
     <row r="69" customHeight="1" spans="3:11">
       <c r="C69" s="1">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D69" s="11" t="s">
         <v>80</v>
@@ -3300,7 +3306,7 @@
         <v>81</v>
       </c>
       <c r="F69" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G69" s="1">
         <v>3001</v>
@@ -3312,7 +3318,7 @@
         <v>3</v>
       </c>
       <c r="J69" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K69" s="2">
         <v>1</v>
@@ -3320,7 +3326,7 @@
     </row>
     <row r="70" customHeight="1" spans="3:11">
       <c r="C70" s="1">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="D70" s="11" t="s">
         <v>82</v>
@@ -3329,19 +3335,19 @@
         <v>83</v>
       </c>
       <c r="F70" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G70" s="1">
-        <v>3501</v>
+        <v>3001</v>
       </c>
       <c r="H70" s="1">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="I70" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J70" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K70" s="2">
         <v>1</v>
@@ -3349,36 +3355,36 @@
     </row>
     <row r="71" customHeight="1" spans="3:11">
       <c r="C71" s="1">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F71" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G71" s="1">
-        <v>4001</v>
+        <v>3501</v>
       </c>
       <c r="H71" s="1">
         <v>5000</v>
       </c>
       <c r="I71" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J71" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K71" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
       <c r="C72" s="1">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D72" s="11" t="s">
         <v>78</v>
@@ -3387,7 +3393,7 @@
         <v>79</v>
       </c>
       <c r="F72" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G72" s="1">
         <v>4001</v>
@@ -3399,7 +3405,7 @@
         <v>3</v>
       </c>
       <c r="J72" s="1">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K72" s="2">
         <v>2</v>
@@ -3407,7 +3413,7 @@
     </row>
     <row r="73" customHeight="1" spans="3:11">
       <c r="C73" s="1">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D73" s="11" t="s">
         <v>80</v>
@@ -3416,7 +3422,7 @@
         <v>81</v>
       </c>
       <c r="F73" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G73" s="1">
         <v>4001</v>
@@ -3428,56 +3434,53 @@
         <v>3</v>
       </c>
       <c r="J73" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K73" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="3:12">
-      <c r="C76" s="1">
-        <v>10001</v>
-      </c>
-      <c r="D76" s="6">
-        <v>180001</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F76" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G76" s="1">
-        <v>100</v>
-      </c>
-      <c r="H76" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I76" s="1">
-        <v>100</v>
-      </c>
-      <c r="J76" s="1">
-        <v>1</v>
-      </c>
-      <c r="K76" s="2">
-        <v>1</v>
-      </c>
-      <c r="L76" s="1" t="s">
-        <v>85</v>
+    <row r="74" customHeight="1" spans="3:11">
+      <c r="C74" s="1">
+        <v>907</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F74" s="1">
+        <v>3</v>
+      </c>
+      <c r="G74" s="1">
+        <v>4001</v>
+      </c>
+      <c r="H74" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I74" s="1">
+        <v>3</v>
+      </c>
+      <c r="J74" s="1">
+        <v>2</v>
+      </c>
+      <c r="K74" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:12">
       <c r="C77" s="1">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="D77" s="6">
-        <v>180002</v>
+        <v>180001</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>86</v>
       </c>
       <c r="F77" s="1">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G77" s="1">
         <v>100</v>
@@ -3495,21 +3498,21 @@
         <v>1</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:12">
       <c r="C78" s="1">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="D78" s="6">
-        <v>180003</v>
+        <v>180002</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F78" s="1">
-        <v>150000</v>
+        <v>4000</v>
       </c>
       <c r="G78" s="1">
         <v>100</v>
@@ -3521,27 +3524,27 @@
         <v>100</v>
       </c>
       <c r="J78" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K78" s="2">
         <v>1</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:12">
       <c r="C79" s="1">
-        <v>10004</v>
+        <v>10003</v>
       </c>
       <c r="D79" s="6">
-        <v>180004</v>
+        <v>180003</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F79" s="1">
-        <v>8000</v>
+        <v>150000</v>
       </c>
       <c r="G79" s="1">
         <v>100</v>
@@ -3553,27 +3556,27 @@
         <v>100</v>
       </c>
       <c r="J79" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K79" s="2">
         <v>1</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:12">
       <c r="C80" s="1">
-        <v>10005</v>
+        <v>10004</v>
       </c>
       <c r="D80" s="6">
-        <v>180005</v>
+        <v>180004</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F80" s="1">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="G80" s="1">
         <v>100</v>
@@ -3591,21 +3594,21 @@
         <v>1</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:12">
       <c r="C81" s="1">
-        <v>10006</v>
+        <v>10005</v>
       </c>
       <c r="D81" s="6">
-        <v>180006</v>
+        <v>180005</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F81" s="1">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="G81" s="1">
         <v>100</v>
@@ -3617,27 +3620,27 @@
         <v>100</v>
       </c>
       <c r="J81" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K81" s="2">
         <v>1</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:12">
       <c r="C82" s="1">
-        <v>10007</v>
+        <v>10006</v>
       </c>
       <c r="D82" s="6">
-        <v>180007</v>
+        <v>180006</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F82" s="1">
-        <v>2000</v>
+        <v>50000</v>
       </c>
       <c r="G82" s="1">
         <v>100</v>
@@ -3649,27 +3652,27 @@
         <v>100</v>
       </c>
       <c r="J82" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K82" s="2">
         <v>1</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:12">
       <c r="C83" s="1">
-        <v>10008</v>
+        <v>10007</v>
       </c>
       <c r="D83" s="6">
-        <v>180008</v>
+        <v>180007</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F83" s="1">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="G83" s="1">
         <v>100</v>
@@ -3681,27 +3684,27 @@
         <v>100</v>
       </c>
       <c r="J83" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K83" s="2">
         <v>1</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:12">
       <c r="C84" s="1">
-        <v>10009</v>
+        <v>10008</v>
       </c>
       <c r="D84" s="6">
-        <v>180009</v>
+        <v>180008</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F84" s="1">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="G84" s="1">
         <v>100</v>
@@ -3713,27 +3716,27 @@
         <v>100</v>
       </c>
       <c r="J84" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K84" s="2">
         <v>1</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:12">
       <c r="C85" s="1">
-        <v>10010</v>
+        <v>10009</v>
       </c>
       <c r="D85" s="6">
-        <v>180010</v>
+        <v>180009</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F85" s="1">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="G85" s="1">
         <v>100</v>
@@ -3751,21 +3754,21 @@
         <v>1</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:12">
       <c r="C86" s="1">
-        <v>10011</v>
+        <v>10010</v>
       </c>
       <c r="D86" s="6">
-        <v>180011</v>
+        <v>180010</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F86" s="1">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="G86" s="1">
         <v>100</v>
@@ -3777,24 +3780,24 @@
         <v>100</v>
       </c>
       <c r="J86" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K86" s="2">
         <v>1</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:12">
       <c r="C87" s="1">
-        <v>10012</v>
+        <v>10011</v>
       </c>
       <c r="D87" s="6">
-        <v>180012</v>
+        <v>180011</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F87" s="1">
         <v>100000</v>
@@ -3815,21 +3818,21 @@
         <v>1</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:12">
       <c r="C88" s="1">
-        <v>10013</v>
+        <v>10012</v>
       </c>
       <c r="D88" s="6">
-        <v>180013</v>
+        <v>180012</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F88" s="1">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="G88" s="1">
         <v>100</v>
@@ -3847,21 +3850,21 @@
         <v>1</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:12">
       <c r="C89" s="1">
-        <v>10014</v>
+        <v>10013</v>
       </c>
       <c r="D89" s="6">
-        <v>180014</v>
+        <v>180013</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F89" s="1">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G89" s="1">
         <v>100</v>
@@ -3879,18 +3882,18 @@
         <v>1</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:12">
       <c r="C90" s="1">
-        <v>10015</v>
+        <v>10014</v>
       </c>
       <c r="D90" s="6">
-        <v>180015</v>
+        <v>180014</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F90" s="1">
         <v>100000</v>
@@ -3911,21 +3914,21 @@
         <v>1</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:12">
       <c r="C91" s="1">
-        <v>10016</v>
+        <v>10015</v>
       </c>
       <c r="D91" s="6">
-        <v>180020</v>
+        <v>180015</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F91" s="1">
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="G91" s="1">
         <v>100</v>
@@ -3937,24 +3940,24 @@
         <v>100</v>
       </c>
       <c r="J91" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K91" s="2">
         <v>1</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:12">
       <c r="C92" s="1">
-        <v>10017</v>
+        <v>10016</v>
       </c>
       <c r="D92" s="6">
-        <v>180021</v>
+        <v>180020</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F92" s="1">
         <v>30000</v>
@@ -3975,21 +3978,21 @@
         <v>1</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:12">
       <c r="C93" s="1">
-        <v>10018</v>
+        <v>10017</v>
       </c>
       <c r="D93" s="6">
-        <v>180022</v>
+        <v>180021</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F93" s="1">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="G93" s="1">
         <v>100</v>
@@ -4001,65 +4004,65 @@
         <v>100</v>
       </c>
       <c r="J93" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K93" s="2">
         <v>1</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="95" customHeight="1" spans="3:12">
-      <c r="C95" s="1">
-        <v>10030</v>
-      </c>
-      <c r="D95" s="1">
-        <v>180030</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F95" s="1">
-        <v>5</v>
-      </c>
-      <c r="G95" s="1">
-        <v>1100</v>
-      </c>
-      <c r="H95" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I95" s="1">
-        <v>100</v>
-      </c>
-      <c r="J95" s="1">
-        <v>1</v>
-      </c>
-      <c r="K95" s="2">
-        <v>1</v>
-      </c>
-      <c r="L95" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="3:12">
+      <c r="C94" s="1">
+        <v>10018</v>
+      </c>
+      <c r="D94" s="6">
+        <v>180022</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>104</v>
+      </c>
+      <c r="F94" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G94" s="1">
+        <v>100</v>
+      </c>
+      <c r="H94" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I94" s="1">
+        <v>100</v>
+      </c>
+      <c r="J94" s="1">
+        <v>1</v>
+      </c>
+      <c r="K94" s="2">
+        <v>1</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:12">
       <c r="C96" s="1">
-        <v>10031</v>
-      </c>
-      <c r="D96" s="6">
-        <v>180032</v>
+        <v>10030</v>
+      </c>
+      <c r="D96" s="1">
+        <v>180030</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>105</v>
       </c>
       <c r="F96" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G96" s="1">
         <v>1100</v>
       </c>
       <c r="H96" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I96" s="1">
         <v>100</v>
@@ -4071,24 +4074,24 @@
         <v>1</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:12">
       <c r="C97" s="1">
-        <v>10032</v>
+        <v>10031</v>
       </c>
       <c r="D97" s="6">
-        <v>180033</v>
+        <v>180032</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F97" s="1">
         <v>1</v>
       </c>
       <c r="G97" s="1">
-        <v>1600</v>
+        <v>1100</v>
       </c>
       <c r="H97" s="1">
         <v>2000</v>
@@ -4103,27 +4106,27 @@
         <v>1</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:12">
       <c r="C98" s="1">
-        <v>10033</v>
+        <v>10032</v>
       </c>
       <c r="D98" s="6">
-        <v>180034</v>
+        <v>180033</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F98" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G98" s="1">
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="H98" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I98" s="1">
         <v>100</v>
@@ -4135,27 +4138,27 @@
         <v>1</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:12">
       <c r="C99" s="1">
-        <v>10034</v>
+        <v>10033</v>
       </c>
       <c r="D99" s="6">
-        <v>180035</v>
+        <v>180034</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F99" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G99" s="1">
-        <v>2000</v>
+        <v>1100</v>
       </c>
       <c r="H99" s="1">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I99" s="1">
         <v>100</v>
@@ -4167,18 +4170,18 @@
         <v>1</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:12">
       <c r="C100" s="1">
-        <v>10035</v>
+        <v>10034</v>
       </c>
       <c r="D100" s="6">
-        <v>180036</v>
+        <v>180035</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F100" s="1">
         <v>1</v>
@@ -4199,28 +4202,28 @@
         <v>1</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:12">
       <c r="C101" s="1">
-        <v>10036</v>
+        <v>10035</v>
       </c>
       <c r="D101" s="6">
-        <v>180037</v>
+        <v>180036</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F101" s="1">
         <v>1</v>
       </c>
       <c r="G101" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H101" s="1">
         <v>2500</v>
       </c>
-      <c r="H101" s="1">
-        <v>3500</v>
-      </c>
       <c r="I101" s="1">
         <v>100</v>
       </c>
@@ -4231,24 +4234,24 @@
         <v>1</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:12">
       <c r="C102" s="1">
-        <v>10037</v>
+        <v>10036</v>
       </c>
       <c r="D102" s="6">
-        <v>180038</v>
+        <v>180037</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F102" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G102" s="1">
-        <v>1600</v>
+        <v>2500</v>
       </c>
       <c r="H102" s="1">
         <v>3500</v>
@@ -4263,24 +4266,24 @@
         <v>1</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:12">
       <c r="C103" s="1">
-        <v>10038</v>
+        <v>10037</v>
       </c>
       <c r="D103" s="6">
-        <v>180039</v>
+        <v>180038</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F103" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G103" s="1">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="H103" s="1">
         <v>3500</v>
@@ -4295,44 +4298,44 @@
         <v>1</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="105" customHeight="1" spans="3:12">
-      <c r="C105" s="1">
-        <v>11001</v>
-      </c>
-      <c r="D105" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="E105" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="3:12">
+      <c r="C104" s="1">
+        <v>10038</v>
+      </c>
+      <c r="D104" s="6">
+        <v>180039</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F105" s="1">
-        <v>5</v>
-      </c>
-      <c r="G105" s="1">
-        <v>150</v>
-      </c>
-      <c r="H105" s="1">
-        <v>1200</v>
-      </c>
-      <c r="I105" s="1">
-        <v>20</v>
-      </c>
-      <c r="J105" s="1">
-        <v>2</v>
-      </c>
-      <c r="K105" s="2">
-        <v>1</v>
-      </c>
-      <c r="L105" s="1" t="s">
-        <v>39</v>
+      <c r="F104" s="1">
+        <v>3</v>
+      </c>
+      <c r="G104" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H104" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I104" s="1">
+        <v>100</v>
+      </c>
+      <c r="J104" s="1">
+        <v>1</v>
+      </c>
+      <c r="K104" s="2">
+        <v>1</v>
+      </c>
+      <c r="L104" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:12">
       <c r="C106" s="1">
-        <v>11002</v>
+        <v>11001</v>
       </c>
       <c r="D106" s="9" t="s">
         <v>115</v>
@@ -4344,13 +4347,13 @@
         <v>5</v>
       </c>
       <c r="G106" s="1">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H106" s="1">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="I106" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J106" s="1">
         <v>2</v>
@@ -4364,7 +4367,7 @@
     </row>
     <row r="107" customHeight="1" spans="3:12">
       <c r="C107" s="1">
-        <v>11003</v>
+        <v>11002</v>
       </c>
       <c r="D107" s="9" t="s">
         <v>117</v>
@@ -4373,16 +4376,16 @@
         <v>118</v>
       </c>
       <c r="F107" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G107" s="1">
-        <v>1050</v>
+        <v>200</v>
       </c>
       <c r="H107" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I107" s="1">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="J107" s="1">
         <v>2</v>
@@ -4396,25 +4399,25 @@
     </row>
     <row r="108" customHeight="1" spans="3:12">
       <c r="C108" s="1">
-        <v>11004</v>
+        <v>11003</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F108" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G108" s="1">
-        <v>4001</v>
+        <v>1050</v>
       </c>
       <c r="H108" s="1">
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="I108" s="1">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J108" s="1">
         <v>2</v>
@@ -4428,54 +4431,54 @@
     </row>
     <row r="109" customHeight="1" spans="3:12">
       <c r="C109" s="1">
-        <v>11005</v>
+        <v>11004</v>
       </c>
       <c r="D109" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E109" s="7" t="s">
+      <c r="E109" s="1" t="s">
         <v>120</v>
       </c>
       <c r="F109" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G109" s="1">
-        <v>101</v>
+        <v>4001</v>
       </c>
       <c r="H109" s="1">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="I109" s="1">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="J109" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K109" s="2">
         <v>1</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:12">
       <c r="C110" s="1">
-        <v>11006</v>
+        <v>11005</v>
       </c>
       <c r="D110" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E110" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="E110" s="7" t="s">
-        <v>123</v>
-      </c>
       <c r="F110" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G110" s="1">
-        <v>501</v>
+        <v>101</v>
       </c>
       <c r="H110" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="I110" s="1">
         <v>10</v>
@@ -4487,59 +4490,59 @@
         <v>1</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:12">
       <c r="C111" s="1">
-        <v>11007</v>
+        <v>11006</v>
       </c>
       <c r="D111" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E111" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="E111" s="7" t="s">
+      <c r="F111" s="1">
+        <v>15</v>
+      </c>
+      <c r="G111" s="1">
+        <v>501</v>
+      </c>
+      <c r="H111" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I111" s="1">
+        <v>10</v>
+      </c>
+      <c r="J111" s="1">
+        <v>1</v>
+      </c>
+      <c r="K111" s="2">
+        <v>1</v>
+      </c>
+      <c r="L111" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="F111" s="1">
-        <v>10</v>
-      </c>
-      <c r="G111" s="1">
-        <v>1001</v>
-      </c>
-      <c r="H111" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I111" s="1">
-        <v>20</v>
-      </c>
-      <c r="J111" s="1">
-        <v>1</v>
-      </c>
-      <c r="K111" s="2">
-        <v>1</v>
-      </c>
-      <c r="L111" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:12">
       <c r="C112" s="1">
-        <v>11008</v>
+        <v>11007</v>
       </c>
       <c r="D112" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E112" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E112" s="7" t="s">
-        <v>129</v>
-      </c>
       <c r="F112" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G112" s="1">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H112" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I112" s="1">
         <v>20</v>
@@ -4551,59 +4554,59 @@
         <v>1</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:12">
       <c r="C113" s="1">
-        <v>11009</v>
+        <v>11008</v>
       </c>
       <c r="D113" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E113" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="E113" s="7" t="s">
+      <c r="F113" s="1">
+        <v>8</v>
+      </c>
+      <c r="G113" s="1">
+        <v>1501</v>
+      </c>
+      <c r="H113" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I113" s="1">
+        <v>20</v>
+      </c>
+      <c r="J113" s="1">
+        <v>1</v>
+      </c>
+      <c r="K113" s="2">
+        <v>1</v>
+      </c>
+      <c r="L113" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="F113" s="1">
-        <v>15</v>
-      </c>
-      <c r="G113" s="1">
-        <v>2001</v>
-      </c>
-      <c r="H113" s="1">
-        <v>2500</v>
-      </c>
-      <c r="I113" s="1">
-        <v>52</v>
-      </c>
-      <c r="J113" s="1">
-        <v>1</v>
-      </c>
-      <c r="K113" s="2">
-        <v>1</v>
-      </c>
-      <c r="L113" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:12">
       <c r="C114" s="1">
-        <v>11010</v>
+        <v>11009</v>
       </c>
       <c r="D114" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E114" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="E114" s="7" t="s">
-        <v>135</v>
-      </c>
       <c r="F114" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G114" s="1">
-        <v>2501</v>
+        <v>2001</v>
       </c>
       <c r="H114" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I114" s="1">
         <v>52</v>
@@ -4615,27 +4618,27 @@
         <v>1</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="3:12">
       <c r="C115" s="1">
-        <v>11011</v>
+        <v>11010</v>
       </c>
       <c r="D115" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="E115" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E115" s="7" t="s">
-        <v>138</v>
-      </c>
       <c r="F115" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G115" s="1">
-        <v>3001</v>
+        <v>2501</v>
       </c>
       <c r="H115" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="I115" s="1">
         <v>52</v>
@@ -4647,7 +4650,39 @@
         <v>1</v>
       </c>
       <c r="L115" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="3:12">
+      <c r="C116" s="1">
+        <v>11011</v>
+      </c>
+      <c r="D116" s="9" t="s">
         <v>139</v>
+      </c>
+      <c r="E116" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F116" s="1">
+        <v>3</v>
+      </c>
+      <c r="G116" s="1">
+        <v>3001</v>
+      </c>
+      <c r="H116" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I116" s="1">
+        <v>52</v>
+      </c>
+      <c r="J116" s="1">
+        <v>1</v>
+      </c>
+      <c r="K116" s="2">
+        <v>1</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -3254,7 +3254,7 @@
         <v>5000</v>
       </c>
       <c r="I66" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J66" s="2">
         <v>5</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="150">
   <si>
     <t>#</t>
   </si>
@@ -229,6 +229,30 @@
   </si>
   <si>
     <t>超级书页</t>
+  </si>
+  <si>
+    <t>1015</t>
+  </si>
+  <si>
+    <t>传奇精华</t>
+  </si>
+  <si>
+    <t>1016</t>
+  </si>
+  <si>
+    <t>不朽精华</t>
+  </si>
+  <si>
+    <t>1017</t>
+  </si>
+  <si>
+    <t>永恒精华</t>
+  </si>
+  <si>
+    <t>1018</t>
+  </si>
+  <si>
+    <t>混沌精华</t>
   </si>
   <si>
     <t>220036</t>
@@ -1162,8 +1186,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1483,7 +1507,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M116"/>
+  <dimension ref="A1:M120"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1871,13 +1895,13 @@
         <v>1250</v>
       </c>
       <c r="H14" s="1">
-        <v>4250</v>
+        <v>5250</v>
       </c>
       <c r="I14" s="1">
         <v>1000</v>
       </c>
       <c r="J14" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14" s="2">
         <v>1</v>
@@ -1903,13 +1927,13 @@
         <v>1350</v>
       </c>
       <c r="H15" s="1">
-        <v>4350</v>
+        <v>5350</v>
       </c>
       <c r="I15" s="1">
         <v>1000</v>
       </c>
       <c r="J15" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15" s="2">
         <v>1</v>
@@ -1935,13 +1959,13 @@
         <v>1450</v>
       </c>
       <c r="H16" s="1">
-        <v>4450</v>
+        <v>5450</v>
       </c>
       <c r="I16" s="1">
         <v>1000</v>
       </c>
       <c r="J16" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" s="2">
         <v>1</v>
@@ -2223,353 +2247,382 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:12">
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C26" s="2">
+        <v>21</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="2">
+        <v>3</v>
+      </c>
+      <c r="G26" s="2">
+        <v>4000</v>
+      </c>
+      <c r="H26" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I26" s="2">
+        <v>3</v>
+      </c>
+      <c r="J26" s="2">
+        <v>5</v>
+      </c>
+      <c r="K26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C27" s="2">
-        <v>151</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>56</v>
+        <v>22</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F27" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G27" s="2">
-        <v>300</v>
+        <v>5001</v>
       </c>
       <c r="H27" s="2">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="I27" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J27" s="2">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="K27" s="2">
         <v>1</v>
       </c>
-      <c r="L27" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:12">
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A28" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C28" s="2">
-        <v>152</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>59</v>
+        <v>23</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>60</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F28" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G28" s="2">
-        <v>1501</v>
+        <v>6001</v>
       </c>
       <c r="H28" s="2">
-        <v>4000</v>
+        <v>7000</v>
       </c>
       <c r="I28" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J28" s="2">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="K28" s="2">
         <v>1</v>
       </c>
-      <c r="L28" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:12">
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:11">
       <c r="C29" s="2">
-        <v>153</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>56</v>
+        <v>24</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>62</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F29" s="2">
         <v>3</v>
       </c>
       <c r="G29" s="2">
-        <v>4001</v>
+        <v>4800</v>
       </c>
       <c r="H29" s="2">
-        <v>10000</v>
+        <v>5300</v>
       </c>
       <c r="I29" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J29" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K29" s="2">
-        <v>2</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>58</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="4:4">
       <c r="D30" s="4"/>
     </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C31" s="1">
-        <v>100</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F31" s="1">
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C31" s="2">
+        <v>151</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F31" s="2">
+        <v>12</v>
+      </c>
+      <c r="G31" s="2">
+        <v>300</v>
+      </c>
+      <c r="H31" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I31" s="2">
+        <v>1</v>
+      </c>
+      <c r="J31" s="2">
+        <v>25</v>
+      </c>
+      <c r="K31" s="2">
+        <v>1</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C32" s="2">
+        <v>152</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F32" s="2">
+        <v>6</v>
+      </c>
+      <c r="G32" s="2">
+        <v>1501</v>
+      </c>
+      <c r="H32" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I32" s="2">
+        <v>1</v>
+      </c>
+      <c r="J32" s="2">
+        <v>25</v>
+      </c>
+      <c r="K32" s="2">
+        <v>1</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C33" s="2">
+        <v>153</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F33" s="2">
+        <v>3</v>
+      </c>
+      <c r="G33" s="2">
+        <v>4001</v>
+      </c>
+      <c r="H33" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I33" s="2">
+        <v>1</v>
+      </c>
+      <c r="J33" s="2">
+        <v>15</v>
+      </c>
+      <c r="K33" s="2">
+        <v>2</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="4:4">
+      <c r="D34" s="4"/>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C35" s="1">
+        <v>100</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F35" s="1">
         <v>50</v>
       </c>
-      <c r="G31" s="1">
-        <v>1</v>
-      </c>
-      <c r="H31" s="1">
+      <c r="G35" s="1">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1">
         <v>300</v>
       </c>
-      <c r="I31" s="1">
-        <v>1</v>
-      </c>
-      <c r="J31" s="1">
+      <c r="I35" s="1">
+        <v>1</v>
+      </c>
+      <c r="J35" s="1">
         <v>10000</v>
       </c>
-      <c r="K31" s="2">
-        <v>1</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
-      <c r="C32" s="1">
+      <c r="K35" s="2">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C36" s="1">
         <v>101</v>
       </c>
-      <c r="D32" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F32" s="1">
+      <c r="D36" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F36" s="1">
         <v>50</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G36" s="1">
         <v>301</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H36" s="1">
         <v>600</v>
       </c>
-      <c r="I32" s="1">
-        <v>1</v>
-      </c>
-      <c r="J32" s="1">
+      <c r="I36" s="1">
+        <v>1</v>
+      </c>
+      <c r="J36" s="1">
         <v>10000</v>
       </c>
-      <c r="K32" s="2">
+      <c r="K36" s="2">
         <v>2</v>
       </c>
-      <c r="L32" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:12">
-      <c r="C33" s="1">
+      <c r="L36" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:12">
+      <c r="C37" s="1">
         <v>102</v>
       </c>
-      <c r="D33" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F33" s="1">
+      <c r="D37" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F37" s="1">
         <v>50</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G37" s="1">
         <v>601</v>
       </c>
-      <c r="H33" s="1">
+      <c r="H37" s="1">
         <v>1000</v>
       </c>
-      <c r="I33" s="1">
-        <v>1</v>
-      </c>
-      <c r="J33" s="1">
+      <c r="I37" s="1">
+        <v>1</v>
+      </c>
+      <c r="J37" s="1">
         <v>10000</v>
       </c>
-      <c r="K33" s="2">
+      <c r="K37" s="2">
         <v>4</v>
       </c>
-      <c r="L33" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:12">
-      <c r="C34" s="1">
+      <c r="L37" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:12">
+      <c r="C38" s="1">
         <v>103</v>
       </c>
-      <c r="D34" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F34" s="1">
+      <c r="D38" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F38" s="1">
         <v>50</v>
       </c>
-      <c r="G34" s="1">
+      <c r="G38" s="1">
         <v>1001</v>
       </c>
-      <c r="H34" s="1">
+      <c r="H38" s="1">
         <v>1500</v>
       </c>
-      <c r="I34" s="1">
-        <v>1</v>
-      </c>
-      <c r="J34" s="1">
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="J38" s="1">
         <v>10000</v>
       </c>
-      <c r="K34" s="2">
+      <c r="K38" s="2">
         <v>10</v>
       </c>
-      <c r="L34" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C35" s="1">
+      <c r="L38" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C39" s="1">
         <v>104</v>
       </c>
-      <c r="D35" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F35" s="2">
-        <v>50</v>
-      </c>
-      <c r="G35" s="2">
-        <v>1501</v>
-      </c>
-      <c r="H35" s="2">
-        <v>3500</v>
-      </c>
-      <c r="I35" s="2">
-        <v>1</v>
-      </c>
-      <c r="J35" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K35" s="2">
-        <v>20</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C36" s="1">
-        <v>105</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F36" s="2">
-        <v>50</v>
-      </c>
-      <c r="G36" s="2">
-        <v>3501</v>
-      </c>
-      <c r="H36" s="2">
-        <v>10000</v>
-      </c>
-      <c r="I36" s="2">
-        <v>1</v>
-      </c>
-      <c r="J36" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K36" s="2">
-        <v>40</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D37" s="4"/>
-    </row>
-    <row r="38" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
-      <c r="C38" s="2">
-        <v>200</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F38" s="2">
-        <v>50</v>
-      </c>
-      <c r="G38" s="2">
-        <v>1</v>
-      </c>
-      <c r="H38" s="2">
-        <v>300</v>
-      </c>
-      <c r="I38" s="2">
-        <v>1</v>
-      </c>
-      <c r="J38" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K38" s="2">
-        <v>1</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C39" s="2">
-        <v>201</v>
-      </c>
       <c r="D39" s="8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F39" s="2">
         <v>50</v>
       </c>
       <c r="G39" s="2">
-        <v>301</v>
+        <v>1501</v>
       </c>
       <c r="H39" s="2">
-        <v>600</v>
+        <v>3500</v>
       </c>
       <c r="I39" s="2">
         <v>1</v>
@@ -2578,30 +2631,30 @@
         <v>10000</v>
       </c>
       <c r="K39" s="2">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C40" s="2">
-        <v>202</v>
+      <c r="C40" s="1">
+        <v>105</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F40" s="2">
         <v>50</v>
       </c>
       <c r="G40" s="2">
-        <v>601</v>
+        <v>3501</v>
       </c>
       <c r="H40" s="2">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="I40" s="2">
         <v>1</v>
@@ -2610,62 +2663,33 @@
         <v>10000</v>
       </c>
       <c r="K40" s="2">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C41" s="2">
-        <v>203</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F41" s="2">
-        <v>50</v>
-      </c>
-      <c r="G41" s="2">
-        <v>1001</v>
-      </c>
-      <c r="H41" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I41" s="2">
-        <v>1</v>
-      </c>
-      <c r="J41" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K41" s="2">
-        <v>10</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>64</v>
-      </c>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="4:4">
+      <c r="D41" s="4"/>
     </row>
     <row r="42" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
       <c r="C42" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F42" s="2">
         <v>50</v>
       </c>
       <c r="G42" s="2">
-        <v>1501</v>
+        <v>1</v>
       </c>
       <c r="H42" s="2">
-        <v>3500</v>
+        <v>300</v>
       </c>
       <c r="I42" s="2">
         <v>1</v>
@@ -2674,30 +2698,30 @@
         <v>10000</v>
       </c>
       <c r="K42" s="2">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C43" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F43" s="2">
         <v>50</v>
       </c>
       <c r="G43" s="2">
-        <v>3501</v>
+        <v>301</v>
       </c>
       <c r="H43" s="2">
-        <v>10000</v>
+        <v>600</v>
       </c>
       <c r="I43" s="2">
         <v>1</v>
@@ -2706,33 +2730,62 @@
         <v>10000</v>
       </c>
       <c r="K43" s="2">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="44" s="2" customFormat="1" ht="20" customHeight="1" spans="4:4">
-      <c r="D44" s="4"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C44" s="2">
+        <v>202</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F44" s="2">
+        <v>50</v>
+      </c>
+      <c r="G44" s="2">
+        <v>601</v>
+      </c>
+      <c r="H44" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I44" s="2">
+        <v>1</v>
+      </c>
+      <c r="J44" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K44" s="2">
+        <v>4</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C45" s="2">
-        <v>300</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>67</v>
+        <v>203</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F45" s="2">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G45" s="2">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="H45" s="2">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I45" s="2">
         <v>1</v>
@@ -2741,30 +2794,30 @@
         <v>10000</v>
       </c>
       <c r="K45" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:12">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
       <c r="C46" s="2">
-        <v>301</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>67</v>
+        <v>204</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F46" s="2">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G46" s="2">
-        <v>1001</v>
+        <v>1501</v>
       </c>
       <c r="H46" s="2">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="I46" s="2">
         <v>1</v>
@@ -2773,27 +2826,27 @@
         <v>10000</v>
       </c>
       <c r="K46" s="2">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:12">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
       <c r="C47" s="2">
-        <v>302</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>67</v>
+        <v>205</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F47" s="2">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G47" s="2">
-        <v>3001</v>
+        <v>3501</v>
       </c>
       <c r="H47" s="2">
         <v>10000</v>
@@ -2805,28 +2858,30 @@
         <v>10000</v>
       </c>
       <c r="K47" s="2">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" customHeight="1"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" ht="20" customHeight="1" spans="4:4">
+      <c r="D48" s="4"/>
+    </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C49" s="2">
-        <v>400</v>
-      </c>
-      <c r="D49" s="10" t="s">
-        <v>69</v>
+        <v>300</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F49" s="2">
         <v>10</v>
       </c>
       <c r="G49" s="2">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H49" s="2">
         <v>1000</v>
@@ -2846,13 +2901,13 @@
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C50" s="2">
-        <v>401</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>69</v>
+        <v>301</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F50" s="2">
         <v>10</v>
@@ -2878,13 +2933,13 @@
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C51" s="2">
-        <v>402</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>69</v>
+        <v>302</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F51" s="2">
         <v>10</v>
@@ -2911,19 +2966,19 @@
     <row r="52" s="2" customFormat="1" customHeight="1"/>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C53" s="2">
-        <v>500</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>71</v>
+        <v>400</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F53" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G53" s="2">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="H53" s="2">
         <v>1000</v>
@@ -2932,27 +2987,27 @@
         <v>1</v>
       </c>
       <c r="J53" s="2">
-        <v>20</v>
+        <v>10000</v>
       </c>
       <c r="K53" s="2">
         <v>1</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C54" s="2">
-        <v>501</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>71</v>
+        <v>401</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F54" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G54" s="2">
         <v>1001</v>
@@ -2964,27 +3019,27 @@
         <v>1</v>
       </c>
       <c r="J54" s="2">
-        <v>20</v>
+        <v>10000</v>
       </c>
       <c r="K54" s="2">
         <v>2</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C55" s="2">
-        <v>502</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>71</v>
+        <v>402</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F55" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G55" s="2">
         <v>3001</v>
@@ -2996,31 +3051,31 @@
         <v>1</v>
       </c>
       <c r="J55" s="2">
-        <v>20</v>
+        <v>10000</v>
       </c>
       <c r="K55" s="2">
         <v>3</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" s="2" customFormat="1" customHeight="1"/>
     <row r="57" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C57" s="2">
-        <v>600</v>
-      </c>
-      <c r="D57" s="2">
-        <v>3001</v>
+        <v>500</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>79</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F57" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G57" s="2">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="H57" s="2">
         <v>1000</v>
@@ -3029,27 +3084,27 @@
         <v>1</v>
       </c>
       <c r="J57" s="2">
-        <v>10000</v>
+        <v>20</v>
       </c>
       <c r="K57" s="2">
         <v>1</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C58" s="2">
-        <v>601</v>
-      </c>
-      <c r="D58" s="2">
-        <v>3001</v>
+        <v>501</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>79</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F58" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G58" s="2">
         <v>1001</v>
@@ -3061,27 +3116,27 @@
         <v>1</v>
       </c>
       <c r="J58" s="2">
-        <v>10000</v>
+        <v>20</v>
       </c>
       <c r="K58" s="2">
         <v>2</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C59" s="2">
-        <v>602</v>
-      </c>
-      <c r="D59" s="2">
-        <v>3001</v>
+        <v>502</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>79</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F59" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G59" s="2">
         <v>3001</v>
@@ -3093,31 +3148,31 @@
         <v>1</v>
       </c>
       <c r="J59" s="2">
-        <v>10000</v>
+        <v>20</v>
       </c>
       <c r="K59" s="2">
         <v>3</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1"/>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C61" s="2">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="D61" s="2">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F61" s="2">
         <v>10</v>
       </c>
       <c r="G61" s="2">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="H61" s="2">
         <v>1000</v>
@@ -3137,13 +3192,13 @@
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C62" s="2">
-        <v>701</v>
+        <v>601</v>
       </c>
       <c r="D62" s="2">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F62" s="2">
         <v>10</v>
@@ -3169,13 +3224,13 @@
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C63" s="2">
-        <v>702</v>
+        <v>602</v>
       </c>
       <c r="D63" s="2">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F63" s="2">
         <v>10</v>
@@ -3199,36 +3254,34 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64" customHeight="1" spans="11:11">
-      <c r="K64" s="2"/>
-    </row>
+    <row r="64" s="2" customFormat="1" customHeight="1"/>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C65" s="2">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="D65" s="2">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F65" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G65" s="2">
-        <v>4001</v>
+        <v>200</v>
       </c>
       <c r="H65" s="2">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="I65" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J65" s="2">
-        <v>13</v>
+        <v>10000</v>
       </c>
       <c r="K65" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>21</v>
@@ -3236,379 +3289,350 @@
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C66" s="2">
-        <v>801</v>
+        <v>701</v>
       </c>
       <c r="D66" s="2">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F66" s="2">
+        <v>10</v>
+      </c>
+      <c r="G66" s="2">
+        <v>1001</v>
+      </c>
+      <c r="H66" s="2">
+        <v>3000</v>
+      </c>
+      <c r="I66" s="2">
+        <v>1</v>
+      </c>
+      <c r="J66" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K66" s="2">
         <v>2</v>
-      </c>
-      <c r="G66" s="2">
-        <v>4001</v>
-      </c>
-      <c r="H66" s="2">
-        <v>5000</v>
-      </c>
-      <c r="I66" s="2">
-        <v>13</v>
-      </c>
-      <c r="J66" s="2">
-        <v>5</v>
-      </c>
-      <c r="K66" s="2">
-        <v>1</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="68" customHeight="1" spans="3:11">
-      <c r="C68" s="1">
-        <v>901</v>
-      </c>
-      <c r="D68" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F68" s="1">
-        <v>20</v>
-      </c>
-      <c r="G68" s="1">
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C67" s="2">
+        <v>702</v>
+      </c>
+      <c r="D67" s="2">
+        <v>3002</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F67" s="2">
+        <v>10</v>
+      </c>
+      <c r="G67" s="2">
         <v>3001</v>
       </c>
-      <c r="H68" s="1">
-        <v>4000</v>
-      </c>
-      <c r="I68" s="1">
+      <c r="H67" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I67" s="2">
+        <v>1</v>
+      </c>
+      <c r="J67" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K67" s="2">
         <v>3</v>
       </c>
-      <c r="J68" s="1">
-        <v>30</v>
-      </c>
-      <c r="K68" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" customHeight="1" spans="3:11">
-      <c r="C69" s="1">
-        <v>902</v>
-      </c>
-      <c r="D69" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F69" s="1">
-        <v>10</v>
-      </c>
-      <c r="G69" s="1">
-        <v>3001</v>
-      </c>
-      <c r="H69" s="1">
-        <v>4000</v>
-      </c>
-      <c r="I69" s="1">
-        <v>3</v>
-      </c>
-      <c r="J69" s="1">
+      <c r="L67" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="11:11">
+      <c r="K68" s="2"/>
+    </row>
+    <row r="69" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C69" s="2">
+        <v>800</v>
+      </c>
+      <c r="D69" s="2">
+        <v>3003</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F69" s="2">
+        <v>2</v>
+      </c>
+      <c r="G69" s="2">
+        <v>4001</v>
+      </c>
+      <c r="H69" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I69" s="2">
+        <v>7</v>
+      </c>
+      <c r="J69" s="2">
+        <v>13</v>
+      </c>
+      <c r="K69" s="2">
         <v>5</v>
       </c>
-      <c r="K69" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="3:11">
-      <c r="C70" s="1">
-        <v>903</v>
-      </c>
-      <c r="D70" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F70" s="1">
+      <c r="L69" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C70" s="2">
+        <v>801</v>
+      </c>
+      <c r="D70" s="2">
+        <v>3004</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F70" s="2">
+        <v>2</v>
+      </c>
+      <c r="G70" s="2">
+        <v>4001</v>
+      </c>
+      <c r="H70" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I70" s="2">
+        <v>13</v>
+      </c>
+      <c r="J70" s="2">
         <v>5</v>
       </c>
-      <c r="G70" s="1">
-        <v>3001</v>
-      </c>
-      <c r="H70" s="1">
-        <v>4000</v>
-      </c>
-      <c r="I70" s="1">
-        <v>3</v>
-      </c>
-      <c r="J70" s="1">
-        <v>3</v>
-      </c>
       <c r="K70" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" customHeight="1" spans="3:11">
-      <c r="C71" s="1">
-        <v>904</v>
-      </c>
-      <c r="D71" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F71" s="1">
-        <v>2</v>
-      </c>
-      <c r="G71" s="1">
-        <v>3501</v>
-      </c>
-      <c r="H71" s="1">
-        <v>5000</v>
-      </c>
-      <c r="I71" s="1">
-        <v>4</v>
-      </c>
-      <c r="J71" s="1">
-        <v>5</v>
-      </c>
-      <c r="K71" s="2">
-        <v>1</v>
+      <c r="L70" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
       <c r="C72" s="1">
-        <v>905</v>
-      </c>
-      <c r="D72" s="11" t="s">
-        <v>78</v>
+        <v>901</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F72" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G72" s="1">
-        <v>4001</v>
+        <v>3001</v>
       </c>
       <c r="H72" s="1">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="I72" s="1">
         <v>3</v>
       </c>
       <c r="J72" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K72" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
       <c r="C73" s="1">
-        <v>906</v>
-      </c>
-      <c r="D73" s="11" t="s">
-        <v>80</v>
+        <v>902</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F73" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G73" s="1">
-        <v>4001</v>
+        <v>3001</v>
       </c>
       <c r="H73" s="1">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="I73" s="1">
         <v>3</v>
       </c>
       <c r="J73" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K73" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
       <c r="C74" s="1">
-        <v>907</v>
-      </c>
-      <c r="D74" s="11" t="s">
-        <v>82</v>
+        <v>903</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>90</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F74" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G74" s="1">
-        <v>4001</v>
+        <v>3001</v>
       </c>
       <c r="H74" s="1">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="I74" s="1">
         <v>3</v>
       </c>
       <c r="J74" s="1">
+        <v>3</v>
+      </c>
+      <c r="K74" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:11">
+      <c r="C75" s="1">
+        <v>904</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F75" s="1">
         <v>2</v>
       </c>
-      <c r="K74" s="2">
+      <c r="G75" s="1">
+        <v>3501</v>
+      </c>
+      <c r="H75" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I75" s="1">
+        <v>4</v>
+      </c>
+      <c r="J75" s="1">
+        <v>5</v>
+      </c>
+      <c r="K75" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:11">
+      <c r="C76" s="1">
+        <v>905</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F76" s="1">
+        <v>10</v>
+      </c>
+      <c r="G76" s="1">
+        <v>4001</v>
+      </c>
+      <c r="H76" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I76" s="1">
+        <v>3</v>
+      </c>
+      <c r="J76" s="1">
+        <v>20</v>
+      </c>
+      <c r="K76" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="3:12">
+    <row r="77" customHeight="1" spans="3:11">
       <c r="C77" s="1">
-        <v>10001</v>
-      </c>
-      <c r="D77" s="6">
-        <v>180001</v>
+        <v>906</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F77" s="1">
-        <v>2000</v>
+        <v>5</v>
       </c>
       <c r="G77" s="1">
-        <v>100</v>
+        <v>4001</v>
       </c>
       <c r="H77" s="1">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="I77" s="1">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="J77" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K77" s="2">
-        <v>1</v>
-      </c>
-      <c r="L77" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="78" customHeight="1" spans="3:12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:11">
       <c r="C78" s="1">
-        <v>10002</v>
-      </c>
-      <c r="D78" s="6">
-        <v>180002</v>
+        <v>907</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>90</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F78" s="1">
-        <v>4000</v>
+        <v>3</v>
       </c>
       <c r="G78" s="1">
-        <v>100</v>
+        <v>4001</v>
       </c>
       <c r="H78" s="1">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="I78" s="1">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="J78" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K78" s="2">
-        <v>1</v>
-      </c>
-      <c r="L78" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="79" customHeight="1" spans="3:12">
-      <c r="C79" s="1">
-        <v>10003</v>
-      </c>
-      <c r="D79" s="6">
-        <v>180003</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F79" s="1">
-        <v>150000</v>
-      </c>
-      <c r="G79" s="1">
-        <v>100</v>
-      </c>
-      <c r="H79" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I79" s="1">
-        <v>100</v>
-      </c>
-      <c r="J79" s="1">
-        <v>5</v>
-      </c>
-      <c r="K79" s="2">
-        <v>1</v>
-      </c>
-      <c r="L79" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="80" customHeight="1" spans="3:12">
-      <c r="C80" s="1">
-        <v>10004</v>
-      </c>
-      <c r="D80" s="6">
-        <v>180004</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F80" s="1">
-        <v>8000</v>
-      </c>
-      <c r="G80" s="1">
-        <v>100</v>
-      </c>
-      <c r="H80" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I80" s="1">
-        <v>100</v>
-      </c>
-      <c r="J80" s="1">
-        <v>1</v>
-      </c>
-      <c r="K80" s="2">
-        <v>1</v>
-      </c>
-      <c r="L80" s="1" t="s">
-        <v>87</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:12">
       <c r="C81" s="1">
-        <v>10005</v>
+        <v>10001</v>
       </c>
       <c r="D81" s="6">
-        <v>180005</v>
+        <v>180001</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F81" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G81" s="1">
         <v>100</v>
@@ -3626,21 +3650,21 @@
         <v>1</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:12">
       <c r="C82" s="1">
-        <v>10006</v>
+        <v>10002</v>
       </c>
       <c r="D82" s="6">
-        <v>180006</v>
+        <v>180002</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F82" s="1">
-        <v>50000</v>
+        <v>4000</v>
       </c>
       <c r="G82" s="1">
         <v>100</v>
@@ -3652,27 +3676,27 @@
         <v>100</v>
       </c>
       <c r="J82" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K82" s="2">
         <v>1</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:12">
       <c r="C83" s="1">
-        <v>10007</v>
+        <v>10003</v>
       </c>
       <c r="D83" s="6">
-        <v>180007</v>
+        <v>180003</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F83" s="1">
-        <v>2000</v>
+        <v>150000</v>
       </c>
       <c r="G83" s="1">
         <v>100</v>
@@ -3684,27 +3708,27 @@
         <v>100</v>
       </c>
       <c r="J83" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K83" s="2">
         <v>1</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:12">
       <c r="C84" s="1">
-        <v>10008</v>
+        <v>10004</v>
       </c>
       <c r="D84" s="6">
-        <v>180008</v>
+        <v>180004</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F84" s="1">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="G84" s="1">
         <v>100</v>
@@ -3716,24 +3740,24 @@
         <v>100</v>
       </c>
       <c r="J84" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K84" s="2">
         <v>1</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:12">
       <c r="C85" s="1">
-        <v>10009</v>
+        <v>10005</v>
       </c>
       <c r="D85" s="6">
-        <v>180009</v>
+        <v>180005</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F85" s="1">
         <v>3000</v>
@@ -3754,21 +3778,21 @@
         <v>1</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:12">
       <c r="C86" s="1">
-        <v>10010</v>
+        <v>10006</v>
       </c>
       <c r="D86" s="6">
-        <v>180010</v>
+        <v>180006</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F86" s="1">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="G86" s="1">
         <v>100</v>
@@ -3780,27 +3804,27 @@
         <v>100</v>
       </c>
       <c r="J86" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K86" s="2">
         <v>1</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:12">
       <c r="C87" s="1">
-        <v>10011</v>
+        <v>10007</v>
       </c>
       <c r="D87" s="6">
-        <v>180011</v>
+        <v>180007</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F87" s="1">
-        <v>100000</v>
+        <v>2000</v>
       </c>
       <c r="G87" s="1">
         <v>100</v>
@@ -3812,27 +3836,27 @@
         <v>100</v>
       </c>
       <c r="J87" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K87" s="2">
         <v>1</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:12">
       <c r="C88" s="1">
-        <v>10012</v>
+        <v>10008</v>
       </c>
       <c r="D88" s="6">
-        <v>180012</v>
+        <v>180008</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F88" s="1">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="G88" s="1">
         <v>100</v>
@@ -3844,27 +3868,27 @@
         <v>100</v>
       </c>
       <c r="J88" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K88" s="2">
         <v>1</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:12">
       <c r="C89" s="1">
-        <v>10013</v>
+        <v>10009</v>
       </c>
       <c r="D89" s="6">
-        <v>180013</v>
+        <v>180009</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F89" s="1">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="G89" s="1">
         <v>100</v>
@@ -3876,27 +3900,27 @@
         <v>100</v>
       </c>
       <c r="J89" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K89" s="2">
         <v>1</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:12">
       <c r="C90" s="1">
-        <v>10014</v>
+        <v>10010</v>
       </c>
       <c r="D90" s="6">
-        <v>180014</v>
+        <v>180010</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F90" s="1">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="G90" s="1">
         <v>100</v>
@@ -3908,24 +3932,24 @@
         <v>100</v>
       </c>
       <c r="J90" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K90" s="2">
         <v>1</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:12">
       <c r="C91" s="1">
-        <v>10015</v>
+        <v>10011</v>
       </c>
       <c r="D91" s="6">
-        <v>180015</v>
+        <v>180011</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F91" s="1">
         <v>100000</v>
@@ -3946,21 +3970,21 @@
         <v>1</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:12">
       <c r="C92" s="1">
-        <v>10016</v>
+        <v>10012</v>
       </c>
       <c r="D92" s="6">
-        <v>180020</v>
+        <v>180012</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F92" s="1">
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="G92" s="1">
         <v>100</v>
@@ -3972,27 +3996,27 @@
         <v>100</v>
       </c>
       <c r="J92" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K92" s="2">
         <v>1</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:12">
       <c r="C93" s="1">
-        <v>10017</v>
+        <v>10013</v>
       </c>
       <c r="D93" s="6">
-        <v>180021</v>
+        <v>180013</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F93" s="1">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="G93" s="1">
         <v>100</v>
@@ -4004,27 +4028,27 @@
         <v>100</v>
       </c>
       <c r="J93" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K93" s="2">
         <v>1</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:12">
       <c r="C94" s="1">
-        <v>10018</v>
+        <v>10014</v>
       </c>
       <c r="D94" s="6">
-        <v>180022</v>
+        <v>180014</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F94" s="1">
-        <v>3000</v>
+        <v>100000</v>
       </c>
       <c r="G94" s="1">
         <v>100</v>
@@ -4036,97 +4060,129 @@
         <v>100</v>
       </c>
       <c r="J94" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K94" s="2">
         <v>1</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="3:12">
+      <c r="C95" s="1">
+        <v>10015</v>
+      </c>
+      <c r="D95" s="6">
+        <v>180015</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F95" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G95" s="1">
+        <v>100</v>
+      </c>
+      <c r="H95" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I95" s="1">
+        <v>100</v>
+      </c>
+      <c r="J95" s="1">
+        <v>5</v>
+      </c>
+      <c r="K95" s="2">
+        <v>1</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:12">
       <c r="C96" s="1">
-        <v>10030</v>
-      </c>
-      <c r="D96" s="1">
-        <v>180030</v>
+        <v>10016</v>
+      </c>
+      <c r="D96" s="6">
+        <v>180020</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F96" s="1">
-        <v>5</v>
+        <v>30000</v>
       </c>
       <c r="G96" s="1">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="H96" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I96" s="1">
         <v>100</v>
       </c>
       <c r="J96" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K96" s="2">
         <v>1</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:12">
       <c r="C97" s="1">
-        <v>10031</v>
+        <v>10017</v>
       </c>
       <c r="D97" s="6">
-        <v>180032</v>
+        <v>180021</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F97" s="1">
-        <v>1</v>
+        <v>30000</v>
       </c>
       <c r="G97" s="1">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="H97" s="1">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I97" s="1">
         <v>100</v>
       </c>
       <c r="J97" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K97" s="2">
         <v>1</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:12">
       <c r="C98" s="1">
-        <v>10032</v>
+        <v>10018</v>
       </c>
       <c r="D98" s="6">
-        <v>180033</v>
+        <v>180022</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F98" s="1">
-        <v>1</v>
+        <v>3000</v>
       </c>
       <c r="G98" s="1">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="H98" s="1">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I98" s="1">
         <v>100</v>
@@ -4138,59 +4194,27 @@
         <v>1</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="99" customHeight="1" spans="3:12">
-      <c r="C99" s="1">
-        <v>10033</v>
-      </c>
-      <c r="D99" s="6">
-        <v>180034</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F99" s="1">
-        <v>2</v>
-      </c>
-      <c r="G99" s="1">
-        <v>1100</v>
-      </c>
-      <c r="H99" s="1">
-        <v>3000</v>
-      </c>
-      <c r="I99" s="1">
-        <v>100</v>
-      </c>
-      <c r="J99" s="1">
-        <v>1</v>
-      </c>
-      <c r="K99" s="2">
-        <v>1</v>
-      </c>
-      <c r="L99" s="1" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:12">
       <c r="C100" s="1">
-        <v>10034</v>
-      </c>
-      <c r="D100" s="6">
-        <v>180035</v>
+        <v>10030</v>
+      </c>
+      <c r="D100" s="1">
+        <v>180030</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F100" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G100" s="1">
-        <v>2000</v>
+        <v>1100</v>
       </c>
       <c r="H100" s="1">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="I100" s="1">
         <v>100</v>
@@ -4202,28 +4226,28 @@
         <v>1</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:12">
       <c r="C101" s="1">
-        <v>10035</v>
+        <v>10031</v>
       </c>
       <c r="D101" s="6">
-        <v>180036</v>
+        <v>180032</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F101" s="1">
         <v>1</v>
       </c>
       <c r="G101" s="1">
+        <v>1100</v>
+      </c>
+      <c r="H101" s="1">
         <v>2000</v>
       </c>
-      <c r="H101" s="1">
-        <v>2500</v>
-      </c>
       <c r="I101" s="1">
         <v>100</v>
       </c>
@@ -4234,27 +4258,27 @@
         <v>1</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:12">
       <c r="C102" s="1">
-        <v>10036</v>
+        <v>10032</v>
       </c>
       <c r="D102" s="6">
-        <v>180037</v>
+        <v>180033</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F102" s="1">
         <v>1</v>
       </c>
       <c r="G102" s="1">
-        <v>2500</v>
+        <v>1600</v>
       </c>
       <c r="H102" s="1">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="I102" s="1">
         <v>100</v>
@@ -4266,27 +4290,27 @@
         <v>1</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:12">
       <c r="C103" s="1">
-        <v>10037</v>
+        <v>10033</v>
       </c>
       <c r="D103" s="6">
-        <v>180038</v>
+        <v>180034</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F103" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G103" s="1">
-        <v>1600</v>
+        <v>1100</v>
       </c>
       <c r="H103" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="I103" s="1">
         <v>100</v>
@@ -4298,27 +4322,27 @@
         <v>1</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:12">
       <c r="C104" s="1">
-        <v>10038</v>
+        <v>10034</v>
       </c>
       <c r="D104" s="6">
-        <v>180039</v>
+        <v>180035</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F104" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G104" s="1">
         <v>2000</v>
       </c>
       <c r="H104" s="1">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="I104" s="1">
         <v>100</v>
@@ -4330,286 +4354,286 @@
         <v>1</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="3:12">
+      <c r="C105" s="1">
+        <v>10035</v>
+      </c>
+      <c r="D105" s="6">
+        <v>180036</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F105" s="1">
+        <v>1</v>
+      </c>
+      <c r="G105" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H105" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I105" s="1">
+        <v>100</v>
+      </c>
+      <c r="J105" s="1">
+        <v>1</v>
+      </c>
+      <c r="K105" s="2">
+        <v>1</v>
+      </c>
+      <c r="L105" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:12">
       <c r="C106" s="1">
-        <v>11001</v>
-      </c>
-      <c r="D106" s="9" t="s">
-        <v>115</v>
+        <v>10036</v>
+      </c>
+      <c r="D106" s="6">
+        <v>180037</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F106" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G106" s="1">
-        <v>150</v>
+        <v>2500</v>
       </c>
       <c r="H106" s="1">
-        <v>1200</v>
+        <v>3500</v>
       </c>
       <c r="I106" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="J106" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K106" s="2">
         <v>1</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:12">
       <c r="C107" s="1">
-        <v>11002</v>
-      </c>
-      <c r="D107" s="9" t="s">
-        <v>117</v>
+        <v>10037</v>
+      </c>
+      <c r="D107" s="6">
+        <v>180038</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F107" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G107" s="1">
-        <v>200</v>
+        <v>1600</v>
       </c>
       <c r="H107" s="1">
-        <v>1000</v>
+        <v>3500</v>
       </c>
       <c r="I107" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J107" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K107" s="2">
         <v>1</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:12">
       <c r="C108" s="1">
-        <v>11003</v>
-      </c>
-      <c r="D108" s="9" t="s">
-        <v>119</v>
+        <v>10038</v>
+      </c>
+      <c r="D108" s="6">
+        <v>180039</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F108" s="1">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G108" s="1">
-        <v>1050</v>
+        <v>2000</v>
       </c>
       <c r="H108" s="1">
-        <v>1500</v>
+        <v>3500</v>
       </c>
       <c r="I108" s="1">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="J108" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K108" s="2">
         <v>1</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="109" customHeight="1" spans="3:12">
-      <c r="C109" s="1">
-        <v>11004</v>
-      </c>
-      <c r="D109" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F109" s="1">
-        <v>5</v>
-      </c>
-      <c r="G109" s="1">
-        <v>4001</v>
-      </c>
-      <c r="H109" s="1">
-        <v>6000</v>
-      </c>
-      <c r="I109" s="1">
-        <v>53</v>
-      </c>
-      <c r="J109" s="1">
-        <v>2</v>
-      </c>
-      <c r="K109" s="2">
-        <v>1</v>
-      </c>
-      <c r="L109" s="1" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:12">
       <c r="C110" s="1">
-        <v>11005</v>
+        <v>11001</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E110" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="F110" s="1">
+        <v>5</v>
+      </c>
+      <c r="G110" s="1">
+        <v>150</v>
+      </c>
+      <c r="H110" s="1">
+        <v>1200</v>
+      </c>
+      <c r="I110" s="1">
         <v>20</v>
       </c>
-      <c r="G110" s="1">
-        <v>101</v>
-      </c>
-      <c r="H110" s="1">
-        <v>500</v>
-      </c>
-      <c r="I110" s="1">
-        <v>10</v>
-      </c>
       <c r="J110" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K110" s="2">
         <v>1</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>123</v>
+        <v>39</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:12">
       <c r="C111" s="1">
-        <v>11006</v>
+        <v>11002</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="E111" s="7" t="s">
         <v>125</v>
       </c>
+      <c r="E111" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="F111" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G111" s="1">
-        <v>501</v>
+        <v>200</v>
       </c>
       <c r="H111" s="1">
         <v>1000</v>
       </c>
       <c r="I111" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J111" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K111" s="2">
         <v>1</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>126</v>
+        <v>39</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:12">
       <c r="C112" s="1">
-        <v>11007</v>
+        <v>11003</v>
       </c>
       <c r="D112" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="E112" s="7" t="s">
+      <c r="E112" s="1" t="s">
         <v>128</v>
       </c>
       <c r="F112" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G112" s="1">
-        <v>1001</v>
+        <v>1050</v>
       </c>
       <c r="H112" s="1">
         <v>1500</v>
       </c>
       <c r="I112" s="1">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="J112" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K112" s="2">
         <v>1</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>129</v>
+        <v>39</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:12">
       <c r="C113" s="1">
-        <v>11008</v>
+        <v>11004</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E113" s="7" t="s">
-        <v>131</v>
+        <v>127</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="F113" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G113" s="1">
-        <v>1501</v>
+        <v>4001</v>
       </c>
       <c r="H113" s="1">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="I113" s="1">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="J113" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K113" s="2">
         <v>1</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>132</v>
+        <v>39</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:12">
       <c r="C114" s="1">
-        <v>11009</v>
+        <v>11005</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F114" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G114" s="1">
-        <v>2001</v>
+        <v>101</v>
       </c>
       <c r="H114" s="1">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="I114" s="1">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="J114" s="1">
         <v>1</v>
@@ -4618,30 +4642,30 @@
         <v>1</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="3:12">
       <c r="C115" s="1">
-        <v>11010</v>
+        <v>11006</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F115" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G115" s="1">
-        <v>2501</v>
+        <v>501</v>
       </c>
       <c r="H115" s="1">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I115" s="1">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="J115" s="1">
         <v>1</v>
@@ -4650,39 +4674,167 @@
         <v>1</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="3:12">
       <c r="C116" s="1">
+        <v>11007</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E116" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F116" s="1">
+        <v>10</v>
+      </c>
+      <c r="G116" s="1">
+        <v>1001</v>
+      </c>
+      <c r="H116" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I116" s="1">
+        <v>20</v>
+      </c>
+      <c r="J116" s="1">
+        <v>1</v>
+      </c>
+      <c r="K116" s="2">
+        <v>1</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="3:12">
+      <c r="C117" s="1">
+        <v>11008</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E117" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F117" s="1">
+        <v>8</v>
+      </c>
+      <c r="G117" s="1">
+        <v>1501</v>
+      </c>
+      <c r="H117" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I117" s="1">
+        <v>20</v>
+      </c>
+      <c r="J117" s="1">
+        <v>1</v>
+      </c>
+      <c r="K117" s="2">
+        <v>1</v>
+      </c>
+      <c r="L117" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="3:12">
+      <c r="C118" s="1">
+        <v>11009</v>
+      </c>
+      <c r="D118" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E118" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="F118" s="1">
+        <v>15</v>
+      </c>
+      <c r="G118" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H118" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I118" s="1">
+        <v>52</v>
+      </c>
+      <c r="J118" s="1">
+        <v>1</v>
+      </c>
+      <c r="K118" s="2">
+        <v>1</v>
+      </c>
+      <c r="L118" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="3:12">
+      <c r="C119" s="1">
+        <v>11010</v>
+      </c>
+      <c r="D119" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E119" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F119" s="1">
+        <v>7</v>
+      </c>
+      <c r="G119" s="1">
+        <v>2501</v>
+      </c>
+      <c r="H119" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I119" s="1">
+        <v>52</v>
+      </c>
+      <c r="J119" s="1">
+        <v>1</v>
+      </c>
+      <c r="K119" s="2">
+        <v>1</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="3:12">
+      <c r="C120" s="1">
         <v>11011</v>
       </c>
-      <c r="D116" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E116" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="F116" s="1">
+      <c r="D120" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="E120" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F120" s="1">
         <v>3</v>
       </c>
-      <c r="G116" s="1">
+      <c r="G120" s="1">
         <v>3001</v>
       </c>
-      <c r="H116" s="1">
+      <c r="H120" s="1">
         <v>3500</v>
       </c>
-      <c r="I116" s="1">
+      <c r="I120" s="1">
         <v>52</v>
       </c>
-      <c r="J116" s="1">
-        <v>1</v>
-      </c>
-      <c r="K116" s="2">
-        <v>1</v>
-      </c>
-      <c r="L116" s="1" t="s">
-        <v>141</v>
+      <c r="J120" s="1">
+        <v>1</v>
+      </c>
+      <c r="K120" s="2">
+        <v>1</v>
+      </c>
+      <c r="L120" s="1" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -2261,13 +2261,13 @@
         <v>3</v>
       </c>
       <c r="G26" s="2">
-        <v>4000</v>
+        <v>4001</v>
       </c>
       <c r="H26" s="2">
         <v>5000</v>
       </c>
       <c r="I26" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J26" s="2">
         <v>5</v>
@@ -2360,13 +2360,13 @@
         <v>3</v>
       </c>
       <c r="G29" s="2">
-        <v>4800</v>
+        <v>4803</v>
       </c>
       <c r="H29" s="2">
-        <v>5300</v>
+        <v>5800</v>
       </c>
       <c r="I29" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J29" s="2">
         <v>5</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="152">
   <si>
     <t>#</t>
   </si>
@@ -253,6 +253,12 @@
   </si>
   <si>
     <t>混沌精华</t>
+  </si>
+  <si>
+    <t>601</t>
+  </si>
+  <si>
+    <t>随机宝石</t>
   </si>
   <si>
     <t>220036</t>
@@ -1507,7 +1513,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M120"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2375,59 +2381,56 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D30" s="4"/>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C31" s="2">
-        <v>151</v>
-      </c>
-      <c r="D31" s="8" t="s">
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C30" s="2">
+        <v>25</v>
+      </c>
+      <c r="D30" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E30" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F31" s="2">
-        <v>12</v>
-      </c>
-      <c r="G31" s="2">
-        <v>300</v>
-      </c>
-      <c r="H31" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I31" s="2">
-        <v>1</v>
-      </c>
-      <c r="J31" s="2">
-        <v>25</v>
-      </c>
-      <c r="K31" s="2">
-        <v>1</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="F30" s="2">
+        <v>20</v>
+      </c>
+      <c r="G30" s="2">
+        <v>4215</v>
+      </c>
+      <c r="H30" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I30" s="2">
+        <v>3</v>
+      </c>
+      <c r="J30" s="2">
+        <v>100</v>
+      </c>
+      <c r="K30" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="4:4">
+      <c r="D31" s="4"/>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C32" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D32" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="F32" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G32" s="2">
-        <v>1501</v>
+        <v>300</v>
       </c>
       <c r="H32" s="2">
-        <v>4000</v>
+        <v>1500</v>
       </c>
       <c r="I32" s="2">
         <v>1</v>
@@ -2439,94 +2442,94 @@
         <v>1</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C33" s="2">
+        <v>152</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F33" s="2">
+        <v>6</v>
+      </c>
+      <c r="G33" s="2">
+        <v>1501</v>
+      </c>
+      <c r="H33" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I33" s="2">
+        <v>1</v>
+      </c>
+      <c r="J33" s="2">
+        <v>25</v>
+      </c>
+      <c r="K33" s="2">
+        <v>1</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C34" s="2">
         <v>153</v>
       </c>
-      <c r="D33" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F33" s="2">
+      <c r="D34" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F34" s="2">
         <v>3</v>
       </c>
-      <c r="G33" s="2">
+      <c r="G34" s="2">
         <v>4001</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H34" s="2">
         <v>10000</v>
       </c>
-      <c r="I33" s="2">
-        <v>1</v>
-      </c>
-      <c r="J33" s="2">
+      <c r="I34" s="2">
+        <v>1</v>
+      </c>
+      <c r="J34" s="2">
         <v>15</v>
       </c>
-      <c r="K33" s="2">
+      <c r="K34" s="2">
         <v>2</v>
       </c>
-      <c r="L33" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D34" s="4"/>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C35" s="1">
-        <v>100</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F35" s="1">
-        <v>50</v>
-      </c>
-      <c r="G35" s="1">
-        <v>1</v>
-      </c>
-      <c r="H35" s="1">
-        <v>300</v>
-      </c>
-      <c r="I35" s="1">
-        <v>1</v>
-      </c>
-      <c r="J35" s="1">
-        <v>10000</v>
-      </c>
-      <c r="K35" s="2">
-        <v>1</v>
-      </c>
-      <c r="L35" s="1" t="s">
+      <c r="L34" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="4:4">
+      <c r="D35" s="4"/>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C36" s="1">
+        <v>100</v>
+      </c>
+      <c r="D36" s="9" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="36" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
-      <c r="C36" s="1">
-        <v>101</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>70</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F36" s="1">
         <v>50</v>
       </c>
       <c r="G36" s="1">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="H36" s="1">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I36" s="1">
         <v>1</v>
@@ -2535,30 +2538,30 @@
         <v>10000</v>
       </c>
       <c r="K36" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L36" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C37" s="1">
+        <v>101</v>
+      </c>
+      <c r="D37" s="9" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:12">
-      <c r="C37" s="1">
-        <v>102</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>70</v>
-      </c>
       <c r="E37" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F37" s="1">
         <v>50</v>
       </c>
       <c r="G37" s="1">
-        <v>601</v>
+        <v>301</v>
       </c>
       <c r="H37" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="I37" s="1">
         <v>1</v>
@@ -2567,30 +2570,30 @@
         <v>10000</v>
       </c>
       <c r="K37" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:12">
       <c r="C38" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F38" s="1">
         <v>50</v>
       </c>
       <c r="G38" s="1">
-        <v>1001</v>
+        <v>601</v>
       </c>
       <c r="H38" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I38" s="1">
         <v>1</v>
@@ -2599,62 +2602,62 @@
         <v>10000</v>
       </c>
       <c r="K38" s="2">
+        <v>4</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:12">
+      <c r="C39" s="1">
+        <v>103</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F39" s="1">
+        <v>50</v>
+      </c>
+      <c r="G39" s="1">
+        <v>1001</v>
+      </c>
+      <c r="H39" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I39" s="1">
+        <v>1</v>
+      </c>
+      <c r="J39" s="1">
+        <v>10000</v>
+      </c>
+      <c r="K39" s="2">
         <v>10</v>
       </c>
-      <c r="L38" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C39" s="1">
-        <v>104</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F39" s="2">
-        <v>50</v>
-      </c>
-      <c r="G39" s="2">
-        <v>1501</v>
-      </c>
-      <c r="H39" s="2">
-        <v>3500</v>
-      </c>
-      <c r="I39" s="2">
-        <v>1</v>
-      </c>
-      <c r="J39" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K39" s="2">
-        <v>20</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>72</v>
+      <c r="L39" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C40" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F40" s="2">
         <v>50</v>
       </c>
       <c r="G40" s="2">
-        <v>3501</v>
+        <v>1501</v>
       </c>
       <c r="H40" s="2">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="I40" s="2">
         <v>1</v>
@@ -2663,65 +2666,65 @@
         <v>10000</v>
       </c>
       <c r="K40" s="2">
+        <v>20</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C41" s="1">
+        <v>105</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F41" s="2">
+        <v>50</v>
+      </c>
+      <c r="G41" s="2">
+        <v>3501</v>
+      </c>
+      <c r="H41" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I41" s="2">
+        <v>1</v>
+      </c>
+      <c r="J41" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K41" s="2">
         <v>40</v>
       </c>
-      <c r="L40" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="41" s="2" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D41" s="4"/>
-    </row>
-    <row r="42" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
-      <c r="C42" s="2">
+      <c r="L41" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="4:4">
+      <c r="D42" s="4"/>
+    </row>
+    <row r="43" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C43" s="2">
         <v>200</v>
       </c>
-      <c r="D42" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F42" s="2">
-        <v>50</v>
-      </c>
-      <c r="G42" s="2">
-        <v>1</v>
-      </c>
-      <c r="H42" s="2">
-        <v>300</v>
-      </c>
-      <c r="I42" s="2">
-        <v>1</v>
-      </c>
-      <c r="J42" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K42" s="2">
-        <v>1</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C43" s="2">
-        <v>201</v>
-      </c>
       <c r="D43" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F43" s="2">
         <v>50</v>
       </c>
       <c r="G43" s="2">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="H43" s="2">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I43" s="2">
         <v>1</v>
@@ -2730,30 +2733,30 @@
         <v>10000</v>
       </c>
       <c r="K43" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C44" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F44" s="2">
         <v>50</v>
       </c>
       <c r="G44" s="2">
-        <v>601</v>
+        <v>301</v>
       </c>
       <c r="H44" s="2">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="I44" s="2">
         <v>1</v>
@@ -2762,30 +2765,30 @@
         <v>10000</v>
       </c>
       <c r="K44" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C45" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F45" s="2">
         <v>50</v>
       </c>
       <c r="G45" s="2">
-        <v>1001</v>
+        <v>601</v>
       </c>
       <c r="H45" s="2">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I45" s="2">
         <v>1</v>
@@ -2794,30 +2797,30 @@
         <v>10000</v>
       </c>
       <c r="K45" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="46" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C46" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F46" s="2">
         <v>50</v>
       </c>
       <c r="G46" s="2">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H46" s="2">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="I46" s="2">
         <v>1</v>
@@ -2826,30 +2829,30 @@
         <v>10000</v>
       </c>
       <c r="K46" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
       <c r="C47" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F47" s="2">
         <v>50</v>
       </c>
       <c r="G47" s="2">
-        <v>3501</v>
+        <v>1501</v>
       </c>
       <c r="H47" s="2">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="I47" s="2">
         <v>1</v>
@@ -2858,65 +2861,65 @@
         <v>10000</v>
       </c>
       <c r="K47" s="2">
+        <v>20</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C48" s="2">
+        <v>205</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F48" s="2">
+        <v>50</v>
+      </c>
+      <c r="G48" s="2">
+        <v>3501</v>
+      </c>
+      <c r="H48" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I48" s="2">
+        <v>1</v>
+      </c>
+      <c r="J48" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K48" s="2">
         <v>40</v>
       </c>
-      <c r="L47" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" ht="20" customHeight="1" spans="4:4">
-      <c r="D48" s="4"/>
-    </row>
-    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C49" s="2">
-        <v>300</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F49" s="2">
-        <v>10</v>
-      </c>
-      <c r="G49" s="2">
-        <v>1</v>
-      </c>
-      <c r="H49" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I49" s="2">
-        <v>1</v>
-      </c>
-      <c r="J49" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K49" s="2">
-        <v>1</v>
-      </c>
-      <c r="L49" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="L48" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" ht="20" customHeight="1" spans="4:4">
+      <c r="D49" s="4"/>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C50" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F50" s="2">
         <v>10</v>
       </c>
       <c r="G50" s="2">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="H50" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I50" s="2">
         <v>1</v>
@@ -2925,7 +2928,7 @@
         <v>10000</v>
       </c>
       <c r="K50" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>21</v>
@@ -2933,22 +2936,22 @@
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C51" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F51" s="2">
         <v>10</v>
       </c>
       <c r="G51" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H51" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I51" s="2">
         <v>1</v>
@@ -2957,63 +2960,63 @@
         <v>10000</v>
       </c>
       <c r="K51" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="52" s="2" customFormat="1" customHeight="1"/>
-    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C53" s="2">
-        <v>400</v>
-      </c>
-      <c r="D53" s="11" t="s">
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C52" s="2">
+        <v>302</v>
+      </c>
+      <c r="D52" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E52" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F52" s="2">
         <v>10</v>
       </c>
-      <c r="G53" s="2">
-        <v>50</v>
-      </c>
-      <c r="H53" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I53" s="2">
-        <v>1</v>
-      </c>
-      <c r="J53" s="2">
+      <c r="G52" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H52" s="2">
         <v>10000</v>
       </c>
-      <c r="K53" s="2">
-        <v>1</v>
-      </c>
-      <c r="L53" s="2" t="s">
+      <c r="I52" s="2">
+        <v>1</v>
+      </c>
+      <c r="J52" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K52" s="2">
+        <v>3</v>
+      </c>
+      <c r="L52" s="2" t="s">
         <v>21</v>
       </c>
     </row>
+    <row r="53" s="2" customFormat="1" customHeight="1"/>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C54" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F54" s="2">
         <v>10</v>
       </c>
       <c r="G54" s="2">
-        <v>1001</v>
+        <v>50</v>
       </c>
       <c r="H54" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I54" s="2">
         <v>1</v>
@@ -3022,7 +3025,7 @@
         <v>10000</v>
       </c>
       <c r="K54" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>21</v>
@@ -3030,22 +3033,22 @@
     </row>
     <row r="55" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C55" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F55" s="2">
         <v>10</v>
       </c>
       <c r="G55" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H55" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I55" s="2">
         <v>1</v>
@@ -3054,63 +3057,63 @@
         <v>10000</v>
       </c>
       <c r="K55" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="56" s="2" customFormat="1" customHeight="1"/>
-    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C57" s="2">
-        <v>500</v>
-      </c>
-      <c r="D57" s="11" t="s">
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C56" s="2">
+        <v>402</v>
+      </c>
+      <c r="D56" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E56" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F57" s="2">
-        <v>4</v>
-      </c>
-      <c r="G57" s="2">
-        <v>150</v>
-      </c>
-      <c r="H57" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I57" s="2">
-        <v>1</v>
-      </c>
-      <c r="J57" s="2">
-        <v>20</v>
-      </c>
-      <c r="K57" s="2">
-        <v>1</v>
-      </c>
-      <c r="L57" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
+      <c r="F56" s="2">
+        <v>10</v>
+      </c>
+      <c r="G56" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H56" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I56" s="2">
+        <v>1</v>
+      </c>
+      <c r="J56" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K56" s="2">
+        <v>3</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" customHeight="1"/>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C58" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F58" s="2">
         <v>4</v>
       </c>
       <c r="G58" s="2">
-        <v>1001</v>
+        <v>150</v>
       </c>
       <c r="H58" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I58" s="2">
         <v>1</v>
@@ -3119,30 +3122,30 @@
         <v>20</v>
       </c>
       <c r="K58" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C59" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F59" s="2">
         <v>4</v>
       </c>
       <c r="G59" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H59" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I59" s="2">
         <v>1</v>
@@ -3151,63 +3154,63 @@
         <v>20</v>
       </c>
       <c r="K59" s="2">
+        <v>2</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C60" s="2">
+        <v>502</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F60" s="2">
+        <v>4</v>
+      </c>
+      <c r="G60" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H60" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I60" s="2">
+        <v>1</v>
+      </c>
+      <c r="J60" s="2">
+        <v>20</v>
+      </c>
+      <c r="K60" s="2">
         <v>3</v>
       </c>
-      <c r="L59" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="60" s="2" customFormat="1" customHeight="1"/>
-    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C61" s="2">
-        <v>600</v>
-      </c>
-      <c r="D61" s="2">
-        <v>3001</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F61" s="2">
-        <v>10</v>
-      </c>
-      <c r="G61" s="2">
-        <v>1</v>
-      </c>
-      <c r="H61" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I61" s="2">
-        <v>1</v>
-      </c>
-      <c r="J61" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K61" s="2">
-        <v>1</v>
-      </c>
-      <c r="L61" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
+      <c r="L60" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61" s="2" customFormat="1" customHeight="1"/>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C62" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D62" s="2">
         <v>3001</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F62" s="2">
         <v>10</v>
       </c>
       <c r="G62" s="2">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="H62" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I62" s="2">
         <v>1</v>
@@ -3216,7 +3219,7 @@
         <v>10000</v>
       </c>
       <c r="K62" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>21</v>
@@ -3224,22 +3227,22 @@
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C63" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D63" s="2">
         <v>3001</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F63" s="2">
         <v>10</v>
       </c>
       <c r="G63" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H63" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I63" s="2">
         <v>1</v>
@@ -3248,63 +3251,63 @@
         <v>10000</v>
       </c>
       <c r="K63" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="64" s="2" customFormat="1" customHeight="1"/>
-    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C65" s="2">
-        <v>700</v>
-      </c>
-      <c r="D65" s="2">
-        <v>3002</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F65" s="2">
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C64" s="2">
+        <v>602</v>
+      </c>
+      <c r="D64" s="2">
+        <v>3001</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F64" s="2">
         <v>10</v>
       </c>
-      <c r="G65" s="2">
-        <v>200</v>
-      </c>
-      <c r="H65" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I65" s="2">
-        <v>1</v>
-      </c>
-      <c r="J65" s="2">
+      <c r="G64" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H64" s="2">
         <v>10000</v>
       </c>
-      <c r="K65" s="2">
-        <v>1</v>
-      </c>
-      <c r="L65" s="2" t="s">
+      <c r="I64" s="2">
+        <v>1</v>
+      </c>
+      <c r="J64" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K64" s="2">
+        <v>3</v>
+      </c>
+      <c r="L64" s="2" t="s">
         <v>21</v>
       </c>
     </row>
+    <row r="65" s="2" customFormat="1" customHeight="1"/>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C66" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D66" s="2">
         <v>3002</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F66" s="2">
         <v>10</v>
       </c>
       <c r="G66" s="2">
-        <v>1001</v>
+        <v>200</v>
       </c>
       <c r="H66" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I66" s="2">
         <v>1</v>
@@ -3313,7 +3316,7 @@
         <v>10000</v>
       </c>
       <c r="K66" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>21</v>
@@ -3321,22 +3324,22 @@
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C67" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D67" s="2">
         <v>3002</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F67" s="2">
         <v>10</v>
       </c>
       <c r="G67" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H67" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I67" s="2">
         <v>1</v>
@@ -3345,56 +3348,56 @@
         <v>10000</v>
       </c>
       <c r="K67" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="68" customHeight="1" spans="11:11">
-      <c r="K68" s="2"/>
-    </row>
-    <row r="69" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C69" s="2">
-        <v>800</v>
-      </c>
-      <c r="D69" s="2">
-        <v>3003</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F69" s="2">
-        <v>2</v>
-      </c>
-      <c r="G69" s="2">
-        <v>4001</v>
-      </c>
-      <c r="H69" s="2">
-        <v>5000</v>
-      </c>
-      <c r="I69" s="2">
-        <v>7</v>
-      </c>
-      <c r="J69" s="2">
-        <v>13</v>
-      </c>
-      <c r="K69" s="2">
-        <v>5</v>
-      </c>
-      <c r="L69" s="2" t="s">
+    <row r="68" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C68" s="2">
+        <v>702</v>
+      </c>
+      <c r="D68" s="2">
+        <v>3002</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F68" s="2">
+        <v>10</v>
+      </c>
+      <c r="G68" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H68" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I68" s="2">
+        <v>1</v>
+      </c>
+      <c r="J68" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K68" s="2">
+        <v>3</v>
+      </c>
+      <c r="L68" s="2" t="s">
         <v>21</v>
       </c>
+    </row>
+    <row r="69" customHeight="1" spans="11:11">
+      <c r="K69" s="2"/>
     </row>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C70" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D70" s="2">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F70" s="2">
         <v>2</v>
@@ -3406,50 +3409,53 @@
         <v>5000</v>
       </c>
       <c r="I70" s="2">
+        <v>7</v>
+      </c>
+      <c r="J70" s="2">
         <v>13</v>
       </c>
-      <c r="J70" s="2">
+      <c r="K70" s="2">
         <v>5</v>
-      </c>
-      <c r="K70" s="2">
-        <v>1</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="72" customHeight="1" spans="3:11">
-      <c r="C72" s="1">
-        <v>901</v>
-      </c>
-      <c r="D72" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="E72" s="1" t="s">
+    <row r="71" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C71" s="2">
+        <v>801</v>
+      </c>
+      <c r="D71" s="2">
+        <v>3004</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F72" s="1">
-        <v>20</v>
-      </c>
-      <c r="G72" s="1">
-        <v>3001</v>
-      </c>
-      <c r="H72" s="1">
-        <v>4000</v>
-      </c>
-      <c r="I72" s="1">
-        <v>3</v>
-      </c>
-      <c r="J72" s="1">
-        <v>30</v>
-      </c>
-      <c r="K72" s="2">
-        <v>1</v>
+      <c r="F71" s="2">
+        <v>2</v>
+      </c>
+      <c r="G71" s="2">
+        <v>4001</v>
+      </c>
+      <c r="H71" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I71" s="2">
+        <v>13</v>
+      </c>
+      <c r="J71" s="2">
+        <v>5</v>
+      </c>
+      <c r="K71" s="2">
+        <v>1</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
       <c r="C73" s="1">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>88</v>
@@ -3458,7 +3464,7 @@
         <v>89</v>
       </c>
       <c r="F73" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G73" s="1">
         <v>3001</v>
@@ -3470,7 +3476,7 @@
         <v>3</v>
       </c>
       <c r="J73" s="1">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="K73" s="2">
         <v>1</v>
@@ -3478,7 +3484,7 @@
     </row>
     <row r="74" customHeight="1" spans="3:11">
       <c r="C74" s="1">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>90</v>
@@ -3487,7 +3493,7 @@
         <v>91</v>
       </c>
       <c r="F74" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G74" s="1">
         <v>3001</v>
@@ -3499,7 +3505,7 @@
         <v>3</v>
       </c>
       <c r="J74" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K74" s="2">
         <v>1</v>
@@ -3507,7 +3513,7 @@
     </row>
     <row r="75" customHeight="1" spans="3:11">
       <c r="C75" s="1">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>92</v>
@@ -3516,19 +3522,19 @@
         <v>93</v>
       </c>
       <c r="F75" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G75" s="1">
-        <v>3501</v>
+        <v>3001</v>
       </c>
       <c r="H75" s="1">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="I75" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J75" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K75" s="2">
         <v>1</v>
@@ -3536,36 +3542,36 @@
     </row>
     <row r="76" customHeight="1" spans="3:11">
       <c r="C76" s="1">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F76" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G76" s="1">
-        <v>4001</v>
+        <v>3501</v>
       </c>
       <c r="H76" s="1">
         <v>5000</v>
       </c>
       <c r="I76" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J76" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K76" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:11">
       <c r="C77" s="1">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>88</v>
@@ -3574,7 +3580,7 @@
         <v>89</v>
       </c>
       <c r="F77" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G77" s="1">
         <v>4001</v>
@@ -3586,7 +3592,7 @@
         <v>3</v>
       </c>
       <c r="J77" s="1">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K77" s="2">
         <v>2</v>
@@ -3594,7 +3600,7 @@
     </row>
     <row r="78" customHeight="1" spans="3:11">
       <c r="C78" s="1">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>90</v>
@@ -3603,7 +3609,7 @@
         <v>91</v>
       </c>
       <c r="F78" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G78" s="1">
         <v>4001</v>
@@ -3615,56 +3621,53 @@
         <v>3</v>
       </c>
       <c r="J78" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K78" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="81" customHeight="1" spans="3:12">
-      <c r="C81" s="1">
-        <v>10001</v>
-      </c>
-      <c r="D81" s="6">
-        <v>180001</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F81" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G81" s="1">
-        <v>100</v>
-      </c>
-      <c r="H81" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I81" s="1">
-        <v>100</v>
-      </c>
-      <c r="J81" s="1">
-        <v>1</v>
-      </c>
-      <c r="K81" s="2">
-        <v>1</v>
-      </c>
-      <c r="L81" s="1" t="s">
-        <v>95</v>
+    <row r="79" customHeight="1" spans="3:11">
+      <c r="C79" s="1">
+        <v>907</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F79" s="1">
+        <v>3</v>
+      </c>
+      <c r="G79" s="1">
+        <v>4001</v>
+      </c>
+      <c r="H79" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I79" s="1">
+        <v>3</v>
+      </c>
+      <c r="J79" s="1">
+        <v>2</v>
+      </c>
+      <c r="K79" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:12">
       <c r="C82" s="1">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="D82" s="6">
-        <v>180002</v>
+        <v>180001</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>96</v>
       </c>
       <c r="F82" s="1">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G82" s="1">
         <v>100</v>
@@ -3682,21 +3685,21 @@
         <v>1</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:12">
       <c r="C83" s="1">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="D83" s="6">
-        <v>180003</v>
+        <v>180002</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F83" s="1">
-        <v>150000</v>
+        <v>4000</v>
       </c>
       <c r="G83" s="1">
         <v>100</v>
@@ -3708,27 +3711,27 @@
         <v>100</v>
       </c>
       <c r="J83" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K83" s="2">
         <v>1</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:12">
       <c r="C84" s="1">
-        <v>10004</v>
+        <v>10003</v>
       </c>
       <c r="D84" s="6">
-        <v>180004</v>
+        <v>180003</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F84" s="1">
-        <v>8000</v>
+        <v>150000</v>
       </c>
       <c r="G84" s="1">
         <v>100</v>
@@ -3740,27 +3743,27 @@
         <v>100</v>
       </c>
       <c r="J84" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K84" s="2">
         <v>1</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:12">
       <c r="C85" s="1">
-        <v>10005</v>
+        <v>10004</v>
       </c>
       <c r="D85" s="6">
-        <v>180005</v>
+        <v>180004</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F85" s="1">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="G85" s="1">
         <v>100</v>
@@ -3778,21 +3781,21 @@
         <v>1</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:12">
       <c r="C86" s="1">
-        <v>10006</v>
+        <v>10005</v>
       </c>
       <c r="D86" s="6">
-        <v>180006</v>
+        <v>180005</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F86" s="1">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="G86" s="1">
         <v>100</v>
@@ -3804,27 +3807,27 @@
         <v>100</v>
       </c>
       <c r="J86" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K86" s="2">
         <v>1</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:12">
       <c r="C87" s="1">
-        <v>10007</v>
+        <v>10006</v>
       </c>
       <c r="D87" s="6">
-        <v>180007</v>
+        <v>180006</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F87" s="1">
-        <v>2000</v>
+        <v>50000</v>
       </c>
       <c r="G87" s="1">
         <v>100</v>
@@ -3836,27 +3839,27 @@
         <v>100</v>
       </c>
       <c r="J87" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K87" s="2">
         <v>1</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:12">
       <c r="C88" s="1">
-        <v>10008</v>
+        <v>10007</v>
       </c>
       <c r="D88" s="6">
-        <v>180008</v>
+        <v>180007</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F88" s="1">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="G88" s="1">
         <v>100</v>
@@ -3868,27 +3871,27 @@
         <v>100</v>
       </c>
       <c r="J88" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K88" s="2">
         <v>1</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:12">
       <c r="C89" s="1">
-        <v>10009</v>
+        <v>10008</v>
       </c>
       <c r="D89" s="6">
-        <v>180009</v>
+        <v>180008</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F89" s="1">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="G89" s="1">
         <v>100</v>
@@ -3900,27 +3903,27 @@
         <v>100</v>
       </c>
       <c r="J89" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K89" s="2">
         <v>1</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:12">
       <c r="C90" s="1">
-        <v>10010</v>
+        <v>10009</v>
       </c>
       <c r="D90" s="6">
-        <v>180010</v>
+        <v>180009</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F90" s="1">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="G90" s="1">
         <v>100</v>
@@ -3938,21 +3941,21 @@
         <v>1</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:12">
       <c r="C91" s="1">
-        <v>10011</v>
+        <v>10010</v>
       </c>
       <c r="D91" s="6">
-        <v>180011</v>
+        <v>180010</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F91" s="1">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="G91" s="1">
         <v>100</v>
@@ -3964,24 +3967,24 @@
         <v>100</v>
       </c>
       <c r="J91" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K91" s="2">
         <v>1</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:12">
       <c r="C92" s="1">
-        <v>10012</v>
+        <v>10011</v>
       </c>
       <c r="D92" s="6">
-        <v>180012</v>
+        <v>180011</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F92" s="1">
         <v>100000</v>
@@ -4002,21 +4005,21 @@
         <v>1</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:12">
       <c r="C93" s="1">
-        <v>10013</v>
+        <v>10012</v>
       </c>
       <c r="D93" s="6">
-        <v>180013</v>
+        <v>180012</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F93" s="1">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="G93" s="1">
         <v>100</v>
@@ -4034,21 +4037,21 @@
         <v>1</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:12">
       <c r="C94" s="1">
-        <v>10014</v>
+        <v>10013</v>
       </c>
       <c r="D94" s="6">
-        <v>180014</v>
+        <v>180013</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F94" s="1">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G94" s="1">
         <v>100</v>
@@ -4066,18 +4069,18 @@
         <v>1</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:12">
       <c r="C95" s="1">
-        <v>10015</v>
+        <v>10014</v>
       </c>
       <c r="D95" s="6">
-        <v>180015</v>
+        <v>180014</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F95" s="1">
         <v>100000</v>
@@ -4098,21 +4101,21 @@
         <v>1</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:12">
       <c r="C96" s="1">
-        <v>10016</v>
+        <v>10015</v>
       </c>
       <c r="D96" s="6">
-        <v>180020</v>
+        <v>180015</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F96" s="1">
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="G96" s="1">
         <v>100</v>
@@ -4124,24 +4127,24 @@
         <v>100</v>
       </c>
       <c r="J96" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K96" s="2">
         <v>1</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:12">
       <c r="C97" s="1">
-        <v>10017</v>
+        <v>10016</v>
       </c>
       <c r="D97" s="6">
-        <v>180021</v>
+        <v>180020</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F97" s="1">
         <v>30000</v>
@@ -4162,21 +4165,21 @@
         <v>1</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:12">
       <c r="C98" s="1">
-        <v>10018</v>
+        <v>10017</v>
       </c>
       <c r="D98" s="6">
-        <v>180022</v>
+        <v>180021</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F98" s="1">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="G98" s="1">
         <v>100</v>
@@ -4188,65 +4191,65 @@
         <v>100</v>
       </c>
       <c r="J98" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K98" s="2">
         <v>1</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="100" customHeight="1" spans="3:12">
-      <c r="C100" s="1">
-        <v>10030</v>
-      </c>
-      <c r="D100" s="1">
-        <v>180030</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F100" s="1">
-        <v>5</v>
-      </c>
-      <c r="G100" s="1">
-        <v>1100</v>
-      </c>
-      <c r="H100" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I100" s="1">
-        <v>100</v>
-      </c>
-      <c r="J100" s="1">
-        <v>1</v>
-      </c>
-      <c r="K100" s="2">
-        <v>1</v>
-      </c>
-      <c r="L100" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:12">
+      <c r="C99" s="1">
+        <v>10018</v>
+      </c>
+      <c r="D99" s="6">
+        <v>180022</v>
+      </c>
+      <c r="E99" s="1" t="s">
         <v>114</v>
+      </c>
+      <c r="F99" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G99" s="1">
+        <v>100</v>
+      </c>
+      <c r="H99" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I99" s="1">
+        <v>100</v>
+      </c>
+      <c r="J99" s="1">
+        <v>1</v>
+      </c>
+      <c r="K99" s="2">
+        <v>1</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:12">
       <c r="C101" s="1">
-        <v>10031</v>
-      </c>
-      <c r="D101" s="6">
-        <v>180032</v>
+        <v>10030</v>
+      </c>
+      <c r="D101" s="1">
+        <v>180030</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>115</v>
       </c>
       <c r="F101" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G101" s="1">
         <v>1100</v>
       </c>
       <c r="H101" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I101" s="1">
         <v>100</v>
@@ -4258,24 +4261,24 @@
         <v>1</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:12">
       <c r="C102" s="1">
-        <v>10032</v>
+        <v>10031</v>
       </c>
       <c r="D102" s="6">
-        <v>180033</v>
+        <v>180032</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F102" s="1">
         <v>1</v>
       </c>
       <c r="G102" s="1">
-        <v>1600</v>
+        <v>1100</v>
       </c>
       <c r="H102" s="1">
         <v>2000</v>
@@ -4290,27 +4293,27 @@
         <v>1</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:12">
       <c r="C103" s="1">
-        <v>10033</v>
+        <v>10032</v>
       </c>
       <c r="D103" s="6">
-        <v>180034</v>
+        <v>180033</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F103" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G103" s="1">
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="H103" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I103" s="1">
         <v>100</v>
@@ -4322,27 +4325,27 @@
         <v>1</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:12">
       <c r="C104" s="1">
-        <v>10034</v>
+        <v>10033</v>
       </c>
       <c r="D104" s="6">
-        <v>180035</v>
+        <v>180034</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F104" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G104" s="1">
-        <v>2000</v>
+        <v>1100</v>
       </c>
       <c r="H104" s="1">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I104" s="1">
         <v>100</v>
@@ -4354,18 +4357,18 @@
         <v>1</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:12">
       <c r="C105" s="1">
-        <v>10035</v>
+        <v>10034</v>
       </c>
       <c r="D105" s="6">
-        <v>180036</v>
+        <v>180035</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F105" s="1">
         <v>1</v>
@@ -4386,28 +4389,28 @@
         <v>1</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:12">
       <c r="C106" s="1">
-        <v>10036</v>
+        <v>10035</v>
       </c>
       <c r="D106" s="6">
-        <v>180037</v>
+        <v>180036</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F106" s="1">
         <v>1</v>
       </c>
       <c r="G106" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H106" s="1">
         <v>2500</v>
       </c>
-      <c r="H106" s="1">
-        <v>3500</v>
-      </c>
       <c r="I106" s="1">
         <v>100</v>
       </c>
@@ -4418,24 +4421,24 @@
         <v>1</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:12">
       <c r="C107" s="1">
-        <v>10037</v>
+        <v>10036</v>
       </c>
       <c r="D107" s="6">
-        <v>180038</v>
+        <v>180037</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F107" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G107" s="1">
-        <v>1600</v>
+        <v>2500</v>
       </c>
       <c r="H107" s="1">
         <v>3500</v>
@@ -4450,24 +4453,24 @@
         <v>1</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:12">
       <c r="C108" s="1">
-        <v>10038</v>
+        <v>10037</v>
       </c>
       <c r="D108" s="6">
-        <v>180039</v>
+        <v>180038</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F108" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G108" s="1">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="H108" s="1">
         <v>3500</v>
@@ -4482,44 +4485,44 @@
         <v>1</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="110" customHeight="1" spans="3:12">
-      <c r="C110" s="1">
-        <v>11001</v>
-      </c>
-      <c r="D110" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="E110" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="3:12">
+      <c r="C109" s="1">
+        <v>10038</v>
+      </c>
+      <c r="D109" s="6">
+        <v>180039</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F110" s="1">
-        <v>5</v>
-      </c>
-      <c r="G110" s="1">
-        <v>150</v>
-      </c>
-      <c r="H110" s="1">
-        <v>1200</v>
-      </c>
-      <c r="I110" s="1">
-        <v>20</v>
-      </c>
-      <c r="J110" s="1">
-        <v>2</v>
-      </c>
-      <c r="K110" s="2">
-        <v>1</v>
-      </c>
-      <c r="L110" s="1" t="s">
-        <v>39</v>
+      <c r="F109" s="1">
+        <v>3</v>
+      </c>
+      <c r="G109" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H109" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I109" s="1">
+        <v>100</v>
+      </c>
+      <c r="J109" s="1">
+        <v>1</v>
+      </c>
+      <c r="K109" s="2">
+        <v>1</v>
+      </c>
+      <c r="L109" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:12">
       <c r="C111" s="1">
-        <v>11002</v>
+        <v>11001</v>
       </c>
       <c r="D111" s="9" t="s">
         <v>125</v>
@@ -4531,13 +4534,13 @@
         <v>5</v>
       </c>
       <c r="G111" s="1">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H111" s="1">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="I111" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J111" s="1">
         <v>2</v>
@@ -4551,7 +4554,7 @@
     </row>
     <row r="112" customHeight="1" spans="3:12">
       <c r="C112" s="1">
-        <v>11003</v>
+        <v>11002</v>
       </c>
       <c r="D112" s="9" t="s">
         <v>127</v>
@@ -4560,16 +4563,16 @@
         <v>128</v>
       </c>
       <c r="F112" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G112" s="1">
-        <v>1050</v>
+        <v>200</v>
       </c>
       <c r="H112" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I112" s="1">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="J112" s="1">
         <v>2</v>
@@ -4583,25 +4586,25 @@
     </row>
     <row r="113" customHeight="1" spans="3:12">
       <c r="C113" s="1">
-        <v>11004</v>
+        <v>11003</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F113" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G113" s="1">
-        <v>4001</v>
+        <v>1050</v>
       </c>
       <c r="H113" s="1">
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="I113" s="1">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J113" s="1">
         <v>2</v>
@@ -4615,54 +4618,54 @@
     </row>
     <row r="114" customHeight="1" spans="3:12">
       <c r="C114" s="1">
-        <v>11005</v>
+        <v>11004</v>
       </c>
       <c r="D114" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="E114" s="7" t="s">
+      <c r="E114" s="1" t="s">
         <v>130</v>
       </c>
       <c r="F114" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G114" s="1">
-        <v>101</v>
+        <v>4001</v>
       </c>
       <c r="H114" s="1">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="I114" s="1">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="J114" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K114" s="2">
         <v>1</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>131</v>
+        <v>39</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="3:12">
       <c r="C115" s="1">
-        <v>11006</v>
+        <v>11005</v>
       </c>
       <c r="D115" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E115" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="E115" s="7" t="s">
-        <v>133</v>
-      </c>
       <c r="F115" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G115" s="1">
-        <v>501</v>
+        <v>101</v>
       </c>
       <c r="H115" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="I115" s="1">
         <v>10</v>
@@ -4674,59 +4677,59 @@
         <v>1</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="3:12">
       <c r="C116" s="1">
-        <v>11007</v>
+        <v>11006</v>
       </c>
       <c r="D116" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="E116" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="E116" s="7" t="s">
+      <c r="F116" s="1">
+        <v>15</v>
+      </c>
+      <c r="G116" s="1">
+        <v>501</v>
+      </c>
+      <c r="H116" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I116" s="1">
+        <v>10</v>
+      </c>
+      <c r="J116" s="1">
+        <v>1</v>
+      </c>
+      <c r="K116" s="2">
+        <v>1</v>
+      </c>
+      <c r="L116" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="F116" s="1">
-        <v>10</v>
-      </c>
-      <c r="G116" s="1">
-        <v>1001</v>
-      </c>
-      <c r="H116" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I116" s="1">
-        <v>20</v>
-      </c>
-      <c r="J116" s="1">
-        <v>1</v>
-      </c>
-      <c r="K116" s="2">
-        <v>1</v>
-      </c>
-      <c r="L116" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="3:12">
       <c r="C117" s="1">
-        <v>11008</v>
+        <v>11007</v>
       </c>
       <c r="D117" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E117" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="E117" s="7" t="s">
-        <v>139</v>
-      </c>
       <c r="F117" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G117" s="1">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H117" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I117" s="1">
         <v>20</v>
@@ -4738,59 +4741,59 @@
         <v>1</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="3:12">
       <c r="C118" s="1">
-        <v>11009</v>
+        <v>11008</v>
       </c>
       <c r="D118" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E118" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="E118" s="7" t="s">
+      <c r="F118" s="1">
+        <v>8</v>
+      </c>
+      <c r="G118" s="1">
+        <v>1501</v>
+      </c>
+      <c r="H118" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I118" s="1">
+        <v>20</v>
+      </c>
+      <c r="J118" s="1">
+        <v>1</v>
+      </c>
+      <c r="K118" s="2">
+        <v>1</v>
+      </c>
+      <c r="L118" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="F118" s="1">
-        <v>15</v>
-      </c>
-      <c r="G118" s="1">
-        <v>2001</v>
-      </c>
-      <c r="H118" s="1">
-        <v>2500</v>
-      </c>
-      <c r="I118" s="1">
-        <v>52</v>
-      </c>
-      <c r="J118" s="1">
-        <v>1</v>
-      </c>
-      <c r="K118" s="2">
-        <v>1</v>
-      </c>
-      <c r="L118" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="3:12">
       <c r="C119" s="1">
-        <v>11010</v>
+        <v>11009</v>
       </c>
       <c r="D119" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E119" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E119" s="7" t="s">
-        <v>145</v>
-      </c>
       <c r="F119" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G119" s="1">
-        <v>2501</v>
+        <v>2001</v>
       </c>
       <c r="H119" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I119" s="1">
         <v>52</v>
@@ -4802,27 +4805,27 @@
         <v>1</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="3:12">
       <c r="C120" s="1">
-        <v>11011</v>
+        <v>11010</v>
       </c>
       <c r="D120" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E120" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E120" s="7" t="s">
-        <v>148</v>
-      </c>
       <c r="F120" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G120" s="1">
-        <v>3001</v>
+        <v>2501</v>
       </c>
       <c r="H120" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="I120" s="1">
         <v>52</v>
@@ -4834,7 +4837,39 @@
         <v>1</v>
       </c>
       <c r="L120" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="3:12">
+      <c r="C121" s="1">
+        <v>11011</v>
+      </c>
+      <c r="D121" s="9" t="s">
         <v>149</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F121" s="1">
+        <v>3</v>
+      </c>
+      <c r="G121" s="1">
+        <v>3001</v>
+      </c>
+      <c r="H121" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I121" s="1">
+        <v>52</v>
+      </c>
+      <c r="J121" s="1">
+        <v>1</v>
+      </c>
+      <c r="K121" s="2">
+        <v>1</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -3563,7 +3563,7 @@
         <v>4</v>
       </c>
       <c r="J76" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K76" s="2">
         <v>1</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="154">
   <si>
     <t>#</t>
   </si>
@@ -517,6 +517,12 @@
   </si>
   <si>
     <t>7天一个</t>
+  </si>
+  <si>
+    <t>220042</t>
+  </si>
+  <si>
+    <t>暗金魂心</t>
   </si>
 </sst>
 </file>
@@ -1513,7 +1519,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:M122"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2282,13 +2288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A27" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>0</v>
-      </c>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:11">
       <c r="C27" s="2">
         <v>22</v>
       </c>
@@ -2308,10 +2308,10 @@
         <v>6000</v>
       </c>
       <c r="I27" s="2">
+        <v>9</v>
+      </c>
+      <c r="J27" s="2">
         <v>3</v>
-      </c>
-      <c r="J27" s="2">
-        <v>5</v>
       </c>
       <c r="K27" s="2">
         <v>1</v>
@@ -2343,10 +2343,10 @@
         <v>7000</v>
       </c>
       <c r="I28" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J28" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K28" s="2">
         <v>1</v>
@@ -2372,7 +2372,7 @@
         <v>5800</v>
       </c>
       <c r="I29" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J29" s="2">
         <v>5</v>
@@ -4869,6 +4869,38 @@
         <v>1</v>
       </c>
       <c r="L121" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="3:12">
+      <c r="C122" s="1">
+        <v>11012</v>
+      </c>
+      <c r="D122" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F122" s="2">
+        <v>1</v>
+      </c>
+      <c r="G122" s="2">
+        <v>5001</v>
+      </c>
+      <c r="H122" s="2">
+        <v>5500</v>
+      </c>
+      <c r="I122" s="2">
+        <v>61</v>
+      </c>
+      <c r="J122" s="2">
+        <v>1</v>
+      </c>
+      <c r="K122" s="2">
+        <v>1</v>
+      </c>
+      <c r="L122" s="1" t="s">
         <v>151</v>
       </c>
     </row>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="157">
   <si>
     <t>#</t>
   </si>
@@ -436,6 +436,15 @@
   </si>
   <si>
     <t>极·金蛟剪</t>
+  </si>
+  <si>
+    <t>极·炼体证明</t>
+  </si>
+  <si>
+    <t>极·炼气证明</t>
+  </si>
+  <si>
+    <t>极·炼神证明</t>
   </si>
   <si>
     <t>220016</t>
@@ -1519,7 +1528,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M122"/>
+  <dimension ref="A1:M125"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -4520,123 +4529,129 @@
         <v>116</v>
       </c>
     </row>
+    <row r="110" customHeight="1" spans="1:12">
+      <c r="A110" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C110" s="1">
+        <v>10039</v>
+      </c>
+      <c r="D110" s="6">
+        <v>180040</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F110" s="1">
+        <v>1</v>
+      </c>
+      <c r="G110" s="1">
+        <v>3000</v>
+      </c>
+      <c r="H110" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I110" s="1">
+        <v>100</v>
+      </c>
+      <c r="J110" s="1">
+        <v>1</v>
+      </c>
+      <c r="K110" s="2">
+        <v>1</v>
+      </c>
+      <c r="L110" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
     <row r="111" customHeight="1" spans="3:12">
       <c r="C111" s="1">
-        <v>11001</v>
-      </c>
-      <c r="D111" s="9" t="s">
-        <v>125</v>
+        <v>10040</v>
+      </c>
+      <c r="D111" s="6">
+        <v>180041</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>126</v>
       </c>
       <c r="F111" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G111" s="1">
-        <v>150</v>
+        <v>4000</v>
       </c>
       <c r="H111" s="1">
-        <v>1200</v>
+        <v>5000</v>
       </c>
       <c r="I111" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="J111" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K111" s="2">
         <v>1</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>39</v>
+        <v>116</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:12">
       <c r="C112" s="1">
-        <v>11002</v>
-      </c>
-      <c r="D112" s="9" t="s">
+        <v>10041</v>
+      </c>
+      <c r="D112" s="6">
+        <v>180042</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E112" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="F112" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G112" s="1">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="H112" s="1">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="I112" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J112" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K112" s="2">
         <v>1</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="113" customHeight="1" spans="3:12">
-      <c r="C113" s="1">
-        <v>11003</v>
-      </c>
-      <c r="D113" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F113" s="1">
-        <v>15</v>
-      </c>
-      <c r="G113" s="1">
-        <v>1050</v>
-      </c>
-      <c r="H113" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I113" s="1">
-        <v>51</v>
-      </c>
-      <c r="J113" s="1">
-        <v>2</v>
-      </c>
-      <c r="K113" s="2">
-        <v>1</v>
-      </c>
-      <c r="L113" s="1" t="s">
-        <v>39</v>
+        <v>116</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:12">
       <c r="C114" s="1">
-        <v>11004</v>
+        <v>11001</v>
       </c>
       <c r="D114" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="F114" s="1">
         <v>5</v>
       </c>
       <c r="G114" s="1">
-        <v>4001</v>
+        <v>150</v>
       </c>
       <c r="H114" s="1">
-        <v>6000</v>
+        <v>1200</v>
       </c>
       <c r="I114" s="1">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="J114" s="1">
         <v>2</v>
@@ -4650,121 +4665,121 @@
     </row>
     <row r="115" customHeight="1" spans="3:12">
       <c r="C115" s="1">
-        <v>11005</v>
+        <v>11002</v>
       </c>
       <c r="D115" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E115" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E115" s="7" t="s">
-        <v>132</v>
-      </c>
       <c r="F115" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G115" s="1">
-        <v>101</v>
+        <v>200</v>
       </c>
       <c r="H115" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="I115" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J115" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K115" s="2">
         <v>1</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>133</v>
+        <v>39</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="3:12">
       <c r="C116" s="1">
-        <v>11006</v>
+        <v>11003</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E116" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="F116" s="1">
         <v>15</v>
       </c>
       <c r="G116" s="1">
-        <v>501</v>
+        <v>1050</v>
       </c>
       <c r="H116" s="1">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I116" s="1">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="J116" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K116" s="2">
         <v>1</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>136</v>
+        <v>39</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="3:12">
       <c r="C117" s="1">
-        <v>11007</v>
+        <v>11004</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="E117" s="7" t="s">
-        <v>138</v>
+        <v>132</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="F117" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G117" s="1">
-        <v>1001</v>
+        <v>4001</v>
       </c>
       <c r="H117" s="1">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="I117" s="1">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="J117" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K117" s="2">
         <v>1</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>139</v>
+        <v>39</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="3:12">
       <c r="C118" s="1">
-        <v>11008</v>
+        <v>11005</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="F118" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G118" s="1">
-        <v>1501</v>
+        <v>101</v>
       </c>
       <c r="H118" s="1">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="I118" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J118" s="1">
         <v>1</v>
@@ -4773,30 +4788,30 @@
         <v>1</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="3:12">
       <c r="C119" s="1">
-        <v>11009</v>
+        <v>11006</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F119" s="1">
         <v>15</v>
       </c>
       <c r="G119" s="1">
-        <v>2001</v>
+        <v>501</v>
       </c>
       <c r="H119" s="1">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="I119" s="1">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="J119" s="1">
         <v>1</v>
@@ -4805,30 +4820,30 @@
         <v>1</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="3:12">
       <c r="C120" s="1">
-        <v>11010</v>
+        <v>11007</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F120" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G120" s="1">
-        <v>2501</v>
+        <v>1001</v>
       </c>
       <c r="H120" s="1">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="I120" s="1">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="J120" s="1">
         <v>1</v>
@@ -4837,30 +4852,30 @@
         <v>1</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="121" customHeight="1" spans="3:12">
       <c r="C121" s="1">
-        <v>11011</v>
+        <v>11008</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="F121" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G121" s="1">
-        <v>3001</v>
+        <v>1501</v>
       </c>
       <c r="H121" s="1">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="I121" s="1">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="J121" s="1">
         <v>1</v>
@@ -4869,39 +4884,135 @@
         <v>1</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="122" customHeight="1" spans="3:12">
       <c r="C122" s="1">
+        <v>11009</v>
+      </c>
+      <c r="D122" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F122" s="1">
+        <v>15</v>
+      </c>
+      <c r="G122" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H122" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I122" s="1">
+        <v>52</v>
+      </c>
+      <c r="J122" s="1">
+        <v>1</v>
+      </c>
+      <c r="K122" s="2">
+        <v>1</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" spans="3:12">
+      <c r="C123" s="1">
+        <v>11010</v>
+      </c>
+      <c r="D123" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F123" s="1">
+        <v>7</v>
+      </c>
+      <c r="G123" s="1">
+        <v>2501</v>
+      </c>
+      <c r="H123" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I123" s="1">
+        <v>52</v>
+      </c>
+      <c r="J123" s="1">
+        <v>1</v>
+      </c>
+      <c r="K123" s="2">
+        <v>1</v>
+      </c>
+      <c r="L123" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="3:12">
+      <c r="C124" s="1">
+        <v>11011</v>
+      </c>
+      <c r="D124" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E124" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F124" s="1">
+        <v>3</v>
+      </c>
+      <c r="G124" s="1">
+        <v>3001</v>
+      </c>
+      <c r="H124" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I124" s="1">
+        <v>52</v>
+      </c>
+      <c r="J124" s="1">
+        <v>1</v>
+      </c>
+      <c r="K124" s="2">
+        <v>1</v>
+      </c>
+      <c r="L124" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="3:12">
+      <c r="C125" s="1">
         <v>11012</v>
       </c>
-      <c r="D122" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="E122" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="F122" s="2">
-        <v>1</v>
-      </c>
-      <c r="G122" s="2">
+      <c r="D125" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F125" s="2">
+        <v>1</v>
+      </c>
+      <c r="G125" s="2">
         <v>5001</v>
       </c>
-      <c r="H122" s="2">
+      <c r="H125" s="2">
         <v>5500</v>
       </c>
-      <c r="I122" s="2">
+      <c r="I125" s="2">
         <v>61</v>
       </c>
-      <c r="J122" s="2">
-        <v>1</v>
-      </c>
-      <c r="K122" s="2">
-        <v>1</v>
-      </c>
-      <c r="L122" s="1" t="s">
-        <v>151</v>
+      <c r="J125" s="2">
+        <v>1</v>
+      </c>
+      <c r="K125" s="2">
+        <v>1</v>
+      </c>
+      <c r="L125" s="1" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4546,7 +4546,7 @@
         <v>125</v>
       </c>
       <c r="F110" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G110" s="1">
         <v>3000</v>
@@ -4578,7 +4578,7 @@
         <v>126</v>
       </c>
       <c r="F111" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G111" s="1">
         <v>4000</v>
@@ -4610,7 +4610,7 @@
         <v>127</v>
       </c>
       <c r="F112" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G112" s="1">
         <v>5000</v>
@@ -4968,7 +4968,7 @@
         <v>3001</v>
       </c>
       <c r="H124" s="1">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="I124" s="1">
         <v>52</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -4971,7 +4971,7 @@
         <v>3800</v>
       </c>
       <c r="I124" s="1">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J124" s="1">
         <v>1</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -729,12 +729,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4578,7 +4578,7 @@
         <v>126</v>
       </c>
       <c r="F111" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G111" s="1">
         <v>4000</v>
@@ -4610,7 +4610,7 @@
         <v>127</v>
       </c>
       <c r="F112" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G112" s="1">
         <v>5000</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="159">
   <si>
     <t>#</t>
   </si>
@@ -532,6 +532,12 @@
   </si>
   <si>
     <t>暗金魂心</t>
+  </si>
+  <si>
+    <t>220043</t>
+  </si>
+  <si>
+    <t>六大极戒</t>
   </si>
 </sst>
 </file>
@@ -729,12 +735,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1528,7 +1534,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M125"/>
+  <dimension ref="A1:M127"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1540,7 +1546,7 @@
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="12:13">
+    <row r="1" customHeight="1" spans="3:13">
       <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1548,7 +1554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="12:13">
+    <row r="2" customHeight="1" spans="3:13">
       <c r="L2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1556,7 +1562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1585,7 +1591,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1614,7 +1620,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
@@ -1643,7 +1649,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:12">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C6" s="2">
         <v>1</v>
       </c>
@@ -1675,7 +1681,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:12">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C7" s="2">
         <v>2</v>
       </c>
@@ -1707,7 +1713,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C8" s="2">
         <v>3</v>
       </c>
@@ -1739,7 +1745,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:12">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C9" s="2">
         <v>4</v>
       </c>
@@ -1771,7 +1777,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:12">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C10" s="2">
         <v>5</v>
       </c>
@@ -1803,7 +1809,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="3:12">
+    <row r="11" customHeight="1" spans="3:13">
       <c r="C11" s="2">
         <v>6</v>
       </c>
@@ -1835,7 +1841,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="3:12">
+    <row r="12" customHeight="1" spans="3:13">
       <c r="C12" s="2">
         <v>7</v>
       </c>
@@ -1867,7 +1873,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C13" s="2">
         <v>8</v>
       </c>
@@ -1899,7 +1905,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:12">
+    <row r="14" customHeight="1" spans="3:13">
       <c r="C14" s="2">
         <v>9</v>
       </c>
@@ -1910,7 +1916,7 @@
         <v>32</v>
       </c>
       <c r="F14" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1">
         <v>1250</v>
@@ -1931,7 +1937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:12">
+    <row r="15" customHeight="1" spans="3:13">
       <c r="C15" s="2">
         <v>10</v>
       </c>
@@ -1942,7 +1948,7 @@
         <v>34</v>
       </c>
       <c r="F15" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G15" s="1">
         <v>1350</v>
@@ -1963,7 +1969,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C16" s="2">
         <v>11</v>
       </c>
@@ -1974,7 +1980,7 @@
         <v>36</v>
       </c>
       <c r="F16" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G16" s="1">
         <v>1450</v>
@@ -1995,7 +2001,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:12">
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="C17" s="2">
         <v>12</v>
       </c>
@@ -2027,7 +2033,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:12">
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="C18" s="2">
         <v>13</v>
       </c>
@@ -2059,7 +2065,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="20" customHeight="1" spans="3:11">
+    <row r="19" s="1" customFormat="1" ht="20" customHeight="1" spans="1:12">
       <c r="C19" s="2">
         <v>14</v>
       </c>
@@ -2088,7 +2094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="20" customHeight="1" spans="3:11">
+    <row r="20" s="1" customFormat="1" ht="20" customHeight="1" spans="1:12">
       <c r="C20" s="2">
         <v>15</v>
       </c>
@@ -2117,7 +2123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:12">
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="C21" s="2">
         <v>16</v>
       </c>
@@ -2149,7 +2155,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:12">
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="C22" s="2">
         <v>17</v>
       </c>
@@ -2181,7 +2187,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:11">
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="C23" s="2">
         <v>18</v>
       </c>
@@ -2210,7 +2216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:11">
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="C24" s="2">
         <v>19</v>
       </c>
@@ -2239,7 +2245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:11">
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="C25" s="2">
         <v>20</v>
       </c>
@@ -2268,7 +2274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:11">
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="C26" s="2">
         <v>21</v>
       </c>
@@ -2297,7 +2303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:11">
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="C27" s="2">
         <v>22</v>
       </c>
@@ -2326,7 +2332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="1:11">
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A28" s="2" t="s">
         <v>0</v>
       </c>
@@ -2361,7 +2367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:11">
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="C29" s="2">
         <v>24</v>
       </c>
@@ -2390,7 +2396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:11">
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="C30" s="2">
         <v>25</v>
       </c>
@@ -2419,59 +2425,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="4:4">
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="D31" s="4"/>
     </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C32" s="2">
-        <v>151</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F32" s="2">
-        <v>12</v>
-      </c>
-      <c r="G32" s="2">
-        <v>300</v>
-      </c>
-      <c r="H32" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I32" s="2">
-        <v>1</v>
-      </c>
-      <c r="J32" s="2">
-        <v>25</v>
-      </c>
-      <c r="K32" s="2">
-        <v>1</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>68</v>
-      </c>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="D32" s="4"/>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C33" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F33" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G33" s="2">
-        <v>1501</v>
+        <v>300</v>
       </c>
       <c r="H33" s="2">
-        <v>4000</v>
+        <v>1500</v>
       </c>
       <c r="I33" s="2">
         <v>1</v>
@@ -2488,74 +2465,74 @@
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C34" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F34" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G34" s="2">
-        <v>4001</v>
+        <v>1501</v>
       </c>
       <c r="H34" s="2">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="I34" s="2">
         <v>1</v>
       </c>
       <c r="J34" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K34" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D35" s="4"/>
-    </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C36" s="1">
-        <v>100</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F36" s="1">
-        <v>50</v>
-      </c>
-      <c r="G36" s="1">
-        <v>1</v>
-      </c>
-      <c r="H36" s="1">
-        <v>300</v>
-      </c>
-      <c r="I36" s="1">
-        <v>1</v>
-      </c>
-      <c r="J36" s="1">
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C35" s="2">
+        <v>153</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F35" s="2">
+        <v>3</v>
+      </c>
+      <c r="G35" s="2">
+        <v>4001</v>
+      </c>
+      <c r="H35" s="2">
         <v>10000</v>
       </c>
-      <c r="K36" s="2">
-        <v>1</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="I35" s="2">
+        <v>1</v>
+      </c>
+      <c r="J35" s="2">
+        <v>15</v>
+      </c>
+      <c r="K35" s="2">
+        <v>2</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="D36" s="4"/>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C37" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>72</v>
@@ -2567,10 +2544,10 @@
         <v>50</v>
       </c>
       <c r="G37" s="1">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="H37" s="1">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I37" s="1">
         <v>1</v>
@@ -2579,15 +2556,15 @@
         <v>10000</v>
       </c>
       <c r="K37" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="3:12">
+    <row r="38" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
       <c r="C38" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>72</v>
@@ -2599,10 +2576,10 @@
         <v>50</v>
       </c>
       <c r="G38" s="1">
-        <v>601</v>
+        <v>301</v>
       </c>
       <c r="H38" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="I38" s="1">
         <v>1</v>
@@ -2611,7 +2588,7 @@
         <v>10000</v>
       </c>
       <c r="K38" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>74</v>
@@ -2619,7 +2596,7 @@
     </row>
     <row r="39" customHeight="1" spans="3:12">
       <c r="C39" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>72</v>
@@ -2631,10 +2608,10 @@
         <v>50</v>
       </c>
       <c r="G39" s="1">
-        <v>1001</v>
+        <v>601</v>
       </c>
       <c r="H39" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I39" s="1">
         <v>1</v>
@@ -2643,47 +2620,47 @@
         <v>10000</v>
       </c>
       <c r="K39" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:12">
+    <row r="40" customHeight="1" spans="3:12">
       <c r="C40" s="1">
-        <v>104</v>
-      </c>
-      <c r="D40" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D40" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="1">
         <v>50</v>
       </c>
-      <c r="G40" s="2">
-        <v>1501</v>
-      </c>
-      <c r="H40" s="2">
-        <v>3500</v>
-      </c>
-      <c r="I40" s="2">
-        <v>1</v>
-      </c>
-      <c r="J40" s="2">
+      <c r="G40" s="1">
+        <v>1001</v>
+      </c>
+      <c r="H40" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I40" s="1">
+        <v>1</v>
+      </c>
+      <c r="J40" s="1">
         <v>10000</v>
       </c>
       <c r="K40" s="2">
-        <v>20</v>
-      </c>
-      <c r="L40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L40" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C41" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>72</v>
@@ -2695,10 +2672,10 @@
         <v>50</v>
       </c>
       <c r="G41" s="2">
-        <v>3501</v>
+        <v>1501</v>
       </c>
       <c r="H41" s="2">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="I41" s="2">
         <v>1</v>
@@ -2707,50 +2684,50 @@
         <v>10000</v>
       </c>
       <c r="K41" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="42" s="2" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D42" s="4"/>
-    </row>
-    <row r="43" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
-      <c r="C43" s="2">
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C42" s="1">
+        <v>105</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F42" s="2">
+        <v>50</v>
+      </c>
+      <c r="G42" s="2">
+        <v>3501</v>
+      </c>
+      <c r="H42" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I42" s="2">
+        <v>1</v>
+      </c>
+      <c r="J42" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K42" s="2">
+        <v>40</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="D43" s="4"/>
+    </row>
+    <row r="44" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C44" s="2">
         <v>200</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F43" s="2">
-        <v>50</v>
-      </c>
-      <c r="G43" s="2">
-        <v>1</v>
-      </c>
-      <c r="H43" s="2">
-        <v>300</v>
-      </c>
-      <c r="I43" s="2">
-        <v>1</v>
-      </c>
-      <c r="J43" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K43" s="2">
-        <v>1</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C44" s="2">
-        <v>201</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>75</v>
@@ -2762,10 +2739,10 @@
         <v>50</v>
       </c>
       <c r="G44" s="2">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="H44" s="2">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I44" s="2">
         <v>1</v>
@@ -2774,7 +2751,7 @@
         <v>10000</v>
       </c>
       <c r="K44" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>74</v>
@@ -2782,7 +2759,7 @@
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C45" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>75</v>
@@ -2794,10 +2771,10 @@
         <v>50</v>
       </c>
       <c r="G45" s="2">
-        <v>601</v>
+        <v>301</v>
       </c>
       <c r="H45" s="2">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="I45" s="2">
         <v>1</v>
@@ -2806,7 +2783,7 @@
         <v>10000</v>
       </c>
       <c r="K45" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>74</v>
@@ -2814,7 +2791,7 @@
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C46" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>75</v>
@@ -2826,10 +2803,10 @@
         <v>50</v>
       </c>
       <c r="G46" s="2">
-        <v>1001</v>
+        <v>601</v>
       </c>
       <c r="H46" s="2">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I46" s="2">
         <v>1</v>
@@ -2838,15 +2815,15 @@
         <v>10000</v>
       </c>
       <c r="K46" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="47" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C47" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>75</v>
@@ -2858,10 +2835,10 @@
         <v>50</v>
       </c>
       <c r="G47" s="2">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H47" s="2">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="I47" s="2">
         <v>1</v>
@@ -2870,7 +2847,7 @@
         <v>10000</v>
       </c>
       <c r="K47" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>74</v>
@@ -2878,7 +2855,7 @@
     </row>
     <row r="48" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
       <c r="C48" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D48" s="8" t="s">
         <v>75</v>
@@ -2890,10 +2867,10 @@
         <v>50</v>
       </c>
       <c r="G48" s="2">
-        <v>3501</v>
+        <v>1501</v>
       </c>
       <c r="H48" s="2">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="I48" s="2">
         <v>1</v>
@@ -2902,50 +2879,50 @@
         <v>10000</v>
       </c>
       <c r="K48" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="49" s="2" customFormat="1" ht="20" customHeight="1" spans="4:4">
-      <c r="D49" s="4"/>
-    </row>
-    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C50" s="2">
-        <v>300</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F50" s="2">
-        <v>10</v>
-      </c>
-      <c r="G50" s="2">
-        <v>1</v>
-      </c>
-      <c r="H50" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I50" s="2">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2">
+    <row r="49" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C49" s="2">
+        <v>205</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F49" s="2">
+        <v>50</v>
+      </c>
+      <c r="G49" s="2">
+        <v>3501</v>
+      </c>
+      <c r="H49" s="2">
         <v>10000</v>
       </c>
-      <c r="K50" s="2">
-        <v>1</v>
-      </c>
-      <c r="L50" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="I49" s="2">
+        <v>1</v>
+      </c>
+      <c r="J49" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K49" s="2">
+        <v>40</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="D50" s="4"/>
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C51" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D51" s="11" t="s">
         <v>77</v>
@@ -2957,10 +2934,10 @@
         <v>10</v>
       </c>
       <c r="G51" s="2">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="H51" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I51" s="2">
         <v>1</v>
@@ -2969,7 +2946,7 @@
         <v>10000</v>
       </c>
       <c r="K51" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>21</v>
@@ -2977,7 +2954,7 @@
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C52" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D52" s="11" t="s">
         <v>77</v>
@@ -2989,10 +2966,10 @@
         <v>10</v>
       </c>
       <c r="G52" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H52" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I52" s="2">
         <v>1</v>
@@ -3001,48 +2978,48 @@
         <v>10000</v>
       </c>
       <c r="K52" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="53" s="2" customFormat="1" customHeight="1"/>
-    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C54" s="2">
-        <v>400</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F54" s="2">
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C53" s="2">
+        <v>302</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F53" s="2">
         <v>10</v>
       </c>
-      <c r="G54" s="2">
-        <v>50</v>
-      </c>
-      <c r="H54" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I54" s="2">
-        <v>1</v>
-      </c>
-      <c r="J54" s="2">
+      <c r="G53" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H53" s="2">
         <v>10000</v>
       </c>
-      <c r="K54" s="2">
-        <v>1</v>
-      </c>
-      <c r="L54" s="2" t="s">
+      <c r="I53" s="2">
+        <v>1</v>
+      </c>
+      <c r="J53" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K53" s="2">
+        <v>3</v>
+      </c>
+      <c r="L53" s="2" t="s">
         <v>21</v>
       </c>
     </row>
+    <row r="54" s="2" customFormat="1" customHeight="1"/>
     <row r="55" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C55" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D55" s="11" t="s">
         <v>79</v>
@@ -3054,10 +3031,10 @@
         <v>10</v>
       </c>
       <c r="G55" s="2">
-        <v>1001</v>
+        <v>50</v>
       </c>
       <c r="H55" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I55" s="2">
         <v>1</v>
@@ -3066,7 +3043,7 @@
         <v>10000</v>
       </c>
       <c r="K55" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>21</v>
@@ -3074,7 +3051,7 @@
     </row>
     <row r="56" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C56" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D56" s="11" t="s">
         <v>79</v>
@@ -3086,10 +3063,10 @@
         <v>10</v>
       </c>
       <c r="G56" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H56" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I56" s="2">
         <v>1</v>
@@ -3098,48 +3075,48 @@
         <v>10000</v>
       </c>
       <c r="K56" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="57" s="2" customFormat="1" customHeight="1"/>
-    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C58" s="2">
-        <v>500</v>
-      </c>
-      <c r="D58" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F58" s="2">
-        <v>4</v>
-      </c>
-      <c r="G58" s="2">
-        <v>150</v>
-      </c>
-      <c r="H58" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I58" s="2">
-        <v>1</v>
-      </c>
-      <c r="J58" s="2">
-        <v>20</v>
-      </c>
-      <c r="K58" s="2">
-        <v>1</v>
-      </c>
-      <c r="L58" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C57" s="2">
+        <v>402</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F57" s="2">
+        <v>10</v>
+      </c>
+      <c r="G57" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H57" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I57" s="2">
+        <v>1</v>
+      </c>
+      <c r="J57" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K57" s="2">
+        <v>3</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" s="2" customFormat="1" customHeight="1"/>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C59" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D59" s="11" t="s">
         <v>81</v>
@@ -3151,10 +3128,10 @@
         <v>4</v>
       </c>
       <c r="G59" s="2">
-        <v>1001</v>
+        <v>150</v>
       </c>
       <c r="H59" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I59" s="2">
         <v>1</v>
@@ -3163,7 +3140,7 @@
         <v>20</v>
       </c>
       <c r="K59" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>83</v>
@@ -3171,7 +3148,7 @@
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C60" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D60" s="11" t="s">
         <v>81</v>
@@ -3183,10 +3160,10 @@
         <v>4</v>
       </c>
       <c r="G60" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H60" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I60" s="2">
         <v>1</v>
@@ -3195,48 +3172,48 @@
         <v>20</v>
       </c>
       <c r="K60" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="61" s="2" customFormat="1" customHeight="1"/>
-    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C62" s="2">
-        <v>600</v>
-      </c>
-      <c r="D62" s="2">
+    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C61" s="2">
+        <v>502</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F61" s="2">
+        <v>4</v>
+      </c>
+      <c r="G61" s="2">
         <v>3001</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F62" s="2">
-        <v>10</v>
-      </c>
-      <c r="G62" s="2">
-        <v>1</v>
-      </c>
-      <c r="H62" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I62" s="2">
-        <v>1</v>
-      </c>
-      <c r="J62" s="2">
+      <c r="H61" s="2">
         <v>10000</v>
       </c>
-      <c r="K62" s="2">
-        <v>1</v>
-      </c>
-      <c r="L62" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
+      <c r="I61" s="2">
+        <v>1</v>
+      </c>
+      <c r="J61" s="2">
+        <v>20</v>
+      </c>
+      <c r="K61" s="2">
+        <v>3</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62" s="2" customFormat="1" customHeight="1"/>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C63" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D63" s="2">
         <v>3001</v>
@@ -3248,10 +3225,10 @@
         <v>10</v>
       </c>
       <c r="G63" s="2">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="H63" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I63" s="2">
         <v>1</v>
@@ -3260,7 +3237,7 @@
         <v>10000</v>
       </c>
       <c r="K63" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>21</v>
@@ -3268,7 +3245,7 @@
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C64" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D64" s="2">
         <v>3001</v>
@@ -3280,10 +3257,10 @@
         <v>10</v>
       </c>
       <c r="G64" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H64" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I64" s="2">
         <v>1</v>
@@ -3292,48 +3269,48 @@
         <v>10000</v>
       </c>
       <c r="K64" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="65" s="2" customFormat="1" customHeight="1"/>
-    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C66" s="2">
-        <v>700</v>
-      </c>
-      <c r="D66" s="2">
-        <v>3002</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F66" s="2">
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C65" s="2">
+        <v>602</v>
+      </c>
+      <c r="D65" s="2">
+        <v>3001</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F65" s="2">
         <v>10</v>
       </c>
-      <c r="G66" s="2">
-        <v>200</v>
-      </c>
-      <c r="H66" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I66" s="2">
-        <v>1</v>
-      </c>
-      <c r="J66" s="2">
+      <c r="G65" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H65" s="2">
         <v>10000</v>
       </c>
-      <c r="K66" s="2">
-        <v>1</v>
-      </c>
-      <c r="L66" s="2" t="s">
+      <c r="I65" s="2">
+        <v>1</v>
+      </c>
+      <c r="J65" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K65" s="2">
+        <v>3</v>
+      </c>
+      <c r="L65" s="2" t="s">
         <v>21</v>
       </c>
     </row>
+    <row r="66" s="2" customFormat="1" customHeight="1"/>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C67" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D67" s="2">
         <v>3002</v>
@@ -3345,10 +3322,10 @@
         <v>10</v>
       </c>
       <c r="G67" s="2">
-        <v>1001</v>
+        <v>200</v>
       </c>
       <c r="H67" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I67" s="2">
         <v>1</v>
@@ -3357,7 +3334,7 @@
         <v>10000</v>
       </c>
       <c r="K67" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>21</v>
@@ -3365,7 +3342,7 @@
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C68" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D68" s="2">
         <v>3002</v>
@@ -3377,10 +3354,10 @@
         <v>10</v>
       </c>
       <c r="G68" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H68" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I68" s="2">
         <v>1</v>
@@ -3389,56 +3366,56 @@
         <v>10000</v>
       </c>
       <c r="K68" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="69" customHeight="1" spans="11:11">
-      <c r="K69" s="2"/>
-    </row>
-    <row r="70" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C70" s="2">
-        <v>800</v>
-      </c>
-      <c r="D70" s="2">
-        <v>3003</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F70" s="2">
-        <v>2</v>
-      </c>
-      <c r="G70" s="2">
-        <v>4001</v>
-      </c>
-      <c r="H70" s="2">
-        <v>5000</v>
-      </c>
-      <c r="I70" s="2">
-        <v>7</v>
-      </c>
-      <c r="J70" s="2">
-        <v>13</v>
-      </c>
-      <c r="K70" s="2">
-        <v>5</v>
-      </c>
-      <c r="L70" s="2" t="s">
+    <row r="69" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C69" s="2">
+        <v>702</v>
+      </c>
+      <c r="D69" s="2">
+        <v>3002</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F69" s="2">
+        <v>10</v>
+      </c>
+      <c r="G69" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H69" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I69" s="2">
+        <v>1</v>
+      </c>
+      <c r="J69" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K69" s="2">
+        <v>3</v>
+      </c>
+      <c r="L69" s="2" t="s">
         <v>21</v>
       </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:12">
+      <c r="K70" s="2"/>
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C71" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D71" s="2">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F71" s="2">
         <v>2</v>
@@ -3450,59 +3427,62 @@
         <v>5000</v>
       </c>
       <c r="I71" s="2">
+        <v>7</v>
+      </c>
+      <c r="J71" s="2">
         <v>13</v>
       </c>
-      <c r="J71" s="2">
+      <c r="K71" s="2">
         <v>5</v>
-      </c>
-      <c r="K71" s="2">
-        <v>1</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="73" customHeight="1" spans="3:11">
-      <c r="C73" s="1">
+    <row r="72" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C72" s="2">
+        <v>801</v>
+      </c>
+      <c r="D72" s="2">
+        <v>3004</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F72" s="2">
+        <v>2</v>
+      </c>
+      <c r="G72" s="2">
+        <v>4001</v>
+      </c>
+      <c r="H72" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I72" s="2">
+        <v>13</v>
+      </c>
+      <c r="J72" s="2">
+        <v>5</v>
+      </c>
+      <c r="K72" s="2">
+        <v>1</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:12">
+      <c r="C74" s="1">
         <v>901</v>
       </c>
-      <c r="D73" s="10" t="s">
+      <c r="D74" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E74" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F74" s="1">
         <v>20</v>
-      </c>
-      <c r="G73" s="1">
-        <v>3001</v>
-      </c>
-      <c r="H73" s="1">
-        <v>4000</v>
-      </c>
-      <c r="I73" s="1">
-        <v>3</v>
-      </c>
-      <c r="J73" s="1">
-        <v>30</v>
-      </c>
-      <c r="K73" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" customHeight="1" spans="3:11">
-      <c r="C74" s="1">
-        <v>902</v>
-      </c>
-      <c r="D74" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F74" s="1">
-        <v>10</v>
       </c>
       <c r="G74" s="1">
         <v>3001</v>
@@ -3514,24 +3494,24 @@
         <v>3</v>
       </c>
       <c r="J74" s="1">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="K74" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="3:11">
+    <row r="75" customHeight="1" spans="3:12">
       <c r="C75" s="1">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F75" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G75" s="1">
         <v>3001</v>
@@ -3543,82 +3523,82 @@
         <v>3</v>
       </c>
       <c r="J75" s="1">
+        <v>5</v>
+      </c>
+      <c r="K75" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:12">
+      <c r="C76" s="1">
+        <v>903</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F76" s="1">
+        <v>5</v>
+      </c>
+      <c r="G76" s="1">
+        <v>3001</v>
+      </c>
+      <c r="H76" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I76" s="1">
         <v>3</v>
       </c>
-      <c r="K75" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" customHeight="1" spans="3:11">
-      <c r="C76" s="1">
+      <c r="J76" s="1">
+        <v>3</v>
+      </c>
+      <c r="K76" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:12">
+      <c r="C77" s="1">
         <v>904</v>
       </c>
-      <c r="D76" s="10" t="s">
+      <c r="D77" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E77" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F77" s="1">
         <v>2</v>
       </c>
-      <c r="G76" s="1">
+      <c r="G77" s="1">
         <v>3501</v>
-      </c>
-      <c r="H76" s="1">
-        <v>5000</v>
-      </c>
-      <c r="I76" s="1">
-        <v>4</v>
-      </c>
-      <c r="J76" s="1">
-        <v>6</v>
-      </c>
-      <c r="K76" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" customHeight="1" spans="3:11">
-      <c r="C77" s="1">
-        <v>905</v>
-      </c>
-      <c r="D77" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F77" s="1">
-        <v>10</v>
-      </c>
-      <c r="G77" s="1">
-        <v>4001</v>
       </c>
       <c r="H77" s="1">
         <v>5000</v>
       </c>
       <c r="I77" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J77" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K77" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" customHeight="1" spans="3:11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:12">
       <c r="C78" s="1">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F78" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G78" s="1">
         <v>4001</v>
@@ -3630,24 +3610,24 @@
         <v>3</v>
       </c>
       <c r="J78" s="1">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K78" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="79" customHeight="1" spans="3:11">
+    <row r="79" customHeight="1" spans="3:12">
       <c r="C79" s="1">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F79" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G79" s="1">
         <v>4001</v>
@@ -3659,56 +3639,53 @@
         <v>3</v>
       </c>
       <c r="J79" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K79" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="82" customHeight="1" spans="3:12">
-      <c r="C82" s="1">
-        <v>10001</v>
-      </c>
-      <c r="D82" s="6">
-        <v>180001</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F82" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G82" s="1">
-        <v>100</v>
-      </c>
-      <c r="H82" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I82" s="1">
-        <v>100</v>
-      </c>
-      <c r="J82" s="1">
-        <v>1</v>
-      </c>
-      <c r="K82" s="2">
-        <v>1</v>
-      </c>
-      <c r="L82" s="1" t="s">
-        <v>97</v>
+    <row r="80" customHeight="1" spans="3:12">
+      <c r="C80" s="1">
+        <v>907</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F80" s="1">
+        <v>3</v>
+      </c>
+      <c r="G80" s="1">
+        <v>4001</v>
+      </c>
+      <c r="H80" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I80" s="1">
+        <v>3</v>
+      </c>
+      <c r="J80" s="1">
+        <v>2</v>
+      </c>
+      <c r="K80" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:12">
       <c r="C83" s="1">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="D83" s="6">
-        <v>180002</v>
+        <v>180001</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F83" s="1">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G83" s="1">
         <v>100</v>
@@ -3731,16 +3708,16 @@
     </row>
     <row r="84" customHeight="1" spans="3:12">
       <c r="C84" s="1">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="D84" s="6">
-        <v>180003</v>
+        <v>180002</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F84" s="1">
-        <v>150000</v>
+        <v>4000</v>
       </c>
       <c r="G84" s="1">
         <v>100</v>
@@ -3752,7 +3729,7 @@
         <v>100</v>
       </c>
       <c r="J84" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K84" s="2">
         <v>1</v>
@@ -3763,16 +3740,16 @@
     </row>
     <row r="85" customHeight="1" spans="3:12">
       <c r="C85" s="1">
-        <v>10004</v>
+        <v>10003</v>
       </c>
       <c r="D85" s="6">
-        <v>180004</v>
+        <v>180003</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F85" s="1">
-        <v>8000</v>
+        <v>150000</v>
       </c>
       <c r="G85" s="1">
         <v>100</v>
@@ -3784,7 +3761,7 @@
         <v>100</v>
       </c>
       <c r="J85" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K85" s="2">
         <v>1</v>
@@ -3795,16 +3772,16 @@
     </row>
     <row r="86" customHeight="1" spans="3:12">
       <c r="C86" s="1">
-        <v>10005</v>
+        <v>10004</v>
       </c>
       <c r="D86" s="6">
-        <v>180005</v>
+        <v>180004</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F86" s="1">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="G86" s="1">
         <v>100</v>
@@ -3827,16 +3804,16 @@
     </row>
     <row r="87" customHeight="1" spans="3:12">
       <c r="C87" s="1">
-        <v>10006</v>
+        <v>10005</v>
       </c>
       <c r="D87" s="6">
-        <v>180006</v>
+        <v>180005</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F87" s="1">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="G87" s="1">
         <v>100</v>
@@ -3848,7 +3825,7 @@
         <v>100</v>
       </c>
       <c r="J87" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K87" s="2">
         <v>1</v>
@@ -3859,16 +3836,16 @@
     </row>
     <row r="88" customHeight="1" spans="3:12">
       <c r="C88" s="1">
-        <v>10007</v>
+        <v>10006</v>
       </c>
       <c r="D88" s="6">
-        <v>180007</v>
+        <v>180006</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F88" s="1">
-        <v>2000</v>
+        <v>50000</v>
       </c>
       <c r="G88" s="1">
         <v>100</v>
@@ -3880,7 +3857,7 @@
         <v>100</v>
       </c>
       <c r="J88" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K88" s="2">
         <v>1</v>
@@ -3891,16 +3868,16 @@
     </row>
     <row r="89" customHeight="1" spans="3:12">
       <c r="C89" s="1">
-        <v>10008</v>
+        <v>10007</v>
       </c>
       <c r="D89" s="6">
-        <v>180008</v>
+        <v>180007</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F89" s="1">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="G89" s="1">
         <v>100</v>
@@ -3912,7 +3889,7 @@
         <v>100</v>
       </c>
       <c r="J89" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K89" s="2">
         <v>1</v>
@@ -3923,16 +3900,16 @@
     </row>
     <row r="90" customHeight="1" spans="3:12">
       <c r="C90" s="1">
-        <v>10009</v>
+        <v>10008</v>
       </c>
       <c r="D90" s="6">
-        <v>180009</v>
+        <v>180008</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F90" s="1">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="G90" s="1">
         <v>100</v>
@@ -3944,7 +3921,7 @@
         <v>100</v>
       </c>
       <c r="J90" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K90" s="2">
         <v>1</v>
@@ -3955,16 +3932,16 @@
     </row>
     <row r="91" customHeight="1" spans="3:12">
       <c r="C91" s="1">
-        <v>10010</v>
+        <v>10009</v>
       </c>
       <c r="D91" s="6">
-        <v>180010</v>
+        <v>180009</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F91" s="1">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="G91" s="1">
         <v>100</v>
@@ -3987,16 +3964,16 @@
     </row>
     <row r="92" customHeight="1" spans="3:12">
       <c r="C92" s="1">
-        <v>10011</v>
+        <v>10010</v>
       </c>
       <c r="D92" s="6">
-        <v>180011</v>
+        <v>180010</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F92" s="1">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="G92" s="1">
         <v>100</v>
@@ -4008,7 +3985,7 @@
         <v>100</v>
       </c>
       <c r="J92" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K92" s="2">
         <v>1</v>
@@ -4019,13 +3996,13 @@
     </row>
     <row r="93" customHeight="1" spans="3:12">
       <c r="C93" s="1">
-        <v>10012</v>
+        <v>10011</v>
       </c>
       <c r="D93" s="6">
-        <v>180012</v>
+        <v>180011</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F93" s="1">
         <v>100000</v>
@@ -4051,16 +4028,16 @@
     </row>
     <row r="94" customHeight="1" spans="3:12">
       <c r="C94" s="1">
-        <v>10013</v>
+        <v>10012</v>
       </c>
       <c r="D94" s="6">
-        <v>180013</v>
+        <v>180012</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F94" s="1">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="G94" s="1">
         <v>100</v>
@@ -4083,16 +4060,16 @@
     </row>
     <row r="95" customHeight="1" spans="3:12">
       <c r="C95" s="1">
-        <v>10014</v>
+        <v>10013</v>
       </c>
       <c r="D95" s="6">
-        <v>180014</v>
+        <v>180013</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F95" s="1">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G95" s="1">
         <v>100</v>
@@ -4115,13 +4092,13 @@
     </row>
     <row r="96" customHeight="1" spans="3:12">
       <c r="C96" s="1">
-        <v>10015</v>
+        <v>10014</v>
       </c>
       <c r="D96" s="6">
-        <v>180015</v>
+        <v>180014</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F96" s="1">
         <v>100000</v>
@@ -4145,18 +4122,18 @@
         <v>97</v>
       </c>
     </row>
-    <row r="97" customHeight="1" spans="3:12">
+    <row r="97" customHeight="1" spans="1:12">
       <c r="C97" s="1">
-        <v>10016</v>
+        <v>10015</v>
       </c>
       <c r="D97" s="6">
-        <v>180020</v>
+        <v>180015</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F97" s="1">
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="G97" s="1">
         <v>100</v>
@@ -4168,7 +4145,7 @@
         <v>100</v>
       </c>
       <c r="J97" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K97" s="2">
         <v>1</v>
@@ -4177,15 +4154,15 @@
         <v>97</v>
       </c>
     </row>
-    <row r="98" customHeight="1" spans="3:12">
+    <row r="98" customHeight="1" spans="1:12">
       <c r="C98" s="1">
-        <v>10017</v>
+        <v>10016</v>
       </c>
       <c r="D98" s="6">
-        <v>180021</v>
+        <v>180020</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F98" s="1">
         <v>30000</v>
@@ -4209,18 +4186,18 @@
         <v>97</v>
       </c>
     </row>
-    <row r="99" customHeight="1" spans="3:12">
+    <row r="99" customHeight="1" spans="1:12">
       <c r="C99" s="1">
-        <v>10018</v>
+        <v>10017</v>
       </c>
       <c r="D99" s="6">
-        <v>180022</v>
+        <v>180021</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F99" s="1">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="G99" s="1">
         <v>100</v>
@@ -4232,7 +4209,7 @@
         <v>100</v>
       </c>
       <c r="J99" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K99" s="2">
         <v>1</v>
@@ -4241,56 +4218,56 @@
         <v>97</v>
       </c>
     </row>
-    <row r="101" customHeight="1" spans="3:12">
-      <c r="C101" s="1">
+    <row r="100" customHeight="1" spans="1:12">
+      <c r="C100" s="1">
+        <v>10018</v>
+      </c>
+      <c r="D100" s="6">
+        <v>180022</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F100" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G100" s="1">
+        <v>100</v>
+      </c>
+      <c r="H100" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I100" s="1">
+        <v>100</v>
+      </c>
+      <c r="J100" s="1">
+        <v>1</v>
+      </c>
+      <c r="K100" s="2">
+        <v>1</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="1:12">
+      <c r="C102" s="1">
         <v>10030</v>
       </c>
-      <c r="D101" s="1">
+      <c r="D102" s="1">
         <v>180030</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="E102" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F101" s="1">
+      <c r="F102" s="1">
         <v>5</v>
-      </c>
-      <c r="G101" s="1">
-        <v>1100</v>
-      </c>
-      <c r="H101" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I101" s="1">
-        <v>100</v>
-      </c>
-      <c r="J101" s="1">
-        <v>1</v>
-      </c>
-      <c r="K101" s="2">
-        <v>1</v>
-      </c>
-      <c r="L101" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="102" customHeight="1" spans="3:12">
-      <c r="C102" s="1">
-        <v>10031</v>
-      </c>
-      <c r="D102" s="6">
-        <v>180032</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F102" s="1">
-        <v>1</v>
       </c>
       <c r="G102" s="1">
         <v>1100</v>
       </c>
       <c r="H102" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I102" s="1">
         <v>100</v>
@@ -4305,21 +4282,21 @@
         <v>116</v>
       </c>
     </row>
-    <row r="103" customHeight="1" spans="3:12">
+    <row r="103" customHeight="1" spans="1:12">
       <c r="C103" s="1">
-        <v>10032</v>
+        <v>10031</v>
       </c>
       <c r="D103" s="6">
-        <v>180033</v>
+        <v>180032</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F103" s="1">
         <v>1</v>
       </c>
       <c r="G103" s="1">
-        <v>1600</v>
+        <v>1100</v>
       </c>
       <c r="H103" s="1">
         <v>2000</v>
@@ -4337,24 +4314,24 @@
         <v>116</v>
       </c>
     </row>
-    <row r="104" customHeight="1" spans="3:12">
+    <row r="104" customHeight="1" spans="1:12">
       <c r="C104" s="1">
-        <v>10033</v>
+        <v>10032</v>
       </c>
       <c r="D104" s="6">
-        <v>180034</v>
+        <v>180033</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F104" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G104" s="1">
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="H104" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I104" s="1">
         <v>100</v>
@@ -4369,24 +4346,24 @@
         <v>116</v>
       </c>
     </row>
-    <row r="105" customHeight="1" spans="3:12">
+    <row r="105" customHeight="1" spans="1:12">
       <c r="C105" s="1">
-        <v>10034</v>
+        <v>10033</v>
       </c>
       <c r="D105" s="6">
-        <v>180035</v>
+        <v>180034</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F105" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G105" s="1">
-        <v>2000</v>
+        <v>1100</v>
       </c>
       <c r="H105" s="1">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I105" s="1">
         <v>100</v>
@@ -4401,15 +4378,15 @@
         <v>116</v>
       </c>
     </row>
-    <row r="106" customHeight="1" spans="3:12">
+    <row r="106" customHeight="1" spans="1:12">
       <c r="C106" s="1">
-        <v>10035</v>
+        <v>10034</v>
       </c>
       <c r="D106" s="6">
-        <v>180036</v>
+        <v>180035</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F106" s="1">
         <v>1</v>
@@ -4433,24 +4410,24 @@
         <v>116</v>
       </c>
     </row>
-    <row r="107" customHeight="1" spans="3:12">
+    <row r="107" customHeight="1" spans="1:12">
       <c r="C107" s="1">
-        <v>10036</v>
+        <v>10035</v>
       </c>
       <c r="D107" s="6">
-        <v>180037</v>
+        <v>180036</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F107" s="1">
         <v>1</v>
       </c>
       <c r="G107" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H107" s="1">
         <v>2500</v>
-      </c>
-      <c r="H107" s="1">
-        <v>3500</v>
       </c>
       <c r="I107" s="1">
         <v>100</v>
@@ -4465,21 +4442,21 @@
         <v>116</v>
       </c>
     </row>
-    <row r="108" customHeight="1" spans="3:12">
+    <row r="108" customHeight="1" spans="1:12">
       <c r="C108" s="1">
-        <v>10037</v>
+        <v>10036</v>
       </c>
       <c r="D108" s="6">
-        <v>180038</v>
+        <v>180037</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F108" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G108" s="1">
-        <v>1600</v>
+        <v>2500</v>
       </c>
       <c r="H108" s="1">
         <v>3500</v>
@@ -4497,21 +4474,21 @@
         <v>116</v>
       </c>
     </row>
-    <row r="109" customHeight="1" spans="3:12">
+    <row r="109" customHeight="1" spans="1:12">
       <c r="C109" s="1">
-        <v>10038</v>
+        <v>10037</v>
       </c>
       <c r="D109" s="6">
-        <v>180039</v>
+        <v>180038</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F109" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G109" s="1">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="H109" s="1">
         <v>3500</v>
@@ -4530,29 +4507,23 @@
       </c>
     </row>
     <row r="110" customHeight="1" spans="1:12">
-      <c r="A110" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C110" s="1">
-        <v>10039</v>
+        <v>10038</v>
       </c>
       <c r="D110" s="6">
-        <v>180040</v>
+        <v>180039</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F110" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G110" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="H110" s="1">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="I110" s="1">
         <v>100</v>
@@ -4567,24 +4538,30 @@
         <v>116</v>
       </c>
     </row>
-    <row r="111" customHeight="1" spans="3:12">
+    <row r="111" customHeight="1" spans="1:12">
+      <c r="A111" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C111" s="1">
-        <v>10040</v>
+        <v>10039</v>
       </c>
       <c r="D111" s="6">
-        <v>180041</v>
+        <v>180040</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F111" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G111" s="1">
+        <v>3000</v>
+      </c>
+      <c r="H111" s="1">
         <v>4000</v>
-      </c>
-      <c r="H111" s="1">
-        <v>5000</v>
       </c>
       <c r="I111" s="1">
         <v>100</v>
@@ -4599,24 +4576,24 @@
         <v>116</v>
       </c>
     </row>
-    <row r="112" customHeight="1" spans="3:12">
+    <row r="112" customHeight="1" spans="1:12">
       <c r="C112" s="1">
-        <v>10041</v>
+        <v>10040</v>
       </c>
       <c r="D112" s="6">
-        <v>180042</v>
+        <v>180041</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F112" s="1">
         <v>3</v>
       </c>
       <c r="G112" s="1">
+        <v>4000</v>
+      </c>
+      <c r="H112" s="1">
         <v>5000</v>
-      </c>
-      <c r="H112" s="1">
-        <v>6000</v>
       </c>
       <c r="I112" s="1">
         <v>100</v>
@@ -4631,59 +4608,59 @@
         <v>116</v>
       </c>
     </row>
-    <row r="114" customHeight="1" spans="3:12">
-      <c r="C114" s="1">
-        <v>11001</v>
-      </c>
-      <c r="D114" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F114" s="1">
-        <v>5</v>
-      </c>
-      <c r="G114" s="1">
-        <v>150</v>
-      </c>
-      <c r="H114" s="1">
-        <v>1200</v>
-      </c>
-      <c r="I114" s="1">
-        <v>20</v>
-      </c>
-      <c r="J114" s="1">
-        <v>2</v>
-      </c>
-      <c r="K114" s="2">
-        <v>1</v>
-      </c>
-      <c r="L114" s="1" t="s">
-        <v>39</v>
+    <row r="113" customHeight="1" spans="3:12">
+      <c r="C113" s="1">
+        <v>10041</v>
+      </c>
+      <c r="D113" s="6">
+        <v>180042</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F113" s="1">
+        <v>3</v>
+      </c>
+      <c r="G113" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H113" s="1">
+        <v>6000</v>
+      </c>
+      <c r="I113" s="1">
+        <v>100</v>
+      </c>
+      <c r="J113" s="1">
+        <v>1</v>
+      </c>
+      <c r="K113" s="2">
+        <v>1</v>
+      </c>
+      <c r="L113" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="3:12">
       <c r="C115" s="1">
-        <v>11002</v>
+        <v>11001</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F115" s="1">
         <v>5</v>
       </c>
       <c r="G115" s="1">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H115" s="1">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="I115" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J115" s="1">
         <v>2</v>
@@ -4697,25 +4674,25 @@
     </row>
     <row r="116" customHeight="1" spans="3:12">
       <c r="C116" s="1">
-        <v>11003</v>
+        <v>11002</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F116" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G116" s="1">
-        <v>1050</v>
+        <v>200</v>
       </c>
       <c r="H116" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I116" s="1">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="J116" s="1">
         <v>2</v>
@@ -4729,7 +4706,7 @@
     </row>
     <row r="117" customHeight="1" spans="3:12">
       <c r="C117" s="1">
-        <v>11004</v>
+        <v>11003</v>
       </c>
       <c r="D117" s="9" t="s">
         <v>132</v>
@@ -4738,16 +4715,16 @@
         <v>133</v>
       </c>
       <c r="F117" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G117" s="1">
-        <v>4001</v>
+        <v>1050</v>
       </c>
       <c r="H117" s="1">
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="I117" s="1">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J117" s="1">
         <v>2</v>
@@ -4761,54 +4738,54 @@
     </row>
     <row r="118" customHeight="1" spans="3:12">
       <c r="C118" s="1">
-        <v>11005</v>
+        <v>11004</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="F118" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G118" s="1">
-        <v>101</v>
+        <v>4001</v>
       </c>
       <c r="H118" s="1">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="I118" s="1">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="J118" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K118" s="2">
         <v>1</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>136</v>
+        <v>39</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="3:12">
       <c r="C119" s="1">
-        <v>11006</v>
+        <v>11005</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F119" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G119" s="1">
-        <v>501</v>
+        <v>101</v>
       </c>
       <c r="H119" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="I119" s="1">
         <v>10</v>
@@ -4820,31 +4797,31 @@
         <v>1</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="3:12">
       <c r="C120" s="1">
-        <v>11007</v>
+        <v>11006</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F120" s="1">
+        <v>15</v>
+      </c>
+      <c r="G120" s="1">
+        <v>501</v>
+      </c>
+      <c r="H120" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I120" s="1">
         <v>10</v>
       </c>
-      <c r="G120" s="1">
-        <v>1001</v>
-      </c>
-      <c r="H120" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I120" s="1">
-        <v>20</v>
-      </c>
       <c r="J120" s="1">
         <v>1</v>
       </c>
@@ -4852,27 +4829,27 @@
         <v>1</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="121" customHeight="1" spans="3:12">
       <c r="C121" s="1">
-        <v>11008</v>
+        <v>11007</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F121" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G121" s="1">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H121" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I121" s="1">
         <v>20</v>
@@ -4884,30 +4861,30 @@
         <v>1</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="122" customHeight="1" spans="3:12">
       <c r="C122" s="1">
-        <v>11009</v>
+        <v>11008</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F122" s="1">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G122" s="1">
-        <v>2001</v>
+        <v>1501</v>
       </c>
       <c r="H122" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I122" s="1">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="J122" s="1">
         <v>1</v>
@@ -4916,27 +4893,27 @@
         <v>1</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="123" customHeight="1" spans="3:12">
       <c r="C123" s="1">
-        <v>11010</v>
+        <v>11009</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F123" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G123" s="1">
-        <v>2501</v>
+        <v>2001</v>
       </c>
       <c r="H123" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I123" s="1">
         <v>52</v>
@@ -4948,30 +4925,30 @@
         <v>1</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="124" customHeight="1" spans="3:12">
       <c r="C124" s="1">
-        <v>11011</v>
+        <v>11010</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F124" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G124" s="1">
-        <v>3001</v>
+        <v>2501</v>
       </c>
       <c r="H124" s="1">
-        <v>3800</v>
+        <v>3000</v>
       </c>
       <c r="I124" s="1">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="J124" s="1">
         <v>1</v>
@@ -4980,32 +4957,32 @@
         <v>1</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="125" customHeight="1" spans="3:12">
       <c r="C125" s="1">
-        <v>11012</v>
+        <v>11011</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="F125" s="2">
-        <v>1</v>
-      </c>
-      <c r="G125" s="2">
-        <v>5001</v>
-      </c>
-      <c r="H125" s="2">
-        <v>5500</v>
-      </c>
-      <c r="I125" s="2">
-        <v>61</v>
-      </c>
-      <c r="J125" s="2">
+        <v>153</v>
+      </c>
+      <c r="F125" s="1">
+        <v>3</v>
+      </c>
+      <c r="G125" s="1">
+        <v>3001</v>
+      </c>
+      <c r="H125" s="1">
+        <v>3800</v>
+      </c>
+      <c r="I125" s="1">
+        <v>62</v>
+      </c>
+      <c r="J125" s="1">
         <v>1</v>
       </c>
       <c r="K125" s="2">
@@ -5013,6 +4990,70 @@
       </c>
       <c r="L125" s="1" t="s">
         <v>154</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="3:12">
+      <c r="C126" s="1">
+        <v>11012</v>
+      </c>
+      <c r="D126" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F126" s="2">
+        <v>2</v>
+      </c>
+      <c r="G126" s="2">
+        <v>5001</v>
+      </c>
+      <c r="H126" s="2">
+        <v>5500</v>
+      </c>
+      <c r="I126" s="2">
+        <v>61</v>
+      </c>
+      <c r="J126" s="2">
+        <v>1</v>
+      </c>
+      <c r="K126" s="2">
+        <v>1</v>
+      </c>
+      <c r="L126" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="3:12">
+      <c r="C127" s="1">
+        <v>11013</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F127" s="1">
+        <v>5</v>
+      </c>
+      <c r="G127" s="1">
+        <v>5501</v>
+      </c>
+      <c r="H127" s="1">
+        <v>6000</v>
+      </c>
+      <c r="I127" s="1">
+        <v>39</v>
+      </c>
+      <c r="J127" s="1">
+        <v>1</v>
+      </c>
+      <c r="K127" s="2">
+        <v>1</v>
+      </c>
+      <c r="L127" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="159">
   <si>
     <t>#</t>
   </si>
@@ -1534,7 +1534,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M127"/>
+  <dimension ref="A1:M129"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -3471,47 +3471,50 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" customHeight="1" spans="3:12">
-      <c r="C74" s="1">
-        <v>901</v>
-      </c>
-      <c r="D74" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F74" s="1">
+    <row r="73" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C73" s="2">
+        <v>802</v>
+      </c>
+      <c r="D73" s="2">
+        <v>3003</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F73" s="2">
+        <v>3</v>
+      </c>
+      <c r="G73" s="2">
+        <v>5500</v>
+      </c>
+      <c r="H73" s="2">
+        <v>6500</v>
+      </c>
+      <c r="I73" s="2">
+        <v>7</v>
+      </c>
+      <c r="J73" s="2">
         <v>20</v>
       </c>
-      <c r="G74" s="1">
-        <v>3001</v>
-      </c>
-      <c r="H74" s="1">
-        <v>4000</v>
-      </c>
-      <c r="I74" s="1">
-        <v>3</v>
-      </c>
-      <c r="J74" s="1">
-        <v>30</v>
-      </c>
-      <c r="K74" s="2">
-        <v>1</v>
+      <c r="K73" s="2">
+        <v>7</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:12">
       <c r="C75" s="1">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F75" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G75" s="1">
         <v>3001</v>
@@ -3523,7 +3526,7 @@
         <v>3</v>
       </c>
       <c r="J75" s="1">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="K75" s="2">
         <v>1</v>
@@ -3531,16 +3534,16 @@
     </row>
     <row r="76" customHeight="1" spans="3:12">
       <c r="C76" s="1">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F76" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G76" s="1">
         <v>3001</v>
@@ -3552,7 +3555,7 @@
         <v>3</v>
       </c>
       <c r="J76" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K76" s="2">
         <v>1</v>
@@ -3560,28 +3563,28 @@
     </row>
     <row r="77" customHeight="1" spans="3:12">
       <c r="C77" s="1">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F77" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G77" s="1">
-        <v>3501</v>
+        <v>3001</v>
       </c>
       <c r="H77" s="1">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="I77" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J77" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K77" s="2">
         <v>1</v>
@@ -3589,57 +3592,57 @@
     </row>
     <row r="78" customHeight="1" spans="3:12">
       <c r="C78" s="1">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F78" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G78" s="1">
-        <v>4001</v>
+        <v>3501</v>
       </c>
       <c r="H78" s="1">
         <v>5000</v>
       </c>
       <c r="I78" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J78" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K78" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:12">
       <c r="C79" s="1">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F79" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G79" s="1">
         <v>4001</v>
       </c>
       <c r="H79" s="1">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="I79" s="1">
         <v>3</v>
       </c>
       <c r="J79" s="1">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K79" s="2">
         <v>2</v>
@@ -3647,16 +3650,16 @@
     </row>
     <row r="80" customHeight="1" spans="3:12">
       <c r="C80" s="1">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F80" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G80" s="1">
         <v>4001</v>
@@ -3668,56 +3671,53 @@
         <v>3</v>
       </c>
       <c r="J80" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K80" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="83" customHeight="1" spans="3:12">
-      <c r="C83" s="1">
-        <v>10001</v>
-      </c>
-      <c r="D83" s="6">
-        <v>180001</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F83" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G83" s="1">
-        <v>100</v>
-      </c>
-      <c r="H83" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I83" s="1">
-        <v>100</v>
-      </c>
-      <c r="J83" s="1">
-        <v>1</v>
-      </c>
-      <c r="K83" s="2">
-        <v>1</v>
-      </c>
-      <c r="L83" s="1" t="s">
-        <v>97</v>
+    <row r="81" customHeight="1" spans="3:12">
+      <c r="C81" s="1">
+        <v>907</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F81" s="1">
+        <v>3</v>
+      </c>
+      <c r="G81" s="1">
+        <v>4001</v>
+      </c>
+      <c r="H81" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I81" s="1">
+        <v>3</v>
+      </c>
+      <c r="J81" s="1">
+        <v>2</v>
+      </c>
+      <c r="K81" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:12">
       <c r="C84" s="1">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="D84" s="6">
-        <v>180002</v>
+        <v>180001</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F84" s="1">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G84" s="1">
         <v>100</v>
@@ -3740,16 +3740,16 @@
     </row>
     <row r="85" customHeight="1" spans="3:12">
       <c r="C85" s="1">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="D85" s="6">
-        <v>180003</v>
+        <v>180002</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F85" s="1">
-        <v>150000</v>
+        <v>4000</v>
       </c>
       <c r="G85" s="1">
         <v>100</v>
@@ -3761,7 +3761,7 @@
         <v>100</v>
       </c>
       <c r="J85" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K85" s="2">
         <v>1</v>
@@ -3772,16 +3772,16 @@
     </row>
     <row r="86" customHeight="1" spans="3:12">
       <c r="C86" s="1">
-        <v>10004</v>
+        <v>10003</v>
       </c>
       <c r="D86" s="6">
-        <v>180004</v>
+        <v>180003</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F86" s="1">
-        <v>8000</v>
+        <v>150000</v>
       </c>
       <c r="G86" s="1">
         <v>100</v>
@@ -3793,7 +3793,7 @@
         <v>100</v>
       </c>
       <c r="J86" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K86" s="2">
         <v>1</v>
@@ -3804,16 +3804,16 @@
     </row>
     <row r="87" customHeight="1" spans="3:12">
       <c r="C87" s="1">
-        <v>10005</v>
+        <v>10004</v>
       </c>
       <c r="D87" s="6">
-        <v>180005</v>
+        <v>180004</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F87" s="1">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="G87" s="1">
         <v>100</v>
@@ -3836,16 +3836,16 @@
     </row>
     <row r="88" customHeight="1" spans="3:12">
       <c r="C88" s="1">
-        <v>10006</v>
+        <v>10005</v>
       </c>
       <c r="D88" s="6">
-        <v>180006</v>
+        <v>180005</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F88" s="1">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="G88" s="1">
         <v>100</v>
@@ -3857,7 +3857,7 @@
         <v>100</v>
       </c>
       <c r="J88" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K88" s="2">
         <v>1</v>
@@ -3868,16 +3868,16 @@
     </row>
     <row r="89" customHeight="1" spans="3:12">
       <c r="C89" s="1">
-        <v>10007</v>
+        <v>10006</v>
       </c>
       <c r="D89" s="6">
-        <v>180007</v>
+        <v>180006</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F89" s="1">
-        <v>2000</v>
+        <v>50000</v>
       </c>
       <c r="G89" s="1">
         <v>100</v>
@@ -3889,7 +3889,7 @@
         <v>100</v>
       </c>
       <c r="J89" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K89" s="2">
         <v>1</v>
@@ -3900,16 +3900,16 @@
     </row>
     <row r="90" customHeight="1" spans="3:12">
       <c r="C90" s="1">
-        <v>10008</v>
+        <v>10007</v>
       </c>
       <c r="D90" s="6">
-        <v>180008</v>
+        <v>180007</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F90" s="1">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="G90" s="1">
         <v>100</v>
@@ -3921,7 +3921,7 @@
         <v>100</v>
       </c>
       <c r="J90" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K90" s="2">
         <v>1</v>
@@ -3932,16 +3932,16 @@
     </row>
     <row r="91" customHeight="1" spans="3:12">
       <c r="C91" s="1">
-        <v>10009</v>
+        <v>10008</v>
       </c>
       <c r="D91" s="6">
-        <v>180009</v>
+        <v>180008</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F91" s="1">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="G91" s="1">
         <v>100</v>
@@ -3953,7 +3953,7 @@
         <v>100</v>
       </c>
       <c r="J91" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K91" s="2">
         <v>1</v>
@@ -3964,16 +3964,16 @@
     </row>
     <row r="92" customHeight="1" spans="3:12">
       <c r="C92" s="1">
-        <v>10010</v>
+        <v>10009</v>
       </c>
       <c r="D92" s="6">
-        <v>180010</v>
+        <v>180009</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F92" s="1">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="G92" s="1">
         <v>100</v>
@@ -3996,16 +3996,16 @@
     </row>
     <row r="93" customHeight="1" spans="3:12">
       <c r="C93" s="1">
-        <v>10011</v>
+        <v>10010</v>
       </c>
       <c r="D93" s="6">
-        <v>180011</v>
+        <v>180010</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F93" s="1">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="G93" s="1">
         <v>100</v>
@@ -4017,7 +4017,7 @@
         <v>100</v>
       </c>
       <c r="J93" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K93" s="2">
         <v>1</v>
@@ -4028,13 +4028,13 @@
     </row>
     <row r="94" customHeight="1" spans="3:12">
       <c r="C94" s="1">
-        <v>10012</v>
+        <v>10011</v>
       </c>
       <c r="D94" s="6">
-        <v>180012</v>
+        <v>180011</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F94" s="1">
         <v>100000</v>
@@ -4060,16 +4060,16 @@
     </row>
     <row r="95" customHeight="1" spans="3:12">
       <c r="C95" s="1">
-        <v>10013</v>
+        <v>10012</v>
       </c>
       <c r="D95" s="6">
-        <v>180013</v>
+        <v>180012</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F95" s="1">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="G95" s="1">
         <v>100</v>
@@ -4092,16 +4092,16 @@
     </row>
     <row r="96" customHeight="1" spans="3:12">
       <c r="C96" s="1">
-        <v>10014</v>
+        <v>10013</v>
       </c>
       <c r="D96" s="6">
-        <v>180014</v>
+        <v>180013</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F96" s="1">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G96" s="1">
         <v>100</v>
@@ -4124,13 +4124,13 @@
     </row>
     <row r="97" customHeight="1" spans="1:12">
       <c r="C97" s="1">
-        <v>10015</v>
+        <v>10014</v>
       </c>
       <c r="D97" s="6">
-        <v>180015</v>
+        <v>180014</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F97" s="1">
         <v>100000</v>
@@ -4156,16 +4156,16 @@
     </row>
     <row r="98" customHeight="1" spans="1:12">
       <c r="C98" s="1">
-        <v>10016</v>
+        <v>10015</v>
       </c>
       <c r="D98" s="6">
-        <v>180020</v>
+        <v>180015</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F98" s="1">
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="G98" s="1">
         <v>100</v>
@@ -4177,7 +4177,7 @@
         <v>100</v>
       </c>
       <c r="J98" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K98" s="2">
         <v>1</v>
@@ -4188,13 +4188,13 @@
     </row>
     <row r="99" customHeight="1" spans="1:12">
       <c r="C99" s="1">
-        <v>10017</v>
+        <v>10016</v>
       </c>
       <c r="D99" s="6">
-        <v>180021</v>
+        <v>180020</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F99" s="1">
         <v>30000</v>
@@ -4220,16 +4220,16 @@
     </row>
     <row r="100" customHeight="1" spans="1:12">
       <c r="C100" s="1">
-        <v>10018</v>
+        <v>10017</v>
       </c>
       <c r="D100" s="6">
-        <v>180022</v>
+        <v>180021</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F100" s="1">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="G100" s="1">
         <v>100</v>
@@ -4241,7 +4241,7 @@
         <v>100</v>
       </c>
       <c r="J100" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K100" s="2">
         <v>1</v>
@@ -4250,56 +4250,56 @@
         <v>97</v>
       </c>
     </row>
-    <row r="102" customHeight="1" spans="1:12">
-      <c r="C102" s="1">
-        <v>10030</v>
-      </c>
-      <c r="D102" s="1">
-        <v>180030</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F102" s="1">
-        <v>5</v>
-      </c>
-      <c r="G102" s="1">
-        <v>1100</v>
-      </c>
-      <c r="H102" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I102" s="1">
-        <v>100</v>
-      </c>
-      <c r="J102" s="1">
-        <v>1</v>
-      </c>
-      <c r="K102" s="2">
-        <v>1</v>
-      </c>
-      <c r="L102" s="1" t="s">
-        <v>116</v>
+    <row r="101" customHeight="1" spans="1:12">
+      <c r="C101" s="1">
+        <v>10018</v>
+      </c>
+      <c r="D101" s="6">
+        <v>180022</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F101" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G101" s="1">
+        <v>100</v>
+      </c>
+      <c r="H101" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I101" s="1">
+        <v>100</v>
+      </c>
+      <c r="J101" s="1">
+        <v>1</v>
+      </c>
+      <c r="K101" s="2">
+        <v>1</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="1:12">
       <c r="C103" s="1">
-        <v>10031</v>
-      </c>
-      <c r="D103" s="6">
-        <v>180032</v>
+        <v>10030</v>
+      </c>
+      <c r="D103" s="1">
+        <v>180030</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F103" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G103" s="1">
         <v>1100</v>
       </c>
       <c r="H103" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I103" s="1">
         <v>100</v>
@@ -4316,19 +4316,19 @@
     </row>
     <row r="104" customHeight="1" spans="1:12">
       <c r="C104" s="1">
-        <v>10032</v>
+        <v>10031</v>
       </c>
       <c r="D104" s="6">
-        <v>180033</v>
+        <v>180032</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F104" s="1">
         <v>1</v>
       </c>
       <c r="G104" s="1">
-        <v>1600</v>
+        <v>1100</v>
       </c>
       <c r="H104" s="1">
         <v>2000</v>
@@ -4348,22 +4348,22 @@
     </row>
     <row r="105" customHeight="1" spans="1:12">
       <c r="C105" s="1">
-        <v>10033</v>
+        <v>10032</v>
       </c>
       <c r="D105" s="6">
-        <v>180034</v>
+        <v>180033</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F105" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G105" s="1">
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="H105" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I105" s="1">
         <v>100</v>
@@ -4380,22 +4380,22 @@
     </row>
     <row r="106" customHeight="1" spans="1:12">
       <c r="C106" s="1">
-        <v>10034</v>
+        <v>10033</v>
       </c>
       <c r="D106" s="6">
-        <v>180035</v>
+        <v>180034</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F106" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G106" s="1">
-        <v>2000</v>
+        <v>1100</v>
       </c>
       <c r="H106" s="1">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I106" s="1">
         <v>100</v>
@@ -4412,13 +4412,13 @@
     </row>
     <row r="107" customHeight="1" spans="1:12">
       <c r="C107" s="1">
-        <v>10035</v>
+        <v>10034</v>
       </c>
       <c r="D107" s="6">
-        <v>180036</v>
+        <v>180035</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F107" s="1">
         <v>1</v>
@@ -4444,22 +4444,22 @@
     </row>
     <row r="108" customHeight="1" spans="1:12">
       <c r="C108" s="1">
-        <v>10036</v>
+        <v>10035</v>
       </c>
       <c r="D108" s="6">
-        <v>180037</v>
+        <v>180036</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F108" s="1">
         <v>1</v>
       </c>
       <c r="G108" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H108" s="1">
         <v>2500</v>
-      </c>
-      <c r="H108" s="1">
-        <v>3500</v>
       </c>
       <c r="I108" s="1">
         <v>100</v>
@@ -4476,19 +4476,19 @@
     </row>
     <row r="109" customHeight="1" spans="1:12">
       <c r="C109" s="1">
-        <v>10037</v>
+        <v>10036</v>
       </c>
       <c r="D109" s="6">
-        <v>180038</v>
+        <v>180037</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F109" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G109" s="1">
-        <v>1600</v>
+        <v>2500</v>
       </c>
       <c r="H109" s="1">
         <v>3500</v>
@@ -4508,19 +4508,19 @@
     </row>
     <row r="110" customHeight="1" spans="1:12">
       <c r="C110" s="1">
-        <v>10038</v>
+        <v>10037</v>
       </c>
       <c r="D110" s="6">
-        <v>180039</v>
+        <v>180038</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F110" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G110" s="1">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="H110" s="1">
         <v>3500</v>
@@ -4539,29 +4539,23 @@
       </c>
     </row>
     <row r="111" customHeight="1" spans="1:12">
-      <c r="A111" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C111" s="1">
-        <v>10039</v>
+        <v>10038</v>
       </c>
       <c r="D111" s="6">
-        <v>180040</v>
+        <v>180039</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F111" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G111" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="H111" s="1">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="I111" s="1">
         <v>100</v>
@@ -4577,23 +4571,29 @@
       </c>
     </row>
     <row r="112" customHeight="1" spans="1:12">
+      <c r="A112" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C112" s="1">
-        <v>10040</v>
+        <v>10039</v>
       </c>
       <c r="D112" s="6">
-        <v>180041</v>
+        <v>180040</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F112" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G112" s="1">
+        <v>3000</v>
+      </c>
+      <c r="H112" s="1">
         <v>4000</v>
-      </c>
-      <c r="H112" s="1">
-        <v>5000</v>
       </c>
       <c r="I112" s="1">
         <v>100</v>
@@ -4610,22 +4610,22 @@
     </row>
     <row r="113" customHeight="1" spans="3:12">
       <c r="C113" s="1">
-        <v>10041</v>
+        <v>10040</v>
       </c>
       <c r="D113" s="6">
-        <v>180042</v>
+        <v>180041</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F113" s="1">
         <v>3</v>
       </c>
       <c r="G113" s="1">
+        <v>4000</v>
+      </c>
+      <c r="H113" s="1">
         <v>5000</v>
-      </c>
-      <c r="H113" s="1">
-        <v>6000</v>
       </c>
       <c r="I113" s="1">
         <v>100</v>
@@ -4640,59 +4640,59 @@
         <v>116</v>
       </c>
     </row>
-    <row r="115" customHeight="1" spans="3:12">
-      <c r="C115" s="1">
-        <v>11001</v>
-      </c>
-      <c r="D115" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F115" s="1">
-        <v>5</v>
-      </c>
-      <c r="G115" s="1">
-        <v>150</v>
-      </c>
-      <c r="H115" s="1">
-        <v>1200</v>
-      </c>
-      <c r="I115" s="1">
-        <v>20</v>
-      </c>
-      <c r="J115" s="1">
-        <v>2</v>
-      </c>
-      <c r="K115" s="2">
-        <v>1</v>
-      </c>
-      <c r="L115" s="1" t="s">
-        <v>39</v>
+    <row r="114" customHeight="1" spans="3:12">
+      <c r="C114" s="1">
+        <v>10041</v>
+      </c>
+      <c r="D114" s="6">
+        <v>180042</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F114" s="1">
+        <v>3</v>
+      </c>
+      <c r="G114" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H114" s="1">
+        <v>6000</v>
+      </c>
+      <c r="I114" s="1">
+        <v>100</v>
+      </c>
+      <c r="J114" s="1">
+        <v>1</v>
+      </c>
+      <c r="K114" s="2">
+        <v>1</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="3:12">
       <c r="C116" s="1">
-        <v>11002</v>
+        <v>11001</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F116" s="1">
         <v>5</v>
       </c>
       <c r="G116" s="1">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H116" s="1">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="I116" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J116" s="1">
         <v>2</v>
@@ -4706,25 +4706,25 @@
     </row>
     <row r="117" customHeight="1" spans="3:12">
       <c r="C117" s="1">
-        <v>11003</v>
+        <v>11002</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F117" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G117" s="1">
-        <v>1050</v>
+        <v>200</v>
       </c>
       <c r="H117" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I117" s="1">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="J117" s="1">
         <v>2</v>
@@ -4738,7 +4738,7 @@
     </row>
     <row r="118" customHeight="1" spans="3:12">
       <c r="C118" s="1">
-        <v>11004</v>
+        <v>11003</v>
       </c>
       <c r="D118" s="9" t="s">
         <v>132</v>
@@ -4747,16 +4747,16 @@
         <v>133</v>
       </c>
       <c r="F118" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G118" s="1">
-        <v>4001</v>
+        <v>1050</v>
       </c>
       <c r="H118" s="1">
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="I118" s="1">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="J118" s="1">
         <v>2</v>
@@ -4770,54 +4770,54 @@
     </row>
     <row r="119" customHeight="1" spans="3:12">
       <c r="C119" s="1">
-        <v>11005</v>
+        <v>11004</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E119" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="F119" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G119" s="1">
-        <v>101</v>
+        <v>4001</v>
       </c>
       <c r="H119" s="1">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="I119" s="1">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="J119" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K119" s="2">
         <v>1</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>136</v>
+        <v>39</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="3:12">
       <c r="C120" s="1">
-        <v>11006</v>
+        <v>11005</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F120" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G120" s="1">
-        <v>501</v>
+        <v>101</v>
       </c>
       <c r="H120" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="I120" s="1">
         <v>10</v>
@@ -4829,31 +4829,31 @@
         <v>1</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="121" customHeight="1" spans="3:12">
       <c r="C121" s="1">
-        <v>11007</v>
+        <v>11006</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F121" s="1">
+        <v>15</v>
+      </c>
+      <c r="G121" s="1">
+        <v>501</v>
+      </c>
+      <c r="H121" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I121" s="1">
         <v>10</v>
       </c>
-      <c r="G121" s="1">
-        <v>1001</v>
-      </c>
-      <c r="H121" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I121" s="1">
-        <v>20</v>
-      </c>
       <c r="J121" s="1">
         <v>1</v>
       </c>
@@ -4861,27 +4861,27 @@
         <v>1</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="122" customHeight="1" spans="3:12">
       <c r="C122" s="1">
-        <v>11008</v>
+        <v>11007</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F122" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G122" s="1">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H122" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I122" s="1">
         <v>20</v>
@@ -4893,30 +4893,30 @@
         <v>1</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="123" customHeight="1" spans="3:12">
       <c r="C123" s="1">
-        <v>11009</v>
+        <v>11008</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F123" s="1">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G123" s="1">
-        <v>2001</v>
+        <v>1501</v>
       </c>
       <c r="H123" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I123" s="1">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="J123" s="1">
         <v>1</v>
@@ -4925,27 +4925,27 @@
         <v>1</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="124" customHeight="1" spans="3:12">
       <c r="C124" s="1">
-        <v>11010</v>
+        <v>11009</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F124" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G124" s="1">
-        <v>2501</v>
+        <v>2001</v>
       </c>
       <c r="H124" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I124" s="1">
         <v>52</v>
@@ -4957,30 +4957,30 @@
         <v>1</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="125" customHeight="1" spans="3:12">
       <c r="C125" s="1">
-        <v>11011</v>
+        <v>11010</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F125" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G125" s="1">
-        <v>3001</v>
+        <v>2501</v>
       </c>
       <c r="H125" s="1">
-        <v>3800</v>
+        <v>3000</v>
       </c>
       <c r="I125" s="1">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="J125" s="1">
         <v>1</v>
@@ -4989,32 +4989,32 @@
         <v>1</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="126" customHeight="1" spans="3:12">
       <c r="C126" s="1">
-        <v>11012</v>
+        <v>11011</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E126" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="F126" s="2">
-        <v>2</v>
-      </c>
-      <c r="G126" s="2">
-        <v>5001</v>
-      </c>
-      <c r="H126" s="2">
-        <v>5500</v>
-      </c>
-      <c r="I126" s="2">
-        <v>61</v>
-      </c>
-      <c r="J126" s="2">
+        <v>153</v>
+      </c>
+      <c r="F126" s="1">
+        <v>3</v>
+      </c>
+      <c r="G126" s="1">
+        <v>3001</v>
+      </c>
+      <c r="H126" s="1">
+        <v>3800</v>
+      </c>
+      <c r="I126" s="1">
+        <v>62</v>
+      </c>
+      <c r="J126" s="1">
         <v>1</v>
       </c>
       <c r="K126" s="2">
@@ -5026,34 +5026,92 @@
     </row>
     <row r="127" customHeight="1" spans="3:12">
       <c r="C127" s="1">
+        <v>11012</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F127" s="2">
+        <v>1</v>
+      </c>
+      <c r="G127" s="2">
+        <v>5001</v>
+      </c>
+      <c r="H127" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I127" s="2">
+        <v>61</v>
+      </c>
+      <c r="J127" s="2">
+        <v>1</v>
+      </c>
+      <c r="K127" s="2">
+        <v>1</v>
+      </c>
+      <c r="L127" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="3:12">
+      <c r="C128" s="1">
         <v>11013</v>
       </c>
-      <c r="D127" s="9" t="s">
+      <c r="D128" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="E127" s="1" t="s">
+      <c r="E128" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="F127" s="1">
-        <v>5</v>
-      </c>
-      <c r="G127" s="1">
+      <c r="F128" s="1">
+        <v>3</v>
+      </c>
+      <c r="G128" s="1">
         <v>5501</v>
       </c>
-      <c r="H127" s="1">
+      <c r="H128" s="1">
         <v>6000</v>
       </c>
-      <c r="I127" s="1">
-        <v>39</v>
-      </c>
-      <c r="J127" s="1">
-        <v>1</v>
-      </c>
-      <c r="K127" s="2">
-        <v>1</v>
-      </c>
-      <c r="L127" s="1" t="s">
-        <v>39</v>
+      <c r="I128" s="1">
+        <v>43</v>
+      </c>
+      <c r="J128" s="1">
+        <v>1</v>
+      </c>
+      <c r="K128" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="3:11">
+      <c r="C129" s="1">
+        <v>11014</v>
+      </c>
+      <c r="D129" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E129" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F129" s="1">
+        <v>3</v>
+      </c>
+      <c r="G129" s="1">
+        <v>5501</v>
+      </c>
+      <c r="H129" s="1">
+        <v>6500</v>
+      </c>
+      <c r="I129" s="1">
+        <v>67</v>
+      </c>
+      <c r="J129" s="1">
+        <v>1</v>
+      </c>
+      <c r="K129" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="161">
   <si>
     <t>#</t>
   </si>
@@ -538,6 +538,12 @@
   </si>
   <si>
     <t>六大极戒</t>
+  </si>
+  <si>
+    <t>220109</t>
+  </si>
+  <si>
+    <t>粉色宠物</t>
   </si>
 </sst>
 </file>
@@ -1534,7 +1540,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M129"/>
+  <dimension ref="A1:M130"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -5096,7 +5102,7 @@
         <v>153</v>
       </c>
       <c r="F129" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G129" s="1">
         <v>5501</v>
@@ -5111,6 +5117,35 @@
         <v>1</v>
       </c>
       <c r="K129" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="3:11">
+      <c r="C130" s="1">
+        <v>11015</v>
+      </c>
+      <c r="D130" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E130" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F130" s="1">
+        <v>1</v>
+      </c>
+      <c r="G130" s="1">
+        <v>6401</v>
+      </c>
+      <c r="H130" s="1">
+        <v>6900</v>
+      </c>
+      <c r="I130" s="1">
+        <v>99</v>
+      </c>
+      <c r="J130" s="1">
+        <v>1</v>
+      </c>
+      <c r="K130" s="2">
         <v>1</v>
       </c>
     </row>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="163">
   <si>
     <t>#</t>
   </si>
@@ -259,6 +259,12 @@
   </si>
   <si>
     <t>随机宝石</t>
+  </si>
+  <si>
+    <t>1009</t>
+  </si>
+  <si>
+    <t>宠物口粮</t>
   </si>
   <si>
     <t>220036</t>
@@ -1540,7 +1546,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M130"/>
+  <dimension ref="A1:M131"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2117,7 +2123,7 @@
         <v>1500</v>
       </c>
       <c r="H20" s="2">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="I20" s="1">
         <v>3</v>
@@ -2431,62 +2437,85 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="D31" s="4"/>
+    <row r="31" s="1" customFormat="1" ht="20" customHeight="1" spans="1:12">
+      <c r="C31" s="2">
+        <v>26</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31" s="1">
+        <v>100</v>
+      </c>
+      <c r="G31" s="2">
+        <v>6001</v>
+      </c>
+      <c r="H31" s="2">
+        <v>8000</v>
+      </c>
+      <c r="I31" s="1">
+        <v>1</v>
+      </c>
+      <c r="J31" s="1">
+        <v>200</v>
+      </c>
+      <c r="K31" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="D32" s="4"/>
+      <c r="C32" s="2">
+        <v>27</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F32" s="2">
+        <v>50</v>
+      </c>
+      <c r="G32" s="2">
+        <v>6001</v>
+      </c>
+      <c r="H32" s="2">
+        <v>8000</v>
+      </c>
+      <c r="I32" s="1">
+        <v>1</v>
+      </c>
+      <c r="J32" s="1">
+        <v>500</v>
+      </c>
+      <c r="K32" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C33" s="2">
-        <v>151</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F33" s="2">
-        <v>12</v>
-      </c>
-      <c r="G33" s="2">
-        <v>300</v>
-      </c>
-      <c r="H33" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I33" s="2">
-        <v>1</v>
-      </c>
-      <c r="J33" s="2">
-        <v>25</v>
-      </c>
-      <c r="K33" s="2">
-        <v>1</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>68</v>
-      </c>
+      <c r="D33" s="4"/>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C34" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D34" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="F34" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G34" s="2">
-        <v>1501</v>
+        <v>300</v>
       </c>
       <c r="H34" s="2">
-        <v>4000</v>
+        <v>1500</v>
       </c>
       <c r="I34" s="2">
         <v>1</v>
@@ -2498,94 +2527,94 @@
         <v>1</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C35" s="2">
+        <v>152</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F35" s="2">
+        <v>6</v>
+      </c>
+      <c r="G35" s="2">
+        <v>1501</v>
+      </c>
+      <c r="H35" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I35" s="2">
+        <v>1</v>
+      </c>
+      <c r="J35" s="2">
+        <v>25</v>
+      </c>
+      <c r="K35" s="2">
+        <v>1</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C36" s="2">
         <v>153</v>
       </c>
-      <c r="D35" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F35" s="2">
+      <c r="D36" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F36" s="2">
         <v>3</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G36" s="2">
         <v>4001</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H36" s="2">
         <v>10000</v>
       </c>
-      <c r="I35" s="2">
-        <v>1</v>
-      </c>
-      <c r="J35" s="2">
+      <c r="I36" s="2">
+        <v>1</v>
+      </c>
+      <c r="J36" s="2">
         <v>15</v>
       </c>
-      <c r="K35" s="2">
+      <c r="K36" s="2">
         <v>2</v>
       </c>
-      <c r="L35" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="D36" s="4"/>
-    </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C37" s="1">
-        <v>100</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F37" s="1">
-        <v>50</v>
-      </c>
-      <c r="G37" s="1">
-        <v>1</v>
-      </c>
-      <c r="H37" s="1">
-        <v>300</v>
-      </c>
-      <c r="I37" s="1">
-        <v>1</v>
-      </c>
-      <c r="J37" s="1">
-        <v>10000</v>
-      </c>
-      <c r="K37" s="2">
-        <v>1</v>
-      </c>
-      <c r="L37" s="1" t="s">
+      <c r="L36" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="D37" s="4"/>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C38" s="1">
+        <v>100</v>
+      </c>
+      <c r="D38" s="9" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
-      <c r="C38" s="1">
-        <v>101</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>72</v>
-      </c>
       <c r="E38" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F38" s="1">
         <v>50</v>
       </c>
       <c r="G38" s="1">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="H38" s="1">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I38" s="1">
         <v>1</v>
@@ -2594,30 +2623,30 @@
         <v>10000</v>
       </c>
       <c r="K38" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L38" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C39" s="1">
+        <v>101</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:12">
-      <c r="C39" s="1">
-        <v>102</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>72</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F39" s="1">
         <v>50</v>
       </c>
       <c r="G39" s="1">
-        <v>601</v>
+        <v>301</v>
       </c>
       <c r="H39" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="I39" s="1">
         <v>1</v>
@@ -2626,30 +2655,30 @@
         <v>10000</v>
       </c>
       <c r="K39" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:12">
       <c r="C40" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F40" s="1">
         <v>50</v>
       </c>
       <c r="G40" s="1">
-        <v>1001</v>
+        <v>601</v>
       </c>
       <c r="H40" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I40" s="1">
         <v>1</v>
@@ -2658,62 +2687,62 @@
         <v>10000</v>
       </c>
       <c r="K40" s="2">
+        <v>4</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:12">
+      <c r="C41" s="1">
+        <v>103</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F41" s="1">
+        <v>50</v>
+      </c>
+      <c r="G41" s="1">
+        <v>1001</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I41" s="1">
+        <v>1</v>
+      </c>
+      <c r="J41" s="1">
+        <v>10000</v>
+      </c>
+      <c r="K41" s="2">
         <v>10</v>
       </c>
-      <c r="L40" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C41" s="1">
-        <v>104</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F41" s="2">
-        <v>50</v>
-      </c>
-      <c r="G41" s="2">
-        <v>1501</v>
-      </c>
-      <c r="H41" s="2">
-        <v>3500</v>
-      </c>
-      <c r="I41" s="2">
-        <v>1</v>
-      </c>
-      <c r="J41" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K41" s="2">
-        <v>20</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>74</v>
+      <c r="L41" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C42" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F42" s="2">
         <v>50</v>
       </c>
       <c r="G42" s="2">
-        <v>3501</v>
+        <v>1501</v>
       </c>
       <c r="H42" s="2">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="I42" s="2">
         <v>1</v>
@@ -2722,65 +2751,65 @@
         <v>10000</v>
       </c>
       <c r="K42" s="2">
+        <v>20</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C43" s="1">
+        <v>105</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F43" s="2">
+        <v>50</v>
+      </c>
+      <c r="G43" s="2">
+        <v>3501</v>
+      </c>
+      <c r="H43" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I43" s="2">
+        <v>1</v>
+      </c>
+      <c r="J43" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K43" s="2">
         <v>40</v>
       </c>
-      <c r="L42" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="D43" s="4"/>
-    </row>
-    <row r="44" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
-      <c r="C44" s="2">
+      <c r="L43" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="D44" s="4"/>
+    </row>
+    <row r="45" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C45" s="2">
         <v>200</v>
       </c>
-      <c r="D44" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F44" s="2">
-        <v>50</v>
-      </c>
-      <c r="G44" s="2">
-        <v>1</v>
-      </c>
-      <c r="H44" s="2">
-        <v>300</v>
-      </c>
-      <c r="I44" s="2">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K44" s="2">
-        <v>1</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C45" s="2">
-        <v>201</v>
-      </c>
       <c r="D45" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F45" s="2">
         <v>50</v>
       </c>
       <c r="G45" s="2">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="H45" s="2">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I45" s="2">
         <v>1</v>
@@ -2789,30 +2818,30 @@
         <v>10000</v>
       </c>
       <c r="K45" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C46" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F46" s="2">
         <v>50</v>
       </c>
       <c r="G46" s="2">
-        <v>601</v>
+        <v>301</v>
       </c>
       <c r="H46" s="2">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="I46" s="2">
         <v>1</v>
@@ -2821,30 +2850,30 @@
         <v>10000</v>
       </c>
       <c r="K46" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C47" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F47" s="2">
         <v>50</v>
       </c>
       <c r="G47" s="2">
-        <v>1001</v>
+        <v>601</v>
       </c>
       <c r="H47" s="2">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I47" s="2">
         <v>1</v>
@@ -2853,30 +2882,30 @@
         <v>10000</v>
       </c>
       <c r="K47" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C48" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F48" s="2">
         <v>50</v>
       </c>
       <c r="G48" s="2">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H48" s="2">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="I48" s="2">
         <v>1</v>
@@ -2885,30 +2914,30 @@
         <v>10000</v>
       </c>
       <c r="K48" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
       <c r="C49" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F49" s="2">
         <v>50</v>
       </c>
       <c r="G49" s="2">
-        <v>3501</v>
+        <v>1501</v>
       </c>
       <c r="H49" s="2">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="I49" s="2">
         <v>1</v>
@@ -2917,65 +2946,65 @@
         <v>10000</v>
       </c>
       <c r="K49" s="2">
+        <v>20</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C50" s="2">
+        <v>205</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F50" s="2">
+        <v>50</v>
+      </c>
+      <c r="G50" s="2">
+        <v>3501</v>
+      </c>
+      <c r="H50" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I50" s="2">
+        <v>1</v>
+      </c>
+      <c r="J50" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K50" s="2">
         <v>40</v>
       </c>
-      <c r="L49" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="50" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
-      <c r="D50" s="4"/>
-    </row>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C51" s="2">
-        <v>300</v>
-      </c>
-      <c r="D51" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F51" s="2">
-        <v>10</v>
-      </c>
-      <c r="G51" s="2">
-        <v>1</v>
-      </c>
-      <c r="H51" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I51" s="2">
-        <v>1</v>
-      </c>
-      <c r="J51" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K51" s="2">
-        <v>1</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="L50" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="D51" s="4"/>
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C52" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F52" s="2">
         <v>10</v>
       </c>
       <c r="G52" s="2">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="H52" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I52" s="2">
         <v>1</v>
@@ -2984,7 +3013,7 @@
         <v>10000</v>
       </c>
       <c r="K52" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>21</v>
@@ -2992,22 +3021,22 @@
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C53" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F53" s="2">
         <v>10</v>
       </c>
       <c r="G53" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H53" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I53" s="2">
         <v>1</v>
@@ -3016,63 +3045,63 @@
         <v>10000</v>
       </c>
       <c r="K53" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="54" s="2" customFormat="1" customHeight="1"/>
-    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C55" s="2">
-        <v>400</v>
-      </c>
-      <c r="D55" s="11" t="s">
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C54" s="2">
+        <v>302</v>
+      </c>
+      <c r="D54" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E54" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F54" s="2">
         <v>10</v>
       </c>
-      <c r="G55" s="2">
-        <v>50</v>
-      </c>
-      <c r="H55" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I55" s="2">
-        <v>1</v>
-      </c>
-      <c r="J55" s="2">
+      <c r="G54" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H54" s="2">
         <v>10000</v>
       </c>
-      <c r="K55" s="2">
-        <v>1</v>
-      </c>
-      <c r="L55" s="2" t="s">
+      <c r="I54" s="2">
+        <v>1</v>
+      </c>
+      <c r="J54" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K54" s="2">
+        <v>3</v>
+      </c>
+      <c r="L54" s="2" t="s">
         <v>21</v>
       </c>
     </row>
+    <row r="55" s="2" customFormat="1" customHeight="1"/>
     <row r="56" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C56" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F56" s="2">
         <v>10</v>
       </c>
       <c r="G56" s="2">
-        <v>1001</v>
+        <v>50</v>
       </c>
       <c r="H56" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I56" s="2">
         <v>1</v>
@@ -3081,7 +3110,7 @@
         <v>10000</v>
       </c>
       <c r="K56" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>21</v>
@@ -3089,22 +3118,22 @@
     </row>
     <row r="57" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C57" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F57" s="2">
         <v>10</v>
       </c>
       <c r="G57" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H57" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I57" s="2">
         <v>1</v>
@@ -3113,63 +3142,63 @@
         <v>10000</v>
       </c>
       <c r="K57" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="58" s="2" customFormat="1" customHeight="1"/>
-    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C59" s="2">
-        <v>500</v>
-      </c>
-      <c r="D59" s="11" t="s">
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C58" s="2">
+        <v>402</v>
+      </c>
+      <c r="D58" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="E58" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F59" s="2">
-        <v>4</v>
-      </c>
-      <c r="G59" s="2">
-        <v>150</v>
-      </c>
-      <c r="H59" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I59" s="2">
-        <v>1</v>
-      </c>
-      <c r="J59" s="2">
-        <v>20</v>
-      </c>
-      <c r="K59" s="2">
-        <v>1</v>
-      </c>
-      <c r="L59" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
+      <c r="F58" s="2">
+        <v>10</v>
+      </c>
+      <c r="G58" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H58" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I58" s="2">
+        <v>1</v>
+      </c>
+      <c r="J58" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K58" s="2">
+        <v>3</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" s="2" customFormat="1" customHeight="1"/>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C60" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F60" s="2">
         <v>4</v>
       </c>
       <c r="G60" s="2">
-        <v>1001</v>
+        <v>150</v>
       </c>
       <c r="H60" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I60" s="2">
         <v>1</v>
@@ -3178,30 +3207,30 @@
         <v>20</v>
       </c>
       <c r="K60" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C61" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F61" s="2">
         <v>4</v>
       </c>
       <c r="G61" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H61" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I61" s="2">
         <v>1</v>
@@ -3210,63 +3239,63 @@
         <v>20</v>
       </c>
       <c r="K61" s="2">
+        <v>2</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C62" s="2">
+        <v>502</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F62" s="2">
+        <v>4</v>
+      </c>
+      <c r="G62" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H62" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I62" s="2">
+        <v>1</v>
+      </c>
+      <c r="J62" s="2">
+        <v>20</v>
+      </c>
+      <c r="K62" s="2">
         <v>3</v>
       </c>
-      <c r="L61" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="62" s="2" customFormat="1" customHeight="1"/>
-    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C63" s="2">
-        <v>600</v>
-      </c>
-      <c r="D63" s="2">
-        <v>3001</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F63" s="2">
-        <v>10</v>
-      </c>
-      <c r="G63" s="2">
-        <v>1</v>
-      </c>
-      <c r="H63" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I63" s="2">
-        <v>1</v>
-      </c>
-      <c r="J63" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K63" s="2">
-        <v>1</v>
-      </c>
-      <c r="L63" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
+      <c r="L62" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="63" s="2" customFormat="1" customHeight="1"/>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C64" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D64" s="2">
         <v>3001</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F64" s="2">
         <v>10</v>
       </c>
       <c r="G64" s="2">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="H64" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I64" s="2">
         <v>1</v>
@@ -3275,7 +3304,7 @@
         <v>10000</v>
       </c>
       <c r="K64" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>21</v>
@@ -3283,22 +3312,22 @@
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C65" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D65" s="2">
         <v>3001</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F65" s="2">
         <v>10</v>
       </c>
       <c r="G65" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H65" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I65" s="2">
         <v>1</v>
@@ -3307,63 +3336,63 @@
         <v>10000</v>
       </c>
       <c r="K65" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="66" s="2" customFormat="1" customHeight="1"/>
-    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C67" s="2">
-        <v>700</v>
-      </c>
-      <c r="D67" s="2">
-        <v>3002</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F67" s="2">
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C66" s="2">
+        <v>602</v>
+      </c>
+      <c r="D66" s="2">
+        <v>3001</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F66" s="2">
         <v>10</v>
       </c>
-      <c r="G67" s="2">
-        <v>200</v>
-      </c>
-      <c r="H67" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I67" s="2">
-        <v>1</v>
-      </c>
-      <c r="J67" s="2">
+      <c r="G66" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H66" s="2">
         <v>10000</v>
       </c>
-      <c r="K67" s="2">
-        <v>1</v>
-      </c>
-      <c r="L67" s="2" t="s">
+      <c r="I66" s="2">
+        <v>1</v>
+      </c>
+      <c r="J66" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K66" s="2">
+        <v>3</v>
+      </c>
+      <c r="L66" s="2" t="s">
         <v>21</v>
       </c>
     </row>
+    <row r="67" s="2" customFormat="1" customHeight="1"/>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C68" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D68" s="2">
         <v>3002</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F68" s="2">
         <v>10</v>
       </c>
       <c r="G68" s="2">
-        <v>1001</v>
+        <v>200</v>
       </c>
       <c r="H68" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I68" s="2">
         <v>1</v>
@@ -3372,7 +3401,7 @@
         <v>10000</v>
       </c>
       <c r="K68" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>21</v>
@@ -3380,22 +3409,22 @@
     </row>
     <row r="69" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C69" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D69" s="2">
         <v>3002</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F69" s="2">
         <v>10</v>
       </c>
       <c r="G69" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H69" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I69" s="2">
         <v>1</v>
@@ -3404,56 +3433,56 @@
         <v>10000</v>
       </c>
       <c r="K69" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="70" customHeight="1" spans="3:12">
-      <c r="K70" s="2"/>
-    </row>
-    <row r="71" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C71" s="2">
-        <v>800</v>
-      </c>
-      <c r="D71" s="2">
-        <v>3003</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F71" s="2">
-        <v>2</v>
-      </c>
-      <c r="G71" s="2">
-        <v>4001</v>
-      </c>
-      <c r="H71" s="2">
-        <v>5000</v>
-      </c>
-      <c r="I71" s="2">
-        <v>7</v>
-      </c>
-      <c r="J71" s="2">
-        <v>13</v>
-      </c>
-      <c r="K71" s="2">
-        <v>5</v>
-      </c>
-      <c r="L71" s="2" t="s">
+    <row r="70" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C70" s="2">
+        <v>702</v>
+      </c>
+      <c r="D70" s="2">
+        <v>3002</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F70" s="2">
+        <v>10</v>
+      </c>
+      <c r="G70" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H70" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I70" s="2">
+        <v>1</v>
+      </c>
+      <c r="J70" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K70" s="2">
+        <v>3</v>
+      </c>
+      <c r="L70" s="2" t="s">
         <v>21</v>
       </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:12">
+      <c r="K71" s="2"/>
     </row>
     <row r="72" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C72" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D72" s="2">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F72" s="2">
         <v>2</v>
@@ -3465,13 +3494,13 @@
         <v>5000</v>
       </c>
       <c r="I72" s="2">
+        <v>7</v>
+      </c>
+      <c r="J72" s="2">
         <v>13</v>
       </c>
-      <c r="J72" s="2">
+      <c r="K72" s="2">
         <v>5</v>
-      </c>
-      <c r="K72" s="2">
-        <v>1</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>21</v>
@@ -3479,68 +3508,71 @@
     </row>
     <row r="73" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C73" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D73" s="2">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F73" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G73" s="2">
-        <v>5500</v>
+        <v>4001</v>
       </c>
       <c r="H73" s="2">
-        <v>6500</v>
+        <v>5000</v>
       </c>
       <c r="I73" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J73" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K73" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="3:12">
-      <c r="C75" s="1">
-        <v>901</v>
-      </c>
-      <c r="D75" s="10" t="s">
+    <row r="74" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C74" s="2">
+        <v>802</v>
+      </c>
+      <c r="D74" s="2">
+        <v>3003</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F75" s="1">
+      <c r="F74" s="2">
+        <v>3</v>
+      </c>
+      <c r="G74" s="2">
+        <v>5500</v>
+      </c>
+      <c r="H74" s="2">
+        <v>6500</v>
+      </c>
+      <c r="I74" s="2">
+        <v>7</v>
+      </c>
+      <c r="J74" s="2">
         <v>20</v>
       </c>
-      <c r="G75" s="1">
-        <v>3001</v>
-      </c>
-      <c r="H75" s="1">
-        <v>4000</v>
-      </c>
-      <c r="I75" s="1">
-        <v>3</v>
-      </c>
-      <c r="J75" s="1">
-        <v>30</v>
-      </c>
-      <c r="K75" s="2">
-        <v>1</v>
+      <c r="K74" s="2">
+        <v>7</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:12">
       <c r="C76" s="1">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>90</v>
@@ -3549,7 +3581,7 @@
         <v>91</v>
       </c>
       <c r="F76" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G76" s="1">
         <v>3001</v>
@@ -3561,7 +3593,7 @@
         <v>3</v>
       </c>
       <c r="J76" s="1">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="K76" s="2">
         <v>1</v>
@@ -3569,7 +3601,7 @@
     </row>
     <row r="77" customHeight="1" spans="3:12">
       <c r="C77" s="1">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>92</v>
@@ -3578,7 +3610,7 @@
         <v>93</v>
       </c>
       <c r="F77" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G77" s="1">
         <v>3001</v>
@@ -3590,7 +3622,7 @@
         <v>3</v>
       </c>
       <c r="J77" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K77" s="2">
         <v>1</v>
@@ -3598,7 +3630,7 @@
     </row>
     <row r="78" customHeight="1" spans="3:12">
       <c r="C78" s="1">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>94</v>
@@ -3607,19 +3639,19 @@
         <v>95</v>
       </c>
       <c r="F78" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G78" s="1">
-        <v>3501</v>
+        <v>3001</v>
       </c>
       <c r="H78" s="1">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="I78" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J78" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K78" s="2">
         <v>1</v>
@@ -3627,36 +3659,36 @@
     </row>
     <row r="79" customHeight="1" spans="3:12">
       <c r="C79" s="1">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F79" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G79" s="1">
-        <v>4001</v>
+        <v>3501</v>
       </c>
       <c r="H79" s="1">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="I79" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J79" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K79" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:12">
       <c r="C80" s="1">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D80" s="10" t="s">
         <v>90</v>
@@ -3665,19 +3697,19 @@
         <v>91</v>
       </c>
       <c r="F80" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G80" s="1">
         <v>4001</v>
       </c>
       <c r="H80" s="1">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="I80" s="1">
         <v>3</v>
       </c>
       <c r="J80" s="1">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K80" s="2">
         <v>2</v>
@@ -3685,7 +3717,7 @@
     </row>
     <row r="81" customHeight="1" spans="3:12">
       <c r="C81" s="1">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>92</v>
@@ -3694,7 +3726,7 @@
         <v>93</v>
       </c>
       <c r="F81" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G81" s="1">
         <v>4001</v>
@@ -3706,56 +3738,53 @@
         <v>3</v>
       </c>
       <c r="J81" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K81" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="84" customHeight="1" spans="3:12">
-      <c r="C84" s="1">
-        <v>10001</v>
-      </c>
-      <c r="D84" s="6">
-        <v>180001</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F84" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G84" s="1">
-        <v>100</v>
-      </c>
-      <c r="H84" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I84" s="1">
-        <v>100</v>
-      </c>
-      <c r="J84" s="1">
-        <v>1</v>
-      </c>
-      <c r="K84" s="2">
-        <v>1</v>
-      </c>
-      <c r="L84" s="1" t="s">
-        <v>97</v>
+    <row r="82" customHeight="1" spans="3:12">
+      <c r="C82" s="1">
+        <v>907</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F82" s="1">
+        <v>3</v>
+      </c>
+      <c r="G82" s="1">
+        <v>4001</v>
+      </c>
+      <c r="H82" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I82" s="1">
+        <v>3</v>
+      </c>
+      <c r="J82" s="1">
+        <v>2</v>
+      </c>
+      <c r="K82" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:12">
       <c r="C85" s="1">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="D85" s="6">
-        <v>180002</v>
+        <v>180001</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>98</v>
       </c>
       <c r="F85" s="1">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G85" s="1">
         <v>100</v>
@@ -3773,21 +3802,21 @@
         <v>1</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:12">
       <c r="C86" s="1">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="D86" s="6">
-        <v>180003</v>
+        <v>180002</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F86" s="1">
-        <v>150000</v>
+        <v>4000</v>
       </c>
       <c r="G86" s="1">
         <v>100</v>
@@ -3799,27 +3828,27 @@
         <v>100</v>
       </c>
       <c r="J86" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K86" s="2">
         <v>1</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:12">
       <c r="C87" s="1">
-        <v>10004</v>
+        <v>10003</v>
       </c>
       <c r="D87" s="6">
-        <v>180004</v>
+        <v>180003</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F87" s="1">
-        <v>8000</v>
+        <v>150000</v>
       </c>
       <c r="G87" s="1">
         <v>100</v>
@@ -3831,27 +3860,27 @@
         <v>100</v>
       </c>
       <c r="J87" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K87" s="2">
         <v>1</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:12">
       <c r="C88" s="1">
-        <v>10005</v>
+        <v>10004</v>
       </c>
       <c r="D88" s="6">
-        <v>180005</v>
+        <v>180004</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F88" s="1">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="G88" s="1">
         <v>100</v>
@@ -3869,21 +3898,21 @@
         <v>1</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:12">
       <c r="C89" s="1">
-        <v>10006</v>
+        <v>10005</v>
       </c>
       <c r="D89" s="6">
-        <v>180006</v>
+        <v>180005</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F89" s="1">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="G89" s="1">
         <v>100</v>
@@ -3895,27 +3924,27 @@
         <v>100</v>
       </c>
       <c r="J89" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K89" s="2">
         <v>1</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:12">
       <c r="C90" s="1">
-        <v>10007</v>
+        <v>10006</v>
       </c>
       <c r="D90" s="6">
-        <v>180007</v>
+        <v>180006</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F90" s="1">
-        <v>2000</v>
+        <v>50000</v>
       </c>
       <c r="G90" s="1">
         <v>100</v>
@@ -3927,27 +3956,27 @@
         <v>100</v>
       </c>
       <c r="J90" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K90" s="2">
         <v>1</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:12">
       <c r="C91" s="1">
-        <v>10008</v>
+        <v>10007</v>
       </c>
       <c r="D91" s="6">
-        <v>180008</v>
+        <v>180007</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F91" s="1">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="G91" s="1">
         <v>100</v>
@@ -3959,27 +3988,27 @@
         <v>100</v>
       </c>
       <c r="J91" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K91" s="2">
         <v>1</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:12">
       <c r="C92" s="1">
-        <v>10009</v>
+        <v>10008</v>
       </c>
       <c r="D92" s="6">
-        <v>180009</v>
+        <v>180008</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F92" s="1">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="G92" s="1">
         <v>100</v>
@@ -3991,27 +4020,27 @@
         <v>100</v>
       </c>
       <c r="J92" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K92" s="2">
         <v>1</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:12">
       <c r="C93" s="1">
-        <v>10010</v>
+        <v>10009</v>
       </c>
       <c r="D93" s="6">
-        <v>180010</v>
+        <v>180009</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F93" s="1">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="G93" s="1">
         <v>100</v>
@@ -4029,21 +4058,21 @@
         <v>1</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:12">
       <c r="C94" s="1">
-        <v>10011</v>
+        <v>10010</v>
       </c>
       <c r="D94" s="6">
-        <v>180011</v>
+        <v>180010</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F94" s="1">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="G94" s="1">
         <v>100</v>
@@ -4055,24 +4084,24 @@
         <v>100</v>
       </c>
       <c r="J94" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K94" s="2">
         <v>1</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:12">
       <c r="C95" s="1">
-        <v>10012</v>
+        <v>10011</v>
       </c>
       <c r="D95" s="6">
-        <v>180012</v>
+        <v>180011</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F95" s="1">
         <v>100000</v>
@@ -4093,21 +4122,21 @@
         <v>1</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:12">
       <c r="C96" s="1">
-        <v>10013</v>
+        <v>10012</v>
       </c>
       <c r="D96" s="6">
-        <v>180013</v>
+        <v>180012</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F96" s="1">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="G96" s="1">
         <v>100</v>
@@ -4125,21 +4154,21 @@
         <v>1</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="97" customHeight="1" spans="1:12">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="3:12">
       <c r="C97" s="1">
-        <v>10014</v>
+        <v>10013</v>
       </c>
       <c r="D97" s="6">
-        <v>180014</v>
+        <v>180013</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F97" s="1">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G97" s="1">
         <v>100</v>
@@ -4157,18 +4186,18 @@
         <v>1</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="98" customHeight="1" spans="1:12">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="3:12">
       <c r="C98" s="1">
-        <v>10015</v>
+        <v>10014</v>
       </c>
       <c r="D98" s="6">
-        <v>180015</v>
+        <v>180014</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F98" s="1">
         <v>100000</v>
@@ -4189,21 +4218,21 @@
         <v>1</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="99" customHeight="1" spans="1:12">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:12">
       <c r="C99" s="1">
-        <v>10016</v>
+        <v>10015</v>
       </c>
       <c r="D99" s="6">
-        <v>180020</v>
+        <v>180015</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F99" s="1">
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="G99" s="1">
         <v>100</v>
@@ -4215,24 +4244,24 @@
         <v>100</v>
       </c>
       <c r="J99" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K99" s="2">
         <v>1</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="100" customHeight="1" spans="1:12">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="3:12">
       <c r="C100" s="1">
-        <v>10017</v>
+        <v>10016</v>
       </c>
       <c r="D100" s="6">
-        <v>180021</v>
+        <v>180020</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F100" s="1">
         <v>30000</v>
@@ -4253,21 +4282,21 @@
         <v>1</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="101" customHeight="1" spans="1:12">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="3:12">
       <c r="C101" s="1">
-        <v>10018</v>
+        <v>10017</v>
       </c>
       <c r="D101" s="6">
-        <v>180022</v>
+        <v>180021</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F101" s="1">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="G101" s="1">
         <v>100</v>
@@ -4279,65 +4308,65 @@
         <v>100</v>
       </c>
       <c r="J101" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K101" s="2">
         <v>1</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="103" customHeight="1" spans="1:12">
-      <c r="C103" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="3:12">
+      <c r="C102" s="1">
+        <v>10018</v>
+      </c>
+      <c r="D102" s="6">
+        <v>180022</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F102" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G102" s="1">
+        <v>100</v>
+      </c>
+      <c r="H102" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I102" s="1">
+        <v>100</v>
+      </c>
+      <c r="J102" s="1">
+        <v>1</v>
+      </c>
+      <c r="K102" s="2">
+        <v>1</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="3:12">
+      <c r="C104" s="1">
         <v>10030</v>
       </c>
-      <c r="D103" s="1">
+      <c r="D104" s="1">
         <v>180030</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F103" s="1">
-        <v>5</v>
-      </c>
-      <c r="G103" s="1">
-        <v>1100</v>
-      </c>
-      <c r="H103" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I103" s="1">
-        <v>100</v>
-      </c>
-      <c r="J103" s="1">
-        <v>1</v>
-      </c>
-      <c r="K103" s="2">
-        <v>1</v>
-      </c>
-      <c r="L103" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="104" customHeight="1" spans="1:12">
-      <c r="C104" s="1">
-        <v>10031</v>
-      </c>
-      <c r="D104" s="6">
-        <v>180032</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>117</v>
       </c>
       <c r="F104" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G104" s="1">
         <v>1100</v>
       </c>
       <c r="H104" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I104" s="1">
         <v>100</v>
@@ -4349,24 +4378,24 @@
         <v>1</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="105" customHeight="1" spans="1:12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="3:12">
       <c r="C105" s="1">
-        <v>10032</v>
+        <v>10031</v>
       </c>
       <c r="D105" s="6">
-        <v>180033</v>
+        <v>180032</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F105" s="1">
         <v>1</v>
       </c>
       <c r="G105" s="1">
-        <v>1600</v>
+        <v>1100</v>
       </c>
       <c r="H105" s="1">
         <v>2000</v>
@@ -4381,82 +4410,82 @@
         <v>1</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="106" customHeight="1" spans="1:12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:12">
       <c r="C106" s="1">
+        <v>10032</v>
+      </c>
+      <c r="D106" s="6">
+        <v>180033</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F106" s="1">
+        <v>1</v>
+      </c>
+      <c r="G106" s="1">
+        <v>1600</v>
+      </c>
+      <c r="H106" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I106" s="1">
+        <v>100</v>
+      </c>
+      <c r="J106" s="1">
+        <v>1</v>
+      </c>
+      <c r="K106" s="2">
+        <v>1</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="3:12">
+      <c r="C107" s="1">
         <v>10033</v>
       </c>
-      <c r="D106" s="6">
+      <c r="D107" s="6">
         <v>180034</v>
       </c>
-      <c r="E106" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F106" s="1">
+      <c r="E107" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F107" s="1">
         <v>2</v>
       </c>
-      <c r="G106" s="1">
+      <c r="G107" s="1">
         <v>1100</v>
       </c>
-      <c r="H106" s="1">
+      <c r="H107" s="1">
         <v>3000</v>
       </c>
-      <c r="I106" s="1">
-        <v>100</v>
-      </c>
-      <c r="J106" s="1">
-        <v>1</v>
-      </c>
-      <c r="K106" s="2">
-        <v>1</v>
-      </c>
-      <c r="L106" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="107" customHeight="1" spans="1:12">
-      <c r="C107" s="1">
+      <c r="I107" s="1">
+        <v>100</v>
+      </c>
+      <c r="J107" s="1">
+        <v>1</v>
+      </c>
+      <c r="K107" s="2">
+        <v>1</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="3:12">
+      <c r="C108" s="1">
         <v>10034</v>
       </c>
-      <c r="D107" s="6">
+      <c r="D108" s="6">
         <v>180035</v>
       </c>
-      <c r="E107" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F107" s="1">
-        <v>1</v>
-      </c>
-      <c r="G107" s="1">
-        <v>2000</v>
-      </c>
-      <c r="H107" s="1">
-        <v>2500</v>
-      </c>
-      <c r="I107" s="1">
-        <v>100</v>
-      </c>
-      <c r="J107" s="1">
-        <v>1</v>
-      </c>
-      <c r="K107" s="2">
-        <v>1</v>
-      </c>
-      <c r="L107" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="108" customHeight="1" spans="1:12">
-      <c r="C108" s="1">
-        <v>10035</v>
-      </c>
-      <c r="D108" s="6">
-        <v>180036</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F108" s="1">
         <v>1</v>
@@ -4477,56 +4506,56 @@
         <v>1</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="109" customHeight="1" spans="1:12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="3:12">
       <c r="C109" s="1">
+        <v>10035</v>
+      </c>
+      <c r="D109" s="6">
+        <v>180036</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F109" s="1">
+        <v>1</v>
+      </c>
+      <c r="G109" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H109" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I109" s="1">
+        <v>100</v>
+      </c>
+      <c r="J109" s="1">
+        <v>1</v>
+      </c>
+      <c r="K109" s="2">
+        <v>1</v>
+      </c>
+      <c r="L109" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="3:12">
+      <c r="C110" s="1">
         <v>10036</v>
       </c>
-      <c r="D109" s="6">
+      <c r="D110" s="6">
         <v>180037</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F109" s="1">
-        <v>1</v>
-      </c>
-      <c r="G109" s="1">
+      <c r="E110" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F110" s="1">
+        <v>1</v>
+      </c>
+      <c r="G110" s="1">
         <v>2500</v>
-      </c>
-      <c r="H109" s="1">
-        <v>3500</v>
-      </c>
-      <c r="I109" s="1">
-        <v>100</v>
-      </c>
-      <c r="J109" s="1">
-        <v>1</v>
-      </c>
-      <c r="K109" s="2">
-        <v>1</v>
-      </c>
-      <c r="L109" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="110" customHeight="1" spans="1:12">
-      <c r="C110" s="1">
-        <v>10037</v>
-      </c>
-      <c r="D110" s="6">
-        <v>180038</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F110" s="1">
-        <v>4</v>
-      </c>
-      <c r="G110" s="1">
-        <v>1600</v>
       </c>
       <c r="H110" s="1">
         <v>3500</v>
@@ -4541,24 +4570,24 @@
         <v>1</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="111" customHeight="1" spans="1:12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="3:12">
       <c r="C111" s="1">
-        <v>10038</v>
+        <v>10037</v>
       </c>
       <c r="D111" s="6">
-        <v>180039</v>
+        <v>180038</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F111" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G111" s="1">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="H111" s="1">
         <v>3500</v>
@@ -4573,146 +4602,146 @@
         <v>1</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="112" customHeight="1" spans="1:12">
-      <c r="A112" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="3:12">
+      <c r="C112" s="1">
+        <v>10038</v>
+      </c>
+      <c r="D112" s="6">
+        <v>180039</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F112" s="1">
+        <v>3</v>
+      </c>
+      <c r="G112" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H112" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I112" s="1">
+        <v>100</v>
+      </c>
+      <c r="J112" s="1">
+        <v>1</v>
+      </c>
+      <c r="K112" s="2">
+        <v>1</v>
+      </c>
+      <c r="L112" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="1:12">
+      <c r="A113" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B113" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C112" s="1">
+      <c r="C113" s="1">
         <v>10039</v>
       </c>
-      <c r="D112" s="6">
+      <c r="D113" s="6">
         <v>180040</v>
       </c>
-      <c r="E112" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F112" s="1">
+      <c r="E113" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F113" s="1">
         <v>2</v>
       </c>
-      <c r="G112" s="1">
+      <c r="G113" s="1">
         <v>3000</v>
       </c>
-      <c r="H112" s="1">
+      <c r="H113" s="1">
         <v>4000</v>
       </c>
-      <c r="I112" s="1">
-        <v>100</v>
-      </c>
-      <c r="J112" s="1">
-        <v>1</v>
-      </c>
-      <c r="K112" s="2">
-        <v>1</v>
-      </c>
-      <c r="L112" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="113" customHeight="1" spans="3:12">
-      <c r="C113" s="1">
+      <c r="I113" s="1">
+        <v>100</v>
+      </c>
+      <c r="J113" s="1">
+        <v>1</v>
+      </c>
+      <c r="K113" s="2">
+        <v>1</v>
+      </c>
+      <c r="L113" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="1:12">
+      <c r="C114" s="1">
         <v>10040</v>
       </c>
-      <c r="D113" s="6">
+      <c r="D114" s="6">
         <v>180041</v>
       </c>
-      <c r="E113" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F113" s="1">
-        <v>3</v>
-      </c>
-      <c r="G113" s="1">
-        <v>4000</v>
-      </c>
-      <c r="H113" s="1">
-        <v>5000</v>
-      </c>
-      <c r="I113" s="1">
-        <v>100</v>
-      </c>
-      <c r="J113" s="1">
-        <v>1</v>
-      </c>
-      <c r="K113" s="2">
-        <v>1</v>
-      </c>
-      <c r="L113" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="114" customHeight="1" spans="3:12">
-      <c r="C114" s="1">
-        <v>10041</v>
-      </c>
-      <c r="D114" s="6">
-        <v>180042</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F114" s="1">
         <v>3</v>
       </c>
       <c r="G114" s="1">
+        <v>4000</v>
+      </c>
+      <c r="H114" s="1">
         <v>5000</v>
       </c>
-      <c r="H114" s="1">
+      <c r="I114" s="1">
+        <v>100</v>
+      </c>
+      <c r="J114" s="1">
+        <v>1</v>
+      </c>
+      <c r="K114" s="2">
+        <v>1</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="1:12">
+      <c r="C115" s="1">
+        <v>10041</v>
+      </c>
+      <c r="D115" s="6">
+        <v>180042</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F115" s="1">
+        <v>3</v>
+      </c>
+      <c r="G115" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H115" s="1">
         <v>6000</v>
       </c>
-      <c r="I114" s="1">
-        <v>100</v>
-      </c>
-      <c r="J114" s="1">
-        <v>1</v>
-      </c>
-      <c r="K114" s="2">
-        <v>1</v>
-      </c>
-      <c r="L114" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="116" customHeight="1" spans="3:12">
-      <c r="C116" s="1">
+      <c r="I115" s="1">
+        <v>100</v>
+      </c>
+      <c r="J115" s="1">
+        <v>1</v>
+      </c>
+      <c r="K115" s="2">
+        <v>1</v>
+      </c>
+      <c r="L115" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="1:12">
+      <c r="C117" s="1">
         <v>11001</v>
-      </c>
-      <c r="D116" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F116" s="1">
-        <v>5</v>
-      </c>
-      <c r="G116" s="1">
-        <v>150</v>
-      </c>
-      <c r="H116" s="1">
-        <v>1200</v>
-      </c>
-      <c r="I116" s="1">
-        <v>20</v>
-      </c>
-      <c r="J116" s="1">
-        <v>2</v>
-      </c>
-      <c r="K116" s="2">
-        <v>1</v>
-      </c>
-      <c r="L116" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="117" customHeight="1" spans="3:12">
-      <c r="C117" s="1">
-        <v>11002</v>
       </c>
       <c r="D117" s="9" t="s">
         <v>130</v>
@@ -4724,13 +4753,13 @@
         <v>5</v>
       </c>
       <c r="G117" s="1">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H117" s="1">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="I117" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J117" s="1">
         <v>2</v>
@@ -4742,9 +4771,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="118" customHeight="1" spans="3:12">
+    <row r="118" customHeight="1" spans="1:12">
       <c r="C118" s="1">
-        <v>11003</v>
+        <v>11002</v>
       </c>
       <c r="D118" s="9" t="s">
         <v>132</v>
@@ -4753,16 +4782,16 @@
         <v>133</v>
       </c>
       <c r="F118" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G118" s="1">
-        <v>1050</v>
+        <v>200</v>
       </c>
       <c r="H118" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I118" s="1">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="J118" s="1">
         <v>2</v>
@@ -4774,27 +4803,27 @@
         <v>39</v>
       </c>
     </row>
-    <row r="119" customHeight="1" spans="3:12">
+    <row r="119" customHeight="1" spans="1:12">
       <c r="C119" s="1">
-        <v>11004</v>
+        <v>11003</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F119" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G119" s="1">
-        <v>4001</v>
+        <v>1050</v>
       </c>
       <c r="H119" s="1">
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="I119" s="1">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="J119" s="1">
         <v>2</v>
@@ -4806,56 +4835,56 @@
         <v>39</v>
       </c>
     </row>
-    <row r="120" customHeight="1" spans="3:12">
+    <row r="120" customHeight="1" spans="1:12">
       <c r="C120" s="1">
-        <v>11005</v>
+        <v>11004</v>
       </c>
       <c r="D120" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="E120" s="7" t="s">
+      <c r="E120" s="1" t="s">
         <v>135</v>
       </c>
       <c r="F120" s="1">
+        <v>5</v>
+      </c>
+      <c r="G120" s="1">
+        <v>4001</v>
+      </c>
+      <c r="H120" s="1">
+        <v>6000</v>
+      </c>
+      <c r="I120" s="1">
+        <v>79</v>
+      </c>
+      <c r="J120" s="1">
+        <v>2</v>
+      </c>
+      <c r="K120" s="2">
+        <v>1</v>
+      </c>
+      <c r="L120" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="1:12">
+      <c r="C121" s="1">
+        <v>11005</v>
+      </c>
+      <c r="D121" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F121" s="1">
         <v>20</v>
       </c>
-      <c r="G120" s="1">
+      <c r="G121" s="1">
         <v>101</v>
       </c>
-      <c r="H120" s="1">
+      <c r="H121" s="1">
         <v>500</v>
-      </c>
-      <c r="I120" s="1">
-        <v>10</v>
-      </c>
-      <c r="J120" s="1">
-        <v>1</v>
-      </c>
-      <c r="K120" s="2">
-        <v>1</v>
-      </c>
-      <c r="L120" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="121" customHeight="1" spans="3:12">
-      <c r="C121" s="1">
-        <v>11006</v>
-      </c>
-      <c r="D121" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="E121" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="F121" s="1">
-        <v>15</v>
-      </c>
-      <c r="G121" s="1">
-        <v>501</v>
-      </c>
-      <c r="H121" s="1">
-        <v>1000</v>
       </c>
       <c r="I121" s="1">
         <v>10</v>
@@ -4867,59 +4896,59 @@
         <v>1</v>
       </c>
       <c r="L121" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="1:12">
+      <c r="C122" s="1">
+        <v>11006</v>
+      </c>
+      <c r="D122" s="9" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="122" customHeight="1" spans="3:12">
-      <c r="C122" s="1">
+      <c r="E122" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F122" s="1">
+        <v>15</v>
+      </c>
+      <c r="G122" s="1">
+        <v>501</v>
+      </c>
+      <c r="H122" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I122" s="1">
+        <v>10</v>
+      </c>
+      <c r="J122" s="1">
+        <v>1</v>
+      </c>
+      <c r="K122" s="2">
+        <v>1</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" spans="1:12">
+      <c r="C123" s="1">
         <v>11007</v>
       </c>
-      <c r="D122" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="E122" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="F122" s="1">
+      <c r="D123" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F123" s="1">
         <v>10</v>
       </c>
-      <c r="G122" s="1">
+      <c r="G123" s="1">
         <v>1001</v>
       </c>
-      <c r="H122" s="1">
+      <c r="H123" s="1">
         <v>1500</v>
-      </c>
-      <c r="I122" s="1">
-        <v>20</v>
-      </c>
-      <c r="J122" s="1">
-        <v>1</v>
-      </c>
-      <c r="K122" s="2">
-        <v>1</v>
-      </c>
-      <c r="L122" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="123" customHeight="1" spans="3:12">
-      <c r="C123" s="1">
-        <v>11008</v>
-      </c>
-      <c r="D123" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="E123" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="F123" s="1">
-        <v>8</v>
-      </c>
-      <c r="G123" s="1">
-        <v>1501</v>
-      </c>
-      <c r="H123" s="1">
-        <v>2000</v>
       </c>
       <c r="I123" s="1">
         <v>20</v>
@@ -4931,59 +4960,59 @@
         <v>1</v>
       </c>
       <c r="L123" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="1:12">
+      <c r="C124" s="1">
+        <v>11008</v>
+      </c>
+      <c r="D124" s="9" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="124" customHeight="1" spans="3:12">
-      <c r="C124" s="1">
+      <c r="E124" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F124" s="1">
+        <v>8</v>
+      </c>
+      <c r="G124" s="1">
+        <v>1501</v>
+      </c>
+      <c r="H124" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I124" s="1">
+        <v>20</v>
+      </c>
+      <c r="J124" s="1">
+        <v>1</v>
+      </c>
+      <c r="K124" s="2">
+        <v>1</v>
+      </c>
+      <c r="L124" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="1:12">
+      <c r="C125" s="1">
         <v>11009</v>
       </c>
-      <c r="D124" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="E124" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="F124" s="1">
+      <c r="D125" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="F125" s="1">
         <v>15</v>
       </c>
-      <c r="G124" s="1">
+      <c r="G125" s="1">
         <v>2001</v>
       </c>
-      <c r="H124" s="1">
+      <c r="H125" s="1">
         <v>2500</v>
-      </c>
-      <c r="I124" s="1">
-        <v>52</v>
-      </c>
-      <c r="J124" s="1">
-        <v>1</v>
-      </c>
-      <c r="K124" s="2">
-        <v>1</v>
-      </c>
-      <c r="L124" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="125" customHeight="1" spans="3:12">
-      <c r="C125" s="1">
-        <v>11010</v>
-      </c>
-      <c r="D125" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E125" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="F125" s="1">
-        <v>7</v>
-      </c>
-      <c r="G125" s="1">
-        <v>2501</v>
-      </c>
-      <c r="H125" s="1">
-        <v>3000</v>
       </c>
       <c r="I125" s="1">
         <v>52</v>
@@ -4995,123 +5024,126 @@
         <v>1</v>
       </c>
       <c r="L125" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="1:12">
+      <c r="C126" s="1">
+        <v>11010</v>
+      </c>
+      <c r="D126" s="9" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="126" customHeight="1" spans="3:12">
-      <c r="C126" s="1">
+      <c r="E126" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F126" s="1">
+        <v>7</v>
+      </c>
+      <c r="G126" s="1">
+        <v>2501</v>
+      </c>
+      <c r="H126" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I126" s="1">
+        <v>52</v>
+      </c>
+      <c r="J126" s="1">
+        <v>1</v>
+      </c>
+      <c r="K126" s="2">
+        <v>1</v>
+      </c>
+      <c r="L126" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="1:12">
+      <c r="C127" s="1">
         <v>11011</v>
       </c>
-      <c r="D126" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="E126" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="F126" s="1">
+      <c r="D127" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="F127" s="1">
         <v>3</v>
       </c>
-      <c r="G126" s="1">
+      <c r="G127" s="1">
         <v>3001</v>
       </c>
-      <c r="H126" s="1">
+      <c r="H127" s="1">
         <v>3800</v>
       </c>
-      <c r="I126" s="1">
+      <c r="I127" s="1">
         <v>62</v>
       </c>
-      <c r="J126" s="1">
-        <v>1</v>
-      </c>
-      <c r="K126" s="2">
-        <v>1</v>
-      </c>
-      <c r="L126" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="127" customHeight="1" spans="3:12">
-      <c r="C127" s="1">
+      <c r="J127" s="1">
+        <v>1</v>
+      </c>
+      <c r="K127" s="2">
+        <v>1</v>
+      </c>
+      <c r="L127" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="1:12">
+      <c r="C128" s="1">
         <v>11012</v>
-      </c>
-      <c r="D127" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="E127" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="F127" s="2">
-        <v>1</v>
-      </c>
-      <c r="G127" s="2">
-        <v>5001</v>
-      </c>
-      <c r="H127" s="2">
-        <v>6000</v>
-      </c>
-      <c r="I127" s="2">
-        <v>61</v>
-      </c>
-      <c r="J127" s="2">
-        <v>1</v>
-      </c>
-      <c r="K127" s="2">
-        <v>1</v>
-      </c>
-      <c r="L127" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="128" customHeight="1" spans="3:12">
-      <c r="C128" s="1">
-        <v>11013</v>
       </c>
       <c r="D128" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="E128" s="1" t="s">
+      <c r="E128" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="F128" s="1">
-        <v>3</v>
-      </c>
-      <c r="G128" s="1">
-        <v>5501</v>
-      </c>
-      <c r="H128" s="1">
+      <c r="F128" s="2">
+        <v>1</v>
+      </c>
+      <c r="G128" s="2">
+        <v>5001</v>
+      </c>
+      <c r="H128" s="2">
         <v>6000</v>
       </c>
-      <c r="I128" s="1">
-        <v>43</v>
-      </c>
-      <c r="J128" s="1">
+      <c r="I128" s="2">
+        <v>61</v>
+      </c>
+      <c r="J128" s="2">
         <v>1</v>
       </c>
       <c r="K128" s="2">
         <v>1</v>
+      </c>
+      <c r="L128" s="1" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="129" customHeight="1" spans="3:11">
       <c r="C129" s="1">
-        <v>11014</v>
+        <v>11013</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="E129" s="7" t="s">
-        <v>153</v>
+        <v>159</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="F129" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G129" s="1">
         <v>5501</v>
       </c>
       <c r="H129" s="1">
-        <v>6500</v>
+        <v>6000</v>
       </c>
       <c r="I129" s="1">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="J129" s="1">
         <v>1</v>
@@ -5122,30 +5154,59 @@
     </row>
     <row r="130" customHeight="1" spans="3:11">
       <c r="C130" s="1">
+        <v>11014</v>
+      </c>
+      <c r="D130" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="E130" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="F130" s="1">
+        <v>2</v>
+      </c>
+      <c r="G130" s="1">
+        <v>5501</v>
+      </c>
+      <c r="H130" s="1">
+        <v>6500</v>
+      </c>
+      <c r="I130" s="1">
+        <v>67</v>
+      </c>
+      <c r="J130" s="1">
+        <v>1</v>
+      </c>
+      <c r="K130" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="3:11">
+      <c r="C131" s="1">
         <v>11015</v>
       </c>
-      <c r="D130" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E130" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="F130" s="1">
-        <v>1</v>
-      </c>
-      <c r="G130" s="1">
+      <c r="D131" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="E131" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F131" s="1">
+        <v>1</v>
+      </c>
+      <c r="G131" s="1">
         <v>6401</v>
       </c>
-      <c r="H130" s="1">
+      <c r="H131" s="1">
         <v>6900</v>
       </c>
-      <c r="I130" s="1">
-        <v>99</v>
-      </c>
-      <c r="J130" s="1">
-        <v>1</v>
-      </c>
-      <c r="K130" s="2">
+      <c r="I131" s="1">
+        <v>91</v>
+      </c>
+      <c r="J131" s="1">
+        <v>1</v>
+      </c>
+      <c r="K131" s="2">
         <v>1</v>
       </c>
     </row>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="166">
   <si>
     <t>#</t>
   </si>
@@ -267,6 +267,9 @@
     <t>宠物口粮</t>
   </si>
   <si>
+    <t>虚无精华</t>
+  </si>
+  <si>
     <t>220036</t>
   </si>
   <si>
@@ -330,7 +333,13 @@
     <t>三期时装</t>
   </si>
   <si>
-    <t>暗金时装</t>
+    <t>4金时装</t>
+  </si>
+  <si>
+    <t>5期时装</t>
+  </si>
+  <si>
+    <t>6期时装</t>
   </si>
   <si>
     <t>2007</t>
@@ -1546,7 +1555,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M131"/>
+  <dimension ref="A1:M141"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2013,7 +2022,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:12">
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C17" s="2">
         <v>12</v>
       </c>
@@ -2045,7 +2054,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="1:12">
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C18" s="2">
         <v>13</v>
       </c>
@@ -2077,7 +2086,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="20" customHeight="1" spans="1:12">
+    <row r="19" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
       <c r="C19" s="2">
         <v>14</v>
       </c>
@@ -2106,7 +2115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="20" customHeight="1" spans="1:12">
+    <row r="20" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
       <c r="C20" s="2">
         <v>15</v>
       </c>
@@ -2135,7 +2144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="1:12">
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C21" s="2">
         <v>16</v>
       </c>
@@ -2167,7 +2176,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="1:12">
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C22" s="2">
         <v>17</v>
       </c>
@@ -2199,7 +2208,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="1:12">
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C23" s="2">
         <v>18</v>
       </c>
@@ -2228,7 +2237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="1:12">
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C24" s="2">
         <v>19</v>
       </c>
@@ -2257,7 +2266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="1:12">
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C25" s="2">
         <v>20</v>
       </c>
@@ -2286,7 +2295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="1:12">
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C26" s="2">
         <v>21</v>
       </c>
@@ -2315,7 +2324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="1:12">
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C27" s="2">
         <v>22</v>
       </c>
@@ -2344,13 +2353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A28" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>0</v>
-      </c>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C28" s="2">
         <v>23</v>
       </c>
@@ -2364,22 +2367,22 @@
         <v>3</v>
       </c>
       <c r="G28" s="2">
-        <v>6001</v>
+        <v>6503</v>
       </c>
       <c r="H28" s="2">
-        <v>7000</v>
+        <v>7500</v>
       </c>
       <c r="I28" s="2">
         <v>11</v>
       </c>
       <c r="J28" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K28" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="1:12">
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C29" s="2">
         <v>24</v>
       </c>
@@ -2390,7 +2393,7 @@
         <v>63</v>
       </c>
       <c r="F29" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" s="2">
         <v>4803</v>
@@ -2408,7 +2411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="1:12">
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C30" s="2">
         <v>25</v>
       </c>
@@ -2437,7 +2440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="20" customHeight="1" spans="1:12">
+    <row r="31" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
       <c r="C31" s="2">
         <v>26</v>
       </c>
@@ -2466,7 +2469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="1:12">
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C32" s="2">
         <v>27</v>
       </c>
@@ -2495,59 +2498,62 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="D33" s="4"/>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C34" s="2">
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A33" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="2">
+        <v>28</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F33" s="2">
+        <v>2</v>
+      </c>
+      <c r="G33" s="2">
+        <v>7007</v>
+      </c>
+      <c r="H33" s="2">
+        <v>8000</v>
+      </c>
+      <c r="I33" s="2">
+        <v>13</v>
+      </c>
+      <c r="J33" s="2">
+        <v>5</v>
+      </c>
+      <c r="K33" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="D34" s="4"/>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C35" s="2">
         <v>151</v>
       </c>
-      <c r="D34" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E34" s="2" t="s">
+      <c r="D35" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="F34" s="2">
+      <c r="E35" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F35" s="2">
         <v>12</v>
       </c>
-      <c r="G34" s="2">
+      <c r="G35" s="2">
         <v>300</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H35" s="2">
         <v>1500</v>
-      </c>
-      <c r="I34" s="2">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2">
-        <v>25</v>
-      </c>
-      <c r="K34" s="2">
-        <v>1</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C35" s="2">
-        <v>152</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F35" s="2">
-        <v>6</v>
-      </c>
-      <c r="G35" s="2">
-        <v>1501</v>
-      </c>
-      <c r="H35" s="2">
-        <v>4000</v>
       </c>
       <c r="I35" s="2">
         <v>1</v>
@@ -2559,94 +2565,94 @@
         <v>1</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:12">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="C36" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>73</v>
       </c>
       <c r="F36" s="2">
+        <v>6</v>
+      </c>
+      <c r="G36" s="2">
+        <v>1501</v>
+      </c>
+      <c r="H36" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I36" s="2">
+        <v>1</v>
+      </c>
+      <c r="J36" s="2">
+        <v>25</v>
+      </c>
+      <c r="K36" s="2">
+        <v>1</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C37" s="2">
+        <v>153</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F37" s="2">
         <v>3</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G37" s="2">
         <v>4001</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H37" s="2">
         <v>10000</v>
       </c>
-      <c r="I36" s="2">
-        <v>1</v>
-      </c>
-      <c r="J36" s="2">
+      <c r="I37" s="2">
+        <v>1</v>
+      </c>
+      <c r="J37" s="2">
         <v>15</v>
       </c>
-      <c r="K36" s="2">
+      <c r="K37" s="2">
         <v>2</v>
       </c>
-      <c r="L36" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="D37" s="4"/>
-    </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C38" s="1">
+      <c r="L37" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="D38" s="4"/>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C39" s="1">
         <v>100</v>
       </c>
-      <c r="D38" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E38" s="1" t="s">
+      <c r="D39" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F38" s="1">
-        <v>50</v>
-      </c>
-      <c r="G38" s="1">
-        <v>1</v>
-      </c>
-      <c r="H38" s="1">
-        <v>300</v>
-      </c>
-      <c r="I38" s="1">
-        <v>1</v>
-      </c>
-      <c r="J38" s="1">
-        <v>10000</v>
-      </c>
-      <c r="K38" s="2">
-        <v>1</v>
-      </c>
-      <c r="L38" s="1" t="s">
+      <c r="E39" s="1" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="39" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
-      <c r="C39" s="1">
-        <v>101</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="F39" s="1">
         <v>50</v>
       </c>
       <c r="G39" s="1">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="H39" s="1">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I39" s="1">
         <v>1</v>
@@ -2655,30 +2661,30 @@
         <v>10000</v>
       </c>
       <c r="K39" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L39" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="20" customHeight="1" spans="1:12">
+      <c r="C40" s="1">
+        <v>101</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:12">
-      <c r="C40" s="1">
-        <v>102</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="F40" s="1">
         <v>50</v>
       </c>
       <c r="G40" s="1">
-        <v>601</v>
+        <v>301</v>
       </c>
       <c r="H40" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="I40" s="1">
         <v>1</v>
@@ -2687,30 +2693,30 @@
         <v>10000</v>
       </c>
       <c r="K40" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L40" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:12">
+      <c r="C41" s="1">
+        <v>102</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:12">
-      <c r="C41" s="1">
-        <v>103</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="F41" s="1">
         <v>50</v>
       </c>
       <c r="G41" s="1">
-        <v>1001</v>
+        <v>601</v>
       </c>
       <c r="H41" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I41" s="1">
         <v>1</v>
@@ -2719,62 +2725,62 @@
         <v>10000</v>
       </c>
       <c r="K41" s="2">
+        <v>4</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="1:12">
+      <c r="C42" s="1">
+        <v>103</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42" s="1">
+        <v>50</v>
+      </c>
+      <c r="G42" s="1">
+        <v>1001</v>
+      </c>
+      <c r="H42" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I42" s="1">
+        <v>1</v>
+      </c>
+      <c r="J42" s="1">
+        <v>10000</v>
+      </c>
+      <c r="K42" s="2">
         <v>10</v>
       </c>
-      <c r="L41" s="1" t="s">
+      <c r="L42" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C43" s="1">
+        <v>104</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C42" s="1">
-        <v>104</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F42" s="2">
-        <v>50</v>
-      </c>
-      <c r="G42" s="2">
-        <v>1501</v>
-      </c>
-      <c r="H42" s="2">
-        <v>3500</v>
-      </c>
-      <c r="I42" s="2">
-        <v>1</v>
-      </c>
-      <c r="J42" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K42" s="2">
-        <v>20</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C43" s="1">
-        <v>105</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="F43" s="2">
         <v>50</v>
       </c>
       <c r="G43" s="2">
-        <v>3501</v>
+        <v>1501</v>
       </c>
       <c r="H43" s="2">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="I43" s="2">
         <v>1</v>
@@ -2783,65 +2789,65 @@
         <v>10000</v>
       </c>
       <c r="K43" s="2">
+        <v>20</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C44" s="1">
+        <v>105</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F44" s="2">
+        <v>50</v>
+      </c>
+      <c r="G44" s="2">
+        <v>3501</v>
+      </c>
+      <c r="H44" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I44" s="2">
+        <v>1</v>
+      </c>
+      <c r="J44" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K44" s="2">
         <v>40</v>
       </c>
-      <c r="L43" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="D44" s="4"/>
-    </row>
-    <row r="45" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
-      <c r="C45" s="2">
+      <c r="L44" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="D45" s="4"/>
+    </row>
+    <row r="46" s="2" customFormat="1" ht="20" customHeight="1" spans="1:12">
+      <c r="C46" s="2">
         <v>200</v>
       </c>
-      <c r="D45" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="E45" s="2" t="s">
+      <c r="D46" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F45" s="2">
-        <v>50</v>
-      </c>
-      <c r="G45" s="2">
-        <v>1</v>
-      </c>
-      <c r="H45" s="2">
-        <v>300</v>
-      </c>
-      <c r="I45" s="2">
-        <v>1</v>
-      </c>
-      <c r="J45" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K45" s="2">
-        <v>1</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C46" s="2">
-        <v>201</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>77</v>
-      </c>
       <c r="E46" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F46" s="2">
         <v>50</v>
       </c>
       <c r="G46" s="2">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="H46" s="2">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I46" s="2">
         <v>1</v>
@@ -2850,30 +2856,30 @@
         <v>10000</v>
       </c>
       <c r="K46" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:12">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="C47" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F47" s="2">
         <v>50</v>
       </c>
       <c r="G47" s="2">
-        <v>601</v>
+        <v>301</v>
       </c>
       <c r="H47" s="2">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="I47" s="2">
         <v>1</v>
@@ -2882,30 +2888,30 @@
         <v>10000</v>
       </c>
       <c r="K47" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:12">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="C48" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F48" s="2">
         <v>50</v>
       </c>
       <c r="G48" s="2">
-        <v>1001</v>
+        <v>601</v>
       </c>
       <c r="H48" s="2">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I48" s="2">
         <v>1</v>
@@ -2914,30 +2920,30 @@
         <v>10000</v>
       </c>
       <c r="K48" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="49" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C49" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F49" s="2">
         <v>50</v>
       </c>
       <c r="G49" s="2">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H49" s="2">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="I49" s="2">
         <v>1</v>
@@ -2946,30 +2952,30 @@
         <v>10000</v>
       </c>
       <c r="K49" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
       <c r="C50" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F50" s="2">
         <v>50</v>
       </c>
       <c r="G50" s="2">
-        <v>3501</v>
+        <v>1501</v>
       </c>
       <c r="H50" s="2">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="I50" s="2">
         <v>1</v>
@@ -2978,65 +2984,65 @@
         <v>10000</v>
       </c>
       <c r="K50" s="2">
+        <v>20</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C51" s="2">
+        <v>205</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F51" s="2">
+        <v>50</v>
+      </c>
+      <c r="G51" s="2">
+        <v>3501</v>
+      </c>
+      <c r="H51" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I51" s="2">
+        <v>1</v>
+      </c>
+      <c r="J51" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K51" s="2">
         <v>40</v>
       </c>
-      <c r="L50" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="51" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
-      <c r="D51" s="4"/>
-    </row>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C52" s="2">
-        <v>300</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F52" s="2">
-        <v>10</v>
-      </c>
-      <c r="G52" s="2">
-        <v>1</v>
-      </c>
-      <c r="H52" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I52" s="2">
-        <v>1</v>
-      </c>
-      <c r="J52" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K52" s="2">
-        <v>1</v>
-      </c>
-      <c r="L52" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="L51" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="D52" s="4"/>
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C53" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F53" s="2">
         <v>10</v>
       </c>
       <c r="G53" s="2">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="H53" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I53" s="2">
         <v>1</v>
@@ -3045,7 +3051,7 @@
         <v>10000</v>
       </c>
       <c r="K53" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>21</v>
@@ -3053,22 +3059,22 @@
     </row>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C54" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F54" s="2">
         <v>10</v>
       </c>
       <c r="G54" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H54" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I54" s="2">
         <v>1</v>
@@ -3077,63 +3083,63 @@
         <v>10000</v>
       </c>
       <c r="K54" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="55" s="2" customFormat="1" customHeight="1"/>
-    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C56" s="2">
-        <v>400</v>
-      </c>
-      <c r="D56" s="11" t="s">
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C55" s="2">
+        <v>302</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F56" s="2">
+      <c r="F55" s="2">
         <v>10</v>
       </c>
-      <c r="G56" s="2">
-        <v>50</v>
-      </c>
-      <c r="H56" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I56" s="2">
-        <v>1</v>
-      </c>
-      <c r="J56" s="2">
+      <c r="G55" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H55" s="2">
         <v>10000</v>
       </c>
-      <c r="K56" s="2">
-        <v>1</v>
-      </c>
-      <c r="L56" s="2" t="s">
+      <c r="I55" s="2">
+        <v>1</v>
+      </c>
+      <c r="J55" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K55" s="2">
+        <v>3</v>
+      </c>
+      <c r="L55" s="2" t="s">
         <v>21</v>
       </c>
     </row>
+    <row r="56" s="2" customFormat="1" customHeight="1"/>
     <row r="57" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C57" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F57" s="2">
         <v>10</v>
       </c>
       <c r="G57" s="2">
-        <v>1001</v>
+        <v>50</v>
       </c>
       <c r="H57" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I57" s="2">
         <v>1</v>
@@ -3142,7 +3148,7 @@
         <v>10000</v>
       </c>
       <c r="K57" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>21</v>
@@ -3150,22 +3156,22 @@
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C58" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F58" s="2">
         <v>10</v>
       </c>
       <c r="G58" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H58" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I58" s="2">
         <v>1</v>
@@ -3174,63 +3180,63 @@
         <v>10000</v>
       </c>
       <c r="K58" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="59" s="2" customFormat="1" customHeight="1"/>
-    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C60" s="2">
-        <v>500</v>
-      </c>
-      <c r="D60" s="11" t="s">
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C59" s="2">
+        <v>402</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F60" s="2">
-        <v>4</v>
-      </c>
-      <c r="G60" s="2">
-        <v>150</v>
-      </c>
-      <c r="H60" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I60" s="2">
-        <v>1</v>
-      </c>
-      <c r="J60" s="2">
-        <v>20</v>
-      </c>
-      <c r="K60" s="2">
-        <v>1</v>
-      </c>
-      <c r="L60" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
+      <c r="F59" s="2">
+        <v>10</v>
+      </c>
+      <c r="G59" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H59" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I59" s="2">
+        <v>1</v>
+      </c>
+      <c r="J59" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K59" s="2">
+        <v>3</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" s="2" customFormat="1" customHeight="1"/>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C61" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F61" s="2">
         <v>4</v>
       </c>
       <c r="G61" s="2">
-        <v>1001</v>
+        <v>150</v>
       </c>
       <c r="H61" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I61" s="2">
         <v>1</v>
@@ -3239,30 +3245,30 @@
         <v>20</v>
       </c>
       <c r="K61" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C62" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F62" s="2">
         <v>4</v>
       </c>
       <c r="G62" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H62" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I62" s="2">
         <v>1</v>
@@ -3271,63 +3277,63 @@
         <v>20</v>
       </c>
       <c r="K62" s="2">
+        <v>2</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C63" s="2">
+        <v>502</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F63" s="2">
+        <v>4</v>
+      </c>
+      <c r="G63" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H63" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I63" s="2">
+        <v>1</v>
+      </c>
+      <c r="J63" s="2">
+        <v>20</v>
+      </c>
+      <c r="K63" s="2">
         <v>3</v>
       </c>
-      <c r="L62" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="63" s="2" customFormat="1" customHeight="1"/>
-    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C64" s="2">
-        <v>600</v>
-      </c>
-      <c r="D64" s="2">
-        <v>3001</v>
-      </c>
-      <c r="E64" s="2" t="s">
+      <c r="L63" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F64" s="2">
-        <v>10</v>
-      </c>
-      <c r="G64" s="2">
-        <v>1</v>
-      </c>
-      <c r="H64" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I64" s="2">
-        <v>1</v>
-      </c>
-      <c r="J64" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K64" s="2">
-        <v>1</v>
-      </c>
-      <c r="L64" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
+    </row>
+    <row r="64" s="2" customFormat="1" customHeight="1"/>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C65" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D65" s="2">
         <v>3001</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F65" s="2">
         <v>10</v>
       </c>
       <c r="G65" s="2">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="H65" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I65" s="2">
         <v>1</v>
@@ -3336,7 +3342,7 @@
         <v>10000</v>
       </c>
       <c r="K65" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>21</v>
@@ -3344,22 +3350,22 @@
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C66" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D66" s="2">
         <v>3001</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F66" s="2">
         <v>10</v>
       </c>
       <c r="G66" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H66" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I66" s="2">
         <v>1</v>
@@ -3368,63 +3374,63 @@
         <v>10000</v>
       </c>
       <c r="K66" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="67" s="2" customFormat="1" customHeight="1"/>
-    <row r="68" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C68" s="2">
-        <v>700</v>
-      </c>
-      <c r="D68" s="2">
-        <v>3002</v>
-      </c>
-      <c r="E68" s="2" t="s">
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C67" s="2">
+        <v>602</v>
+      </c>
+      <c r="D67" s="2">
+        <v>3001</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F67" s="2">
         <v>10</v>
       </c>
-      <c r="G68" s="2">
-        <v>200</v>
-      </c>
-      <c r="H68" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I68" s="2">
-        <v>1</v>
-      </c>
-      <c r="J68" s="2">
+      <c r="G67" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H67" s="2">
         <v>10000</v>
       </c>
-      <c r="K68" s="2">
-        <v>1</v>
-      </c>
-      <c r="L68" s="2" t="s">
+      <c r="I67" s="2">
+        <v>1</v>
+      </c>
+      <c r="J67" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K67" s="2">
+        <v>3</v>
+      </c>
+      <c r="L67" s="2" t="s">
         <v>21</v>
       </c>
     </row>
+    <row r="68" s="2" customFormat="1" customHeight="1"/>
     <row r="69" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C69" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D69" s="2">
         <v>3002</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F69" s="2">
         <v>10</v>
       </c>
       <c r="G69" s="2">
-        <v>1001</v>
+        <v>200</v>
       </c>
       <c r="H69" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I69" s="2">
         <v>1</v>
@@ -3433,7 +3439,7 @@
         <v>10000</v>
       </c>
       <c r="K69" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>21</v>
@@ -3441,22 +3447,22 @@
     </row>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C70" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D70" s="2">
         <v>3002</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F70" s="2">
         <v>10</v>
       </c>
       <c r="G70" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H70" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I70" s="2">
         <v>1</v>
@@ -3465,53 +3471,53 @@
         <v>10000</v>
       </c>
       <c r="K70" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="71" customHeight="1" spans="3:12">
-      <c r="K71" s="2"/>
-    </row>
-    <row r="72" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C72" s="2">
-        <v>800</v>
-      </c>
-      <c r="D72" s="2">
-        <v>3003</v>
-      </c>
-      <c r="E72" s="2" t="s">
+    <row r="71" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C71" s="2">
+        <v>702</v>
+      </c>
+      <c r="D71" s="2">
+        <v>3002</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F72" s="2">
-        <v>2</v>
-      </c>
-      <c r="G72" s="2">
-        <v>4001</v>
-      </c>
-      <c r="H72" s="2">
-        <v>5000</v>
-      </c>
-      <c r="I72" s="2">
-        <v>7</v>
-      </c>
-      <c r="J72" s="2">
-        <v>13</v>
-      </c>
-      <c r="K72" s="2">
-        <v>5</v>
-      </c>
-      <c r="L72" s="2" t="s">
+      <c r="F71" s="2">
+        <v>10</v>
+      </c>
+      <c r="G71" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H71" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I71" s="2">
+        <v>1</v>
+      </c>
+      <c r="J71" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K71" s="2">
+        <v>3</v>
+      </c>
+      <c r="L71" s="2" t="s">
         <v>21</v>
       </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:12">
+      <c r="K72" s="2"/>
     </row>
     <row r="73" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C73" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D73" s="2">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>89</v>
@@ -3526,13 +3532,13 @@
         <v>5000</v>
       </c>
       <c r="I73" s="2">
+        <v>7</v>
+      </c>
+      <c r="J73" s="2">
         <v>13</v>
       </c>
-      <c r="J73" s="2">
+      <c r="K73" s="2">
         <v>5</v>
-      </c>
-      <c r="K73" s="2">
-        <v>1</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>21</v>
@@ -3540,571 +3546,554 @@
     </row>
     <row r="74" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C74" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D74" s="2">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F74" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G74" s="2">
-        <v>5500</v>
+        <v>4001</v>
       </c>
       <c r="H74" s="2">
-        <v>6500</v>
+        <v>5000</v>
       </c>
       <c r="I74" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J74" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K74" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="3:12">
-      <c r="C76" s="1">
-        <v>901</v>
-      </c>
-      <c r="D76" s="10" t="s">
+    <row r="75" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C75" s="2">
+        <v>802</v>
+      </c>
+      <c r="D75" s="2">
+        <v>3003</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F75" s="2">
+        <v>3</v>
+      </c>
+      <c r="G75" s="2">
+        <v>5500</v>
+      </c>
+      <c r="H75" s="2">
+        <v>6500</v>
+      </c>
+      <c r="I75" s="2">
+        <v>7</v>
+      </c>
+      <c r="J75" s="2">
+        <v>20</v>
+      </c>
+      <c r="K75" s="2">
+        <v>7</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76" s="2" customFormat="1" customHeight="1"/>
+    <row r="77" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C77" s="2">
+        <v>803</v>
+      </c>
+      <c r="D77" s="2">
+        <v>3004</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="F77" s="2">
+        <v>2</v>
+      </c>
+      <c r="G77" s="2">
+        <v>5500</v>
+      </c>
+      <c r="H77" s="2">
+        <v>6500</v>
+      </c>
+      <c r="I77" s="2">
+        <v>13</v>
+      </c>
+      <c r="J77" s="2">
+        <v>20</v>
+      </c>
+      <c r="K77" s="2">
+        <v>2</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:12">
+      <c r="C78" s="2">
+        <v>804</v>
+      </c>
+      <c r="D78" s="2">
+        <v>3005</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F78" s="2">
+        <v>2</v>
+      </c>
+      <c r="G78" s="2">
+        <v>6000</v>
+      </c>
+      <c r="H78" s="2">
+        <v>7000</v>
+      </c>
+      <c r="I78" s="2">
+        <v>15</v>
+      </c>
+      <c r="J78" s="2">
         <v>20</v>
       </c>
-      <c r="G76" s="1">
-        <v>3001</v>
-      </c>
-      <c r="H76" s="1">
-        <v>4000</v>
-      </c>
-      <c r="I76" s="1">
-        <v>3</v>
-      </c>
-      <c r="J76" s="1">
-        <v>30</v>
-      </c>
-      <c r="K76" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" customHeight="1" spans="3:12">
-      <c r="C77" s="1">
-        <v>902</v>
-      </c>
-      <c r="D77" s="10" t="s">
+      <c r="K78" s="2">
+        <v>2</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:12">
+      <c r="C79" s="2">
+        <v>805</v>
+      </c>
+      <c r="D79" s="2">
+        <v>3006</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F77" s="1">
-        <v>10</v>
-      </c>
-      <c r="G77" s="1">
-        <v>3001</v>
-      </c>
-      <c r="H77" s="1">
-        <v>4000</v>
-      </c>
-      <c r="I77" s="1">
-        <v>3</v>
-      </c>
-      <c r="J77" s="1">
-        <v>5</v>
-      </c>
-      <c r="K77" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" customHeight="1" spans="3:12">
-      <c r="C78" s="1">
-        <v>903</v>
-      </c>
-      <c r="D78" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F78" s="1">
-        <v>5</v>
-      </c>
-      <c r="G78" s="1">
-        <v>3001</v>
-      </c>
-      <c r="H78" s="1">
-        <v>4000</v>
-      </c>
-      <c r="I78" s="1">
-        <v>3</v>
-      </c>
-      <c r="J78" s="1">
-        <v>3</v>
-      </c>
-      <c r="K78" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" customHeight="1" spans="3:12">
-      <c r="C79" s="1">
-        <v>904</v>
-      </c>
-      <c r="D79" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F79" s="1">
+      <c r="F79" s="2">
         <v>2</v>
       </c>
-      <c r="G79" s="1">
-        <v>3501</v>
-      </c>
-      <c r="H79" s="1">
-        <v>5000</v>
-      </c>
-      <c r="I79" s="1">
-        <v>4</v>
-      </c>
-      <c r="J79" s="1">
-        <v>6</v>
+      <c r="G79" s="2">
+        <v>6500</v>
+      </c>
+      <c r="H79" s="2">
+        <v>7500</v>
+      </c>
+      <c r="I79" s="2">
+        <v>17</v>
+      </c>
+      <c r="J79" s="2">
+        <v>20</v>
       </c>
       <c r="K79" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" customHeight="1" spans="3:12">
-      <c r="C80" s="1">
-        <v>905</v>
-      </c>
-      <c r="D80" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F80" s="1">
-        <v>10</v>
-      </c>
-      <c r="G80" s="1">
-        <v>4001</v>
-      </c>
-      <c r="H80" s="1">
-        <v>6000</v>
-      </c>
-      <c r="I80" s="1">
-        <v>3</v>
-      </c>
-      <c r="J80" s="1">
-        <v>20</v>
-      </c>
-      <c r="K80" s="2">
         <v>2</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:12">
       <c r="C81" s="1">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F81" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G81" s="1">
-        <v>4001</v>
+        <v>3001</v>
       </c>
       <c r="H81" s="1">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="I81" s="1">
         <v>3</v>
       </c>
       <c r="J81" s="1">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="K81" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:12">
       <c r="C82" s="1">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F82" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G82" s="1">
-        <v>4001</v>
+        <v>3001</v>
       </c>
       <c r="H82" s="1">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="I82" s="1">
         <v>3</v>
       </c>
       <c r="J82" s="1">
+        <v>5</v>
+      </c>
+      <c r="K82" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:12">
+      <c r="C83" s="1">
+        <v>903</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F83" s="1">
+        <v>5</v>
+      </c>
+      <c r="G83" s="1">
+        <v>3001</v>
+      </c>
+      <c r="H83" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I83" s="1">
+        <v>3</v>
+      </c>
+      <c r="J83" s="1">
+        <v>3</v>
+      </c>
+      <c r="K83" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:12">
+      <c r="C84" s="1">
+        <v>904</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F84" s="1">
         <v>2</v>
       </c>
-      <c r="K82" s="2">
-        <v>2</v>
+      <c r="G84" s="1">
+        <v>3501</v>
+      </c>
+      <c r="H84" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I84" s="1">
+        <v>4</v>
+      </c>
+      <c r="J84" s="1">
+        <v>6</v>
+      </c>
+      <c r="K84" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:12">
       <c r="C85" s="1">
-        <v>10001</v>
-      </c>
-      <c r="D85" s="6">
-        <v>180001</v>
+        <v>905</v>
+      </c>
+      <c r="D85" s="10" t="s">
+        <v>93</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F85" s="1">
-        <v>2000</v>
+        <v>10</v>
       </c>
       <c r="G85" s="1">
-        <v>100</v>
+        <v>4001</v>
       </c>
       <c r="H85" s="1">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="I85" s="1">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="J85" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K85" s="2">
-        <v>1</v>
-      </c>
-      <c r="L85" s="1" t="s">
-        <v>99</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:12">
       <c r="C86" s="1">
-        <v>10002</v>
-      </c>
-      <c r="D86" s="6">
-        <v>180002</v>
+        <v>906</v>
+      </c>
+      <c r="D86" s="10" t="s">
+        <v>95</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F86" s="1">
-        <v>4000</v>
+        <v>5</v>
       </c>
       <c r="G86" s="1">
-        <v>100</v>
+        <v>4001</v>
       </c>
       <c r="H86" s="1">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="I86" s="1">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="J86" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K86" s="2">
-        <v>1</v>
-      </c>
-      <c r="L86" s="1" t="s">
-        <v>99</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:12">
       <c r="C87" s="1">
-        <v>10003</v>
-      </c>
-      <c r="D87" s="6">
-        <v>180003</v>
+        <v>907</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>97</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F87" s="1">
-        <v>150000</v>
+        <v>3</v>
       </c>
       <c r="G87" s="1">
-        <v>100</v>
+        <v>4001</v>
       </c>
       <c r="H87" s="1">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="I87" s="1">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="J87" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K87" s="2">
-        <v>1</v>
-      </c>
-      <c r="L87" s="1" t="s">
-        <v>99</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:12">
       <c r="C88" s="1">
-        <v>10004</v>
-      </c>
-      <c r="D88" s="6">
-        <v>180004</v>
+        <v>908</v>
+      </c>
+      <c r="D88" s="10" t="s">
+        <v>93</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F88" s="1">
-        <v>8000</v>
+        <v>10</v>
       </c>
       <c r="G88" s="1">
-        <v>100</v>
+        <v>6001</v>
       </c>
       <c r="H88" s="1">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="I88" s="1">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="J88" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K88" s="2">
-        <v>1</v>
-      </c>
-      <c r="L88" s="1" t="s">
-        <v>99</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:12">
       <c r="C89" s="1">
-        <v>10005</v>
-      </c>
-      <c r="D89" s="6">
-        <v>180005</v>
+        <v>909</v>
+      </c>
+      <c r="D89" s="10" t="s">
+        <v>95</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F89" s="1">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="G89" s="1">
-        <v>100</v>
+        <v>6001</v>
       </c>
       <c r="H89" s="1">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="I89" s="1">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="J89" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K89" s="2">
-        <v>1</v>
-      </c>
-      <c r="L89" s="1" t="s">
-        <v>99</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:12">
       <c r="C90" s="1">
-        <v>10006</v>
-      </c>
-      <c r="D90" s="6">
-        <v>180006</v>
+        <v>910</v>
+      </c>
+      <c r="D90" s="10" t="s">
+        <v>97</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="F90" s="1">
-        <v>50000</v>
+        <v>3</v>
       </c>
       <c r="G90" s="1">
-        <v>100</v>
+        <v>6001</v>
       </c>
       <c r="H90" s="1">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="I90" s="1">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="J90" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K90" s="2">
-        <v>1</v>
-      </c>
-      <c r="L90" s="1" t="s">
-        <v>99</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:12">
       <c r="C91" s="1">
-        <v>10007</v>
-      </c>
-      <c r="D91" s="6">
-        <v>180007</v>
+        <v>911</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>93</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F91" s="1">
-        <v>2000</v>
+        <v>10</v>
       </c>
       <c r="G91" s="1">
-        <v>100</v>
+        <v>7001</v>
       </c>
       <c r="H91" s="1">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="I91" s="1">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="J91" s="1">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="K91" s="2">
-        <v>1</v>
-      </c>
-      <c r="L91" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:12">
       <c r="C92" s="1">
-        <v>10008</v>
-      </c>
-      <c r="D92" s="6">
-        <v>180008</v>
+        <v>912</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>95</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="F92" s="1">
-        <v>20000</v>
+        <v>5</v>
       </c>
       <c r="G92" s="1">
-        <v>100</v>
+        <v>7001</v>
       </c>
       <c r="H92" s="1">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="I92" s="1">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="J92" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K92" s="2">
-        <v>1</v>
-      </c>
-      <c r="L92" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:12">
       <c r="C93" s="1">
-        <v>10009</v>
-      </c>
-      <c r="D93" s="6">
-        <v>180009</v>
+        <v>913</v>
+      </c>
+      <c r="D93" s="10" t="s">
+        <v>97</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="F93" s="1">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="G93" s="1">
-        <v>100</v>
+        <v>7001</v>
       </c>
       <c r="H93" s="1">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="I93" s="1">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="J93" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K93" s="2">
-        <v>1</v>
-      </c>
-      <c r="L93" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="94" customHeight="1" spans="3:12">
-      <c r="C94" s="1">
-        <v>10010</v>
-      </c>
-      <c r="D94" s="6">
-        <v>180010</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F94" s="1">
-        <v>10000</v>
-      </c>
-      <c r="G94" s="1">
-        <v>100</v>
-      </c>
-      <c r="H94" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I94" s="1">
-        <v>100</v>
-      </c>
-      <c r="J94" s="1">
-        <v>1</v>
-      </c>
-      <c r="K94" s="2">
-        <v>1</v>
-      </c>
-      <c r="L94" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:12">
       <c r="C95" s="1">
-        <v>10011</v>
+        <v>10001</v>
       </c>
       <c r="D95" s="6">
-        <v>180011</v>
+        <v>180001</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F95" s="1">
-        <v>100000</v>
+        <v>2000</v>
       </c>
       <c r="G95" s="1">
         <v>100</v>
@@ -4116,27 +4105,27 @@
         <v>100</v>
       </c>
       <c r="J95" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K95" s="2">
         <v>1</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:12">
       <c r="C96" s="1">
-        <v>10012</v>
+        <v>10002</v>
       </c>
       <c r="D96" s="6">
-        <v>180012</v>
+        <v>180002</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F96" s="1">
-        <v>100000</v>
+        <v>4000</v>
       </c>
       <c r="G96" s="1">
         <v>100</v>
@@ -4148,27 +4137,27 @@
         <v>100</v>
       </c>
       <c r="J96" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K96" s="2">
         <v>1</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:12">
       <c r="C97" s="1">
-        <v>10013</v>
+        <v>10003</v>
       </c>
       <c r="D97" s="6">
-        <v>180013</v>
+        <v>180003</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F97" s="1">
-        <v>50000</v>
+        <v>150000</v>
       </c>
       <c r="G97" s="1">
         <v>100</v>
@@ -4186,21 +4175,21 @@
         <v>1</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:12">
       <c r="C98" s="1">
-        <v>10014</v>
+        <v>10004</v>
       </c>
       <c r="D98" s="6">
-        <v>180014</v>
+        <v>180004</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F98" s="1">
-        <v>100000</v>
+        <v>8000</v>
       </c>
       <c r="G98" s="1">
         <v>100</v>
@@ -4212,27 +4201,27 @@
         <v>100</v>
       </c>
       <c r="J98" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K98" s="2">
         <v>1</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:12">
       <c r="C99" s="1">
-        <v>10015</v>
+        <v>10005</v>
       </c>
       <c r="D99" s="6">
-        <v>180015</v>
+        <v>180005</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F99" s="1">
-        <v>100000</v>
+        <v>3000</v>
       </c>
       <c r="G99" s="1">
         <v>100</v>
@@ -4244,27 +4233,27 @@
         <v>100</v>
       </c>
       <c r="J99" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K99" s="2">
         <v>1</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:12">
       <c r="C100" s="1">
-        <v>10016</v>
+        <v>10006</v>
       </c>
       <c r="D100" s="6">
-        <v>180020</v>
+        <v>180006</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="F100" s="1">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="G100" s="1">
         <v>100</v>
@@ -4276,27 +4265,27 @@
         <v>100</v>
       </c>
       <c r="J100" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K100" s="2">
         <v>1</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:12">
       <c r="C101" s="1">
-        <v>10017</v>
+        <v>10007</v>
       </c>
       <c r="D101" s="6">
-        <v>180021</v>
+        <v>180007</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F101" s="1">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="G101" s="1">
         <v>100</v>
@@ -4308,27 +4297,27 @@
         <v>100</v>
       </c>
       <c r="J101" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K101" s="2">
         <v>1</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:12">
       <c r="C102" s="1">
-        <v>10018</v>
+        <v>10008</v>
       </c>
       <c r="D102" s="6">
-        <v>180022</v>
+        <v>180008</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F102" s="1">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="G102" s="1">
         <v>100</v>
@@ -4340,33 +4329,65 @@
         <v>100</v>
       </c>
       <c r="J102" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K102" s="2">
         <v>1</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="3:12">
+      <c r="C103" s="1">
+        <v>10009</v>
+      </c>
+      <c r="D103" s="6">
+        <v>180009</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F103" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G103" s="1">
+        <v>100</v>
+      </c>
+      <c r="H103" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I103" s="1">
+        <v>100</v>
+      </c>
+      <c r="J103" s="1">
+        <v>1</v>
+      </c>
+      <c r="K103" s="2">
+        <v>1</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:12">
       <c r="C104" s="1">
-        <v>10030</v>
-      </c>
-      <c r="D104" s="1">
-        <v>180030</v>
+        <v>10010</v>
+      </c>
+      <c r="D104" s="6">
+        <v>180010</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F104" s="1">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="G104" s="1">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="H104" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I104" s="1">
         <v>100</v>
@@ -4378,251 +4399,251 @@
         <v>1</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:12">
       <c r="C105" s="1">
-        <v>10031</v>
+        <v>10011</v>
       </c>
       <c r="D105" s="6">
-        <v>180032</v>
+        <v>180011</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="F105" s="1">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="G105" s="1">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="H105" s="1">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I105" s="1">
         <v>100</v>
       </c>
       <c r="J105" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K105" s="2">
         <v>1</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:12">
       <c r="C106" s="1">
-        <v>10032</v>
+        <v>10012</v>
       </c>
       <c r="D106" s="6">
-        <v>180033</v>
+        <v>180012</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F106" s="1">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="G106" s="1">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="H106" s="1">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I106" s="1">
         <v>100</v>
       </c>
       <c r="J106" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K106" s="2">
         <v>1</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:12">
       <c r="C107" s="1">
-        <v>10033</v>
+        <v>10013</v>
       </c>
       <c r="D107" s="6">
-        <v>180034</v>
+        <v>180013</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F107" s="1">
-        <v>2</v>
+        <v>50000</v>
       </c>
       <c r="G107" s="1">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="H107" s="1">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I107" s="1">
         <v>100</v>
       </c>
       <c r="J107" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K107" s="2">
         <v>1</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:12">
       <c r="C108" s="1">
-        <v>10034</v>
+        <v>10014</v>
       </c>
       <c r="D108" s="6">
-        <v>180035</v>
+        <v>180014</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F108" s="1">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="G108" s="1">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="H108" s="1">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="I108" s="1">
         <v>100</v>
       </c>
       <c r="J108" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K108" s="2">
         <v>1</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:12">
       <c r="C109" s="1">
-        <v>10035</v>
+        <v>10015</v>
       </c>
       <c r="D109" s="6">
-        <v>180036</v>
+        <v>180015</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F109" s="1">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="G109" s="1">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="H109" s="1">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="I109" s="1">
         <v>100</v>
       </c>
       <c r="J109" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K109" s="2">
         <v>1</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:12">
       <c r="C110" s="1">
-        <v>10036</v>
+        <v>10016</v>
       </c>
       <c r="D110" s="6">
-        <v>180037</v>
+        <v>180020</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F110" s="1">
-        <v>1</v>
+        <v>30000</v>
       </c>
       <c r="G110" s="1">
-        <v>2500</v>
+        <v>100</v>
       </c>
       <c r="H110" s="1">
-        <v>3500</v>
+        <v>1000</v>
       </c>
       <c r="I110" s="1">
         <v>100</v>
       </c>
       <c r="J110" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K110" s="2">
         <v>1</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:12">
       <c r="C111" s="1">
-        <v>10037</v>
+        <v>10017</v>
       </c>
       <c r="D111" s="6">
-        <v>180038</v>
+        <v>180021</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F111" s="1">
-        <v>4</v>
+        <v>30000</v>
       </c>
       <c r="G111" s="1">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="H111" s="1">
-        <v>3500</v>
+        <v>1000</v>
       </c>
       <c r="I111" s="1">
         <v>100</v>
       </c>
       <c r="J111" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K111" s="2">
         <v>1</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:12">
       <c r="C112" s="1">
-        <v>10038</v>
+        <v>10018</v>
       </c>
       <c r="D112" s="6">
-        <v>180039</v>
+        <v>180022</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F112" s="1">
-        <v>3</v>
+        <v>3000</v>
       </c>
       <c r="G112" s="1">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="H112" s="1">
-        <v>3500</v>
+        <v>1000</v>
       </c>
       <c r="I112" s="1">
         <v>100</v>
@@ -4634,65 +4655,27 @@
         <v>1</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="113" customHeight="1" spans="1:12">
-      <c r="A113" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C113" s="1">
-        <v>10039</v>
-      </c>
-      <c r="D113" s="6">
-        <v>180040</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F113" s="1">
-        <v>2</v>
-      </c>
-      <c r="G113" s="1">
-        <v>3000</v>
-      </c>
-      <c r="H113" s="1">
-        <v>4000</v>
-      </c>
-      <c r="I113" s="1">
-        <v>100</v>
-      </c>
-      <c r="J113" s="1">
-        <v>1</v>
-      </c>
-      <c r="K113" s="2">
-        <v>1</v>
-      </c>
-      <c r="L113" s="1" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="1:12">
       <c r="C114" s="1">
-        <v>10040</v>
-      </c>
-      <c r="D114" s="6">
-        <v>180041</v>
+        <v>10030</v>
+      </c>
+      <c r="D114" s="1">
+        <v>180030</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F114" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G114" s="1">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="H114" s="1">
-        <v>5000</v>
+        <v>1500</v>
       </c>
       <c r="I114" s="1">
         <v>100</v>
@@ -4704,27 +4687,27 @@
         <v>1</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="1:12">
       <c r="C115" s="1">
-        <v>10041</v>
+        <v>10031</v>
       </c>
       <c r="D115" s="6">
-        <v>180042</v>
+        <v>180032</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F115" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G115" s="1">
-        <v>5000</v>
+        <v>1100</v>
       </c>
       <c r="H115" s="1">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="I115" s="1">
         <v>100</v>
@@ -4736,158 +4719,190 @@
         <v>1</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="1:12">
+      <c r="C116" s="1">
+        <v>10032</v>
+      </c>
+      <c r="D116" s="6">
+        <v>180033</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F116" s="1">
+        <v>1</v>
+      </c>
+      <c r="G116" s="1">
+        <v>1600</v>
+      </c>
+      <c r="H116" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I116" s="1">
+        <v>100</v>
+      </c>
+      <c r="J116" s="1">
+        <v>1</v>
+      </c>
+      <c r="K116" s="2">
+        <v>1</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="1:12">
       <c r="C117" s="1">
-        <v>11001</v>
-      </c>
-      <c r="D117" s="9" t="s">
-        <v>130</v>
+        <v>10033</v>
+      </c>
+      <c r="D117" s="6">
+        <v>180034</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="F117" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G117" s="1">
-        <v>150</v>
+        <v>1100</v>
       </c>
       <c r="H117" s="1">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="I117" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="J117" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K117" s="2">
         <v>1</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="1:12">
       <c r="C118" s="1">
-        <v>11002</v>
-      </c>
-      <c r="D118" s="9" t="s">
-        <v>132</v>
+        <v>10034</v>
+      </c>
+      <c r="D118" s="6">
+        <v>180035</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F118" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G118" s="1">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="H118" s="1">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="I118" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J118" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K118" s="2">
         <v>1</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="1:12">
       <c r="C119" s="1">
-        <v>11003</v>
-      </c>
-      <c r="D119" s="9" t="s">
-        <v>134</v>
+        <v>10035</v>
+      </c>
+      <c r="D119" s="6">
+        <v>180036</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="F119" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G119" s="1">
-        <v>1050</v>
+        <v>2000</v>
       </c>
       <c r="H119" s="1">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="I119" s="1">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="J119" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K119" s="2">
         <v>1</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="1:12">
       <c r="C120" s="1">
-        <v>11004</v>
-      </c>
-      <c r="D120" s="9" t="s">
-        <v>134</v>
+        <v>10036</v>
+      </c>
+      <c r="D120" s="6">
+        <v>180037</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F120" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G120" s="1">
-        <v>4001</v>
+        <v>2500</v>
       </c>
       <c r="H120" s="1">
-        <v>6000</v>
+        <v>3500</v>
       </c>
       <c r="I120" s="1">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="J120" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K120" s="2">
         <v>1</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
     </row>
     <row r="121" customHeight="1" spans="1:12">
       <c r="C121" s="1">
-        <v>11005</v>
-      </c>
-      <c r="D121" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="E121" s="7" t="s">
-        <v>137</v>
+        <v>10037</v>
+      </c>
+      <c r="D121" s="6">
+        <v>180038</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="F121" s="1">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G121" s="1">
-        <v>101</v>
+        <v>1600</v>
       </c>
       <c r="H121" s="1">
-        <v>500</v>
+        <v>3500</v>
       </c>
       <c r="I121" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J121" s="1">
         <v>1</v>
@@ -4896,30 +4911,30 @@
         <v>1</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
     </row>
     <row r="122" customHeight="1" spans="1:12">
       <c r="C122" s="1">
-        <v>11006</v>
-      </c>
-      <c r="D122" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E122" s="7" t="s">
-        <v>140</v>
+        <v>10038</v>
+      </c>
+      <c r="D122" s="6">
+        <v>180039</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="F122" s="1">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G122" s="1">
-        <v>501</v>
+        <v>2000</v>
       </c>
       <c r="H122" s="1">
-        <v>1000</v>
+        <v>3500</v>
       </c>
       <c r="I122" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J122" s="1">
         <v>1</v>
@@ -4928,30 +4943,36 @@
         <v>1</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
     <row r="123" customHeight="1" spans="1:12">
+      <c r="A123" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C123" s="1">
-        <v>11007</v>
-      </c>
-      <c r="D123" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="E123" s="7" t="s">
-        <v>143</v>
+        <v>10039</v>
+      </c>
+      <c r="D123" s="6">
+        <v>180040</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="F123" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G123" s="1">
-        <v>1001</v>
+        <v>3000</v>
       </c>
       <c r="H123" s="1">
-        <v>1500</v>
+        <v>4000</v>
       </c>
       <c r="I123" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="J123" s="1">
         <v>1</v>
@@ -4960,30 +4981,30 @@
         <v>1</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
     </row>
     <row r="124" customHeight="1" spans="1:12">
       <c r="C124" s="1">
-        <v>11008</v>
-      </c>
-      <c r="D124" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="E124" s="7" t="s">
-        <v>146</v>
+        <v>10040</v>
+      </c>
+      <c r="D124" s="6">
+        <v>180041</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="F124" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G124" s="1">
-        <v>1501</v>
+        <v>4000</v>
       </c>
       <c r="H124" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="I124" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="J124" s="1">
         <v>1</v>
@@ -4992,30 +5013,30 @@
         <v>1</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
     </row>
     <row r="125" customHeight="1" spans="1:12">
       <c r="C125" s="1">
-        <v>11009</v>
-      </c>
-      <c r="D125" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="E125" s="7" t="s">
-        <v>149</v>
+        <v>10041</v>
+      </c>
+      <c r="D125" s="6">
+        <v>180042</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="F125" s="1">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G125" s="1">
-        <v>2001</v>
+        <v>5000</v>
       </c>
       <c r="H125" s="1">
-        <v>2500</v>
+        <v>6000</v>
       </c>
       <c r="I125" s="1">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="J125" s="1">
         <v>1</v>
@@ -5024,189 +5045,477 @@
         <v>1</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="126" customHeight="1" spans="1:12">
-      <c r="C126" s="1">
-        <v>11010</v>
-      </c>
-      <c r="D126" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E126" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="F126" s="1">
-        <v>7</v>
-      </c>
-      <c r="G126" s="1">
-        <v>2501</v>
-      </c>
-      <c r="H126" s="1">
-        <v>3000</v>
-      </c>
-      <c r="I126" s="1">
-        <v>52</v>
-      </c>
-      <c r="J126" s="1">
-        <v>1</v>
-      </c>
-      <c r="K126" s="2">
-        <v>1</v>
-      </c>
-      <c r="L126" s="1" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
     </row>
     <row r="127" customHeight="1" spans="1:12">
       <c r="C127" s="1">
-        <v>11011</v>
+        <v>11001</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="E127" s="7" t="s">
-        <v>155</v>
+        <v>133</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>134</v>
       </c>
       <c r="F127" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G127" s="1">
-        <v>3001</v>
+        <v>150</v>
       </c>
       <c r="H127" s="1">
-        <v>3800</v>
+        <v>1200</v>
       </c>
       <c r="I127" s="1">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="J127" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K127" s="2">
         <v>1</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>156</v>
+        <v>39</v>
       </c>
     </row>
     <row r="128" customHeight="1" spans="1:12">
       <c r="C128" s="1">
+        <v>11002</v>
+      </c>
+      <c r="D128" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F128" s="1">
+        <v>5</v>
+      </c>
+      <c r="G128" s="1">
+        <v>200</v>
+      </c>
+      <c r="H128" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I128" s="1">
+        <v>30</v>
+      </c>
+      <c r="J128" s="1">
+        <v>2</v>
+      </c>
+      <c r="K128" s="2">
+        <v>1</v>
+      </c>
+      <c r="L128" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="3:12">
+      <c r="C129" s="1">
+        <v>11003</v>
+      </c>
+      <c r="D129" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F129" s="1">
+        <v>15</v>
+      </c>
+      <c r="G129" s="1">
+        <v>1050</v>
+      </c>
+      <c r="H129" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I129" s="1">
+        <v>51</v>
+      </c>
+      <c r="J129" s="1">
+        <v>2</v>
+      </c>
+      <c r="K129" s="2">
+        <v>1</v>
+      </c>
+      <c r="L129" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="3:12">
+      <c r="C130" s="1">
+        <v>11004</v>
+      </c>
+      <c r="D130" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F130" s="1">
+        <v>5</v>
+      </c>
+      <c r="G130" s="1">
+        <v>4001</v>
+      </c>
+      <c r="H130" s="1">
+        <v>6000</v>
+      </c>
+      <c r="I130" s="1">
+        <v>79</v>
+      </c>
+      <c r="J130" s="1">
+        <v>2</v>
+      </c>
+      <c r="K130" s="2">
+        <v>1</v>
+      </c>
+      <c r="L130" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="3:12">
+      <c r="C131" s="1">
+        <v>11005</v>
+      </c>
+      <c r="D131" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="E131" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F131" s="1">
+        <v>20</v>
+      </c>
+      <c r="G131" s="1">
+        <v>101</v>
+      </c>
+      <c r="H131" s="1">
+        <v>500</v>
+      </c>
+      <c r="I131" s="1">
+        <v>10</v>
+      </c>
+      <c r="J131" s="1">
+        <v>1</v>
+      </c>
+      <c r="K131" s="2">
+        <v>1</v>
+      </c>
+      <c r="L131" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" spans="3:12">
+      <c r="C132" s="1">
+        <v>11006</v>
+      </c>
+      <c r="D132" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E132" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F132" s="1">
+        <v>15</v>
+      </c>
+      <c r="G132" s="1">
+        <v>501</v>
+      </c>
+      <c r="H132" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I132" s="1">
+        <v>10</v>
+      </c>
+      <c r="J132" s="1">
+        <v>1</v>
+      </c>
+      <c r="K132" s="2">
+        <v>1</v>
+      </c>
+      <c r="L132" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" spans="3:12">
+      <c r="C133" s="1">
+        <v>11007</v>
+      </c>
+      <c r="D133" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="E133" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F133" s="1">
+        <v>10</v>
+      </c>
+      <c r="G133" s="1">
+        <v>1001</v>
+      </c>
+      <c r="H133" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I133" s="1">
+        <v>20</v>
+      </c>
+      <c r="J133" s="1">
+        <v>1</v>
+      </c>
+      <c r="K133" s="2">
+        <v>1</v>
+      </c>
+      <c r="L133" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" spans="3:12">
+      <c r="C134" s="1">
+        <v>11008</v>
+      </c>
+      <c r="D134" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E134" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="F134" s="1">
+        <v>8</v>
+      </c>
+      <c r="G134" s="1">
+        <v>1501</v>
+      </c>
+      <c r="H134" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I134" s="1">
+        <v>20</v>
+      </c>
+      <c r="J134" s="1">
+        <v>1</v>
+      </c>
+      <c r="K134" s="2">
+        <v>1</v>
+      </c>
+      <c r="L134" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" spans="3:12">
+      <c r="C135" s="1">
+        <v>11009</v>
+      </c>
+      <c r="D135" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E135" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F135" s="1">
+        <v>15</v>
+      </c>
+      <c r="G135" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H135" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I135" s="1">
+        <v>52</v>
+      </c>
+      <c r="J135" s="1">
+        <v>1</v>
+      </c>
+      <c r="K135" s="2">
+        <v>1</v>
+      </c>
+      <c r="L135" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" spans="3:12">
+      <c r="C136" s="1">
+        <v>11010</v>
+      </c>
+      <c r="D136" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="E136" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="F136" s="1">
+        <v>7</v>
+      </c>
+      <c r="G136" s="1">
+        <v>2501</v>
+      </c>
+      <c r="H136" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I136" s="1">
+        <v>52</v>
+      </c>
+      <c r="J136" s="1">
+        <v>1</v>
+      </c>
+      <c r="K136" s="2">
+        <v>1</v>
+      </c>
+      <c r="L136" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="137" customHeight="1" spans="3:12">
+      <c r="C137" s="1">
+        <v>11011</v>
+      </c>
+      <c r="D137" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="E137" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F137" s="1">
+        <v>3</v>
+      </c>
+      <c r="G137" s="1">
+        <v>3001</v>
+      </c>
+      <c r="H137" s="1">
+        <v>3800</v>
+      </c>
+      <c r="I137" s="1">
+        <v>62</v>
+      </c>
+      <c r="J137" s="1">
+        <v>1</v>
+      </c>
+      <c r="K137" s="2">
+        <v>1</v>
+      </c>
+      <c r="L137" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="138" customHeight="1" spans="3:12">
+      <c r="C138" s="1">
         <v>11012</v>
       </c>
-      <c r="D128" s="9" t="s">
+      <c r="D138" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="F138" s="2">
+        <v>1</v>
+      </c>
+      <c r="G138" s="2">
+        <v>5001</v>
+      </c>
+      <c r="H138" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I138" s="2">
+        <v>61</v>
+      </c>
+      <c r="J138" s="2">
+        <v>1</v>
+      </c>
+      <c r="K138" s="2">
+        <v>1</v>
+      </c>
+      <c r="L138" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="139" customHeight="1" spans="3:12">
+      <c r="C139" s="1">
+        <v>11013</v>
+      </c>
+      <c r="D139" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F139" s="1">
+        <v>3</v>
+      </c>
+      <c r="G139" s="1">
+        <v>5501</v>
+      </c>
+      <c r="H139" s="1">
+        <v>6000</v>
+      </c>
+      <c r="I139" s="1">
+        <v>43</v>
+      </c>
+      <c r="J139" s="1">
+        <v>1</v>
+      </c>
+      <c r="K139" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" customHeight="1" spans="3:12">
+      <c r="C140" s="1">
+        <v>11014</v>
+      </c>
+      <c r="D140" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="E128" s="7" t="s">
+      <c r="E140" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="F128" s="2">
-        <v>1</v>
-      </c>
-      <c r="G128" s="2">
-        <v>5001</v>
-      </c>
-      <c r="H128" s="2">
-        <v>6000</v>
-      </c>
-      <c r="I128" s="2">
-        <v>61</v>
-      </c>
-      <c r="J128" s="2">
-        <v>1</v>
-      </c>
-      <c r="K128" s="2">
-        <v>1</v>
-      </c>
-      <c r="L128" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="129" customHeight="1" spans="3:11">
-      <c r="C129" s="1">
-        <v>11013</v>
-      </c>
-      <c r="D129" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="F129" s="1">
-        <v>3</v>
-      </c>
-      <c r="G129" s="1">
+      <c r="F140" s="1">
+        <v>2</v>
+      </c>
+      <c r="G140" s="1">
         <v>5501</v>
       </c>
-      <c r="H129" s="1">
-        <v>6000</v>
-      </c>
-      <c r="I129" s="1">
-        <v>43</v>
-      </c>
-      <c r="J129" s="1">
-        <v>1</v>
-      </c>
-      <c r="K129" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130" customHeight="1" spans="3:11">
-      <c r="C130" s="1">
-        <v>11014</v>
-      </c>
-      <c r="D130" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="E130" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="F130" s="1">
-        <v>2</v>
-      </c>
-      <c r="G130" s="1">
-        <v>5501</v>
-      </c>
-      <c r="H130" s="1">
+      <c r="H140" s="1">
         <v>6500</v>
       </c>
-      <c r="I130" s="1">
+      <c r="I140" s="1">
         <v>67</v>
       </c>
-      <c r="J130" s="1">
-        <v>1</v>
-      </c>
-      <c r="K130" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" customHeight="1" spans="3:11">
-      <c r="C131" s="1">
+      <c r="J140" s="1">
+        <v>1</v>
+      </c>
+      <c r="K140" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" customHeight="1" spans="3:12">
+      <c r="C141" s="1">
         <v>11015</v>
       </c>
-      <c r="D131" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="E131" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="F131" s="1">
-        <v>1</v>
-      </c>
-      <c r="G131" s="1">
+      <c r="D141" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E141" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="F141" s="1">
+        <v>1</v>
+      </c>
+      <c r="G141" s="1">
         <v>6401</v>
       </c>
-      <c r="H131" s="1">
+      <c r="H141" s="1">
         <v>6900</v>
       </c>
-      <c r="I131" s="1">
+      <c r="I141" s="1">
         <v>91</v>
       </c>
-      <c r="J131" s="1">
-        <v>1</v>
-      </c>
-      <c r="K131" s="2">
+      <c r="J141" s="1">
+        <v>1</v>
+      </c>
+      <c r="K141" s="2">
         <v>1</v>
       </c>
     </row>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -2367,10 +2367,10 @@
         <v>3</v>
       </c>
       <c r="G28" s="2">
-        <v>6503</v>
+        <v>6903</v>
       </c>
       <c r="H28" s="2">
-        <v>7500</v>
+        <v>8000</v>
       </c>
       <c r="I28" s="2">
         <v>11</v>
@@ -2518,10 +2518,10 @@
         <v>2</v>
       </c>
       <c r="G33" s="2">
-        <v>7007</v>
+        <v>7407</v>
       </c>
       <c r="H33" s="2">
-        <v>8000</v>
+        <v>8500</v>
       </c>
       <c r="I33" s="2">
         <v>13</v>
@@ -3523,7 +3523,7 @@
         <v>89</v>
       </c>
       <c r="F73" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G73" s="2">
         <v>4001</v>
@@ -3555,7 +3555,7 @@
         <v>90</v>
       </c>
       <c r="F74" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G74" s="2">
         <v>4001</v>
@@ -3587,7 +3587,7 @@
         <v>89</v>
       </c>
       <c r="F75" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G75" s="2">
         <v>5500</v>
@@ -3620,7 +3620,7 @@
         <v>90</v>
       </c>
       <c r="F77" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G77" s="2">
         <v>5500</v>
@@ -3652,7 +3652,7 @@
         <v>91</v>
       </c>
       <c r="F78" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G78" s="2">
         <v>6000</v>
@@ -3684,7 +3684,7 @@
         <v>92</v>
       </c>
       <c r="F79" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G79" s="2">
         <v>6500</v>
@@ -3934,7 +3934,7 @@
         <v>20</v>
       </c>
       <c r="K88" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:12">
@@ -3960,7 +3960,7 @@
         <v>3</v>
       </c>
       <c r="J89" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K89" s="2">
         <v>3</v>
@@ -3989,10 +3989,10 @@
         <v>3</v>
       </c>
       <c r="J90" s="1">
+        <v>4</v>
+      </c>
+      <c r="K90" s="2">
         <v>2</v>
-      </c>
-      <c r="K90" s="2">
-        <v>3</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:12">
@@ -4047,10 +4047,10 @@
         <v>3</v>
       </c>
       <c r="J92" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K92" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:12">
@@ -4076,10 +4076,10 @@
         <v>3</v>
       </c>
       <c r="J93" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K93" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:12">

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -2367,10 +2367,10 @@
         <v>3</v>
       </c>
       <c r="G28" s="2">
-        <v>6903</v>
+        <v>6703</v>
       </c>
       <c r="H28" s="2">
-        <v>8000</v>
+        <v>6800</v>
       </c>
       <c r="I28" s="2">
         <v>11</v>
@@ -3523,7 +3523,7 @@
         <v>89</v>
       </c>
       <c r="F73" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G73" s="2">
         <v>4001</v>
@@ -3555,7 +3555,7 @@
         <v>90</v>
       </c>
       <c r="F74" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G74" s="2">
         <v>4001</v>
@@ -3587,7 +3587,7 @@
         <v>89</v>
       </c>
       <c r="F75" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G75" s="2">
         <v>5500</v>
@@ -3620,7 +3620,7 @@
         <v>90</v>
       </c>
       <c r="F77" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G77" s="2">
         <v>5500</v>
@@ -3629,7 +3629,7 @@
         <v>6500</v>
       </c>
       <c r="I77" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J77" s="2">
         <v>20</v>
@@ -3652,7 +3652,7 @@
         <v>91</v>
       </c>
       <c r="F78" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G78" s="2">
         <v>6000</v>
@@ -3661,7 +3661,7 @@
         <v>7000</v>
       </c>
       <c r="I78" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J78" s="2">
         <v>20</v>
@@ -3684,7 +3684,7 @@
         <v>92</v>
       </c>
       <c r="F79" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G79" s="2">
         <v>6500</v>
@@ -3693,7 +3693,7 @@
         <v>7500</v>
       </c>
       <c r="I79" s="2">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J79" s="2">
         <v>20</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="178">
   <si>
     <t>#</t>
   </si>
@@ -559,6 +559,42 @@
   </si>
   <si>
     <t>粉色宠物</t>
+  </si>
+  <si>
+    <t>220303</t>
+  </si>
+  <si>
+    <t>蓝色坐骑</t>
+  </si>
+  <si>
+    <t>220304</t>
+  </si>
+  <si>
+    <t>紫色坐骑</t>
+  </si>
+  <si>
+    <t>220305</t>
+  </si>
+  <si>
+    <t>橙色坐骑</t>
+  </si>
+  <si>
+    <t>220306</t>
+  </si>
+  <si>
+    <t>红色坐骑</t>
+  </si>
+  <si>
+    <t>220307</t>
+  </si>
+  <si>
+    <t>金色坐骑</t>
+  </si>
+  <si>
+    <t>220308</t>
+  </si>
+  <si>
+    <t>暗金坐骑</t>
   </si>
 </sst>
 </file>
@@ -1555,7 +1591,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M141"/>
+  <dimension ref="A1:M150"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -5112,7 +5148,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="129" customHeight="1" spans="3:12">
+    <row r="129" customHeight="1" spans="1:12">
       <c r="C129" s="1">
         <v>11003</v>
       </c>
@@ -5144,7 +5180,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="130" customHeight="1" spans="3:12">
+    <row r="130" customHeight="1" spans="1:12">
       <c r="C130" s="1">
         <v>11004</v>
       </c>
@@ -5176,7 +5212,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="131" customHeight="1" spans="3:12">
+    <row r="131" customHeight="1" spans="1:12">
       <c r="C131" s="1">
         <v>11005</v>
       </c>
@@ -5208,7 +5244,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="132" customHeight="1" spans="3:12">
+    <row r="132" customHeight="1" spans="1:12">
       <c r="C132" s="1">
         <v>11006</v>
       </c>
@@ -5240,7 +5276,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="133" customHeight="1" spans="3:12">
+    <row r="133" customHeight="1" spans="1:12">
       <c r="C133" s="1">
         <v>11007</v>
       </c>
@@ -5272,7 +5308,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="134" customHeight="1" spans="3:12">
+    <row r="134" customHeight="1" spans="1:12">
       <c r="C134" s="1">
         <v>11008</v>
       </c>
@@ -5304,7 +5340,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="135" customHeight="1" spans="3:12">
+    <row r="135" customHeight="1" spans="1:12">
       <c r="C135" s="1">
         <v>11009</v>
       </c>
@@ -5336,7 +5372,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="136" customHeight="1" spans="3:12">
+    <row r="136" customHeight="1" spans="1:12">
       <c r="C136" s="1">
         <v>11010</v>
       </c>
@@ -5368,7 +5404,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="137" customHeight="1" spans="3:12">
+    <row r="137" customHeight="1" spans="1:12">
       <c r="C137" s="1">
         <v>11011</v>
       </c>
@@ -5400,7 +5436,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="138" customHeight="1" spans="3:12">
+    <row r="138" customHeight="1" spans="1:12">
       <c r="C138" s="1">
         <v>11012</v>
       </c>
@@ -5432,7 +5468,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="139" customHeight="1" spans="3:12">
+    <row r="139" customHeight="1" spans="1:12">
       <c r="C139" s="1">
         <v>11013</v>
       </c>
@@ -5461,7 +5497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" customHeight="1" spans="3:12">
+    <row r="140" customHeight="1" spans="1:12">
       <c r="C140" s="1">
         <v>11014</v>
       </c>
@@ -5490,7 +5526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" customHeight="1" spans="3:12">
+    <row r="141" customHeight="1" spans="1:12">
       <c r="C141" s="1">
         <v>11015</v>
       </c>
@@ -5507,7 +5543,7 @@
         <v>6401</v>
       </c>
       <c r="H141" s="1">
-        <v>6900</v>
+        <v>7400</v>
       </c>
       <c r="I141" s="1">
         <v>91</v>
@@ -5518,6 +5554,220 @@
       <c r="K141" s="2">
         <v>1</v>
       </c>
+    </row>
+    <row r="144" customHeight="1" spans="1:12">
+      <c r="A144" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C144" s="1">
+        <v>11303</v>
+      </c>
+      <c r="D144" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="F144" s="1">
+        <v>6</v>
+      </c>
+      <c r="G144" s="1">
+        <v>1401</v>
+      </c>
+      <c r="H144" s="1">
+        <v>2400</v>
+      </c>
+      <c r="I144" s="1">
+        <v>41</v>
+      </c>
+      <c r="J144" s="1">
+        <v>1</v>
+      </c>
+      <c r="K144" s="2">
+        <v>1</v>
+      </c>
+      <c r="L144" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" spans="1:12">
+      <c r="A145" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C145" s="1">
+        <v>11304</v>
+      </c>
+      <c r="D145" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E145" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="F145" s="1">
+        <v>5</v>
+      </c>
+      <c r="G145" s="1">
+        <v>2401</v>
+      </c>
+      <c r="H145" s="1">
+        <v>3400</v>
+      </c>
+      <c r="I145" s="1">
+        <v>51</v>
+      </c>
+      <c r="J145" s="1">
+        <v>1</v>
+      </c>
+      <c r="K145" s="2">
+        <v>1</v>
+      </c>
+      <c r="L145" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" spans="1:12">
+      <c r="C146" s="1">
+        <v>11305</v>
+      </c>
+      <c r="D146" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="E146" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F146" s="1">
+        <v>4</v>
+      </c>
+      <c r="G146" s="1">
+        <v>3401</v>
+      </c>
+      <c r="H146" s="1">
+        <v>5400</v>
+      </c>
+      <c r="I146" s="1">
+        <v>67</v>
+      </c>
+      <c r="J146" s="1">
+        <v>1</v>
+      </c>
+      <c r="K146" s="2">
+        <v>1</v>
+      </c>
+      <c r="L146" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" spans="1:12">
+      <c r="C147" s="1">
+        <v>11306</v>
+      </c>
+      <c r="D147" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E147" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F147" s="1">
+        <v>3</v>
+      </c>
+      <c r="G147" s="1">
+        <v>5401</v>
+      </c>
+      <c r="H147" s="1">
+        <v>6400</v>
+      </c>
+      <c r="I147" s="1">
+        <v>71</v>
+      </c>
+      <c r="J147" s="1">
+        <v>1</v>
+      </c>
+      <c r="K147" s="2">
+        <v>1</v>
+      </c>
+      <c r="L147" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" spans="1:12">
+      <c r="C148" s="1">
+        <v>11307</v>
+      </c>
+      <c r="D148" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="E148" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F148" s="1">
+        <v>2</v>
+      </c>
+      <c r="G148" s="1">
+        <v>6401</v>
+      </c>
+      <c r="H148" s="1">
+        <v>7400</v>
+      </c>
+      <c r="I148" s="1">
+        <v>83</v>
+      </c>
+      <c r="J148" s="1">
+        <v>1</v>
+      </c>
+      <c r="K148" s="2">
+        <v>1</v>
+      </c>
+      <c r="L148" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" spans="1:12">
+      <c r="C149" s="1">
+        <v>11308</v>
+      </c>
+      <c r="D149" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="E149" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="F149" s="1">
+        <v>1</v>
+      </c>
+      <c r="G149" s="1">
+        <v>7401</v>
+      </c>
+      <c r="H149" s="1">
+        <v>8400</v>
+      </c>
+      <c r="I149" s="1">
+        <v>91</v>
+      </c>
+      <c r="J149" s="1">
+        <v>1</v>
+      </c>
+      <c r="K149" s="2">
+        <v>1</v>
+      </c>
+      <c r="L149" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" spans="1:12">
+      <c r="D150" s="5"/>
+      <c r="E150" s="7"/>
+      <c r="F150" s="1"/>
+      <c r="G150" s="1"/>
+      <c r="H150" s="1"/>
+      <c r="I150" s="1"/>
+      <c r="J150" s="1"/>
+      <c r="K150" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="178">
   <si>
     <t>#</t>
   </si>
@@ -792,12 +792,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5148,7 +5148,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="129" customHeight="1" spans="1:12">
+    <row r="129" customHeight="1" spans="3:12">
       <c r="C129" s="1">
         <v>11003</v>
       </c>
@@ -5180,7 +5180,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="130" customHeight="1" spans="1:12">
+    <row r="130" customHeight="1" spans="3:12">
       <c r="C130" s="1">
         <v>11004</v>
       </c>
@@ -5212,7 +5212,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="131" customHeight="1" spans="1:12">
+    <row r="131" customHeight="1" spans="3:12">
       <c r="C131" s="1">
         <v>11005</v>
       </c>
@@ -5244,7 +5244,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="132" customHeight="1" spans="1:12">
+    <row r="132" customHeight="1" spans="3:12">
       <c r="C132" s="1">
         <v>11006</v>
       </c>
@@ -5276,7 +5276,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="133" customHeight="1" spans="1:12">
+    <row r="133" customHeight="1" spans="3:12">
       <c r="C133" s="1">
         <v>11007</v>
       </c>
@@ -5308,7 +5308,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="134" customHeight="1" spans="1:12">
+    <row r="134" customHeight="1" spans="3:12">
       <c r="C134" s="1">
         <v>11008</v>
       </c>
@@ -5340,7 +5340,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="135" customHeight="1" spans="1:12">
+    <row r="135" customHeight="1" spans="3:12">
       <c r="C135" s="1">
         <v>11009</v>
       </c>
@@ -5372,7 +5372,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="136" customHeight="1" spans="1:12">
+    <row r="136" customHeight="1" spans="3:12">
       <c r="C136" s="1">
         <v>11010</v>
       </c>
@@ -5404,7 +5404,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="137" customHeight="1" spans="1:12">
+    <row r="137" customHeight="1" spans="3:12">
       <c r="C137" s="1">
         <v>11011</v>
       </c>
@@ -5436,7 +5436,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="138" customHeight="1" spans="1:12">
+    <row r="138" customHeight="1" spans="3:12">
       <c r="C138" s="1">
         <v>11012</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="139" customHeight="1" spans="1:12">
+    <row r="139" customHeight="1" spans="3:12">
       <c r="C139" s="1">
         <v>11013</v>
       </c>
@@ -5497,7 +5497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" customHeight="1" spans="1:12">
+    <row r="140" customHeight="1" spans="3:12">
       <c r="C140" s="1">
         <v>11014</v>
       </c>
@@ -5526,7 +5526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" customHeight="1" spans="1:12">
+    <row r="141" customHeight="1" spans="3:12">
       <c r="C141" s="1">
         <v>11015</v>
       </c>
@@ -5555,13 +5555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" customHeight="1" spans="1:12">
-      <c r="A144" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="144" customHeight="1" spans="3:12">
       <c r="C144" s="1">
         <v>11303</v>
       </c>
@@ -5572,16 +5566,16 @@
         <v>167</v>
       </c>
       <c r="F144" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G144" s="1">
-        <v>1401</v>
+        <v>3903</v>
       </c>
       <c r="H144" s="1">
-        <v>2400</v>
+        <v>4402</v>
       </c>
       <c r="I144" s="1">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J144" s="1">
         <v>1</v>
@@ -5593,13 +5587,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="145" customHeight="1" spans="1:12">
-      <c r="A145" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="145" customHeight="1" spans="3:12">
       <c r="C145" s="1">
         <v>11304</v>
       </c>
@@ -5610,16 +5598,16 @@
         <v>169</v>
       </c>
       <c r="F145" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G145" s="1">
-        <v>2401</v>
+        <v>4403</v>
       </c>
       <c r="H145" s="1">
-        <v>3400</v>
+        <v>4902</v>
       </c>
       <c r="I145" s="1">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="J145" s="1">
         <v>1</v>
@@ -5631,7 +5619,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="146" customHeight="1" spans="1:12">
+    <row r="146" customHeight="1" spans="3:12">
       <c r="C146" s="1">
         <v>11305</v>
       </c>
@@ -5642,16 +5630,16 @@
         <v>171</v>
       </c>
       <c r="F146" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G146" s="1">
-        <v>3401</v>
+        <v>4903</v>
       </c>
       <c r="H146" s="1">
-        <v>5400</v>
+        <v>5402</v>
       </c>
       <c r="I146" s="1">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="J146" s="1">
         <v>1</v>
@@ -5663,7 +5651,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="147" customHeight="1" spans="1:12">
+    <row r="147" customHeight="1" spans="3:12">
       <c r="C147" s="1">
         <v>11306</v>
       </c>
@@ -5674,16 +5662,16 @@
         <v>173</v>
       </c>
       <c r="F147" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G147" s="1">
-        <v>5401</v>
+        <v>5403</v>
       </c>
       <c r="H147" s="1">
-        <v>6400</v>
+        <v>6402</v>
       </c>
       <c r="I147" s="1">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="J147" s="1">
         <v>1</v>
@@ -5695,7 +5683,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="148" customHeight="1" spans="1:12">
+    <row r="148" customHeight="1" spans="3:12">
       <c r="C148" s="1">
         <v>11307</v>
       </c>
@@ -5706,16 +5694,16 @@
         <v>175</v>
       </c>
       <c r="F148" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G148" s="1">
-        <v>6401</v>
+        <v>6403</v>
       </c>
       <c r="H148" s="1">
-        <v>7400</v>
+        <v>7402</v>
       </c>
       <c r="I148" s="1">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="J148" s="1">
         <v>1</v>
@@ -5727,7 +5715,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="149" customHeight="1" spans="1:12">
+    <row r="149" customHeight="1" spans="3:12">
       <c r="C149" s="1">
         <v>11308</v>
       </c>
@@ -5741,13 +5729,13 @@
         <v>1</v>
       </c>
       <c r="G149" s="1">
-        <v>7401</v>
+        <v>7403</v>
       </c>
       <c r="H149" s="1">
-        <v>8400</v>
+        <v>8402</v>
       </c>
       <c r="I149" s="1">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J149" s="1">
         <v>1</v>
@@ -5759,14 +5747,9 @@
         <v>156</v>
       </c>
     </row>
-    <row r="150" customHeight="1" spans="1:12">
+    <row r="150" customHeight="1" spans="3:12">
       <c r="D150" s="5"/>
       <c r="E150" s="7"/>
-      <c r="F150" s="1"/>
-      <c r="G150" s="1"/>
-      <c r="H150" s="1"/>
-      <c r="I150" s="1"/>
-      <c r="J150" s="1"/>
       <c r="K150" s="2"/>
     </row>
   </sheetData>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -792,12 +792,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3755,7 +3755,7 @@
         <v>20</v>
       </c>
       <c r="G81" s="1">
-        <v>3001</v>
+        <v>3009</v>
       </c>
       <c r="H81" s="1">
         <v>4000</v>
@@ -3784,7 +3784,7 @@
         <v>10</v>
       </c>
       <c r="G82" s="1">
-        <v>3001</v>
+        <v>3009</v>
       </c>
       <c r="H82" s="1">
         <v>4000</v>
@@ -3813,7 +3813,7 @@
         <v>5</v>
       </c>
       <c r="G83" s="1">
-        <v>3001</v>
+        <v>3009</v>
       </c>
       <c r="H83" s="1">
         <v>4000</v>
@@ -3842,7 +3842,7 @@
         <v>2</v>
       </c>
       <c r="G84" s="1">
-        <v>3501</v>
+        <v>3509</v>
       </c>
       <c r="H84" s="1">
         <v>5000</v>
@@ -3871,7 +3871,7 @@
         <v>10</v>
       </c>
       <c r="G85" s="1">
-        <v>4001</v>
+        <v>4009</v>
       </c>
       <c r="H85" s="1">
         <v>6000</v>
@@ -3900,10 +3900,10 @@
         <v>5</v>
       </c>
       <c r="G86" s="1">
-        <v>4001</v>
+        <v>4009</v>
       </c>
       <c r="H86" s="1">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="I86" s="1">
         <v>3</v>
@@ -3929,10 +3929,10 @@
         <v>3</v>
       </c>
       <c r="G87" s="1">
-        <v>4001</v>
+        <v>4009</v>
       </c>
       <c r="H87" s="1">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="I87" s="1">
         <v>3</v>
@@ -3958,7 +3958,7 @@
         <v>10</v>
       </c>
       <c r="G88" s="1">
-        <v>6001</v>
+        <v>6009</v>
       </c>
       <c r="H88" s="1">
         <v>7000</v>
@@ -3987,7 +3987,7 @@
         <v>5</v>
       </c>
       <c r="G89" s="1">
-        <v>6001</v>
+        <v>6009</v>
       </c>
       <c r="H89" s="1">
         <v>7000</v>
@@ -4016,7 +4016,7 @@
         <v>3</v>
       </c>
       <c r="G90" s="1">
-        <v>6001</v>
+        <v>6009</v>
       </c>
       <c r="H90" s="1">
         <v>7000</v>
@@ -4045,7 +4045,7 @@
         <v>10</v>
       </c>
       <c r="G91" s="1">
-        <v>7001</v>
+        <v>7009</v>
       </c>
       <c r="H91" s="1">
         <v>9000</v>
@@ -4074,7 +4074,7 @@
         <v>5</v>
       </c>
       <c r="G92" s="1">
-        <v>7001</v>
+        <v>7009</v>
       </c>
       <c r="H92" s="1">
         <v>9000</v>
@@ -4103,7 +4103,7 @@
         <v>3</v>
       </c>
       <c r="G93" s="1">
-        <v>7001</v>
+        <v>7009</v>
       </c>
       <c r="H93" s="1">
         <v>9000</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="180">
   <si>
     <t>#</t>
   </si>
@@ -268,6 +268,12 @@
   </si>
   <si>
     <t>虚无精华</t>
+  </si>
+  <si>
+    <t>602</t>
+  </si>
+  <si>
+    <t>随机极宝石</t>
   </si>
   <si>
     <t>220036</t>
@@ -1591,7 +1597,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M150"/>
+  <dimension ref="A1:M151"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2534,13 +2540,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A33" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>0</v>
-      </c>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C33" s="2">
         <v>28</v>
       </c>
@@ -2569,59 +2569,56 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="D34" s="4"/>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="C35" s="2">
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C34" s="2">
+        <v>29</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F34" s="2">
+        <v>20</v>
+      </c>
+      <c r="G34" s="2">
+        <v>7515</v>
+      </c>
+      <c r="H34" s="2">
+        <v>9000</v>
+      </c>
+      <c r="I34" s="2">
+        <v>3</v>
+      </c>
+      <c r="J34" s="2">
+        <v>100</v>
+      </c>
+      <c r="K34" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="D35" s="4"/>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C36" s="2">
         <v>151</v>
       </c>
-      <c r="D35" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F35" s="2">
+      <c r="D36" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F36" s="2">
         <v>12</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G36" s="2">
         <v>300</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H36" s="2">
         <v>1500</v>
-      </c>
-      <c r="I35" s="2">
-        <v>1</v>
-      </c>
-      <c r="J35" s="2">
-        <v>25</v>
-      </c>
-      <c r="K35" s="2">
-        <v>1</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="C36" s="2">
-        <v>152</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F36" s="2">
-        <v>6</v>
-      </c>
-      <c r="G36" s="2">
-        <v>1501</v>
-      </c>
-      <c r="H36" s="2">
-        <v>4000</v>
       </c>
       <c r="I36" s="2">
         <v>1</v>
@@ -2633,94 +2630,94 @@
         <v>1</v>
       </c>
       <c r="L36" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C37" s="2">
+        <v>152</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F37" s="2">
+        <v>6</v>
+      </c>
+      <c r="G37" s="2">
+        <v>1501</v>
+      </c>
+      <c r="H37" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I37" s="2">
+        <v>1</v>
+      </c>
+      <c r="J37" s="2">
+        <v>25</v>
+      </c>
+      <c r="K37" s="2">
+        <v>1</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C38" s="2">
+        <v>153</v>
+      </c>
+      <c r="D38" s="8" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="C37" s="2">
-        <v>153</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F37" s="2">
+      <c r="E38" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="2">
         <v>3</v>
       </c>
-      <c r="G37" s="2">
+      <c r="G38" s="2">
         <v>4001</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H38" s="2">
         <v>10000</v>
       </c>
-      <c r="I37" s="2">
-        <v>1</v>
-      </c>
-      <c r="J37" s="2">
+      <c r="I38" s="2">
+        <v>1</v>
+      </c>
+      <c r="J38" s="2">
         <v>15</v>
       </c>
-      <c r="K37" s="2">
+      <c r="K38" s="2">
         <v>2</v>
       </c>
-      <c r="L37" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="D38" s="4"/>
-    </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="C39" s="1">
-        <v>100</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F39" s="1">
-        <v>50</v>
-      </c>
-      <c r="G39" s="1">
-        <v>1</v>
-      </c>
-      <c r="H39" s="1">
-        <v>300</v>
-      </c>
-      <c r="I39" s="1">
-        <v>1</v>
-      </c>
-      <c r="J39" s="1">
-        <v>10000</v>
-      </c>
-      <c r="K39" s="2">
-        <v>1</v>
-      </c>
-      <c r="L39" s="1" t="s">
+      <c r="L38" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="D39" s="4"/>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C40" s="1">
+        <v>100</v>
+      </c>
+      <c r="D40" s="9" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="40" s="1" customFormat="1" ht="20" customHeight="1" spans="1:12">
-      <c r="C40" s="1">
-        <v>101</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>75</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F40" s="1">
         <v>50</v>
       </c>
       <c r="G40" s="1">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="H40" s="1">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I40" s="1">
         <v>1</v>
@@ -2729,30 +2726,30 @@
         <v>10000</v>
       </c>
       <c r="K40" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L40" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C41" s="1">
+        <v>101</v>
+      </c>
+      <c r="D41" s="9" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="41" customHeight="1" spans="1:12">
-      <c r="C41" s="1">
-        <v>102</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>75</v>
-      </c>
       <c r="E41" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F41" s="1">
         <v>50</v>
       </c>
       <c r="G41" s="1">
-        <v>601</v>
+        <v>301</v>
       </c>
       <c r="H41" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="I41" s="1">
         <v>1</v>
@@ -2761,30 +2758,30 @@
         <v>10000</v>
       </c>
       <c r="K41" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L41" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:12">
+      <c r="C42" s="1">
+        <v>102</v>
+      </c>
+      <c r="D42" s="9" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="42" customHeight="1" spans="1:12">
-      <c r="C42" s="1">
-        <v>103</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>75</v>
-      </c>
       <c r="E42" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F42" s="1">
         <v>50</v>
       </c>
       <c r="G42" s="1">
-        <v>1001</v>
+        <v>601</v>
       </c>
       <c r="H42" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I42" s="1">
         <v>1</v>
@@ -2793,62 +2790,62 @@
         <v>10000</v>
       </c>
       <c r="K42" s="2">
+        <v>4</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:12">
+      <c r="C43" s="1">
+        <v>103</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F43" s="1">
+        <v>50</v>
+      </c>
+      <c r="G43" s="1">
+        <v>1001</v>
+      </c>
+      <c r="H43" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I43" s="1">
+        <v>1</v>
+      </c>
+      <c r="J43" s="1">
+        <v>10000</v>
+      </c>
+      <c r="K43" s="2">
         <v>10</v>
       </c>
-      <c r="L42" s="1" t="s">
+      <c r="L43" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C44" s="1">
+        <v>104</v>
+      </c>
+      <c r="D44" s="8" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="43" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="C43" s="1">
-        <v>104</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F43" s="2">
-        <v>50</v>
-      </c>
-      <c r="G43" s="2">
-        <v>1501</v>
-      </c>
-      <c r="H43" s="2">
-        <v>3500</v>
-      </c>
-      <c r="I43" s="2">
-        <v>1</v>
-      </c>
-      <c r="J43" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K43" s="2">
-        <v>20</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="C44" s="1">
-        <v>105</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>75</v>
-      </c>
       <c r="E44" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F44" s="2">
         <v>50</v>
       </c>
       <c r="G44" s="2">
-        <v>3501</v>
+        <v>1501</v>
       </c>
       <c r="H44" s="2">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="I44" s="2">
         <v>1</v>
@@ -2857,65 +2854,65 @@
         <v>10000</v>
       </c>
       <c r="K44" s="2">
+        <v>20</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C45" s="1">
+        <v>105</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F45" s="2">
+        <v>50</v>
+      </c>
+      <c r="G45" s="2">
+        <v>3501</v>
+      </c>
+      <c r="H45" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I45" s="2">
+        <v>1</v>
+      </c>
+      <c r="J45" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K45" s="2">
         <v>40</v>
       </c>
-      <c r="L44" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="45" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="D45" s="4"/>
-    </row>
-    <row r="46" s="2" customFormat="1" ht="20" customHeight="1" spans="1:12">
-      <c r="C46" s="2">
+      <c r="L45" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="D46" s="4"/>
+    </row>
+    <row r="47" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C47" s="2">
         <v>200</v>
       </c>
-      <c r="D46" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F46" s="2">
-        <v>50</v>
-      </c>
-      <c r="G46" s="2">
-        <v>1</v>
-      </c>
-      <c r="H46" s="2">
-        <v>300</v>
-      </c>
-      <c r="I46" s="2">
-        <v>1</v>
-      </c>
-      <c r="J46" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K46" s="2">
-        <v>1</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="47" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="C47" s="2">
-        <v>201</v>
-      </c>
       <c r="D47" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F47" s="2">
         <v>50</v>
       </c>
       <c r="G47" s="2">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="H47" s="2">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I47" s="2">
         <v>1</v>
@@ -2924,30 +2921,30 @@
         <v>10000</v>
       </c>
       <c r="K47" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="1:12">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C48" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F48" s="2">
         <v>50</v>
       </c>
       <c r="G48" s="2">
-        <v>601</v>
+        <v>301</v>
       </c>
       <c r="H48" s="2">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="I48" s="2">
         <v>1</v>
@@ -2956,30 +2953,30 @@
         <v>10000</v>
       </c>
       <c r="K48" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C49" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F49" s="2">
         <v>50</v>
       </c>
       <c r="G49" s="2">
-        <v>1001</v>
+        <v>601</v>
       </c>
       <c r="H49" s="2">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I49" s="2">
         <v>1</v>
@@ -2988,30 +2985,30 @@
         <v>10000</v>
       </c>
       <c r="K49" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="50" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C50" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F50" s="2">
         <v>50</v>
       </c>
       <c r="G50" s="2">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H50" s="2">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="I50" s="2">
         <v>1</v>
@@ -3020,30 +3017,30 @@
         <v>10000</v>
       </c>
       <c r="K50" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
       <c r="C51" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F51" s="2">
         <v>50</v>
       </c>
       <c r="G51" s="2">
-        <v>3501</v>
+        <v>1501</v>
       </c>
       <c r="H51" s="2">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="I51" s="2">
         <v>1</v>
@@ -3052,65 +3049,65 @@
         <v>10000</v>
       </c>
       <c r="K51" s="2">
+        <v>20</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C52" s="2">
+        <v>205</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F52" s="2">
+        <v>50</v>
+      </c>
+      <c r="G52" s="2">
+        <v>3501</v>
+      </c>
+      <c r="H52" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I52" s="2">
+        <v>1</v>
+      </c>
+      <c r="J52" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K52" s="2">
         <v>40</v>
       </c>
-      <c r="L51" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="52" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
-      <c r="D52" s="4"/>
-    </row>
-    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C53" s="2">
-        <v>300</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F53" s="2">
-        <v>10</v>
-      </c>
-      <c r="G53" s="2">
-        <v>1</v>
-      </c>
-      <c r="H53" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I53" s="2">
-        <v>1</v>
-      </c>
-      <c r="J53" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K53" s="2">
-        <v>1</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="L52" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="D53" s="4"/>
     </row>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C54" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F54" s="2">
         <v>10</v>
       </c>
       <c r="G54" s="2">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="H54" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I54" s="2">
         <v>1</v>
@@ -3119,7 +3116,7 @@
         <v>10000</v>
       </c>
       <c r="K54" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>21</v>
@@ -3127,22 +3124,22 @@
     </row>
     <row r="55" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C55" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F55" s="2">
         <v>10</v>
       </c>
       <c r="G55" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H55" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I55" s="2">
         <v>1</v>
@@ -3151,63 +3148,63 @@
         <v>10000</v>
       </c>
       <c r="K55" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="56" s="2" customFormat="1" customHeight="1"/>
-    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C57" s="2">
-        <v>400</v>
-      </c>
-      <c r="D57" s="11" t="s">
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C56" s="2">
+        <v>302</v>
+      </c>
+      <c r="D56" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E56" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F56" s="2">
         <v>10</v>
       </c>
-      <c r="G57" s="2">
-        <v>50</v>
-      </c>
-      <c r="H57" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I57" s="2">
-        <v>1</v>
-      </c>
-      <c r="J57" s="2">
+      <c r="G56" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H56" s="2">
         <v>10000</v>
       </c>
-      <c r="K57" s="2">
-        <v>1</v>
-      </c>
-      <c r="L57" s="2" t="s">
+      <c r="I56" s="2">
+        <v>1</v>
+      </c>
+      <c r="J56" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K56" s="2">
+        <v>3</v>
+      </c>
+      <c r="L56" s="2" t="s">
         <v>21</v>
       </c>
     </row>
+    <row r="57" s="2" customFormat="1" customHeight="1"/>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C58" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F58" s="2">
         <v>10</v>
       </c>
       <c r="G58" s="2">
-        <v>1001</v>
+        <v>50</v>
       </c>
       <c r="H58" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I58" s="2">
         <v>1</v>
@@ -3216,7 +3213,7 @@
         <v>10000</v>
       </c>
       <c r="K58" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>21</v>
@@ -3224,22 +3221,22 @@
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C59" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F59" s="2">
         <v>10</v>
       </c>
       <c r="G59" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H59" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I59" s="2">
         <v>1</v>
@@ -3248,63 +3245,63 @@
         <v>10000</v>
       </c>
       <c r="K59" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="60" s="2" customFormat="1" customHeight="1"/>
-    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C61" s="2">
-        <v>500</v>
-      </c>
-      <c r="D61" s="11" t="s">
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C60" s="2">
+        <v>402</v>
+      </c>
+      <c r="D60" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F61" s="2">
-        <v>4</v>
-      </c>
-      <c r="G61" s="2">
-        <v>150</v>
-      </c>
-      <c r="H61" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I61" s="2">
-        <v>1</v>
-      </c>
-      <c r="J61" s="2">
-        <v>20</v>
-      </c>
-      <c r="K61" s="2">
-        <v>1</v>
-      </c>
-      <c r="L61" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
+      <c r="F60" s="2">
+        <v>10</v>
+      </c>
+      <c r="G60" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H60" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I60" s="2">
+        <v>1</v>
+      </c>
+      <c r="J60" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K60" s="2">
+        <v>3</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61" s="2" customFormat="1" customHeight="1"/>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C62" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F62" s="2">
         <v>4</v>
       </c>
       <c r="G62" s="2">
-        <v>1001</v>
+        <v>150</v>
       </c>
       <c r="H62" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I62" s="2">
         <v>1</v>
@@ -3313,30 +3310,30 @@
         <v>20</v>
       </c>
       <c r="K62" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C63" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F63" s="2">
         <v>4</v>
       </c>
       <c r="G63" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H63" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I63" s="2">
         <v>1</v>
@@ -3345,63 +3342,63 @@
         <v>20</v>
       </c>
       <c r="K63" s="2">
+        <v>2</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C64" s="2">
+        <v>502</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F64" s="2">
+        <v>4</v>
+      </c>
+      <c r="G64" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H64" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I64" s="2">
+        <v>1</v>
+      </c>
+      <c r="J64" s="2">
+        <v>20</v>
+      </c>
+      <c r="K64" s="2">
         <v>3</v>
       </c>
-      <c r="L63" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="64" s="2" customFormat="1" customHeight="1"/>
-    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C65" s="2">
-        <v>600</v>
-      </c>
-      <c r="D65" s="2">
-        <v>3001</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F65" s="2">
-        <v>10</v>
-      </c>
-      <c r="G65" s="2">
-        <v>1</v>
-      </c>
-      <c r="H65" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I65" s="2">
-        <v>1</v>
-      </c>
-      <c r="J65" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K65" s="2">
-        <v>1</v>
-      </c>
-      <c r="L65" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
+      <c r="L64" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="65" s="2" customFormat="1" customHeight="1"/>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C66" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D66" s="2">
         <v>3001</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F66" s="2">
         <v>10</v>
       </c>
       <c r="G66" s="2">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="H66" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I66" s="2">
         <v>1</v>
@@ -3410,7 +3407,7 @@
         <v>10000</v>
       </c>
       <c r="K66" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>21</v>
@@ -3418,22 +3415,22 @@
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C67" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D67" s="2">
         <v>3001</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F67" s="2">
         <v>10</v>
       </c>
       <c r="G67" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H67" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I67" s="2">
         <v>1</v>
@@ -3442,63 +3439,63 @@
         <v>10000</v>
       </c>
       <c r="K67" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="68" s="2" customFormat="1" customHeight="1"/>
-    <row r="69" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C69" s="2">
-        <v>700</v>
-      </c>
-      <c r="D69" s="2">
-        <v>3002</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F69" s="2">
+    <row r="68" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C68" s="2">
+        <v>602</v>
+      </c>
+      <c r="D68" s="2">
+        <v>3001</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F68" s="2">
         <v>10</v>
       </c>
-      <c r="G69" s="2">
-        <v>200</v>
-      </c>
-      <c r="H69" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I69" s="2">
-        <v>1</v>
-      </c>
-      <c r="J69" s="2">
+      <c r="G68" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H68" s="2">
         <v>10000</v>
       </c>
-      <c r="K69" s="2">
-        <v>1</v>
-      </c>
-      <c r="L69" s="2" t="s">
+      <c r="I68" s="2">
+        <v>1</v>
+      </c>
+      <c r="J68" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K68" s="2">
+        <v>3</v>
+      </c>
+      <c r="L68" s="2" t="s">
         <v>21</v>
       </c>
     </row>
+    <row r="69" s="2" customFormat="1" customHeight="1"/>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C70" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D70" s="2">
         <v>3002</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F70" s="2">
         <v>10</v>
       </c>
       <c r="G70" s="2">
-        <v>1001</v>
+        <v>200</v>
       </c>
       <c r="H70" s="2">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I70" s="2">
         <v>1</v>
@@ -3507,7 +3504,7 @@
         <v>10000</v>
       </c>
       <c r="K70" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>21</v>
@@ -3515,22 +3512,22 @@
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C71" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D71" s="2">
         <v>3002</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F71" s="2">
         <v>10</v>
       </c>
       <c r="G71" s="2">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="H71" s="2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I71" s="2">
         <v>1</v>
@@ -3539,56 +3536,56 @@
         <v>10000</v>
       </c>
       <c r="K71" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="72" customHeight="1" spans="3:12">
-      <c r="K72" s="2"/>
-    </row>
-    <row r="73" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C73" s="2">
-        <v>800</v>
-      </c>
-      <c r="D73" s="2">
-        <v>3003</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F73" s="2">
+    <row r="72" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C72" s="2">
+        <v>702</v>
+      </c>
+      <c r="D72" s="2">
+        <v>3002</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F72" s="2">
         <v>10</v>
       </c>
-      <c r="G73" s="2">
-        <v>4001</v>
-      </c>
-      <c r="H73" s="2">
-        <v>5000</v>
-      </c>
-      <c r="I73" s="2">
-        <v>7</v>
-      </c>
-      <c r="J73" s="2">
-        <v>13</v>
-      </c>
-      <c r="K73" s="2">
-        <v>5</v>
-      </c>
-      <c r="L73" s="2" t="s">
+      <c r="G72" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H72" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I72" s="2">
+        <v>1</v>
+      </c>
+      <c r="J72" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K72" s="2">
+        <v>3</v>
+      </c>
+      <c r="L72" s="2" t="s">
         <v>21</v>
       </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:12">
+      <c r="K73" s="2"/>
     </row>
     <row r="74" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C74" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D74" s="2">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F74" s="2">
         <v>10</v>
@@ -3600,13 +3597,13 @@
         <v>5000</v>
       </c>
       <c r="I74" s="2">
+        <v>7</v>
+      </c>
+      <c r="J74" s="2">
         <v>13</v>
       </c>
-      <c r="J74" s="2">
+      <c r="K74" s="2">
         <v>5</v>
-      </c>
-      <c r="K74" s="2">
-        <v>1</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>21</v>
@@ -3614,87 +3611,87 @@
     </row>
     <row r="75" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C75" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D75" s="2">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F75" s="2">
         <v>10</v>
       </c>
       <c r="G75" s="2">
-        <v>5500</v>
+        <v>4001</v>
       </c>
       <c r="H75" s="2">
-        <v>6500</v>
+        <v>5000</v>
       </c>
       <c r="I75" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J75" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K75" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="76" s="2" customFormat="1" customHeight="1"/>
-    <row r="77" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C77" s="2">
+    <row r="76" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C76" s="2">
+        <v>802</v>
+      </c>
+      <c r="D76" s="2">
+        <v>3003</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F76" s="2">
+        <v>10</v>
+      </c>
+      <c r="G76" s="2">
+        <v>5500</v>
+      </c>
+      <c r="H76" s="2">
+        <v>6500</v>
+      </c>
+      <c r="I76" s="2">
+        <v>7</v>
+      </c>
+      <c r="J76" s="2">
+        <v>20</v>
+      </c>
+      <c r="K76" s="2">
+        <v>7</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77" s="2" customFormat="1" customHeight="1"/>
+    <row r="78" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C78" s="2">
         <v>803</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D78" s="2">
         <v>3004</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F77" s="2">
-        <v>10</v>
-      </c>
-      <c r="G77" s="2">
-        <v>5500</v>
-      </c>
-      <c r="H77" s="2">
-        <v>6500</v>
-      </c>
-      <c r="I77" s="2">
-        <v>7</v>
-      </c>
-      <c r="J77" s="2">
-        <v>20</v>
-      </c>
-      <c r="K77" s="2">
-        <v>2</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="78" customHeight="1" spans="3:12">
-      <c r="C78" s="2">
-        <v>804</v>
-      </c>
-      <c r="D78" s="2">
-        <v>3005</v>
-      </c>
       <c r="E78" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F78" s="2">
         <v>10</v>
       </c>
       <c r="G78" s="2">
-        <v>6000</v>
+        <v>5500</v>
       </c>
       <c r="H78" s="2">
-        <v>7000</v>
+        <v>6500</v>
       </c>
       <c r="I78" s="2">
         <v>7</v>
@@ -3711,22 +3708,22 @@
     </row>
     <row r="79" customHeight="1" spans="3:12">
       <c r="C79" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D79" s="2">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F79" s="2">
         <v>10</v>
       </c>
       <c r="G79" s="2">
-        <v>6500</v>
+        <v>6000</v>
       </c>
       <c r="H79" s="2">
-        <v>7500</v>
+        <v>7000</v>
       </c>
       <c r="I79" s="2">
         <v>7</v>
@@ -3741,38 +3738,41 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" customHeight="1" spans="3:12">
-      <c r="C81" s="1">
-        <v>901</v>
-      </c>
-      <c r="D81" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E81" s="1" t="s">
+    <row r="80" customHeight="1" spans="3:12">
+      <c r="C80" s="2">
+        <v>805</v>
+      </c>
+      <c r="D80" s="2">
+        <v>3006</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F81" s="1">
+      <c r="F80" s="2">
+        <v>10</v>
+      </c>
+      <c r="G80" s="2">
+        <v>6500</v>
+      </c>
+      <c r="H80" s="2">
+        <v>7500</v>
+      </c>
+      <c r="I80" s="2">
+        <v>7</v>
+      </c>
+      <c r="J80" s="2">
         <v>20</v>
       </c>
-      <c r="G81" s="1">
-        <v>3009</v>
-      </c>
-      <c r="H81" s="1">
-        <v>4000</v>
-      </c>
-      <c r="I81" s="1">
-        <v>3</v>
-      </c>
-      <c r="J81" s="1">
-        <v>30</v>
-      </c>
-      <c r="K81" s="2">
-        <v>1</v>
+      <c r="K80" s="2">
+        <v>2</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:12">
       <c r="C82" s="1">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D82" s="10" t="s">
         <v>95</v>
@@ -3781,7 +3781,7 @@
         <v>96</v>
       </c>
       <c r="F82" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G82" s="1">
         <v>3009</v>
@@ -3793,7 +3793,7 @@
         <v>3</v>
       </c>
       <c r="J82" s="1">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="K82" s="2">
         <v>1</v>
@@ -3801,7 +3801,7 @@
     </row>
     <row r="83" customHeight="1" spans="3:12">
       <c r="C83" s="1">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D83" s="10" t="s">
         <v>97</v>
@@ -3810,7 +3810,7 @@
         <v>98</v>
       </c>
       <c r="F83" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G83" s="1">
         <v>3009</v>
@@ -3822,7 +3822,7 @@
         <v>3</v>
       </c>
       <c r="J83" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K83" s="2">
         <v>1</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="84" customHeight="1" spans="3:12">
       <c r="C84" s="1">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="D84" s="10" t="s">
         <v>99</v>
@@ -3839,19 +3839,19 @@
         <v>100</v>
       </c>
       <c r="F84" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G84" s="1">
-        <v>3509</v>
+        <v>3009</v>
       </c>
       <c r="H84" s="1">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="I84" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J84" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K84" s="2">
         <v>1</v>
@@ -3859,36 +3859,36 @@
     </row>
     <row r="85" customHeight="1" spans="3:12">
       <c r="C85" s="1">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F85" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G85" s="1">
-        <v>4009</v>
+        <v>3509</v>
       </c>
       <c r="H85" s="1">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="I85" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J85" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K85" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:12">
       <c r="C86" s="1">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D86" s="10" t="s">
         <v>95</v>
@@ -3897,7 +3897,7 @@
         <v>96</v>
       </c>
       <c r="F86" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G86" s="1">
         <v>4009</v>
@@ -3909,7 +3909,7 @@
         <v>3</v>
       </c>
       <c r="J86" s="1">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K86" s="2">
         <v>2</v>
@@ -3917,7 +3917,7 @@
     </row>
     <row r="87" customHeight="1" spans="3:12">
       <c r="C87" s="1">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>97</v>
@@ -3926,7 +3926,7 @@
         <v>98</v>
       </c>
       <c r="F87" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G87" s="1">
         <v>4009</v>
@@ -3938,7 +3938,7 @@
         <v>3</v>
       </c>
       <c r="J87" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K87" s="2">
         <v>2</v>
@@ -3946,28 +3946,28 @@
     </row>
     <row r="88" customHeight="1" spans="3:12">
       <c r="C88" s="1">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F88" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G88" s="1">
-        <v>6009</v>
+        <v>4009</v>
       </c>
       <c r="H88" s="1">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="I88" s="1">
         <v>3</v>
       </c>
       <c r="J88" s="1">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K88" s="2">
         <v>2</v>
@@ -3975,7 +3975,7 @@
     </row>
     <row r="89" customHeight="1" spans="3:12">
       <c r="C89" s="1">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>95</v>
@@ -3984,7 +3984,7 @@
         <v>96</v>
       </c>
       <c r="F89" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G89" s="1">
         <v>6009</v>
@@ -3996,15 +3996,15 @@
         <v>3</v>
       </c>
       <c r="J89" s="1">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K89" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:12">
       <c r="C90" s="1">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D90" s="10" t="s">
         <v>97</v>
@@ -4013,7 +4013,7 @@
         <v>98</v>
       </c>
       <c r="F90" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G90" s="1">
         <v>6009</v>
@@ -4025,44 +4025,44 @@
         <v>3</v>
       </c>
       <c r="J90" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K90" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:12">
       <c r="C91" s="1">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F91" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G91" s="1">
-        <v>7009</v>
+        <v>6009</v>
       </c>
       <c r="H91" s="1">
-        <v>9000</v>
+        <v>7000</v>
       </c>
       <c r="I91" s="1">
         <v>3</v>
       </c>
       <c r="J91" s="1">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="K91" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:12">
       <c r="C92" s="1">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>95</v>
@@ -4071,7 +4071,7 @@
         <v>96</v>
       </c>
       <c r="F92" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G92" s="1">
         <v>7009</v>
@@ -4083,15 +4083,15 @@
         <v>3</v>
       </c>
       <c r="J92" s="1">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="K92" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:12">
       <c r="C93" s="1">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>97</v>
@@ -4100,7 +4100,7 @@
         <v>98</v>
       </c>
       <c r="F93" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G93" s="1">
         <v>7009</v>
@@ -4112,56 +4112,53 @@
         <v>3</v>
       </c>
       <c r="J93" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K93" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="95" customHeight="1" spans="3:12">
-      <c r="C95" s="1">
-        <v>10001</v>
-      </c>
-      <c r="D95" s="6">
-        <v>180001</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F95" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G95" s="1">
-        <v>100</v>
-      </c>
-      <c r="H95" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I95" s="1">
-        <v>100</v>
-      </c>
-      <c r="J95" s="1">
-        <v>1</v>
-      </c>
-      <c r="K95" s="2">
-        <v>1</v>
-      </c>
-      <c r="L95" s="1" t="s">
-        <v>102</v>
+    <row r="94" customHeight="1" spans="3:12">
+      <c r="C94" s="1">
+        <v>913</v>
+      </c>
+      <c r="D94" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F94" s="1">
+        <v>3</v>
+      </c>
+      <c r="G94" s="1">
+        <v>7009</v>
+      </c>
+      <c r="H94" s="1">
+        <v>9000</v>
+      </c>
+      <c r="I94" s="1">
+        <v>3</v>
+      </c>
+      <c r="J94" s="1">
+        <v>6</v>
+      </c>
+      <c r="K94" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:12">
       <c r="C96" s="1">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="D96" s="6">
-        <v>180002</v>
+        <v>180001</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>103</v>
       </c>
       <c r="F96" s="1">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G96" s="1">
         <v>100</v>
@@ -4179,21 +4176,21 @@
         <v>1</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:12">
       <c r="C97" s="1">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="D97" s="6">
-        <v>180003</v>
+        <v>180002</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F97" s="1">
-        <v>150000</v>
+        <v>4000</v>
       </c>
       <c r="G97" s="1">
         <v>100</v>
@@ -4205,27 +4202,27 @@
         <v>100</v>
       </c>
       <c r="J97" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K97" s="2">
         <v>1</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:12">
       <c r="C98" s="1">
-        <v>10004</v>
+        <v>10003</v>
       </c>
       <c r="D98" s="6">
-        <v>180004</v>
+        <v>180003</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F98" s="1">
-        <v>8000</v>
+        <v>150000</v>
       </c>
       <c r="G98" s="1">
         <v>100</v>
@@ -4237,27 +4234,27 @@
         <v>100</v>
       </c>
       <c r="J98" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K98" s="2">
         <v>1</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:12">
       <c r="C99" s="1">
-        <v>10005</v>
+        <v>10004</v>
       </c>
       <c r="D99" s="6">
-        <v>180005</v>
+        <v>180004</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F99" s="1">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="G99" s="1">
         <v>100</v>
@@ -4275,21 +4272,21 @@
         <v>1</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:12">
       <c r="C100" s="1">
-        <v>10006</v>
+        <v>10005</v>
       </c>
       <c r="D100" s="6">
-        <v>180006</v>
+        <v>180005</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F100" s="1">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="G100" s="1">
         <v>100</v>
@@ -4301,27 +4298,27 @@
         <v>100</v>
       </c>
       <c r="J100" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K100" s="2">
         <v>1</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:12">
       <c r="C101" s="1">
-        <v>10007</v>
+        <v>10006</v>
       </c>
       <c r="D101" s="6">
-        <v>180007</v>
+        <v>180006</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F101" s="1">
-        <v>2000</v>
+        <v>50000</v>
       </c>
       <c r="G101" s="1">
         <v>100</v>
@@ -4333,27 +4330,27 @@
         <v>100</v>
       </c>
       <c r="J101" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K101" s="2">
         <v>1</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:12">
       <c r="C102" s="1">
-        <v>10008</v>
+        <v>10007</v>
       </c>
       <c r="D102" s="6">
-        <v>180008</v>
+        <v>180007</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F102" s="1">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="G102" s="1">
         <v>100</v>
@@ -4365,27 +4362,27 @@
         <v>100</v>
       </c>
       <c r="J102" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K102" s="2">
         <v>1</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:12">
       <c r="C103" s="1">
-        <v>10009</v>
+        <v>10008</v>
       </c>
       <c r="D103" s="6">
-        <v>180009</v>
+        <v>180008</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F103" s="1">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="G103" s="1">
         <v>100</v>
@@ -4397,27 +4394,27 @@
         <v>100</v>
       </c>
       <c r="J103" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K103" s="2">
         <v>1</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:12">
       <c r="C104" s="1">
-        <v>10010</v>
+        <v>10009</v>
       </c>
       <c r="D104" s="6">
-        <v>180010</v>
+        <v>180009</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F104" s="1">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="G104" s="1">
         <v>100</v>
@@ -4435,21 +4432,21 @@
         <v>1</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:12">
       <c r="C105" s="1">
-        <v>10011</v>
+        <v>10010</v>
       </c>
       <c r="D105" s="6">
-        <v>180011</v>
+        <v>180010</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F105" s="1">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="G105" s="1">
         <v>100</v>
@@ -4461,24 +4458,24 @@
         <v>100</v>
       </c>
       <c r="J105" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K105" s="2">
         <v>1</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:12">
       <c r="C106" s="1">
-        <v>10012</v>
+        <v>10011</v>
       </c>
       <c r="D106" s="6">
-        <v>180012</v>
+        <v>180011</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F106" s="1">
         <v>100000</v>
@@ -4499,21 +4496,21 @@
         <v>1</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:12">
       <c r="C107" s="1">
-        <v>10013</v>
+        <v>10012</v>
       </c>
       <c r="D107" s="6">
-        <v>180013</v>
+        <v>180012</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F107" s="1">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="G107" s="1">
         <v>100</v>
@@ -4531,21 +4528,21 @@
         <v>1</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:12">
       <c r="C108" s="1">
-        <v>10014</v>
+        <v>10013</v>
       </c>
       <c r="D108" s="6">
-        <v>180014</v>
+        <v>180013</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F108" s="1">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G108" s="1">
         <v>100</v>
@@ -4563,18 +4560,18 @@
         <v>1</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:12">
       <c r="C109" s="1">
-        <v>10015</v>
+        <v>10014</v>
       </c>
       <c r="D109" s="6">
-        <v>180015</v>
+        <v>180014</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F109" s="1">
         <v>100000</v>
@@ -4595,21 +4592,21 @@
         <v>1</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:12">
       <c r="C110" s="1">
-        <v>10016</v>
+        <v>10015</v>
       </c>
       <c r="D110" s="6">
-        <v>180020</v>
+        <v>180015</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F110" s="1">
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="G110" s="1">
         <v>100</v>
@@ -4621,24 +4618,24 @@
         <v>100</v>
       </c>
       <c r="J110" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K110" s="2">
         <v>1</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:12">
       <c r="C111" s="1">
-        <v>10017</v>
+        <v>10016</v>
       </c>
       <c r="D111" s="6">
-        <v>180021</v>
+        <v>180020</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F111" s="1">
         <v>30000</v>
@@ -4659,21 +4656,21 @@
         <v>1</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:12">
       <c r="C112" s="1">
-        <v>10018</v>
+        <v>10017</v>
       </c>
       <c r="D112" s="6">
-        <v>180022</v>
+        <v>180021</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F112" s="1">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="G112" s="1">
         <v>100</v>
@@ -4685,65 +4682,65 @@
         <v>100</v>
       </c>
       <c r="J112" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K112" s="2">
         <v>1</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="114" customHeight="1" spans="1:12">
-      <c r="C114" s="1">
-        <v>10030</v>
-      </c>
-      <c r="D114" s="1">
-        <v>180030</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F114" s="1">
-        <v>5</v>
-      </c>
-      <c r="G114" s="1">
-        <v>1100</v>
-      </c>
-      <c r="H114" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I114" s="1">
-        <v>100</v>
-      </c>
-      <c r="J114" s="1">
-        <v>1</v>
-      </c>
-      <c r="K114" s="2">
-        <v>1</v>
-      </c>
-      <c r="L114" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="1:12">
+      <c r="C113" s="1">
+        <v>10018</v>
+      </c>
+      <c r="D113" s="6">
+        <v>180022</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>121</v>
+      </c>
+      <c r="F113" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G113" s="1">
+        <v>100</v>
+      </c>
+      <c r="H113" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I113" s="1">
+        <v>100</v>
+      </c>
+      <c r="J113" s="1">
+        <v>1</v>
+      </c>
+      <c r="K113" s="2">
+        <v>1</v>
+      </c>
+      <c r="L113" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="1:12">
       <c r="C115" s="1">
-        <v>10031</v>
-      </c>
-      <c r="D115" s="6">
-        <v>180032</v>
+        <v>10030</v>
+      </c>
+      <c r="D115" s="1">
+        <v>180030</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>122</v>
       </c>
       <c r="F115" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G115" s="1">
         <v>1100</v>
       </c>
       <c r="H115" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I115" s="1">
         <v>100</v>
@@ -4755,24 +4752,24 @@
         <v>1</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="1:12">
       <c r="C116" s="1">
-        <v>10032</v>
+        <v>10031</v>
       </c>
       <c r="D116" s="6">
-        <v>180033</v>
+        <v>180032</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F116" s="1">
         <v>1</v>
       </c>
       <c r="G116" s="1">
-        <v>1600</v>
+        <v>1100</v>
       </c>
       <c r="H116" s="1">
         <v>2000</v>
@@ -4787,27 +4784,27 @@
         <v>1</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="1:12">
       <c r="C117" s="1">
-        <v>10033</v>
+        <v>10032</v>
       </c>
       <c r="D117" s="6">
-        <v>180034</v>
+        <v>180033</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F117" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G117" s="1">
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="H117" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I117" s="1">
         <v>100</v>
@@ -4819,27 +4816,27 @@
         <v>1</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="1:12">
       <c r="C118" s="1">
-        <v>10034</v>
+        <v>10033</v>
       </c>
       <c r="D118" s="6">
-        <v>180035</v>
+        <v>180034</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F118" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G118" s="1">
-        <v>2000</v>
+        <v>1100</v>
       </c>
       <c r="H118" s="1">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I118" s="1">
         <v>100</v>
@@ -4851,18 +4848,18 @@
         <v>1</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="1:12">
       <c r="C119" s="1">
-        <v>10035</v>
+        <v>10034</v>
       </c>
       <c r="D119" s="6">
-        <v>180036</v>
+        <v>180035</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F119" s="1">
         <v>1</v>
@@ -4883,28 +4880,28 @@
         <v>1</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="1:12">
       <c r="C120" s="1">
-        <v>10036</v>
+        <v>10035</v>
       </c>
       <c r="D120" s="6">
-        <v>180037</v>
+        <v>180036</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F120" s="1">
         <v>1</v>
       </c>
       <c r="G120" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H120" s="1">
         <v>2500</v>
       </c>
-      <c r="H120" s="1">
-        <v>3500</v>
-      </c>
       <c r="I120" s="1">
         <v>100</v>
       </c>
@@ -4915,24 +4912,24 @@
         <v>1</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="121" customHeight="1" spans="1:12">
       <c r="C121" s="1">
-        <v>10037</v>
+        <v>10036</v>
       </c>
       <c r="D121" s="6">
-        <v>180038</v>
+        <v>180037</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F121" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G121" s="1">
-        <v>1600</v>
+        <v>2500</v>
       </c>
       <c r="H121" s="1">
         <v>3500</v>
@@ -4947,24 +4944,24 @@
         <v>1</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="122" customHeight="1" spans="1:12">
       <c r="C122" s="1">
-        <v>10038</v>
+        <v>10037</v>
       </c>
       <c r="D122" s="6">
-        <v>180039</v>
+        <v>180038</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F122" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G122" s="1">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="H122" s="1">
         <v>3500</v>
@@ -4979,66 +4976,66 @@
         <v>1</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="123" customHeight="1" spans="1:12">
-      <c r="A123" s="1" t="s">
+      <c r="C123" s="1">
+        <v>10038</v>
+      </c>
+      <c r="D123" s="6">
+        <v>180039</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F123" s="1">
+        <v>3</v>
+      </c>
+      <c r="G123" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H123" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I123" s="1">
+        <v>100</v>
+      </c>
+      <c r="J123" s="1">
+        <v>1</v>
+      </c>
+      <c r="K123" s="2">
+        <v>1</v>
+      </c>
+      <c r="L123" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="1:12">
+      <c r="A124" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B124" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C123" s="1">
+      <c r="C124" s="1">
         <v>10039</v>
       </c>
-      <c r="D123" s="6">
+      <c r="D124" s="6">
         <v>180040</v>
       </c>
-      <c r="E123" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F123" s="1">
+      <c r="E124" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F124" s="1">
         <v>2</v>
       </c>
-      <c r="G123" s="1">
+      <c r="G124" s="1">
         <v>3000</v>
       </c>
-      <c r="H123" s="1">
+      <c r="H124" s="1">
         <v>4000</v>
       </c>
-      <c r="I123" s="1">
-        <v>100</v>
-      </c>
-      <c r="J123" s="1">
-        <v>1</v>
-      </c>
-      <c r="K123" s="2">
-        <v>1</v>
-      </c>
-      <c r="L123" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="124" customHeight="1" spans="1:12">
-      <c r="C124" s="1">
-        <v>10040</v>
-      </c>
-      <c r="D124" s="6">
-        <v>180041</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F124" s="1">
-        <v>3</v>
-      </c>
-      <c r="G124" s="1">
-        <v>4000</v>
-      </c>
-      <c r="H124" s="1">
-        <v>5000</v>
-      </c>
       <c r="I124" s="1">
         <v>100</v>
       </c>
@@ -5049,76 +5046,76 @@
         <v>1</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="125" customHeight="1" spans="1:12">
       <c r="C125" s="1">
-        <v>10041</v>
+        <v>10040</v>
       </c>
       <c r="D125" s="6">
-        <v>180042</v>
+        <v>180041</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F125" s="1">
         <v>3</v>
       </c>
       <c r="G125" s="1">
+        <v>4000</v>
+      </c>
+      <c r="H125" s="1">
         <v>5000</v>
       </c>
-      <c r="H125" s="1">
+      <c r="I125" s="1">
+        <v>100</v>
+      </c>
+      <c r="J125" s="1">
+        <v>1</v>
+      </c>
+      <c r="K125" s="2">
+        <v>1</v>
+      </c>
+      <c r="L125" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="1:12">
+      <c r="C126" s="1">
+        <v>10041</v>
+      </c>
+      <c r="D126" s="6">
+        <v>180042</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F126" s="1">
+        <v>3</v>
+      </c>
+      <c r="G126" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H126" s="1">
         <v>6000</v>
       </c>
-      <c r="I125" s="1">
-        <v>100</v>
-      </c>
-      <c r="J125" s="1">
-        <v>1</v>
-      </c>
-      <c r="K125" s="2">
-        <v>1</v>
-      </c>
-      <c r="L125" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="127" customHeight="1" spans="1:12">
-      <c r="C127" s="1">
-        <v>11001</v>
-      </c>
-      <c r="D127" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F127" s="1">
-        <v>5</v>
-      </c>
-      <c r="G127" s="1">
-        <v>150</v>
-      </c>
-      <c r="H127" s="1">
-        <v>1200</v>
-      </c>
-      <c r="I127" s="1">
-        <v>20</v>
-      </c>
-      <c r="J127" s="1">
-        <v>2</v>
-      </c>
-      <c r="K127" s="2">
-        <v>1</v>
-      </c>
-      <c r="L127" s="1" t="s">
-        <v>39</v>
+      <c r="I126" s="1">
+        <v>100</v>
+      </c>
+      <c r="J126" s="1">
+        <v>1</v>
+      </c>
+      <c r="K126" s="2">
+        <v>1</v>
+      </c>
+      <c r="L126" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="128" customHeight="1" spans="1:12">
       <c r="C128" s="1">
-        <v>11002</v>
+        <v>11001</v>
       </c>
       <c r="D128" s="9" t="s">
         <v>135</v>
@@ -5130,13 +5127,13 @@
         <v>5</v>
       </c>
       <c r="G128" s="1">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H128" s="1">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="I128" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J128" s="1">
         <v>2</v>
@@ -5150,7 +5147,7 @@
     </row>
     <row r="129" customHeight="1" spans="3:12">
       <c r="C129" s="1">
-        <v>11003</v>
+        <v>11002</v>
       </c>
       <c r="D129" s="9" t="s">
         <v>137</v>
@@ -5159,16 +5156,16 @@
         <v>138</v>
       </c>
       <c r="F129" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G129" s="1">
-        <v>1050</v>
+        <v>200</v>
       </c>
       <c r="H129" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I129" s="1">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="J129" s="1">
         <v>2</v>
@@ -5182,25 +5179,25 @@
     </row>
     <row r="130" customHeight="1" spans="3:12">
       <c r="C130" s="1">
-        <v>11004</v>
+        <v>11003</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F130" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G130" s="1">
-        <v>4001</v>
+        <v>1050</v>
       </c>
       <c r="H130" s="1">
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="I130" s="1">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="J130" s="1">
         <v>2</v>
@@ -5214,54 +5211,54 @@
     </row>
     <row r="131" customHeight="1" spans="3:12">
       <c r="C131" s="1">
-        <v>11005</v>
+        <v>11004</v>
       </c>
       <c r="D131" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="E131" s="7" t="s">
+      <c r="E131" s="1" t="s">
         <v>140</v>
       </c>
       <c r="F131" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G131" s="1">
-        <v>101</v>
+        <v>4001</v>
       </c>
       <c r="H131" s="1">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="I131" s="1">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="J131" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K131" s="2">
         <v>1</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>141</v>
+        <v>39</v>
       </c>
     </row>
     <row r="132" customHeight="1" spans="3:12">
       <c r="C132" s="1">
-        <v>11006</v>
+        <v>11005</v>
       </c>
       <c r="D132" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E132" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="E132" s="7" t="s">
-        <v>143</v>
-      </c>
       <c r="F132" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G132" s="1">
-        <v>501</v>
+        <v>101</v>
       </c>
       <c r="H132" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="I132" s="1">
         <v>10</v>
@@ -5273,59 +5270,59 @@
         <v>1</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="133" customHeight="1" spans="3:12">
       <c r="C133" s="1">
-        <v>11007</v>
+        <v>11006</v>
       </c>
       <c r="D133" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E133" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E133" s="7" t="s">
+      <c r="F133" s="1">
+        <v>15</v>
+      </c>
+      <c r="G133" s="1">
+        <v>501</v>
+      </c>
+      <c r="H133" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I133" s="1">
+        <v>10</v>
+      </c>
+      <c r="J133" s="1">
+        <v>1</v>
+      </c>
+      <c r="K133" s="2">
+        <v>1</v>
+      </c>
+      <c r="L133" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="F133" s="1">
-        <v>10</v>
-      </c>
-      <c r="G133" s="1">
-        <v>1001</v>
-      </c>
-      <c r="H133" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I133" s="1">
-        <v>20</v>
-      </c>
-      <c r="J133" s="1">
-        <v>1</v>
-      </c>
-      <c r="K133" s="2">
-        <v>1</v>
-      </c>
-      <c r="L133" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="3:12">
       <c r="C134" s="1">
-        <v>11008</v>
+        <v>11007</v>
       </c>
       <c r="D134" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="E134" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E134" s="7" t="s">
-        <v>149</v>
-      </c>
       <c r="F134" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G134" s="1">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H134" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I134" s="1">
         <v>20</v>
@@ -5337,59 +5334,59 @@
         <v>1</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="135" customHeight="1" spans="3:12">
       <c r="C135" s="1">
-        <v>11009</v>
+        <v>11008</v>
       </c>
       <c r="D135" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="E135" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="E135" s="7" t="s">
+      <c r="F135" s="1">
+        <v>8</v>
+      </c>
+      <c r="G135" s="1">
+        <v>1501</v>
+      </c>
+      <c r="H135" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I135" s="1">
+        <v>20</v>
+      </c>
+      <c r="J135" s="1">
+        <v>1</v>
+      </c>
+      <c r="K135" s="2">
+        <v>1</v>
+      </c>
+      <c r="L135" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="F135" s="1">
-        <v>15</v>
-      </c>
-      <c r="G135" s="1">
-        <v>2001</v>
-      </c>
-      <c r="H135" s="1">
-        <v>2500</v>
-      </c>
-      <c r="I135" s="1">
-        <v>52</v>
-      </c>
-      <c r="J135" s="1">
-        <v>1</v>
-      </c>
-      <c r="K135" s="2">
-        <v>1</v>
-      </c>
-      <c r="L135" s="1" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="3:12">
       <c r="C136" s="1">
-        <v>11010</v>
+        <v>11009</v>
       </c>
       <c r="D136" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E136" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="E136" s="7" t="s">
-        <v>155</v>
-      </c>
       <c r="F136" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G136" s="1">
-        <v>2501</v>
+        <v>2001</v>
       </c>
       <c r="H136" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I136" s="1">
         <v>52</v>
@@ -5401,123 +5398,126 @@
         <v>1</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="137" customHeight="1" spans="3:12">
       <c r="C137" s="1">
-        <v>11011</v>
+        <v>11010</v>
       </c>
       <c r="D137" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E137" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="E137" s="7" t="s">
+      <c r="F137" s="1">
+        <v>7</v>
+      </c>
+      <c r="G137" s="1">
+        <v>2501</v>
+      </c>
+      <c r="H137" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I137" s="1">
+        <v>52</v>
+      </c>
+      <c r="J137" s="1">
+        <v>1</v>
+      </c>
+      <c r="K137" s="2">
+        <v>1</v>
+      </c>
+      <c r="L137" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="F137" s="1">
-        <v>3</v>
-      </c>
-      <c r="G137" s="1">
-        <v>3001</v>
-      </c>
-      <c r="H137" s="1">
-        <v>3800</v>
-      </c>
-      <c r="I137" s="1">
-        <v>62</v>
-      </c>
-      <c r="J137" s="1">
-        <v>1</v>
-      </c>
-      <c r="K137" s="2">
-        <v>1</v>
-      </c>
-      <c r="L137" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="3:12">
       <c r="C138" s="1">
-        <v>11012</v>
+        <v>11011</v>
       </c>
       <c r="D138" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E138" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="E138" s="7" t="s">
+      <c r="F138" s="1">
+        <v>3</v>
+      </c>
+      <c r="G138" s="1">
+        <v>3001</v>
+      </c>
+      <c r="H138" s="1">
+        <v>3800</v>
+      </c>
+      <c r="I138" s="1">
+        <v>62</v>
+      </c>
+      <c r="J138" s="1">
+        <v>1</v>
+      </c>
+      <c r="K138" s="2">
+        <v>1</v>
+      </c>
+      <c r="L138" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="F138" s="2">
-        <v>1</v>
-      </c>
-      <c r="G138" s="2">
-        <v>5001</v>
-      </c>
-      <c r="H138" s="2">
-        <v>6000</v>
-      </c>
-      <c r="I138" s="2">
-        <v>61</v>
-      </c>
-      <c r="J138" s="2">
-        <v>1</v>
-      </c>
-      <c r="K138" s="2">
-        <v>1</v>
-      </c>
-      <c r="L138" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="3:12">
       <c r="C139" s="1">
-        <v>11013</v>
+        <v>11012</v>
       </c>
       <c r="D139" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="E139" s="1" t="s">
+      <c r="E139" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F139" s="1">
-        <v>3</v>
-      </c>
-      <c r="G139" s="1">
-        <v>5501</v>
-      </c>
-      <c r="H139" s="1">
+      <c r="F139" s="2">
+        <v>1</v>
+      </c>
+      <c r="G139" s="2">
+        <v>5001</v>
+      </c>
+      <c r="H139" s="2">
         <v>6000</v>
       </c>
-      <c r="I139" s="1">
-        <v>43</v>
-      </c>
-      <c r="J139" s="1">
+      <c r="I139" s="2">
+        <v>61</v>
+      </c>
+      <c r="J139" s="2">
         <v>1</v>
       </c>
       <c r="K139" s="2">
         <v>1</v>
+      </c>
+      <c r="L139" s="1" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="3:12">
       <c r="C140" s="1">
-        <v>11014</v>
+        <v>11013</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="E140" s="7" t="s">
-        <v>158</v>
+        <v>164</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="F140" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G140" s="1">
         <v>5501</v>
       </c>
       <c r="H140" s="1">
-        <v>6500</v>
+        <v>6000</v>
       </c>
       <c r="I140" s="1">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="J140" s="1">
         <v>1</v>
@@ -5528,68 +5528,65 @@
     </row>
     <row r="141" customHeight="1" spans="3:12">
       <c r="C141" s="1">
+        <v>11014</v>
+      </c>
+      <c r="D141" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E141" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F141" s="1">
+        <v>2</v>
+      </c>
+      <c r="G141" s="1">
+        <v>5501</v>
+      </c>
+      <c r="H141" s="1">
+        <v>6500</v>
+      </c>
+      <c r="I141" s="1">
+        <v>67</v>
+      </c>
+      <c r="J141" s="1">
+        <v>1</v>
+      </c>
+      <c r="K141" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" spans="3:12">
+      <c r="C142" s="1">
         <v>11015</v>
       </c>
-      <c r="D141" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="E141" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="F141" s="1">
-        <v>1</v>
-      </c>
-      <c r="G141" s="1">
+      <c r="D142" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="E142" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="F142" s="1">
+        <v>1</v>
+      </c>
+      <c r="G142" s="1">
         <v>6401</v>
       </c>
-      <c r="H141" s="1">
+      <c r="H142" s="1">
         <v>7400</v>
       </c>
-      <c r="I141" s="1">
+      <c r="I142" s="1">
         <v>91</v>
       </c>
-      <c r="J141" s="1">
-        <v>1</v>
-      </c>
-      <c r="K141" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" customHeight="1" spans="3:12">
-      <c r="C144" s="1">
-        <v>11303</v>
-      </c>
-      <c r="D144" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="E144" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="F144" s="1">
-        <v>10</v>
-      </c>
-      <c r="G144" s="1">
-        <v>3903</v>
-      </c>
-      <c r="H144" s="1">
-        <v>4402</v>
-      </c>
-      <c r="I144" s="1">
-        <v>37</v>
-      </c>
-      <c r="J144" s="1">
-        <v>1</v>
-      </c>
-      <c r="K144" s="2">
-        <v>1</v>
-      </c>
-      <c r="L144" s="1" t="s">
-        <v>141</v>
+      <c r="J142" s="1">
+        <v>1</v>
+      </c>
+      <c r="K142" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="145" customHeight="1" spans="3:12">
       <c r="C145" s="1">
-        <v>11304</v>
+        <v>11303</v>
       </c>
       <c r="D145" s="9" t="s">
         <v>168</v>
@@ -5598,16 +5595,16 @@
         <v>169</v>
       </c>
       <c r="F145" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G145" s="1">
-        <v>4403</v>
+        <v>3903</v>
       </c>
       <c r="H145" s="1">
-        <v>4902</v>
+        <v>4402</v>
       </c>
       <c r="I145" s="1">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J145" s="1">
         <v>1</v>
@@ -5616,12 +5613,12 @@
         <v>1</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="146" customHeight="1" spans="3:12">
       <c r="C146" s="1">
-        <v>11305</v>
+        <v>11304</v>
       </c>
       <c r="D146" s="9" t="s">
         <v>170</v>
@@ -5630,16 +5627,16 @@
         <v>171</v>
       </c>
       <c r="F146" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G146" s="1">
-        <v>4903</v>
+        <v>4403</v>
       </c>
       <c r="H146" s="1">
-        <v>5402</v>
+        <v>4902</v>
       </c>
       <c r="I146" s="1">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J146" s="1">
         <v>1</v>
@@ -5648,12 +5645,12 @@
         <v>1</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="147" customHeight="1" spans="3:12">
       <c r="C147" s="1">
-        <v>11306</v>
+        <v>11305</v>
       </c>
       <c r="D147" s="9" t="s">
         <v>172</v>
@@ -5662,16 +5659,16 @@
         <v>173</v>
       </c>
       <c r="F147" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G147" s="1">
-        <v>5403</v>
+        <v>4903</v>
       </c>
       <c r="H147" s="1">
-        <v>6402</v>
+        <v>5402</v>
       </c>
       <c r="I147" s="1">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J147" s="1">
         <v>1</v>
@@ -5680,12 +5677,12 @@
         <v>1</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="148" customHeight="1" spans="3:12">
       <c r="C148" s="1">
-        <v>11307</v>
+        <v>11306</v>
       </c>
       <c r="D148" s="9" t="s">
         <v>174</v>
@@ -5694,16 +5691,16 @@
         <v>175</v>
       </c>
       <c r="F148" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G148" s="1">
-        <v>6403</v>
+        <v>5403</v>
       </c>
       <c r="H148" s="1">
-        <v>7402</v>
+        <v>6402</v>
       </c>
       <c r="I148" s="1">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="J148" s="1">
         <v>1</v>
@@ -5712,12 +5709,12 @@
         <v>1</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="149" customHeight="1" spans="3:12">
       <c r="C149" s="1">
-        <v>11308</v>
+        <v>11307</v>
       </c>
       <c r="D149" s="9" t="s">
         <v>176</v>
@@ -5726,31 +5723,63 @@
         <v>177</v>
       </c>
       <c r="F149" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G149" s="1">
+        <v>6403</v>
+      </c>
+      <c r="H149" s="1">
+        <v>7402</v>
+      </c>
+      <c r="I149" s="1">
+        <v>61</v>
+      </c>
+      <c r="J149" s="1">
+        <v>1</v>
+      </c>
+      <c r="K149" s="2">
+        <v>1</v>
+      </c>
+      <c r="L149" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" spans="3:12">
+      <c r="C150" s="1">
+        <v>11308</v>
+      </c>
+      <c r="D150" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="F150" s="1">
+        <v>1</v>
+      </c>
+      <c r="G150" s="1">
         <v>7403</v>
       </c>
-      <c r="H149" s="1">
+      <c r="H150" s="1">
         <v>8402</v>
       </c>
-      <c r="I149" s="1">
+      <c r="I150" s="1">
         <v>79</v>
       </c>
-      <c r="J149" s="1">
-        <v>1</v>
-      </c>
-      <c r="K149" s="2">
-        <v>1</v>
-      </c>
-      <c r="L149" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="150" customHeight="1" spans="3:12">
-      <c r="D150" s="5"/>
-      <c r="E150" s="7"/>
-      <c r="K150" s="2"/>
+      <c r="J150" s="1">
+        <v>1</v>
+      </c>
+      <c r="K150" s="2">
+        <v>1</v>
+      </c>
+      <c r="L150" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="151" customHeight="1" spans="3:12">
+      <c r="D151" s="5"/>
+      <c r="E151" s="7"/>
+      <c r="K151" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -2464,19 +2464,19 @@
         <v>65</v>
       </c>
       <c r="F30" s="2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G30" s="2">
         <v>4215</v>
       </c>
       <c r="H30" s="2">
-        <v>6000</v>
+        <v>7400</v>
       </c>
       <c r="I30" s="2">
         <v>3</v>
       </c>
       <c r="J30" s="2">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K30" s="2">
         <v>1</v>
@@ -2493,7 +2493,7 @@
         <v>45</v>
       </c>
       <c r="F31" s="1">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G31" s="2">
         <v>6001</v>
@@ -2505,7 +2505,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K31" s="2">
         <v>1</v>
@@ -2580,10 +2580,10 @@
         <v>70</v>
       </c>
       <c r="F34" s="2">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="G34" s="2">
-        <v>7515</v>
+        <v>7415</v>
       </c>
       <c r="H34" s="2">
         <v>9000</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="183">
   <si>
     <t>#</t>
   </si>
@@ -468,6 +468,9 @@
     <t>极·炼神证明</t>
   </si>
   <si>
+    <t>极·炼魂证明</t>
+  </si>
+  <si>
     <t>220016</t>
   </si>
   <si>
@@ -565,6 +568,12 @@
   </si>
   <si>
     <t>粉色宠物</t>
+  </si>
+  <si>
+    <t>220044</t>
+  </si>
+  <si>
+    <t>六大道戒</t>
   </si>
   <si>
     <t>220303</t>
@@ -1597,7 +1606,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M151"/>
+  <dimension ref="A1:M152"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -5113,59 +5122,59 @@
         <v>123</v>
       </c>
     </row>
-    <row r="128" customHeight="1" spans="1:12">
-      <c r="C128" s="1">
-        <v>11001</v>
-      </c>
-      <c r="D128" s="9" t="s">
+    <row r="127" customHeight="1" spans="1:12">
+      <c r="C127" s="1">
+        <v>10042</v>
+      </c>
+      <c r="D127" s="6">
+        <v>180043</v>
+      </c>
+      <c r="E127" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E128" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="F128" s="1">
-        <v>5</v>
-      </c>
-      <c r="G128" s="1">
-        <v>150</v>
-      </c>
-      <c r="H128" s="1">
-        <v>1200</v>
-      </c>
-      <c r="I128" s="1">
-        <v>20</v>
-      </c>
-      <c r="J128" s="1">
-        <v>2</v>
-      </c>
-      <c r="K128" s="2">
-        <v>1</v>
-      </c>
-      <c r="L128" s="1" t="s">
-        <v>39</v>
+      <c r="F127" s="1">
+        <v>3</v>
+      </c>
+      <c r="G127" s="1">
+        <v>6000</v>
+      </c>
+      <c r="H127" s="1">
+        <v>7000</v>
+      </c>
+      <c r="I127" s="1">
+        <v>100</v>
+      </c>
+      <c r="J127" s="1">
+        <v>1</v>
+      </c>
+      <c r="K127" s="2">
+        <v>1</v>
+      </c>
+      <c r="L127" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="129" customHeight="1" spans="3:12">
       <c r="C129" s="1">
-        <v>11002</v>
+        <v>11001</v>
       </c>
       <c r="D129" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="F129" s="1">
         <v>5</v>
       </c>
       <c r="G129" s="1">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H129" s="1">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="I129" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J129" s="1">
         <v>2</v>
@@ -5179,25 +5188,25 @@
     </row>
     <row r="130" customHeight="1" spans="3:12">
       <c r="C130" s="1">
-        <v>11003</v>
+        <v>11002</v>
       </c>
       <c r="D130" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E130" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E130" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F130" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G130" s="1">
-        <v>1050</v>
+        <v>200</v>
       </c>
       <c r="H130" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I130" s="1">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="J130" s="1">
         <v>2</v>
@@ -5211,25 +5220,25 @@
     </row>
     <row r="131" customHeight="1" spans="3:12">
       <c r="C131" s="1">
-        <v>11004</v>
+        <v>11003</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F131" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G131" s="1">
-        <v>4001</v>
+        <v>1050</v>
       </c>
       <c r="H131" s="1">
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="I131" s="1">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="J131" s="1">
         <v>2</v>
@@ -5243,54 +5252,54 @@
     </row>
     <row r="132" customHeight="1" spans="3:12">
       <c r="C132" s="1">
-        <v>11005</v>
+        <v>11004</v>
       </c>
       <c r="D132" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E132" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E132" s="7" t="s">
-        <v>142</v>
-      </c>
       <c r="F132" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G132" s="1">
-        <v>101</v>
+        <v>4001</v>
       </c>
       <c r="H132" s="1">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="I132" s="1">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="J132" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K132" s="2">
         <v>1</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>143</v>
+        <v>39</v>
       </c>
     </row>
     <row r="133" customHeight="1" spans="3:12">
       <c r="C133" s="1">
-        <v>11006</v>
+        <v>11005</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F133" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G133" s="1">
-        <v>501</v>
+        <v>101</v>
       </c>
       <c r="H133" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="I133" s="1">
         <v>10</v>
@@ -5302,59 +5311,59 @@
         <v>1</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="3:12">
       <c r="C134" s="1">
-        <v>11007</v>
+        <v>11006</v>
       </c>
       <c r="D134" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="E134" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F134" s="1">
+        <v>15</v>
+      </c>
+      <c r="G134" s="1">
+        <v>501</v>
+      </c>
+      <c r="H134" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I134" s="1">
+        <v>10</v>
+      </c>
+      <c r="J134" s="1">
+        <v>1</v>
+      </c>
+      <c r="K134" s="2">
+        <v>1</v>
+      </c>
+      <c r="L134" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="E134" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="F134" s="1">
-        <v>10</v>
-      </c>
-      <c r="G134" s="1">
-        <v>1001</v>
-      </c>
-      <c r="H134" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I134" s="1">
-        <v>20</v>
-      </c>
-      <c r="J134" s="1">
-        <v>1</v>
-      </c>
-      <c r="K134" s="2">
-        <v>1</v>
-      </c>
-      <c r="L134" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="135" customHeight="1" spans="3:12">
       <c r="C135" s="1">
-        <v>11008</v>
+        <v>11007</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F135" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G135" s="1">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H135" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I135" s="1">
         <v>20</v>
@@ -5366,59 +5375,59 @@
         <v>1</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="3:12">
       <c r="C136" s="1">
-        <v>11009</v>
+        <v>11008</v>
       </c>
       <c r="D136" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E136" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F136" s="1">
+        <v>8</v>
+      </c>
+      <c r="G136" s="1">
+        <v>1501</v>
+      </c>
+      <c r="H136" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I136" s="1">
+        <v>20</v>
+      </c>
+      <c r="J136" s="1">
+        <v>1</v>
+      </c>
+      <c r="K136" s="2">
+        <v>1</v>
+      </c>
+      <c r="L136" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="E136" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="F136" s="1">
-        <v>15</v>
-      </c>
-      <c r="G136" s="1">
-        <v>2001</v>
-      </c>
-      <c r="H136" s="1">
-        <v>2500</v>
-      </c>
-      <c r="I136" s="1">
-        <v>52</v>
-      </c>
-      <c r="J136" s="1">
-        <v>1</v>
-      </c>
-      <c r="K136" s="2">
-        <v>1</v>
-      </c>
-      <c r="L136" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="137" customHeight="1" spans="3:12">
       <c r="C137" s="1">
-        <v>11010</v>
+        <v>11009</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F137" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G137" s="1">
-        <v>2501</v>
+        <v>2001</v>
       </c>
       <c r="H137" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I137" s="1">
         <v>52</v>
@@ -5430,114 +5439,117 @@
         <v>1</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="3:12">
       <c r="C138" s="1">
-        <v>11011</v>
+        <v>11010</v>
       </c>
       <c r="D138" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F138" s="1">
+        <v>7</v>
+      </c>
+      <c r="G138" s="1">
+        <v>2501</v>
+      </c>
+      <c r="H138" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I138" s="1">
+        <v>52</v>
+      </c>
+      <c r="J138" s="1">
+        <v>1</v>
+      </c>
+      <c r="K138" s="2">
+        <v>1</v>
+      </c>
+      <c r="L138" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="E138" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="F138" s="1">
-        <v>3</v>
-      </c>
-      <c r="G138" s="1">
-        <v>3001</v>
-      </c>
-      <c r="H138" s="1">
-        <v>3800</v>
-      </c>
-      <c r="I138" s="1">
-        <v>62</v>
-      </c>
-      <c r="J138" s="1">
-        <v>1</v>
-      </c>
-      <c r="K138" s="2">
-        <v>1</v>
-      </c>
-      <c r="L138" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="3:12">
       <c r="C139" s="1">
-        <v>11012</v>
+        <v>11011</v>
       </c>
       <c r="D139" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="F139" s="1">
+        <v>3</v>
+      </c>
+      <c r="G139" s="1">
+        <v>3001</v>
+      </c>
+      <c r="H139" s="1">
+        <v>3800</v>
+      </c>
+      <c r="I139" s="1">
+        <v>62</v>
+      </c>
+      <c r="J139" s="1">
+        <v>1</v>
+      </c>
+      <c r="K139" s="2">
+        <v>1</v>
+      </c>
+      <c r="L139" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="E139" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="F139" s="2">
-        <v>1</v>
-      </c>
-      <c r="G139" s="2">
-        <v>5001</v>
-      </c>
-      <c r="H139" s="2">
-        <v>6000</v>
-      </c>
-      <c r="I139" s="2">
-        <v>61</v>
-      </c>
-      <c r="J139" s="2">
-        <v>1</v>
-      </c>
-      <c r="K139" s="2">
-        <v>1</v>
-      </c>
-      <c r="L139" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="3:12">
       <c r="C140" s="1">
-        <v>11013</v>
+        <v>11012</v>
       </c>
       <c r="D140" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="E140" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="E140" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F140" s="1">
-        <v>3</v>
-      </c>
-      <c r="G140" s="1">
-        <v>5501</v>
-      </c>
-      <c r="H140" s="1">
+      <c r="F140" s="2">
+        <v>1</v>
+      </c>
+      <c r="G140" s="2">
+        <v>5001</v>
+      </c>
+      <c r="H140" s="2">
         <v>6000</v>
       </c>
-      <c r="I140" s="1">
-        <v>43</v>
-      </c>
-      <c r="J140" s="1">
+      <c r="I140" s="2">
+        <v>61</v>
+      </c>
+      <c r="J140" s="2">
         <v>1</v>
       </c>
       <c r="K140" s="2">
         <v>1</v>
+      </c>
+      <c r="L140" s="1" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="141" customHeight="1" spans="3:12">
       <c r="C141" s="1">
-        <v>11014</v>
+        <v>11013</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E141" s="7" t="s">
-        <v>160</v>
+        <v>165</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="F141" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G141" s="1">
         <v>5501</v>
@@ -5546,7 +5558,7 @@
         <v>6500</v>
       </c>
       <c r="I141" s="1">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="J141" s="1">
         <v>1</v>
@@ -5557,86 +5569,112 @@
     </row>
     <row r="142" customHeight="1" spans="3:12">
       <c r="C142" s="1">
+        <v>11014</v>
+      </c>
+      <c r="D142" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E142" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="F142" s="1">
+        <v>2</v>
+      </c>
+      <c r="G142" s="1">
+        <v>5501</v>
+      </c>
+      <c r="H142" s="1">
+        <v>6500</v>
+      </c>
+      <c r="I142" s="1">
+        <v>67</v>
+      </c>
+      <c r="J142" s="1">
+        <v>1</v>
+      </c>
+      <c r="K142" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" spans="3:12">
+      <c r="C143" s="1">
         <v>11015</v>
       </c>
-      <c r="D142" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="E142" s="7" t="s">
+      <c r="D143" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="F142" s="1">
-        <v>1</v>
-      </c>
-      <c r="G142" s="1">
+      <c r="E143" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="F143" s="1">
+        <v>1</v>
+      </c>
+      <c r="G143" s="1">
         <v>6401</v>
       </c>
-      <c r="H142" s="1">
+      <c r="H143" s="1">
         <v>7400</v>
       </c>
-      <c r="I142" s="1">
+      <c r="I143" s="1">
         <v>91</v>
       </c>
-      <c r="J142" s="1">
-        <v>1</v>
-      </c>
-      <c r="K142" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" customHeight="1" spans="3:12">
-      <c r="C145" s="1">
-        <v>11303</v>
-      </c>
-      <c r="D145" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E145" s="7" t="s">
+      <c r="J143" s="1">
+        <v>1</v>
+      </c>
+      <c r="K143" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" spans="3:12">
+      <c r="C144" s="1">
+        <v>11016</v>
+      </c>
+      <c r="D144" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="F145" s="1">
-        <v>10</v>
-      </c>
-      <c r="G145" s="1">
-        <v>3903</v>
-      </c>
-      <c r="H145" s="1">
-        <v>4402</v>
-      </c>
-      <c r="I145" s="1">
-        <v>37</v>
-      </c>
-      <c r="J145" s="1">
-        <v>1</v>
-      </c>
-      <c r="K145" s="2">
-        <v>1</v>
-      </c>
-      <c r="L145" s="1" t="s">
-        <v>143</v>
+      <c r="E144" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F144" s="1">
+        <v>2</v>
+      </c>
+      <c r="G144" s="1">
+        <v>8001</v>
+      </c>
+      <c r="H144" s="1">
+        <v>9000</v>
+      </c>
+      <c r="I144" s="1">
+        <v>53</v>
+      </c>
+      <c r="J144" s="1">
+        <v>1</v>
+      </c>
+      <c r="K144" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="146" customHeight="1" spans="3:12">
       <c r="C146" s="1">
-        <v>11304</v>
+        <v>11303</v>
       </c>
       <c r="D146" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F146" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G146" s="1">
-        <v>4403</v>
+        <v>3903</v>
       </c>
       <c r="H146" s="1">
-        <v>4902</v>
+        <v>4402</v>
       </c>
       <c r="I146" s="1">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J146" s="1">
         <v>1</v>
@@ -5645,30 +5683,30 @@
         <v>1</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="147" customHeight="1" spans="3:12">
       <c r="C147" s="1">
-        <v>11305</v>
+        <v>11304</v>
       </c>
       <c r="D147" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F147" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G147" s="1">
-        <v>4903</v>
+        <v>4403</v>
       </c>
       <c r="H147" s="1">
-        <v>5402</v>
+        <v>4902</v>
       </c>
       <c r="I147" s="1">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J147" s="1">
         <v>1</v>
@@ -5677,30 +5715,30 @@
         <v>1</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="148" customHeight="1" spans="3:12">
       <c r="C148" s="1">
-        <v>11306</v>
+        <v>11305</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E148" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F148" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G148" s="1">
-        <v>5403</v>
+        <v>4903</v>
       </c>
       <c r="H148" s="1">
-        <v>6402</v>
+        <v>5402</v>
       </c>
       <c r="I148" s="1">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J148" s="1">
         <v>1</v>
@@ -5709,30 +5747,30 @@
         <v>1</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="149" customHeight="1" spans="3:12">
       <c r="C149" s="1">
-        <v>11307</v>
+        <v>11306</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F149" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G149" s="1">
-        <v>6403</v>
+        <v>5403</v>
       </c>
       <c r="H149" s="1">
-        <v>7402</v>
+        <v>6402</v>
       </c>
       <c r="I149" s="1">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="J149" s="1">
         <v>1</v>
@@ -5741,45 +5779,77 @@
         <v>1</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="150" customHeight="1" spans="3:12">
       <c r="C150" s="1">
+        <v>11307</v>
+      </c>
+      <c r="D150" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F150" s="1">
+        <v>3</v>
+      </c>
+      <c r="G150" s="1">
+        <v>6403</v>
+      </c>
+      <c r="H150" s="1">
+        <v>7402</v>
+      </c>
+      <c r="I150" s="1">
+        <v>61</v>
+      </c>
+      <c r="J150" s="1">
+        <v>1</v>
+      </c>
+      <c r="K150" s="2">
+        <v>1</v>
+      </c>
+      <c r="L150" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="151" customHeight="1" spans="3:12">
+      <c r="C151" s="1">
         <v>11308</v>
       </c>
-      <c r="D150" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E150" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="F150" s="1">
-        <v>1</v>
-      </c>
-      <c r="G150" s="1">
+      <c r="D151" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="F151" s="1">
+        <v>1</v>
+      </c>
+      <c r="G151" s="1">
         <v>7403</v>
       </c>
-      <c r="H150" s="1">
+      <c r="H151" s="1">
         <v>8402</v>
       </c>
-      <c r="I150" s="1">
+      <c r="I151" s="1">
         <v>79</v>
       </c>
-      <c r="J150" s="1">
-        <v>1</v>
-      </c>
-      <c r="K150" s="2">
-        <v>1</v>
-      </c>
-      <c r="L150" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="151" customHeight="1" spans="3:12">
-      <c r="D151" s="5"/>
-      <c r="E151" s="7"/>
-      <c r="K151" s="2"/>
+      <c r="J151" s="1">
+        <v>1</v>
+      </c>
+      <c r="K151" s="2">
+        <v>1</v>
+      </c>
+      <c r="L151" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" spans="3:12">
+      <c r="D152" s="5"/>
+      <c r="E152" s="7"/>
+      <c r="K152" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -61,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="185">
   <si>
     <t>#</t>
   </si>
@@ -469,6 +474,12 @@
   </si>
   <si>
     <t>极·炼魂证明</t>
+  </si>
+  <si>
+    <t>极戒之源</t>
+  </si>
+  <si>
+    <t>道戒之源</t>
   </si>
   <si>
     <t>220016</t>
@@ -1606,7 +1617,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M152"/>
+  <dimension ref="A1:M154"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -5154,91 +5165,91 @@
         <v>123</v>
       </c>
     </row>
+    <row r="128" customHeight="1" spans="1:12">
+      <c r="C128" s="1">
+        <v>10043</v>
+      </c>
+      <c r="D128" s="6">
+        <v>180044</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F128" s="1">
+        <v>3</v>
+      </c>
+      <c r="G128" s="1">
+        <v>7000</v>
+      </c>
+      <c r="H128" s="1">
+        <v>8000</v>
+      </c>
+      <c r="I128" s="1">
+        <v>100</v>
+      </c>
+      <c r="J128" s="1">
+        <v>1</v>
+      </c>
+      <c r="K128" s="2">
+        <v>1</v>
+      </c>
+      <c r="L128" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
     <row r="129" customHeight="1" spans="3:12">
       <c r="C129" s="1">
-        <v>11001</v>
-      </c>
-      <c r="D129" s="9" t="s">
-        <v>136</v>
+        <v>10044</v>
+      </c>
+      <c r="D129" s="6">
+        <v>180045</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>137</v>
       </c>
       <c r="F129" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G129" s="1">
-        <v>150</v>
+        <v>8000</v>
       </c>
       <c r="H129" s="1">
-        <v>1200</v>
+        <v>9000</v>
       </c>
       <c r="I129" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="J129" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K129" s="2">
         <v>1</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="130" customHeight="1" spans="3:12">
-      <c r="C130" s="1">
-        <v>11002</v>
-      </c>
-      <c r="D130" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F130" s="1">
-        <v>5</v>
-      </c>
-      <c r="G130" s="1">
-        <v>200</v>
-      </c>
-      <c r="H130" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I130" s="1">
-        <v>30</v>
-      </c>
-      <c r="J130" s="1">
-        <v>2</v>
-      </c>
-      <c r="K130" s="2">
-        <v>1</v>
-      </c>
-      <c r="L130" s="1" t="s">
-        <v>39</v>
+        <v>123</v>
       </c>
     </row>
     <row r="131" customHeight="1" spans="3:12">
       <c r="C131" s="1">
-        <v>11003</v>
+        <v>11001</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F131" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G131" s="1">
-        <v>1050</v>
+        <v>150</v>
       </c>
       <c r="H131" s="1">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="I131" s="1">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="J131" s="1">
         <v>2</v>
@@ -5252,7 +5263,7 @@
     </row>
     <row r="132" customHeight="1" spans="3:12">
       <c r="C132" s="1">
-        <v>11004</v>
+        <v>11002</v>
       </c>
       <c r="D132" s="9" t="s">
         <v>140</v>
@@ -5264,13 +5275,13 @@
         <v>5</v>
       </c>
       <c r="G132" s="1">
-        <v>4001</v>
+        <v>200</v>
       </c>
       <c r="H132" s="1">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="I132" s="1">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="J132" s="1">
         <v>2</v>
@@ -5284,90 +5295,90 @@
     </row>
     <row r="133" customHeight="1" spans="3:12">
       <c r="C133" s="1">
-        <v>11005</v>
+        <v>11003</v>
       </c>
       <c r="D133" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="E133" s="7" t="s">
+      <c r="E133" s="1" t="s">
         <v>143</v>
       </c>
       <c r="F133" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G133" s="1">
-        <v>101</v>
+        <v>1050</v>
       </c>
       <c r="H133" s="1">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="I133" s="1">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="J133" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K133" s="2">
         <v>1</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>144</v>
+        <v>39</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="3:12">
       <c r="C134" s="1">
-        <v>11006</v>
+        <v>11004</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="E134" s="7" t="s">
-        <v>146</v>
+        <v>142</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="F134" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G134" s="1">
-        <v>501</v>
+        <v>4001</v>
       </c>
       <c r="H134" s="1">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="I134" s="1">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="J134" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K134" s="2">
         <v>1</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>147</v>
+        <v>39</v>
       </c>
     </row>
     <row r="135" customHeight="1" spans="3:12">
       <c r="C135" s="1">
-        <v>11007</v>
+        <v>11005</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F135" s="1">
+        <v>20</v>
+      </c>
+      <c r="G135" s="1">
+        <v>101</v>
+      </c>
+      <c r="H135" s="1">
+        <v>500</v>
+      </c>
+      <c r="I135" s="1">
         <v>10</v>
       </c>
-      <c r="G135" s="1">
-        <v>1001</v>
-      </c>
-      <c r="H135" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I135" s="1">
-        <v>20</v>
-      </c>
       <c r="J135" s="1">
         <v>1</v>
       </c>
@@ -5375,30 +5386,30 @@
         <v>1</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="3:12">
       <c r="C136" s="1">
-        <v>11008</v>
+        <v>11006</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F136" s="1">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G136" s="1">
-        <v>1501</v>
+        <v>501</v>
       </c>
       <c r="H136" s="1">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I136" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J136" s="1">
         <v>1</v>
@@ -5407,30 +5418,30 @@
         <v>1</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="137" customHeight="1" spans="3:12">
       <c r="C137" s="1">
-        <v>11009</v>
+        <v>11007</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F137" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G137" s="1">
-        <v>2001</v>
+        <v>1001</v>
       </c>
       <c r="H137" s="1">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="I137" s="1">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="J137" s="1">
         <v>1</v>
@@ -5439,30 +5450,30 @@
         <v>1</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="3:12">
       <c r="C138" s="1">
-        <v>11010</v>
+        <v>11008</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F138" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G138" s="1">
-        <v>2501</v>
+        <v>1501</v>
       </c>
       <c r="H138" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I138" s="1">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="J138" s="1">
         <v>1</v>
@@ -5471,30 +5482,30 @@
         <v>1</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="3:12">
       <c r="C139" s="1">
-        <v>11011</v>
+        <v>11009</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F139" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G139" s="1">
-        <v>3001</v>
+        <v>2001</v>
       </c>
       <c r="H139" s="1">
-        <v>3800</v>
+        <v>2500</v>
       </c>
       <c r="I139" s="1">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="J139" s="1">
         <v>1</v>
@@ -5503,120 +5514,126 @@
         <v>1</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="3:12">
       <c r="C140" s="1">
-        <v>11012</v>
+        <v>11010</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="F140" s="2">
-        <v>1</v>
-      </c>
-      <c r="G140" s="2">
-        <v>5001</v>
-      </c>
-      <c r="H140" s="2">
-        <v>6000</v>
-      </c>
-      <c r="I140" s="2">
-        <v>61</v>
-      </c>
-      <c r="J140" s="2">
+        <v>160</v>
+      </c>
+      <c r="F140" s="1">
+        <v>7</v>
+      </c>
+      <c r="G140" s="1">
+        <v>2501</v>
+      </c>
+      <c r="H140" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I140" s="1">
+        <v>52</v>
+      </c>
+      <c r="J140" s="1">
         <v>1</v>
       </c>
       <c r="K140" s="2">
         <v>1</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="141" customHeight="1" spans="3:12">
       <c r="C141" s="1">
-        <v>11013</v>
+        <v>11011</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
+      </c>
+      <c r="E141" s="7" t="s">
+        <v>163</v>
       </c>
       <c r="F141" s="1">
         <v>3</v>
       </c>
       <c r="G141" s="1">
-        <v>5501</v>
+        <v>3001</v>
       </c>
       <c r="H141" s="1">
-        <v>6500</v>
+        <v>3800</v>
       </c>
       <c r="I141" s="1">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="J141" s="1">
         <v>1</v>
       </c>
       <c r="K141" s="2">
         <v>1</v>
+      </c>
+      <c r="L141" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="142" customHeight="1" spans="3:12">
       <c r="C142" s="1">
-        <v>11014</v>
+        <v>11012</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="F142" s="1">
-        <v>2</v>
-      </c>
-      <c r="G142" s="1">
-        <v>5501</v>
-      </c>
-      <c r="H142" s="1">
-        <v>6500</v>
-      </c>
-      <c r="I142" s="1">
-        <v>67</v>
-      </c>
-      <c r="J142" s="1">
+        <v>166</v>
+      </c>
+      <c r="F142" s="2">
+        <v>1</v>
+      </c>
+      <c r="G142" s="2">
+        <v>5001</v>
+      </c>
+      <c r="H142" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I142" s="2">
+        <v>61</v>
+      </c>
+      <c r="J142" s="2">
         <v>1</v>
       </c>
       <c r="K142" s="2">
         <v>1</v>
+      </c>
+      <c r="L142" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="143" customHeight="1" spans="3:12">
       <c r="C143" s="1">
-        <v>11015</v>
+        <v>11013</v>
       </c>
       <c r="D143" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="E143" s="7" t="s">
+      <c r="E143" s="1" t="s">
         <v>168</v>
       </c>
       <c r="F143" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G143" s="1">
-        <v>6401</v>
+        <v>5501</v>
       </c>
       <c r="H143" s="1">
-        <v>7400</v>
+        <v>6500</v>
       </c>
       <c r="I143" s="1">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="J143" s="1">
         <v>1</v>
@@ -5627,118 +5644,112 @@
     </row>
     <row r="144" customHeight="1" spans="3:12">
       <c r="C144" s="1">
-        <v>11016</v>
+        <v>11014</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>170</v>
+        <v>162</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>163</v>
       </c>
       <c r="F144" s="1">
         <v>2</v>
       </c>
       <c r="G144" s="1">
-        <v>8001</v>
+        <v>5501</v>
       </c>
       <c r="H144" s="1">
-        <v>9000</v>
+        <v>6500</v>
       </c>
       <c r="I144" s="1">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="J144" s="1">
         <v>1</v>
       </c>
       <c r="K144" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" spans="3:12">
+      <c r="C145" s="1">
+        <v>11015</v>
+      </c>
+      <c r="D145" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="E145" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="F145" s="1">
+        <v>1</v>
+      </c>
+      <c r="G145" s="1">
+        <v>6401</v>
+      </c>
+      <c r="H145" s="1">
+        <v>7400</v>
+      </c>
+      <c r="I145" s="1">
+        <v>91</v>
+      </c>
+      <c r="J145" s="1">
+        <v>1</v>
+      </c>
+      <c r="K145" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="146" customHeight="1" spans="3:12">
       <c r="C146" s="1">
-        <v>11303</v>
+        <v>11016</v>
       </c>
       <c r="D146" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="E146" s="7" t="s">
+      <c r="E146" s="1" t="s">
         <v>172</v>
       </c>
       <c r="F146" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G146" s="1">
-        <v>3903</v>
+        <v>8001</v>
       </c>
       <c r="H146" s="1">
-        <v>4402</v>
+        <v>9000</v>
       </c>
       <c r="I146" s="1">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="J146" s="1">
         <v>1</v>
       </c>
       <c r="K146" s="2">
         <v>1</v>
-      </c>
-      <c r="L146" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="147" customHeight="1" spans="3:12">
-      <c r="C147" s="1">
-        <v>11304</v>
-      </c>
-      <c r="D147" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="E147" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="F147" s="1">
-        <v>8</v>
-      </c>
-      <c r="G147" s="1">
-        <v>4403</v>
-      </c>
-      <c r="H147" s="1">
-        <v>4902</v>
-      </c>
-      <c r="I147" s="1">
-        <v>41</v>
-      </c>
-      <c r="J147" s="1">
-        <v>1</v>
-      </c>
-      <c r="K147" s="2">
-        <v>1</v>
-      </c>
-      <c r="L147" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="148" customHeight="1" spans="3:12">
       <c r="C148" s="1">
-        <v>11305</v>
+        <v>11303</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E148" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F148" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G148" s="1">
-        <v>4903</v>
+        <v>3903</v>
       </c>
       <c r="H148" s="1">
-        <v>5402</v>
+        <v>4402</v>
       </c>
       <c r="I148" s="1">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J148" s="1">
         <v>1</v>
@@ -5747,30 +5758,30 @@
         <v>1</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="149" customHeight="1" spans="3:12">
       <c r="C149" s="1">
-        <v>11306</v>
+        <v>11304</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F149" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G149" s="1">
-        <v>5403</v>
+        <v>4403</v>
       </c>
       <c r="H149" s="1">
-        <v>6402</v>
+        <v>4902</v>
       </c>
       <c r="I149" s="1">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="J149" s="1">
         <v>1</v>
@@ -5779,30 +5790,30 @@
         <v>1</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="150" customHeight="1" spans="3:12">
       <c r="C150" s="1">
-        <v>11307</v>
+        <v>11305</v>
       </c>
       <c r="D150" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F150" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G150" s="1">
-        <v>6403</v>
+        <v>4903</v>
       </c>
       <c r="H150" s="1">
-        <v>7402</v>
+        <v>5402</v>
       </c>
       <c r="I150" s="1">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="J150" s="1">
         <v>1</v>
@@ -5811,45 +5822,109 @@
         <v>1</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="151" customHeight="1" spans="3:12">
       <c r="C151" s="1">
+        <v>11306</v>
+      </c>
+      <c r="D151" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F151" s="1">
+        <v>4</v>
+      </c>
+      <c r="G151" s="1">
+        <v>5403</v>
+      </c>
+      <c r="H151" s="1">
+        <v>6402</v>
+      </c>
+      <c r="I151" s="1">
+        <v>51</v>
+      </c>
+      <c r="J151" s="1">
+        <v>1</v>
+      </c>
+      <c r="K151" s="2">
+        <v>1</v>
+      </c>
+      <c r="L151" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" spans="3:12">
+      <c r="C152" s="1">
+        <v>11307</v>
+      </c>
+      <c r="D152" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="F152" s="1">
+        <v>3</v>
+      </c>
+      <c r="G152" s="1">
+        <v>6403</v>
+      </c>
+      <c r="H152" s="1">
+        <v>7402</v>
+      </c>
+      <c r="I152" s="1">
+        <v>61</v>
+      </c>
+      <c r="J152" s="1">
+        <v>1</v>
+      </c>
+      <c r="K152" s="2">
+        <v>1</v>
+      </c>
+      <c r="L152" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" spans="3:12">
+      <c r="C153" s="1">
         <v>11308</v>
       </c>
-      <c r="D151" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="E151" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="F151" s="1">
-        <v>1</v>
-      </c>
-      <c r="G151" s="1">
+      <c r="D153" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="E153" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F153" s="1">
+        <v>1</v>
+      </c>
+      <c r="G153" s="1">
         <v>7403</v>
       </c>
-      <c r="H151" s="1">
+      <c r="H153" s="1">
         <v>8402</v>
       </c>
-      <c r="I151" s="1">
+      <c r="I153" s="1">
         <v>79</v>
       </c>
-      <c r="J151" s="1">
-        <v>1</v>
-      </c>
-      <c r="K151" s="2">
-        <v>1</v>
-      </c>
-      <c r="L151" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="152" customHeight="1" spans="3:12">
-      <c r="D152" s="5"/>
-      <c r="E152" s="7"/>
-      <c r="K152" s="2"/>
+      <c r="J153" s="1">
+        <v>1</v>
+      </c>
+      <c r="K153" s="2">
+        <v>1</v>
+      </c>
+      <c r="L153" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" spans="3:12">
+      <c r="D154" s="5"/>
+      <c r="E154" s="7"/>
+      <c r="K154" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
